--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33308,6 +33308,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1433">
+      <c r="A1433" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1433" t="n">
+        <v>1343</v>
+      </c>
+      <c r="C1433" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="G1433" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33331,6 +33331,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1434">
+      <c r="A1434" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1434" t="n">
+        <v>5515</v>
+      </c>
+      <c r="C1434" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="G1434" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33354,6 +33354,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1435">
+      <c r="A1435" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1435" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C1435" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="G1435" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33377,6 +33377,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1436">
+      <c r="A1436" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1436" t="n">
+        <v>1658</v>
+      </c>
+      <c r="C1436" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>0.740000009536743</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="G1436" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33218,19 +33218,19 @@
     </row>
     <row r="1429">
       <c r="A1429" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1429" t="n">
-        <v>6815</v>
+        <v>500</v>
       </c>
       <c r="C1429" t="n">
-        <v>0.754999995231628</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="D1429" t="n">
-        <v>0.725000023841858</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="E1429" t="n">
-        <v>0.740000009536743</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="F1429" t="n">
         <v>0.745000004768372</v>
@@ -33241,19 +33241,19 @@
     </row>
     <row r="1430">
       <c r="A1430" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1430" t="n">
-        <v>1500</v>
+        <v>6815</v>
       </c>
       <c r="C1430" t="n">
-        <v>0.745000004768372</v>
+        <v>0.754999995231628</v>
       </c>
       <c r="D1430" t="n">
-        <v>0.735000014305115</v>
+        <v>0.725000023841858</v>
       </c>
       <c r="E1430" t="n">
-        <v>0.735000014305115</v>
+        <v>0.740000009536743</v>
       </c>
       <c r="F1430" t="n">
         <v>0.745000004768372</v>
@@ -33264,19 +33264,19 @@
     </row>
     <row r="1431">
       <c r="A1431" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1431" t="n">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="C1431" t="n">
         <v>0.745000004768372</v>
       </c>
       <c r="D1431" t="n">
-        <v>0.745000004768372</v>
+        <v>0.735000014305115</v>
       </c>
       <c r="E1431" t="n">
-        <v>0.745000004768372</v>
+        <v>0.735000014305115</v>
       </c>
       <c r="F1431" t="n">
         <v>0.745000004768372</v>
@@ -33287,19 +33287,19 @@
     </row>
     <row r="1432">
       <c r="A1432" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1432" t="n">
-        <v>5510</v>
+        <v>0</v>
       </c>
       <c r="C1432" t="n">
         <v>0.745000004768372</v>
       </c>
       <c r="D1432" t="n">
-        <v>0.725000023841858</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="E1432" t="n">
-        <v>0.730000019073486</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="F1432" t="n">
         <v>0.745000004768372</v>
@@ -33310,16 +33310,16 @@
     </row>
     <row r="1433">
       <c r="A1433" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1433" t="n">
-        <v>1343</v>
+        <v>5510</v>
       </c>
       <c r="C1433" t="n">
         <v>0.745000004768372</v>
       </c>
       <c r="D1433" t="n">
-        <v>0.730000019073486</v>
+        <v>0.725000023841858</v>
       </c>
       <c r="E1433" t="n">
         <v>0.730000019073486</v>
@@ -33333,22 +33333,22 @@
     </row>
     <row r="1434">
       <c r="A1434" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1434" t="n">
-        <v>5515</v>
+        <v>1343</v>
       </c>
       <c r="C1434" t="n">
-        <v>0.754999995231628</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="D1434" t="n">
-        <v>0.725000023841858</v>
+        <v>0.730000019073486</v>
       </c>
       <c r="E1434" t="n">
-        <v>0.735000014305115</v>
+        <v>0.730000019073486</v>
       </c>
       <c r="F1434" t="n">
-        <v>0.735000014305115</v>
+        <v>0.745000004768372</v>
       </c>
       <c r="G1434" t="s">
         <v>7</v>
@@ -33356,10 +33356,10 @@
     </row>
     <row r="1435">
       <c r="A1435" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1435" t="n">
-        <v>4200</v>
+        <v>5515</v>
       </c>
       <c r="C1435" t="n">
         <v>0.754999995231628</v>
@@ -33368,10 +33368,10 @@
         <v>0.725000023841858</v>
       </c>
       <c r="E1435" t="n">
-        <v>0.725000023841858</v>
+        <v>0.735000014305115</v>
       </c>
       <c r="F1435" t="n">
-        <v>0.754999995231628</v>
+        <v>0.735000014305115</v>
       </c>
       <c r="G1435" t="s">
         <v>7</v>
@@ -33379,24 +33379,47 @@
     </row>
     <row r="1436">
       <c r="A1436" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1436" t="n">
-        <v>1658</v>
+        <v>4200</v>
       </c>
       <c r="C1436" t="n">
-        <v>0.745000004768372</v>
+        <v>0.754999995231628</v>
       </c>
       <c r="D1436" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>0.754999995231628</v>
+      </c>
+      <c r="G1436" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1437" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C1437" t="n">
+        <v>0.759999990463257</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>0.725000023841858</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F1437" t="n">
         <v>0.740000009536743</v>
       </c>
-      <c r="E1436" t="n">
-        <v>0.745000004768372</v>
-      </c>
-      <c r="F1436" t="n">
-        <v>0.745000004768372</v>
-      </c>
-      <c r="G1436" t="s">
+      <c r="G1437" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74249863624573</v>
+        <v>2.74249839782715</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6414999961853</v>
+        <v>2.64150023460388</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G7" t="n">
-        <v>3.53357744216919</v>
+        <v>3.53357768058777</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.79315757751465</v>
+        <v>3.79315781593323</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79315757751465</v>
+        <v>3.79315781593323</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8114378452301</v>
+        <v>3.81143808364868</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.60121512413025</v>
+        <v>3.60121488571167</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.57379412651062</v>
+        <v>3.5737943649292</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153304100037</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583225250244</v>
+        <v>3.44583249092102</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50981307029724</v>
+        <v>3.50981330871582</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.42755198478699</v>
+        <v>3.42755222320557</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30873012542725</v>
+        <v>3.30872988700867</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>3.40927171707153</v>
+        <v>3.40927195549011</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.37271118164062</v>
+        <v>3.3727114200592</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.01624584197998</v>
+        <v>3.01624608039856</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15334820747375</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15334820747375</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.1350679397583</v>
+        <v>3.13506770133972</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G35" t="n">
-        <v>3.08936715126038</v>
+        <v>3.0893669128418</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818853378296</v>
+        <v>3.20818877220154</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G38" t="n">
-        <v>3.41841173171997</v>
+        <v>3.41841220855713</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057809829712</v>
+        <v>3.82057762145996</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71089625358582</v>
+        <v>3.71089601516724</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>3.67433571815491</v>
+        <v>3.67433547973633</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72003698348999</v>
+        <v>3.72003674507141</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175671577454</v>
+        <v>3.70175623893738</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>3.67433571815491</v>
+        <v>3.67433547973633</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153304100037</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949515342712</v>
+        <v>3.61949491500854</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293485641479</v>
+        <v>3.58293437957764</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G64" t="n">
-        <v>3.60121512413025</v>
+        <v>3.60121488571167</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011861801147</v>
+        <v>3.62011885643005</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.50986123085022</v>
+        <v>3.50986099243164</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>3.44554448127747</v>
+        <v>3.44554424285889</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4179801940918</v>
+        <v>3.41797995567322</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G76" t="n">
-        <v>3.39041566848755</v>
+        <v>3.39041590690613</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G77" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417798042297</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.47310876846313</v>
+        <v>3.47310853004456</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>3.50986123085022</v>
+        <v>3.50986099243164</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.49148488044739</v>
+        <v>3.49148511886597</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.49148488044739</v>
+        <v>3.49148511886597</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.65687108039856</v>
+        <v>3.65687131881714</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G92" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>3.74875211715698</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G95" t="n">
-        <v>3.89576148986816</v>
+        <v>3.8957622051239</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>6.94621753692627</v>
+        <v>6.94621706008911</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237661361694</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G116" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>7.49750423431396</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G120" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G121" t="n">
-        <v>7.36887121200562</v>
+        <v>7.36887168884277</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>6.94621753692627</v>
+        <v>6.94621706008911</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>6.7808313369751</v>
+        <v>6.78083181381226</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G127" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433673858643</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57101011276245</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G139" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237661361694</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>8.15904808044434</v>
+        <v>8.15904998779297</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08554363250732</v>
+        <v>8.08554458618164</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178251266479</v>
+        <v>7.90178298950195</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.5</v>
       </c>
       <c r="G153" t="n">
-        <v>7.80990076065063</v>
+        <v>7.80990123748779</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639535903931</v>
+        <v>7.73639583587646</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015790939331</v>
+        <v>7.92015838623047</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314805984497</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.69964361190796</v>
+        <v>7.69964408874512</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G158" t="n">
-        <v>7.79152297973633</v>
+        <v>7.7915244102478</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G159" t="n">
-        <v>7.79152297973633</v>
+        <v>7.7915244102478</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>7.49750423431396</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237661361694</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.3611888885498</v>
+        <v>8.36118793487549</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57101011276245</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.5</v>
       </c>
       <c r="G179" t="n">
-        <v>7.80990076065063</v>
+        <v>7.80990123748779</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314805984497</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57101011276245</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588153839111</v>
+        <v>7.51588106155396</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425741195679</v>
+        <v>7.53425693511963</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57101011276245</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>7.42399978637695</v>
+        <v>7.42399930953979</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G199" t="n">
-        <v>7.42399978637695</v>
+        <v>7.42399930953979</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G202" t="n">
-        <v>7.40562391281128</v>
+        <v>7.40562343597412</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>7.31374216079712</v>
+        <v>7.31374263763428</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G211" t="n">
-        <v>7.12997961044312</v>
+        <v>7.12998008728027</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="n">
-        <v>6.89108896255493</v>
+        <v>6.89108848571777</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83596038818359</v>
+        <v>6.83595991134644</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>7.5</v>
       </c>
       <c r="G215" t="n">
-        <v>6.89108896255493</v>
+        <v>6.89108848571777</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433673858643</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>6.98296976089478</v>
+        <v>6.98297023773193</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>7.18510818481445</v>
+        <v>7.18510866165161</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>7.13916778564453</v>
+        <v>7.13916826248169</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G235" t="n">
-        <v>6.90027713775635</v>
+        <v>6.90027666091919</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433673858643</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>6.98296976089478</v>
+        <v>6.98297023773193</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>6.94621753692627</v>
+        <v>6.94621706008911</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>7.5</v>
       </c>
       <c r="G243" t="n">
-        <v>6.89108896255493</v>
+        <v>6.89108848571777</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>6.90027713775635</v>
+        <v>6.90027666091919</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G247" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>7</v>
       </c>
       <c r="G248" t="n">
-        <v>6.43168306350708</v>
+        <v>6.43168258666992</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>6.38574171066284</v>
+        <v>6.3857421875</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>6.38574171066284</v>
+        <v>6.3857421875</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>6.3306131362915</v>
+        <v>6.33061361312866</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322738647461</v>
+        <v>7.09322690963745</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>6.65219736099243</v>
+        <v>6.65219783782959</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G267" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>6.55112886428833</v>
+        <v>6.55112838745117</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G270" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G272" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G273" t="n">
-        <v>6.40411853790283</v>
+        <v>6.40411806106567</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>6.44087076187134</v>
+        <v>6.44087171554565</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>5.72419738769531</v>
+        <v>5.72419786453247</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G285" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504863739014</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504863739014</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>6.55112886428833</v>
+        <v>6.55112838745117</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>6.75</v>
       </c>
       <c r="G304" t="n">
-        <v>6.201979637146</v>
+        <v>6.20198011398315</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G306" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>6.06415796279907</v>
+        <v>6.06415843963623</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>6.11009883880615</v>
+        <v>6.11009931564331</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>6.11009883880615</v>
+        <v>6.11009931564331</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>6.09172296524048</v>
+        <v>6.09172248840332</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G318" t="n">
-        <v>5.98146533966064</v>
+        <v>5.9814658164978</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714811325073</v>
+        <v>5.91714859008789</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770231246948</v>
+        <v>5.79770278930664</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>5.76094961166382</v>
+        <v>5.76095008850098</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>6.11009883880615</v>
+        <v>6.11009931564331</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>6.5419397354126</v>
+        <v>6.54194021224976</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>7</v>
       </c>
       <c r="G343" t="n">
-        <v>6.43168306350708</v>
+        <v>6.43168258666992</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342546463013</v>
+        <v>5.39342594146729</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530673980713</v>
+        <v>5.48530626296997</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>5.46693086624146</v>
+        <v>5.4669303894043</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G366" t="n">
-        <v>5.65069246292114</v>
+        <v>5.65069341659546</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>5.46693086624146</v>
+        <v>5.4669303894043</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>5.56799936294556</v>
+        <v>5.56799983978271</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>5.58637571334839</v>
+        <v>5.58637619018555</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>5.70582103729248</v>
+        <v>5.70582151412964</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>6.25</v>
       </c>
       <c r="G388" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932643890381</v>
+        <v>5.77932691574097</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G391" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>6.14685153961182</v>
+        <v>6.14685106277466</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>6.14685153961182</v>
+        <v>6.14685106277466</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.11928701400757</v>
+        <v>6.11928653717041</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G404" t="n">
-        <v>5.85283088684082</v>
+        <v>5.85283184051514</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>6.25</v>
       </c>
       <c r="G413" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504863739014</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>5.42098951339722</v>
+        <v>5.42098999023438</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>5.31992053985596</v>
+        <v>5.31992101669312</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423681259155</v>
+        <v>5.38423776626587</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346488952637</v>
+        <v>5.05346536636353</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>4.86970281600952</v>
+        <v>4.86970329284668</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73188066482544</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.6767520904541</v>
+        <v>4.67675256729126</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.58487033843994</v>
+        <v>4.5848708152771</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760381698608</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948461532593</v>
+        <v>4.41948509216309</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760381698608</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.45164346694946</v>
+        <v>4.4516429901123</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G456" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G457" t="n">
-        <v>4.48839616775513</v>
+        <v>4.48839569091797</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47461318969727</v>
+        <v>4.47461414337158</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.45623683929443</v>
+        <v>4.45623731613159</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.5297417640686</v>
+        <v>4.52974224090576</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34597969055176</v>
+        <v>4.34598064422607</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435556411743</v>
+        <v>4.36435651779175</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G477" t="n">
-        <v>4.4929895401001</v>
+        <v>4.49299001693726</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22193956375122</v>
+        <v>4.22194004058838</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845530509949</v>
+        <v>3.97845506668091</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.97386074066162</v>
+        <v>3.9738609790802</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>3.84522771835327</v>
+        <v>3.84522747993469</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.85900974273682</v>
+        <v>3.8590099811554</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.9508912563324</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.9508912563324</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G500" t="n">
-        <v>3.9876434803009</v>
+        <v>3.98764395713806</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>3.9876434803009</v>
+        <v>3.98764395713806</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>4.32300996780396</v>
+        <v>4.3230094909668</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326759338379</v>
+        <v>4.43326711654663</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G512" t="n">
-        <v>4.30003881454468</v>
+        <v>4.30003929138184</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>4.34138631820679</v>
+        <v>4.34138536453247</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G517" t="n">
-        <v>4.39192056655884</v>
+        <v>4.391921043396</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.73188066482544</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>4.62162351608276</v>
+        <v>4.62162399291992</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G522" t="n">
-        <v>4.95239543914795</v>
+        <v>4.95239591598511</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>4.78700971603394</v>
+        <v>4.78700923919678</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>4.78700971603394</v>
+        <v>4.78700923919678</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>4.89726734161377</v>
+        <v>4.89726686477661</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>4.78700971603394</v>
+        <v>4.78700923919678</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G532" t="n">
-        <v>4.95239543914795</v>
+        <v>4.95239591598511</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G536" t="n">
-        <v>5.11778211593628</v>
+        <v>5.11778163909912</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>5.0167121887207</v>
+        <v>5.01671266555786</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G540" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86970281600952</v>
+        <v>4.86970329284668</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619741439819</v>
+        <v>4.79619789123535</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.20815801620483</v>
+        <v>4.20815849304199</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G552" t="n">
-        <v>4.31382131576538</v>
+        <v>4.31382179260254</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546539306641</v>
+        <v>4.12546491622925</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>3.90035629272461</v>
+        <v>3.90035581588745</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>3.73496985435486</v>
+        <v>3.73497009277344</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>3.74875211715698</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65687108039856</v>
+        <v>3.65687131881714</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G566" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417798042297</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G568" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G569" t="n">
-        <v>3.39041566848755</v>
+        <v>3.39041590690613</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>3.5</v>
       </c>
       <c r="G577" t="n">
-        <v>3.21584153175354</v>
+        <v>3.21584129333496</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09639573097229</v>
+        <v>3.09639596939087</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G580" t="n">
-        <v>3.03207898139954</v>
+        <v>3.03207921981812</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>3.05964350700378</v>
+        <v>3.05964326858521</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>3.56498980522156</v>
+        <v>3.56499004364014</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.9417028427124</v>
+        <v>3.94170260429382</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G593" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>3.4547324180603</v>
+        <v>3.45473265647888</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>3.30772233009338</v>
+        <v>3.30772256851196</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015780448914</v>
+        <v>3.28015804290771</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>3.32609868049622</v>
+        <v>3.32609891891479</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990113258362</v>
+        <v>3.16990089416504</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>3.5</v>
       </c>
       <c r="G612" t="n">
-        <v>3.21584153175354</v>
+        <v>3.21584129333496</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.1147723197937</v>
+        <v>3.11477208137512</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G621" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G624" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G627" t="n">
-        <v>2.93101000785828</v>
+        <v>2.9310097694397</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G630" t="n">
-        <v>3.03276824951172</v>
+        <v>3.03276801109314</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>2.87461757659912</v>
+        <v>2.8746178150177</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G639" t="n">
-        <v>2.87461757659912</v>
+        <v>2.8746178150177</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>2.64204335212708</v>
+        <v>2.64204359054565</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110457420349</v>
+        <v>2.52110505104065</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040766716003</v>
+        <v>2.53040790557861</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761932373047</v>
+        <v>2.56761956214905</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901361465454</v>
+        <v>2.54901385307312</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>2.40946936607361</v>
+        <v>2.40946912765503</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180171966553</v>
+        <v>2.51180195808411</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.40946936607361</v>
+        <v>2.40946912765503</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35365128517151</v>
+        <v>2.35365152359009</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G694" t="n">
-        <v>1.74895823001862</v>
+        <v>1.74895834922791</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>1.58150494098663</v>
+        <v>1.58150482177734</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.51638412475586</v>
+        <v>1.51638400554657</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.44196021556854</v>
+        <v>1.44196033477783</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>1.69779205322266</v>
+        <v>1.69779193401337</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G713" t="n">
-        <v>1.51638412475586</v>
+        <v>1.51638400554657</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.58150494098663</v>
+        <v>1.58150482177734</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G716" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G719" t="n">
-        <v>1.59545946121216</v>
+        <v>1.59545934200287</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.63267111778259</v>
+        <v>1.63267123699188</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G721" t="n">
-        <v>1.60476243495941</v>
+        <v>1.60476231575012</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>2.18619775772095</v>
+        <v>2.18619799613953</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550061225891</v>
+        <v>2.19550085067749</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.00944137573242</v>
+        <v>2.009441614151</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>2.01874446868896</v>
+        <v>2.01874470710754</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.21410703659058</v>
+        <v>2.214106798172</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G758" t="n">
-        <v>2.22340989112854</v>
+        <v>2.22341012954712</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16759181022644</v>
+        <v>2.16759204864502</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.1768946647644</v>
+        <v>2.17689490318298</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.12107706069946</v>
+        <v>2.12107729911804</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12107706069946</v>
+        <v>2.12107729911804</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>2.01874446868896</v>
+        <v>2.01874470710754</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>1.97222936153412</v>
+        <v>1.9722295999527</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G783" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292662620544</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.9908355474472</v>
+        <v>1.99083578586578</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.05595636367798</v>
+        <v>2.05595660209656</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00944137573242</v>
+        <v>2.009441614151</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G798" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G800" t="n">
-        <v>1.90710890293121</v>
+        <v>1.90710878372192</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G805" t="n">
-        <v>1.77686727046967</v>
+        <v>1.77686715126038</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.64662551879883</v>
+        <v>1.64662563800812</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G813" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G820" t="n">
-        <v>1.60941386222839</v>
+        <v>1.6094137430191</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G821" t="n">
-        <v>1.63267111778259</v>
+        <v>1.63267123699188</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97222936153412</v>
+        <v>1.9722295999527</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G836" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G838" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G852" t="n">
-        <v>1.8094277381897</v>
+        <v>1.80942761898041</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G856" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.8698970079422</v>
+        <v>1.86989688873291</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432055950165</v>
+        <v>1.94432067871094</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G860" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292662620544</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -37786,6 +37786,32 @@
         <v>0.740000009536743</v>
       </c>
       <c r="H1439" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1440" t="n">
+        <v>7565</v>
+      </c>
+      <c r="C1440" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="H1440" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64150023460388</v>
+        <v>2.6414999961853</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.81143808364868</v>
+        <v>3.8114378452301</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5737943649292</v>
+        <v>3.57379412651062</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45497226715088</v>
+        <v>3.45497250556946</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583249092102</v>
+        <v>3.44583225250244</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.26302933692932</v>
+        <v>3.26302981376648</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30872988700867</v>
+        <v>3.30873036384583</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248822212219</v>
+        <v>3.16248798370361</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764741897583</v>
+        <v>3.10764718055725</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076825141907</v>
+        <v>3.18076848983765</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.13506770133972</v>
+        <v>3.1350679397583</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818877220154</v>
+        <v>3.20818853378296</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443115234375</v>
+        <v>3.35443139076233</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057762145996</v>
+        <v>3.82057809829712</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71089601516724</v>
+        <v>3.71089625358582</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>3.67433547973633</v>
+        <v>3.67433571815491</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175623893738</v>
+        <v>3.70175671577454</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>3.67433547973633</v>
+        <v>3.67433571815491</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519570350647</v>
+        <v>3.66519594192505</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.4641125202179</v>
+        <v>3.46411275863647</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949491500854</v>
+        <v>3.61949515342712</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293437957764</v>
+        <v>3.58293461799622</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207463264465</v>
+        <v>3.59207487106323</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011885643005</v>
+        <v>3.62011861801147</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.50986099243164</v>
+        <v>3.50986123085022</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.41797995567322</v>
+        <v>3.4179801940918</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G77" t="n">
-        <v>3.57417798042297</v>
+        <v>3.57417821884155</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>3.48229670524597</v>
+        <v>3.48229694366455</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G81" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.47310853004456</v>
+        <v>3.47310876846313</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>3.50986099243164</v>
+        <v>3.50986123085022</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.49148511886597</v>
+        <v>3.49148488044739</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.49148511886597</v>
+        <v>3.49148488044739</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G86" t="n">
-        <v>3.52823734283447</v>
+        <v>3.52823710441589</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.65687131881714</v>
+        <v>3.65687108039856</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524719238281</v>
+        <v>3.67524743080139</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524719238281</v>
+        <v>3.67524743080139</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G92" t="n">
-        <v>3.70281171798706</v>
+        <v>3.70281195640564</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>3.74875235557556</v>
+        <v>3.74875211715698</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251538276672</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910823822021</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>5.36586141586304</v>
+        <v>5.36586093902588</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>5.36586141586304</v>
+        <v>5.36586093902588</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124666213989</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>6.96459341049194</v>
+        <v>6.9645938873291</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.00134611129761</v>
+        <v>7.00134658813477</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>6.94621706008911</v>
+        <v>6.94621753692627</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237661361694</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>7.49750471115112</v>
+        <v>7.49750423431396</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G121" t="n">
-        <v>7.36887168884277</v>
+        <v>7.36887121200562</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>6.94621706008911</v>
+        <v>6.94621753692627</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.8727126121521</v>
+        <v>6.87271213531494</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G127" t="n">
-        <v>6.8727126121521</v>
+        <v>6.87271213531494</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.8727126121521</v>
+        <v>6.87271213531494</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>6.85433673858643</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57101011276245</v>
+        <v>7.57100868225098</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237661361694</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>8.15904998779297</v>
+        <v>8.15904903411865</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366283416748</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08554458618164</v>
+        <v>8.08554363250732</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366283416748</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95690965652466</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178298950195</v>
+        <v>7.90178155899048</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.5</v>
       </c>
       <c r="G153" t="n">
-        <v>7.80990123748779</v>
+        <v>7.80990028381348</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639583587646</v>
+        <v>7.73639631271362</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015838623047</v>
+        <v>7.92015790939331</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314805984497</v>
+        <v>7.77314853668213</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.69964408874512</v>
+        <v>7.6996431350708</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G160" t="n">
-        <v>7.64451456069946</v>
+        <v>7.6445140838623</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G162" t="n">
-        <v>7.68126678466797</v>
+        <v>7.68126630783081</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>7.49750471115112</v>
+        <v>7.49750423431396</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237661361694</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023771286011</v>
+        <v>7.24023723602295</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G169" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95690965652466</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801996231079</v>
+        <v>7.71801853179932</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57101011276245</v>
+        <v>7.57100868225098</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G177" t="n">
-        <v>7.68126678466797</v>
+        <v>7.68126630783081</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.5</v>
       </c>
       <c r="G179" t="n">
-        <v>7.80990123748779</v>
+        <v>7.80990028381348</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314805984497</v>
+        <v>7.77314853668213</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57101011276245</v>
+        <v>7.57100868225098</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425693511963</v>
+        <v>7.53425645828247</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801996231079</v>
+        <v>7.71801853179932</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G192" t="n">
-        <v>7.68126678466797</v>
+        <v>7.68126630783081</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G195" t="n">
-        <v>7.6077618598938</v>
+        <v>7.60776138305664</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57101011276245</v>
+        <v>7.57100868225098</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>7.42399930953979</v>
+        <v>7.42399978637695</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G199" t="n">
-        <v>7.42399930953979</v>
+        <v>7.42399978637695</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G202" t="n">
-        <v>7.40562343597412</v>
+        <v>7.40562391281128</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>7.31374263763428</v>
+        <v>7.31374216079712</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023771286011</v>
+        <v>7.24023723602295</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G212" t="n">
-        <v>7.05647468566895</v>
+        <v>7.05647420883179</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83595991134644</v>
+        <v>6.83596038818359</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>6.57869243621826</v>
+        <v>6.57869291305542</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.85433673858643</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>6.98297023773193</v>
+        <v>6.98296976089478</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>7.18510866165161</v>
+        <v>7.18510818481445</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>7.13916826248169</v>
+        <v>7.13916778564453</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G232" t="n">
-        <v>7.04728698730469</v>
+        <v>7.04728651046753</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G235" t="n">
-        <v>6.90027666091919</v>
+        <v>6.90027713775635</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G236" t="n">
-        <v>6.91865348815918</v>
+        <v>6.91865301132202</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>6.85433673858643</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>6.98297023773193</v>
+        <v>6.98296976089478</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G239" t="n">
-        <v>6.91865348815918</v>
+        <v>6.91865301132202</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G240" t="n">
-        <v>6.91865348815918</v>
+        <v>6.91865301132202</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>6.94621706008911</v>
+        <v>6.94621753692627</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G242" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>6.90027666091919</v>
+        <v>6.90027713775635</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G251" t="n">
-        <v>6.57869243621826</v>
+        <v>6.57869291305542</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>6.35817766189575</v>
+        <v>6.35817813873291</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>6.33061361312866</v>
+        <v>6.3306131362915</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>6.23873233795166</v>
+        <v>6.23873281478882</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G258" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G260" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322690963745</v>
+        <v>7.09322738647461</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>6.92784118652344</v>
+        <v>6.92784070968628</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>6.65219783782959</v>
+        <v>6.65219736099243</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>6.55112838745117</v>
+        <v>6.55112886428833</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G273" t="n">
-        <v>6.40411806106567</v>
+        <v>6.40411853790283</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>6.44087171554565</v>
+        <v>6.44087076187134</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G276" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73338556289673</v>
+        <v>5.73338508605957</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G285" t="n">
-        <v>5.37504863739014</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910823822021</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.37504863739014</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330671310425</v>
+        <v>6.41330575942993</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>6.55112838745117</v>
+        <v>6.55112886428833</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>6.569504737854</v>
+        <v>6.56950426101685</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G306" t="n">
-        <v>6.35817766189575</v>
+        <v>6.35817813873291</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548456192017</v>
+        <v>6.27548408508301</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>6.0457820892334</v>
+        <v>6.04578161239624</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>6.11009931564331</v>
+        <v>6.11009836196899</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05497026443481</v>
+        <v>6.05496978759766</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>6.11009931564331</v>
+        <v>6.11009836196899</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>6.09172248840332</v>
+        <v>6.09172296524048</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G318" t="n">
-        <v>5.9814658164978</v>
+        <v>5.98146533966064</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>6.0457820892334</v>
+        <v>6.04578161239624</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770278930664</v>
+        <v>5.79770231246948</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>6.11009931564331</v>
+        <v>6.11009836196899</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330671310425</v>
+        <v>6.41330575942993</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G353" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342594146729</v>
+        <v>5.39342546463013</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936586380005</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718801498413</v>
+        <v>5.57718849182129</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936586380005</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G366" t="n">
-        <v>5.65069341659546</v>
+        <v>5.65069246292114</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G369" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.0457820892334</v>
+        <v>6.04578161239624</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G377" t="n">
-        <v>5.73338556289673</v>
+        <v>5.73338508605957</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>5.56799983978271</v>
+        <v>5.56799936294556</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>5.58637619018555</v>
+        <v>5.58637571334839</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G392" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G396" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.9906530380249</v>
+        <v>5.99065256118774</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G404" t="n">
-        <v>5.85283184051514</v>
+        <v>5.85283088684082</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>5.9539008140564</v>
+        <v>5.95390033721924</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G408" t="n">
-        <v>5.73338556289673</v>
+        <v>5.73338508605957</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.8987717628479</v>
+        <v>5.89877223968506</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124666213989</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.37504863739014</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423776626587</v>
+        <v>5.38423728942871</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910823822021</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346536636353</v>
+        <v>5.05346488952637</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>4.86970329284668</v>
+        <v>4.86970281600952</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.7318811416626</v>
+        <v>4.73188066482544</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.5848708152771</v>
+        <v>4.58487033843994</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.57108879089355</v>
+        <v>4.5710883140564</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>4.58946514129639</v>
+        <v>4.58946466445923</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>4.32760381698608</v>
+        <v>4.32760334014893</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352521896362</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>4.6399998664856</v>
+        <v>4.64000034332275</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948509216309</v>
+        <v>4.41948461532593</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>4.32760381698608</v>
+        <v>4.32760334014893</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>4.38273239135742</v>
+        <v>4.38273286819458</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G456" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G457" t="n">
-        <v>4.48839569091797</v>
+        <v>4.48839616775513</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47461414337158</v>
+        <v>4.47461318969727</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G461" t="n">
-        <v>4.46542596817017</v>
+        <v>4.46542549133301</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G464" t="n">
-        <v>4.60324764251709</v>
+        <v>4.60324716567993</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352521896362</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.875</v>
       </c>
       <c r="G469" t="n">
-        <v>4.47920751571655</v>
+        <v>4.47920799255371</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34598064422607</v>
+        <v>4.34598016738892</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>4.38732624053955</v>
+        <v>4.38732671737671</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435651779175</v>
+        <v>4.36435604095459</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22194004058838</v>
+        <v>4.22194051742554</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332673072815</v>
+        <v>3.92332625389099</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251538276672</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845506668091</v>
+        <v>3.97845482826233</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.9738609790802</v>
+        <v>3.97386074066162</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G488" t="n">
-        <v>3.84063339233398</v>
+        <v>3.84063315391541</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G489" t="n">
-        <v>3.84063339233398</v>
+        <v>3.84063315391541</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G491" t="n">
-        <v>3.82225728034973</v>
+        <v>3.82225704193115</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144545555115</v>
+        <v>3.83144569396973</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.8590099811554</v>
+        <v>3.85900926589966</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251538276672</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.95089149475098</v>
+        <v>3.95089077949524</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.95089149475098</v>
+        <v>3.95089077949524</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G500" t="n">
-        <v>3.98764395713806</v>
+        <v>3.9876434803009</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G501" t="n">
-        <v>3.98764395713806</v>
+        <v>3.9876434803009</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>4.35057401657104</v>
+        <v>4.3505744934082</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>4.3230094909668</v>
+        <v>4.32300996780396</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326711654663</v>
+        <v>4.43326663970947</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G512" t="n">
-        <v>4.30003929138184</v>
+        <v>4.30003881454468</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463361740112</v>
+        <v>4.30463314056396</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>4.34138536453247</v>
+        <v>4.34138584136963</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.7318811416626</v>
+        <v>4.73188066482544</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>4.62162399291992</v>
+        <v>4.62162351608276</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>4.89726686477661</v>
+        <v>4.89726734161377</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85132646560669</v>
+        <v>4.85132694244385</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.90645551681519</v>
+        <v>4.90645503997803</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G536" t="n">
-        <v>5.11778163909912</v>
+        <v>5.11778211593628</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>4.87889099121094</v>
+        <v>4.87889051437378</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G540" t="n">
-        <v>4.85132646560669</v>
+        <v>4.85132694244385</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G541" t="n">
-        <v>4.88807916641235</v>
+        <v>4.8880786895752</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86970329284668</v>
+        <v>4.86970281600952</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619789123535</v>
+        <v>4.79619741439819</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72269296646118</v>
+        <v>4.72269248962402</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G546" t="n">
-        <v>4.53893089294434</v>
+        <v>4.53893041610718</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>4.26328706741333</v>
+        <v>4.26328659057617</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.1530294418335</v>
+        <v>4.15302991867065</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>3.90035581588745</v>
+        <v>3.90035629272461</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>3.74875235557556</v>
+        <v>3.74875211715698</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65687131881714</v>
+        <v>3.65687108039856</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G566" t="n">
-        <v>3.57417798042297</v>
+        <v>3.57417821884155</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G575" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09639596939087</v>
+        <v>3.09639573097229</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G584" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.54661345481873</v>
+        <v>3.5466136932373</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.54661345481873</v>
+        <v>3.5466136932373</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G589" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.94170260429382</v>
+        <v>3.94170236587524</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712846755981</v>
+        <v>3.76712822914124</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712846755981</v>
+        <v>3.76712822914124</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G593" t="n">
-        <v>3.70281171798706</v>
+        <v>3.70281195640564</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904940605164</v>
+        <v>3.51904916763306</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.54661345481873</v>
+        <v>3.5466136932373</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G599" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>3.45473265647888</v>
+        <v>3.4547324180603</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>3.30772256851196</v>
+        <v>3.30772233009338</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015804290771</v>
+        <v>3.28015828132629</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>3.32609891891479</v>
+        <v>3.32609868049622</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.11477208137512</v>
+        <v>3.1147723197937</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>2.9769504070282</v>
+        <v>2.97695016860962</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G631" t="n">
-        <v>3.05137419700623</v>
+        <v>3.05137395858765</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>2.8746178150177</v>
+        <v>2.87461757659912</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G639" t="n">
-        <v>2.8746178150177</v>
+        <v>2.87461757659912</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>2.64204359054565</v>
+        <v>2.64204335212708</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110505104065</v>
+        <v>2.52110481262207</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040790557861</v>
+        <v>2.53040766716003</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901385307312</v>
+        <v>2.54901361465454</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>2.48389315605164</v>
+        <v>2.48389291763306</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.39086318016052</v>
+        <v>2.39086294174194</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G657" t="n">
-        <v>2.39086318016052</v>
+        <v>2.39086294174194</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G658" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G664" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G665" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G668" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180195808411</v>
+        <v>2.51180171966553</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37225723266602</v>
+        <v>2.37225699424744</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.29783368110657</v>
+        <v>2.29783344268799</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35365152359009</v>
+        <v>2.35365104675293</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G694" t="n">
-        <v>1.74895834922791</v>
+        <v>1.74895823001862</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362377166748</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>1.58150482177734</v>
+        <v>1.58150494098663</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G706" t="n">
-        <v>1.56289887428284</v>
+        <v>1.56289875507355</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G707" t="n">
-        <v>1.56289887428284</v>
+        <v>1.56289875507355</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.56289887428284</v>
+        <v>1.56289875507355</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69314050674438</v>
+        <v>1.69314062595367</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>1.69779193401337</v>
+        <v>1.69779205322266</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.58150482177734</v>
+        <v>1.58150494098663</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G717" t="n">
-        <v>1.69314050674438</v>
+        <v>1.69314062595367</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.63267123699188</v>
+        <v>1.63267111778259</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.85129106044769</v>
+        <v>1.8512909412384</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>2.18619799613953</v>
+        <v>2.18619775772095</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550085067749</v>
+        <v>2.19550061225891</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.214106798172</v>
+        <v>2.21410703659058</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.24201583862305</v>
+        <v>2.24201607704163</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16759204864502</v>
+        <v>2.16759181022644</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15828895568848</v>
+        <v>2.1582887172699</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.17689490318298</v>
+        <v>2.1768946647644</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.12107729911804</v>
+        <v>2.12107706069946</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12107729911804</v>
+        <v>2.12107706069946</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.13968300819397</v>
+        <v>2.13968276977539</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>2.04665350914001</v>
+        <v>2.04665327072144</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G783" t="n">
-        <v>1.96292662620544</v>
+        <v>1.96292650699615</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.05595660209656</v>
+        <v>2.05595636367798</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>2.04665350914001</v>
+        <v>2.04665327072144</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362377166748</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362377166748</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362377166748</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G798" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G805" t="n">
-        <v>1.77686715126038</v>
+        <v>1.77686727046967</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G807" t="n">
-        <v>1.69314050674438</v>
+        <v>1.69314062595367</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G813" t="n">
-        <v>1.67453455924988</v>
+        <v>1.67453444004059</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56289887428284</v>
+        <v>1.56289875507355</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56289887428284</v>
+        <v>1.56289875507355</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G820" t="n">
-        <v>1.6094137430191</v>
+        <v>1.60941386222839</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G821" t="n">
-        <v>1.63267123699188</v>
+        <v>1.63267111778259</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G827" t="n">
-        <v>1.52568709850311</v>
+        <v>1.52568697929382</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G828" t="n">
-        <v>1.56289887428284</v>
+        <v>1.56289875507355</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.67453455924988</v>
+        <v>1.67453444004059</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G836" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G838" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G839" t="n">
-        <v>1.84663951396942</v>
+        <v>1.84663939476013</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.85129106044769</v>
+        <v>1.8512909412384</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G843" t="n">
-        <v>1.83733654022217</v>
+        <v>1.83733642101288</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G844" t="n">
-        <v>1.83733654022217</v>
+        <v>1.83733642101288</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G852" t="n">
-        <v>1.80942761898041</v>
+        <v>1.8094277381897</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G853" t="n">
-        <v>1.84663951396942</v>
+        <v>1.84663939476013</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.93501770496368</v>
+        <v>1.93501758575439</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G856" t="n">
-        <v>1.85129106044769</v>
+        <v>1.8512909412384</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G857" t="n">
-        <v>1.83733654022217</v>
+        <v>1.83733642101288</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.86989688873291</v>
+        <v>1.8698970079422</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432067871094</v>
+        <v>1.94432044029236</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G860" t="n">
-        <v>1.96292662620544</v>
+        <v>1.96292650699615</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.18991041183472</v>
+        <v>2.18991017341614</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>2.18038892745972</v>
+        <v>2.1803891658783</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G868" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.98044073581696</v>
+        <v>1.98044061660767</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98044073581696</v>
+        <v>1.98044061660767</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.99948346614838</v>
+        <v>1.9994832277298</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>1.99948346614838</v>
+        <v>1.9994832277298</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.69480013847351</v>
+        <v>1.6948002576828</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G943" t="n">
-        <v>1.69480013847351</v>
+        <v>1.6948002576828</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.6186295747757</v>
+        <v>1.61862945556641</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G945" t="n">
-        <v>1.54245865345001</v>
+        <v>1.54245853424072</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.35679221153259</v>
+        <v>1.35679233074188</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G951" t="n">
-        <v>1.31394612789154</v>
+        <v>1.31394624710083</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G953" t="n">
-        <v>1.31394612789154</v>
+        <v>1.31394624710083</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>1.34727084636688</v>
+        <v>1.34727096557617</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G963" t="n">
-        <v>1.02830576896667</v>
+        <v>1.02830588817596</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G969" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G975" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G983" t="n">
-        <v>0.847400069236755</v>
+        <v>0.8474001288414</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G985" t="n">
-        <v>0.934996485710144</v>
+        <v>0.934996545314789</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G986" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G996" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.02830576896667</v>
+        <v>1.02830588817596</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.0473484992981</v>
+        <v>1.04734838008881</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.0473484992981</v>
+        <v>1.04734838008881</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.999741733074188</v>
+        <v>0.999741613864899</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.01878440380096</v>
+        <v>1.01878452301025</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.00926291942596</v>
+        <v>1.00926303863525</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00926291942596</v>
+        <v>1.00926303863525</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.885485529899597</v>
+        <v>0.885485470294952</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.999741733074188</v>
+        <v>0.999741613864899</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.975938379764557</v>
+        <v>0.975938320159912</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.990220367908478</v>
+        <v>0.990220308303833</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.975938379764557</v>
+        <v>0.975938320159912</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.940709352493286</v>
+        <v>0.940709292888641</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14732265472412</v>
+        <v>1.14732277393341</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.20445072650909</v>
+        <v>1.2044506072998</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.20921146869659</v>
+        <v>1.2092113494873</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.20445072650909</v>
+        <v>1.2044506072998</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -37812,6 +37812,32 @@
         <v>0.735000014305115</v>
       </c>
       <c r="H1440" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1441" t="n">
+        <v>9116</v>
+      </c>
+      <c r="C1441" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>0.730000019073486</v>
+      </c>
+      <c r="H1441" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74249839782715</v>
+        <v>2.74249863624573</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.53049993515015</v>
       </c>
       <c r="G6" t="n">
-        <v>3.22692584991455</v>
+        <v>3.22692608833313</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.81143808364868</v>
+        <v>3.8114378452301</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.57379412651062</v>
+        <v>3.5737943649292</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50981330871582</v>
+        <v>3.50981307029724</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>3.51895356178284</v>
+        <v>3.51895332336426</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30873012542725</v>
+        <v>3.30873036384583</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248822212219</v>
+        <v>3.16248798370361</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764741897583</v>
+        <v>3.10764718055725</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15334820747375</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15334820747375</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076825141907</v>
+        <v>3.18076848983765</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420795440674</v>
+        <v>3.14420771598816</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.1350679397583</v>
+        <v>3.13506770133972</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.65605545043945</v>
+        <v>3.65605521202087</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55551409721375</v>
+        <v>3.55551433563232</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>3.52809357643127</v>
+        <v>3.5280933380127</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G77" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417845726013</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G86" t="n">
-        <v>3.52823734283447</v>
+        <v>3.52823710441589</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95690965652466</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015790939331</v>
+        <v>7.92015695571899</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.69964361190796</v>
+        <v>7.6996431350708</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95690965652466</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.3611888885498</v>
+        <v>8.36118793487549</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588153839111</v>
+        <v>7.51588106155396</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425741195679</v>
+        <v>7.53425693511963</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G195" t="n">
-        <v>7.6077618598938</v>
+        <v>7.60776138305664</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G211" t="n">
-        <v>7.12997961044312</v>
+        <v>7.12998008728027</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G212" t="n">
-        <v>7.05647468566895</v>
+        <v>7.05647420883179</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>7.18510818481445</v>
+        <v>7.18510866165161</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813776016235</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G258" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322738647461</v>
+        <v>7.09322690963745</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>6.65219736099243</v>
+        <v>6.65219783782959</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G276" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G285" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>6.0825343132019</v>
+        <v>6.08253383636475</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386138916016</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386138916016</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G306" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548456192017</v>
+        <v>6.27548503875732</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>6.16522741317749</v>
+        <v>6.16522693634033</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714811325073</v>
+        <v>5.91714859008789</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770231246948</v>
+        <v>5.79770278930664</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>5.76094961166382</v>
+        <v>5.76095008850098</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813776016235</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>6.5419397354126</v>
+        <v>6.54194021224976</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G346" t="n">
-        <v>6.10091018676758</v>
+        <v>6.10090970993042</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342546463013</v>
+        <v>5.39342498779297</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936681747437</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530673980713</v>
+        <v>5.48530626296997</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>5.46693086624146</v>
+        <v>5.4669303894043</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936681747437</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G366" t="n">
-        <v>5.65069246292114</v>
+        <v>5.6506929397583</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>5.46693086624146</v>
+        <v>5.4669303894043</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G369" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932643890381</v>
+        <v>5.77932691574097</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G391" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G392" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>6.16522741317749</v>
+        <v>6.16522693634033</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.8987717628479</v>
+        <v>5.89877223968506</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>5.42098951339722</v>
+        <v>5.42098999023438</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423681259155</v>
+        <v>5.38423728942871</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>4.57568311691284</v>
+        <v>4.57568264007568</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>4.29544544219971</v>
+        <v>4.29544591903687</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948461532593</v>
+        <v>4.41948509216309</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.45164346694946</v>
+        <v>4.4516429901123</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>4.38273239135742</v>
+        <v>4.38273286819458</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.5297417640686</v>
+        <v>4.52974224090576</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34597969055176</v>
+        <v>4.34598016738892</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435556411743</v>
+        <v>4.36435604095459</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G477" t="n">
-        <v>4.4929895401001</v>
+        <v>4.49299001693726</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22193956375122</v>
+        <v>4.22194004058838</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845530509949</v>
+        <v>3.97845482826233</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144545555115</v>
+        <v>3.83144521713257</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.85900974273682</v>
+        <v>3.8590099811554</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326759338379</v>
+        <v>4.43326711654663</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463361740112</v>
+        <v>4.30463314056396</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G540" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G546" t="n">
-        <v>4.53893089294434</v>
+        <v>4.53893041610718</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.1530294418335</v>
+        <v>4.15302991867065</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546539306641</v>
+        <v>4.12546491622925</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>3.90035629272461</v>
+        <v>3.90035653114319</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631688117981</v>
+        <v>3.77631664276123</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G566" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417845726013</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G568" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G575" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>3.56498980522156</v>
+        <v>3.56499004364014</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904940605164</v>
+        <v>3.51904916763306</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>3.30772233009338</v>
+        <v>3.30772256851196</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>3.32609868049622</v>
+        <v>3.32609891891479</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990113258362</v>
+        <v>3.16990089416504</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233660697937</v>
+        <v>3.14233636856079</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G621" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>2.89425730705261</v>
+        <v>2.89425706863403</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G624" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G627" t="n">
-        <v>2.93101000785828</v>
+        <v>2.9310097694397</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -37942,6 +37942,32 @@
         <v>0.699999988079071</v>
       </c>
       <c r="H1445" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1446" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C1446" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="D1446" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="G1446" t="n">
+        <v>0.699999988079071</v>
+      </c>
+      <c r="H1446" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33692,8 +33692,31 @@
       <c r="E1449" t="n">
         <v>0.680000007152557</v>
       </c>
-      <c r="F1449"/>
+      <c r="F1449" t="n">
+        <v>0.675000011920929</v>
+      </c>
       <c r="G1449" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>2074</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="F1450"/>
+      <c r="G1450" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33715,8 +33715,31 @@
       <c r="E1450" t="n">
         <v>0.670000016689301</v>
       </c>
-      <c r="F1450"/>
+      <c r="F1450" t="n">
+        <v>0.670000016689301</v>
+      </c>
       <c r="G1450" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1451" t="n">
+        <v>1457</v>
+      </c>
+      <c r="C1451" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="D1451" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="E1451" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="F1451"/>
+      <c r="G1451" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33738,8 +33738,31 @@
       <c r="E1451" t="n">
         <v>0.660000026226044</v>
       </c>
-      <c r="F1451"/>
+      <c r="F1451" t="n">
+        <v>0.670000016689301</v>
+      </c>
       <c r="G1451" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1452" t="n">
+        <v>700</v>
+      </c>
+      <c r="C1452" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="D1452" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="E1452" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="F1452"/>
+      <c r="G1452" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33761,7 +33761,9 @@
       <c r="E1452" t="n">
         <v>0.665000021457672</v>
       </c>
-      <c r="F1452"/>
+      <c r="F1452" t="n">
+        <v>0.665000021457672</v>
+      </c>
       <c r="G1452" t="s">
         <v>7</v>
       </c>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -33791,6 +33791,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1454">
+      <c r="A1454" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>33056</v>
+      </c>
+      <c r="C1454" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>0.615000009536743</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="G1454" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -473,7 +473,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6414999961853</v>
+        <v>2.64150047302246</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.53049993515015</v>
       </c>
       <c r="G6" t="n">
-        <v>3.22692584991455</v>
+        <v>3.22692608833313</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.60121488571167</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583225250244</v>
+        <v>3.44583249092102</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50981330871582</v>
+        <v>3.50981283187866</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G19" t="n">
-        <v>3.47325277328491</v>
+        <v>3.47325301170349</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.42755198478699</v>
+        <v>3.42755174636841</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.26302981376648</v>
+        <v>3.26302933692932</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30873012542725</v>
+        <v>3.30873036384583</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>3.40927171707153</v>
+        <v>3.40927195549011</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3727114200592</v>
+        <v>3.37271118164062</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764718055725</v>
+        <v>3.10764765739441</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.01624584197998</v>
+        <v>3.0162456035614</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076825141907</v>
+        <v>3.18076848983765</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420795440674</v>
+        <v>3.14420771598816</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.1350679397583</v>
+        <v>3.13506770133972</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0893669128418</v>
+        <v>3.08936738967896</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443139076233</v>
+        <v>3.35443091392517</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057809829712</v>
+        <v>3.82057785987854</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72003650665283</v>
+        <v>3.72003698348999</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175671577454</v>
+        <v>3.70175623893738</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519594192505</v>
+        <v>3.66519570350647</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46411275863647</v>
+        <v>3.4641125202179</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55551409721375</v>
+        <v>3.55551433563232</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949491500854</v>
+        <v>3.61949467658997</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G60" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.62863492965698</v>
+        <v>3.62863540649414</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207487106323</v>
+        <v>3.59207439422607</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G64" t="n">
-        <v>3.60121488571167</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011861801147</v>
+        <v>3.62011885643005</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.50986123085022</v>
+        <v>3.5098614692688</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4179801940918</v>
+        <v>3.41797995567322</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G76" t="n">
-        <v>3.39041590690613</v>
+        <v>3.39041566848755</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>3.48229694366455</v>
+        <v>3.48229670524597</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G81" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>3.50986123085022</v>
+        <v>3.5098614692688</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.49148488044739</v>
+        <v>3.49148511886597</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.49148488044739</v>
+        <v>3.49148511886597</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G86" t="n">
-        <v>3.52823710441589</v>
+        <v>3.52823734283447</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.63849472999573</v>
+        <v>3.63849496841431</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G92" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251538276672</v>
+        <v>3.93251466751099</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G95" t="n">
-        <v>3.8957622051239</v>
+        <v>3.89576148986816</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G103" t="n">
-        <v>5.34748506546021</v>
+        <v>5.34748554229736</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G104" t="n">
-        <v>5.31073236465454</v>
+        <v>5.3107328414917</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G105" t="n">
-        <v>5.34748506546021</v>
+        <v>5.34748554229736</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G107" t="n">
-        <v>5.34748506546021</v>
+        <v>5.34748554229736</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124666213989</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>6.9645938873291</v>
+        <v>6.96459341049194</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.00134658813477</v>
+        <v>7.00134611129761</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G116" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G120" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G121" t="n">
-        <v>7.36887121200562</v>
+        <v>7.36887073516846</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>6.78083181381226</v>
+        <v>6.7808313369751</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G127" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G133" t="n">
-        <v>7.27698945999146</v>
+        <v>7.27698993682861</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G139" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>8.15904903411865</v>
+        <v>8.15904808044434</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G144" t="n">
-        <v>8.06716823577881</v>
+        <v>8.06716728210449</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08554363250732</v>
+        <v>8.08554458618164</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G148" t="n">
-        <v>8.06716823577881</v>
+        <v>8.06716728210449</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95690965652466</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178155899048</v>
+        <v>7.90178298950195</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>8.5</v>
       </c>
       <c r="G153" t="n">
-        <v>7.80990028381348</v>
+        <v>7.80989980697632</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639631271362</v>
+        <v>7.73639535903931</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314805984497</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.6996431350708</v>
+        <v>7.69964408874512</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G158" t="n">
-        <v>7.7915244102478</v>
+        <v>7.79152297973633</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G159" t="n">
-        <v>7.7915244102478</v>
+        <v>7.79152297973633</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>7.27698945999146</v>
+        <v>7.27698993682861</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G169" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95690965652466</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.36118793487549</v>
+        <v>8.36118698120117</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801853179932</v>
+        <v>7.71801900863647</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>8.5</v>
       </c>
       <c r="G179" t="n">
-        <v>7.80990028381348</v>
+        <v>7.80989980697632</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314805984497</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425645828247</v>
+        <v>7.53425693511963</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801853179932</v>
+        <v>7.71801900863647</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G202" t="n">
-        <v>7.40562391281128</v>
+        <v>7.40562343597412</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G212" t="n">
-        <v>7.05647420883179</v>
+        <v>7.05647468566895</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83596038818359</v>
+        <v>6.83595991134644</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>6.8175835609436</v>
+        <v>6.81758403778076</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>6.46843528747559</v>
+        <v>6.46843481063843</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>6.98296976089478</v>
+        <v>6.98297023773193</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>7.13916778564453</v>
+        <v>7.13916826248169</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813871383667</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G236" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>6.98296976089478</v>
+        <v>6.98297023773193</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G239" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G240" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>6.51437616348267</v>
+        <v>6.51437568664551</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>6.51437616348267</v>
+        <v>6.51437568664551</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>6.15603923797607</v>
+        <v>6.15603876113892</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G258" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322738647461</v>
+        <v>7.09322690963745</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>6.92784070968628</v>
+        <v>6.92784118652344</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>6.46843528747559</v>
+        <v>6.46843481063843</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G275" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G276" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G279" t="n">
-        <v>5.62312841415405</v>
+        <v>5.62312889099121</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73338508605957</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.80689096450806</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>5.72419786453247</v>
+        <v>5.72419738769531</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G288" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G292" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330575942993</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>6.56950426101685</v>
+        <v>6.569504737854</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386043548584</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386043548584</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548408508301</v>
+        <v>6.27548503875732</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>6.06415843963623</v>
+        <v>6.06415796279907</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>6.11009836196899</v>
+        <v>6.11009883880615</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05496978759766</v>
+        <v>6.05497026443481</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>6.11009836196899</v>
+        <v>6.11009883880615</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G316" t="n">
-        <v>6.13766288757324</v>
+        <v>6.13766241073608</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445453643799</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G321" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714859008789</v>
+        <v>5.91714811325073</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364318847656</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G334" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>6.11009836196899</v>
+        <v>6.11009883880615</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813871383667</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330575942993</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G346" t="n">
-        <v>6.10091018676758</v>
+        <v>6.10091066360474</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G353" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342546463013</v>
+        <v>5.39342498779297</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530626296997</v>
+        <v>5.48530673980713</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G362" t="n">
-        <v>5.54962348937988</v>
+        <v>5.54962301254272</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718849182129</v>
+        <v>5.57718753814697</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G366" t="n">
-        <v>5.65069246292114</v>
+        <v>5.6506929397583</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G369" t="n">
-        <v>5.80689096450806</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>5.80689096450806</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G377" t="n">
-        <v>5.73338508605957</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445453643799</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G392" t="n">
-        <v>5.80689096450806</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G393" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.11928653717041</v>
+        <v>6.11928701400757</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>6.00902938842773</v>
+        <v>6.00902891159058</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.99065256118774</v>
+        <v>5.9906530380249</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G402" t="n">
-        <v>5.90795993804932</v>
+        <v>5.90796041488647</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364318847656</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>5.95390033721924</v>
+        <v>5.9539008140564</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G408" t="n">
-        <v>5.73338508605957</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445453643799</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.89877223968506</v>
+        <v>5.8987717628479</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124666213989</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G422" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>5.31992101669312</v>
+        <v>5.31992053985596</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G433" t="n">
-        <v>5.1637225151062</v>
+        <v>5.16372299194336</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346488952637</v>
+        <v>5.05346536636353</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73188066482544</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.67675256729126</v>
+        <v>4.6767520904541</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.58487033843994</v>
+        <v>4.5848708152771</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>4.57568311691284</v>
+        <v>4.57568264007568</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.5710883140564</v>
+        <v>4.57108879089355</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>4.58946466445923</v>
+        <v>4.58946514129639</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352521896362</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>4.64000034332275</v>
+        <v>4.63999938964844</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948461532593</v>
+        <v>4.41948509216309</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.4516429901123</v>
+        <v>4.45164346694946</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G464" t="n">
-        <v>4.60324716567993</v>
+        <v>4.60324811935425</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352521896362</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.875</v>
       </c>
       <c r="G469" t="n">
-        <v>4.47920799255371</v>
+        <v>4.47920751571655</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>4.38732671737671</v>
+        <v>4.38732624053955</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G477" t="n">
-        <v>4.49299001693726</v>
+        <v>4.4929895401001</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22194051742554</v>
+        <v>4.22194004058838</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332625389099</v>
+        <v>3.92332673072815</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251538276672</v>
+        <v>3.93251466751099</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845482826233</v>
+        <v>3.97845530509949</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.97386074066162</v>
+        <v>3.97386050224304</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144569396973</v>
+        <v>3.83144521713257</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.85900926589966</v>
+        <v>3.85900950431824</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251538276672</v>
+        <v>3.93251466751099</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.95089077949524</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.95089077949524</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061344146729</v>
+        <v>4.01061296463013</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>4.3505744934082</v>
+        <v>4.35057401657104</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>4.32300996780396</v>
+        <v>4.3230094909668</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326663970947</v>
+        <v>4.43326711654663</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463314056396</v>
+        <v>4.30463361740112</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>4.40570259094238</v>
+        <v>4.40570211410522</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>4.34138584136963</v>
+        <v>4.34138631820679</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G517" t="n">
-        <v>4.391921043396</v>
+        <v>4.39192056655884</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.73188066482544</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G522" t="n">
-        <v>4.95239591598511</v>
+        <v>4.95239543914795</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>4.89726734161377</v>
+        <v>4.89726686477661</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G532" t="n">
-        <v>4.95239591598511</v>
+        <v>4.95239543914795</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.90645503997803</v>
+        <v>4.90645551681519</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G536" t="n">
-        <v>5.11778211593628</v>
+        <v>5.11778163909912</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>4.87889051437378</v>
+        <v>4.87889099121094</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G541" t="n">
-        <v>4.8880786895752</v>
+        <v>4.88807916641235</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619741439819</v>
+        <v>4.79619693756104</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72269248962402</v>
+        <v>4.72269296646118</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>4.26328659057617</v>
+        <v>4.26328706741333</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.40570259094238</v>
+        <v>4.40570211410522</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.20815849304199</v>
+        <v>4.20815801620483</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.15302991867065</v>
+        <v>4.1530294418335</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546491622925</v>
+        <v>4.12546539306641</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631688117981</v>
+        <v>3.77631664276123</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G569" t="n">
-        <v>3.39041590690613</v>
+        <v>3.39041566848755</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G576" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G578" t="n">
-        <v>3.06883144378662</v>
+        <v>3.06883120536804</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09639573097229</v>
+        <v>3.09639549255371</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G580" t="n">
-        <v>3.03207921981812</v>
+        <v>3.03207898139954</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>3.05964326858521</v>
+        <v>3.05964350700378</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>3.07801961898804</v>
+        <v>3.07801938056946</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G584" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G589" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.94170236587524</v>
+        <v>3.94170260429382</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712822914124</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712822914124</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G593" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G599" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G601" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>3.18827724456787</v>
+        <v>3.18827700614929</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990089416504</v>
+        <v>3.16990113258362</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233660697937</v>
+        <v>3.14233636856079</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.07801961898804</v>
+        <v>3.07801938056946</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>3.00451469421387</v>
+        <v>3.00451445579529</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>2.84831666946411</v>
+        <v>2.84831643104553</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>2.97695016860962</v>
+        <v>2.9769504070282</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G631" t="n">
-        <v>3.05137395858765</v>
+        <v>3.05137419700623</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040766716003</v>
+        <v>2.53040790557861</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761956214905</v>
+        <v>2.56761932373047</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901361465454</v>
+        <v>2.54901385307312</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G648" t="n">
-        <v>2.42807507514954</v>
+        <v>2.42807483673096</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>2.48389291763306</v>
+        <v>2.48389315605164</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.39086294174194</v>
+        <v>2.39086318016052</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G657" t="n">
-        <v>2.39086294174194</v>
+        <v>2.39086318016052</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G658" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G664" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G665" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G668" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.29783344268799</v>
+        <v>2.29783368110657</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.4931960105896</v>
+        <v>2.49319577217102</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35365104675293</v>
+        <v>2.35365128517151</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362341403961</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.4884752035141</v>
+        <v>1.48847508430481</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.44196033477783</v>
+        <v>1.44196021556854</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G706" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G707" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69314062595367</v>
+        <v>1.69314050674438</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G716" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G717" t="n">
-        <v>1.69314062595367</v>
+        <v>1.69314050674438</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.55359590053558</v>
+        <v>1.55359578132629</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G729" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G733" t="n">
-        <v>2.42807507514954</v>
+        <v>2.42807483673096</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>2.01874470710754</v>
+        <v>2.01874446868896</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.21410703659058</v>
+        <v>2.214106798172</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.24201607704163</v>
+        <v>2.24201583862305</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G758" t="n">
-        <v>2.22341012954712</v>
+        <v>2.22340989112854</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16759181022644</v>
+        <v>2.16759204864502</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>2.1582887172699</v>
+        <v>2.15828895568848</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.1768946647644</v>
+        <v>2.17689490318298</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.26992464065552</v>
+        <v>2.26992440223694</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.13968276977539</v>
+        <v>2.13968300819397</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>2.01874470710754</v>
+        <v>2.01874446868896</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>2.04665327072144</v>
+        <v>2.04665350914001</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G783" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292638778687</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.99083578586578</v>
+        <v>1.9908355474472</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03735041618347</v>
+        <v>2.03735017776489</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>2.04665327072144</v>
+        <v>2.04665350914001</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362341403961</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362341403961</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362341403961</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G803" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G807" t="n">
-        <v>1.69314062595367</v>
+        <v>1.69314050674438</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G813" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G817" t="n">
-        <v>1.4884752035141</v>
+        <v>1.48847508430481</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011088848114</v>
+        <v>1.60011076927185</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G820" t="n">
-        <v>1.60941386222839</v>
+        <v>1.6094137430191</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G827" t="n">
-        <v>1.52568697929382</v>
+        <v>1.52568709850311</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G828" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G831" t="n">
-        <v>1.81873059272766</v>
+        <v>1.81873047351837</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G835" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G838" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G839" t="n">
-        <v>1.84663939476013</v>
+        <v>1.84663951396942</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G843" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G844" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G848" t="n">
-        <v>1.81873059272766</v>
+        <v>1.81873047351837</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G850" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G853" t="n">
-        <v>1.84663939476013</v>
+        <v>1.84663951396942</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G856" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G857" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.8698970079422</v>
+        <v>1.86989688873291</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432044029236</v>
+        <v>1.94432055950165</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G860" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292638778687</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.18991017341614</v>
+        <v>2.18991041183472</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>2.1803891658783</v>
+        <v>2.18038892745972</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G868" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G943" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.61862945556641</v>
+        <v>1.6186295747757</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G945" t="n">
-        <v>1.54245853424072</v>
+        <v>1.54245865345001</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.35679233074188</v>
+        <v>1.35679221153259</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G951" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G953" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>1.34727096557617</v>
+        <v>1.34727084636688</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G963" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G969" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G975" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G983" t="n">
-        <v>0.8474001288414</v>
+        <v>0.847400069236755</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G985" t="n">
-        <v>0.934996545314789</v>
+        <v>0.934996485710144</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G986" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G996" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.01878452301025</v>
+        <v>1.01878440380096</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.885485470294952</v>
+        <v>0.885485529899597</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.990220308303833</v>
+        <v>0.990220367908478</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.940709292888641</v>
+        <v>0.940709352493286</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14732277393341</v>
+        <v>1.14732265472412</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.2092113494873</v>
+        <v>1.20921146869659</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -38228,6 +38228,32 @@
         <v>0.694999992847443</v>
       </c>
       <c r="H1456" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1457" t="n">
+        <v>26547</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>0.745000004768372</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="H1457" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>2.83344292640686</v>
+        <v>2.83344316482544</v>
       </c>
       <c r="H2" t="n">
         <v>1050000</v>
@@ -456,7 +456,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74249839782715</v>
+        <v>2.74249863624573</v>
       </c>
       <c r="H3" t="n">
         <v>611000</v>
@@ -514,7 +514,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66892051696777</v>
+        <v>2.66892075538635</v>
       </c>
       <c r="H5" t="n">
         <v>100000</v>
@@ -572,7 +572,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G7" t="n">
-        <v>3.53357744216919</v>
+        <v>3.53357768058777</v>
       </c>
       <c r="H7" t="n">
         <v>623000</v>
@@ -601,7 +601,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H8" t="n">
         <v>726000</v>
@@ -630,7 +630,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H9" t="n">
         <v>550000</v>
@@ -659,7 +659,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.81143832206726</v>
+        <v>3.81143808364868</v>
       </c>
       <c r="H10" t="n">
         <v>389000</v>
@@ -746,7 +746,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.57379412651062</v>
+        <v>3.5737943649292</v>
       </c>
       <c r="H13" t="n">
         <v>75000</v>
@@ -775,7 +775,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45497226715088</v>
+        <v>3.45497250556946</v>
       </c>
       <c r="H14" t="n">
         <v>116000</v>
@@ -804,7 +804,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153327941895</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H15" t="n">
         <v>85000</v>
@@ -862,7 +862,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50981307029724</v>
+        <v>3.50981330871582</v>
       </c>
       <c r="H17" t="n">
         <v>74000</v>
@@ -920,7 +920,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G19" t="n">
-        <v>3.47325301170349</v>
+        <v>3.47325277328491</v>
       </c>
       <c r="H19" t="n">
         <v>32000</v>
@@ -949,7 +949,7 @@
         <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.42755174636841</v>
+        <v>3.42755198478699</v>
       </c>
       <c r="H20" t="n">
         <v>37000</v>
@@ -978,7 +978,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.26302981376648</v>
+        <v>3.26302933692932</v>
       </c>
       <c r="H21" t="n">
         <v>78000</v>
@@ -1007,7 +1007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30873012542725</v>
+        <v>3.30872988700867</v>
       </c>
       <c r="H22" t="n">
         <v>17000</v>
@@ -1094,7 +1094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3727114200592</v>
+        <v>3.37271165847778</v>
       </c>
       <c r="H25" t="n">
         <v>11000</v>
@@ -1181,7 +1181,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764718055725</v>
+        <v>3.10764741897583</v>
       </c>
       <c r="H28" t="n">
         <v>52000</v>
@@ -1210,7 +1210,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.01624608039856</v>
+        <v>3.01624584197998</v>
       </c>
       <c r="H29" t="n">
         <v>41000</v>
@@ -1326,7 +1326,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420795440674</v>
+        <v>3.14420771598816</v>
       </c>
       <c r="H33" t="n">
         <v>53000</v>
@@ -1413,7 +1413,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818853378296</v>
+        <v>3.20818901062012</v>
       </c>
       <c r="H36" t="n">
         <v>50000</v>
@@ -1442,7 +1442,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443115234375</v>
+        <v>3.35443091392517</v>
       </c>
       <c r="H37" t="n">
         <v>264000</v>
@@ -1471,7 +1471,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G38" t="n">
-        <v>3.41841173171997</v>
+        <v>3.41841197013855</v>
       </c>
       <c r="H38" t="n">
         <v>54000</v>
@@ -1616,7 +1616,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71089625358582</v>
+        <v>3.71089601516724</v>
       </c>
       <c r="H43" t="n">
         <v>172000</v>
@@ -1645,7 +1645,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.65605545043945</v>
+        <v>3.65605568885803</v>
       </c>
       <c r="H44" t="n">
         <v>80000</v>
@@ -1674,7 +1674,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>3.67433571815491</v>
+        <v>3.67433595657349</v>
       </c>
       <c r="H45" t="n">
         <v>29000</v>
@@ -1703,7 +1703,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72003650665283</v>
+        <v>3.72003674507141</v>
       </c>
       <c r="H46" t="n">
         <v>44000</v>
@@ -1732,7 +1732,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175647735596</v>
+        <v>3.70175623893738</v>
       </c>
       <c r="H47" t="n">
         <v>30000</v>
@@ -1761,7 +1761,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>3.67433571815491</v>
+        <v>3.67433595657349</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1790,7 +1790,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H49" t="n">
         <v>51000</v>
@@ -1819,7 +1819,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519570350647</v>
+        <v>3.66519594192505</v>
       </c>
       <c r="H50" t="n">
         <v>11000</v>
@@ -1848,7 +1848,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H51" t="n">
         <v>21000</v>
@@ -1877,7 +1877,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H52" t="n">
         <v>35000</v>
@@ -1964,7 +1964,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153327941895</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55551409721375</v>
+        <v>3.55551433563232</v>
       </c>
       <c r="H56" t="n">
         <v>14000</v>
@@ -2022,7 +2022,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>3.52809357643127</v>
+        <v>3.5280933380127</v>
       </c>
       <c r="H57" t="n">
         <v>4000</v>
@@ -2051,7 +2051,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H58" t="n">
         <v>49000</v>
@@ -2080,7 +2080,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949491500854</v>
+        <v>3.61949467658997</v>
       </c>
       <c r="H59" t="n">
         <v>20000</v>
@@ -2109,7 +2109,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G60" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H60" t="n">
         <v>23000</v>
@@ -2196,7 +2196,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207487106323</v>
+        <v>3.59207463264465</v>
       </c>
       <c r="H63" t="n">
         <v>11000</v>
@@ -2254,7 +2254,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H65" t="n">
         <v>9000</v>
@@ -2341,7 +2341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011861801147</v>
+        <v>3.62011909484863</v>
       </c>
       <c r="H68" t="n">
         <v>10000</v>
@@ -2573,7 +2573,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G76" t="n">
-        <v>3.39041590690613</v>
+        <v>3.39041566848755</v>
       </c>
       <c r="H76" t="n">
         <v>28000</v>
@@ -2660,7 +2660,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H79" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>3.48229694366455</v>
+        <v>3.48229670524597</v>
       </c>
       <c r="H80" t="n">
         <v>11500</v>
@@ -2718,7 +2718,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G81" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H81" t="n">
         <v>4500</v>
@@ -2863,7 +2863,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G86" t="n">
-        <v>3.52823710441589</v>
+        <v>3.52823734283447</v>
       </c>
       <c r="H86" t="n">
         <v>5000</v>
@@ -2892,7 +2892,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>3.62930679321289</v>
+        <v>3.62930655479431</v>
       </c>
       <c r="H87" t="n">
         <v>36000</v>
@@ -2950,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3066,7 +3066,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>3.74875211715698</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H93" t="n">
         <v>51500</v>
@@ -3095,7 +3095,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251538276672</v>
+        <v>3.93251490592957</v>
       </c>
       <c r="H94" t="n">
         <v>132500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520729064941</v>
+        <v>4.01520776748657</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3182,7 +3182,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H97" t="n">
         <v>373000</v>
@@ -3269,7 +3269,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H100" t="n">
         <v>243500</v>
@@ -3385,7 +3385,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G104" t="n">
-        <v>5.31073236465454</v>
+        <v>5.31073188781738</v>
       </c>
       <c r="H104" t="n">
         <v>68500</v>
@@ -3443,7 +3443,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H106" t="n">
         <v>15000</v>
@@ -3501,7 +3501,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H108" t="n">
         <v>19000</v>
@@ -3559,7 +3559,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124666213989</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H110" t="n">
         <v>38500</v>
@@ -3588,7 +3588,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>6.9645938873291</v>
+        <v>6.96459341049194</v>
       </c>
       <c r="H111" t="n">
         <v>293500</v>
@@ -3617,7 +3617,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.00134658813477</v>
+        <v>7.00134611129761</v>
       </c>
       <c r="H112" t="n">
         <v>689000</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3762,7 +3762,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H117" t="n">
         <v>118000</v>
@@ -3791,7 +3791,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>7.49750423431396</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H118" t="n">
         <v>22500</v>
@@ -3878,7 +3878,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G121" t="n">
-        <v>7.36887121200562</v>
+        <v>7.36887168884277</v>
       </c>
       <c r="H121" t="n">
         <v>22000</v>
@@ -3965,7 +3965,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>6.78083181381226</v>
+        <v>6.7808313369751</v>
       </c>
       <c r="H124" t="n">
         <v>65500</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4284,7 +4284,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H135" t="n">
         <v>150000</v>
@@ -4342,7 +4342,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>7.25861358642578</v>
+        <v>7.25861310958862</v>
       </c>
       <c r="H137" t="n">
         <v>30500</v>
@@ -4371,7 +4371,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G138" t="n">
-        <v>7.46075201034546</v>
+        <v>7.4607515335083</v>
       </c>
       <c r="H138" t="n">
         <v>29000</v>
@@ -4458,7 +4458,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H141" t="n">
         <v>64000</v>
@@ -4545,7 +4545,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G144" t="n">
-        <v>8.06716823577881</v>
+        <v>8.06716728210449</v>
       </c>
       <c r="H144" t="n">
         <v>182000</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4661,7 +4661,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G148" t="n">
-        <v>8.06716823577881</v>
+        <v>8.06716728210449</v>
       </c>
       <c r="H148" t="n">
         <v>31000</v>
@@ -4690,7 +4690,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G149" t="n">
-        <v>8.14067268371582</v>
+        <v>8.14067363739014</v>
       </c>
       <c r="H149" t="n">
         <v>53500</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95690965652466</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4748,7 +4748,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178155899048</v>
+        <v>7.90178298950195</v>
       </c>
       <c r="H151" t="n">
         <v>20500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4806,7 +4806,7 @@
         <v>8.5</v>
       </c>
       <c r="G153" t="n">
-        <v>7.80990028381348</v>
+        <v>7.80989980697632</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639631271362</v>
+        <v>7.73639583587646</v>
       </c>
       <c r="H154" t="n">
         <v>8500</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015790939331</v>
+        <v>7.92015743255615</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4922,7 +4922,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.6996431350708</v>
+        <v>7.69964408874512</v>
       </c>
       <c r="H157" t="n">
         <v>22500</v>
@@ -5009,7 +5009,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G160" t="n">
-        <v>7.6445140838623</v>
+        <v>7.64451360702515</v>
       </c>
       <c r="H160" t="n">
         <v>19000</v>
@@ -5038,7 +5038,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H161" t="n">
         <v>4000</v>
@@ -5096,7 +5096,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>7.49750423431396</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H163" t="n">
         <v>21000</v>
@@ -5154,7 +5154,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H165" t="n">
         <v>25000</v>
@@ -5183,7 +5183,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H166" t="n">
         <v>25500</v>
@@ -5241,7 +5241,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023818969727</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95690965652466</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5357,7 +5357,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G172" t="n">
-        <v>8.14067268371582</v>
+        <v>8.14067363739014</v>
       </c>
       <c r="H172" t="n">
         <v>81500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84665250778198</v>
+        <v>7.84665298461914</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5473,7 +5473,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.84665250778198</v>
+        <v>7.84665298461914</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5560,7 +5560,7 @@
         <v>8.5</v>
       </c>
       <c r="G179" t="n">
-        <v>7.80990028381348</v>
+        <v>7.80989980697632</v>
       </c>
       <c r="H179" t="n">
         <v>16500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.84665250778198</v>
+        <v>7.84665298461914</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H183" t="n">
         <v>33500</v>
@@ -5705,7 +5705,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H184" t="n">
         <v>12000</v>
@@ -5821,7 +5821,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G188" t="n">
-        <v>7.46075201034546</v>
+        <v>7.4607515335083</v>
       </c>
       <c r="H188" t="n">
         <v>20500</v>
@@ -5850,7 +5850,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>7.46075201034546</v>
+        <v>7.4607515335083</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5879,7 +5879,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H190" t="n">
         <v>36500</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -5995,7 +5995,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H194" t="n">
         <v>11500</v>
@@ -6053,7 +6053,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100868225098</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H203" t="n">
         <v>17500</v>
@@ -6459,7 +6459,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023818969727</v>
       </c>
       <c r="H210" t="n">
         <v>10500</v>
@@ -6517,7 +6517,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G212" t="n">
-        <v>7.05647420883179</v>
+        <v>7.05647468566895</v>
       </c>
       <c r="H212" t="n">
         <v>19500</v>
@@ -6720,7 +6720,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H219" t="n">
         <v>7500</v>
@@ -7039,7 +7039,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>7.18510818481445</v>
+        <v>7.18510866165161</v>
       </c>
       <c r="H230" t="n">
         <v>11500</v>
@@ -7097,7 +7097,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G232" t="n">
-        <v>7.04728651046753</v>
+        <v>7.04728698730469</v>
       </c>
       <c r="H232" t="n">
         <v>25500</v>
@@ -7155,7 +7155,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H234" t="n">
         <v>37500</v>
@@ -7387,7 +7387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G242" t="n">
-        <v>6.79001903533936</v>
+        <v>6.79001951217651</v>
       </c>
       <c r="H242" t="n">
         <v>21500</v>
@@ -7474,7 +7474,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76245498657227</v>
+        <v>6.76245546340942</v>
       </c>
       <c r="H245" t="n">
         <v>4500</v>
@@ -7503,7 +7503,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H246" t="n">
         <v>14000</v>
@@ -7532,7 +7532,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G247" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49599933624268</v>
       </c>
       <c r="H247" t="n">
         <v>19000</v>
@@ -7764,7 +7764,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>6.3306131362915</v>
+        <v>6.33061361312866</v>
       </c>
       <c r="H255" t="n">
         <v>17000</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>6.23873281478882</v>
+        <v>6.23873233795166</v>
       </c>
       <c r="H257" t="n">
         <v>3500</v>
@@ -7909,7 +7909,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G260" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H260" t="n">
         <v>5000</v>
@@ -7938,7 +7938,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H261" t="n">
         <v>25000</v>
@@ -7967,7 +7967,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>6.79001903533936</v>
+        <v>6.79001951217651</v>
       </c>
       <c r="H262" t="n">
         <v>104000</v>
@@ -7996,7 +7996,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322738647461</v>
+        <v>7.09322690963745</v>
       </c>
       <c r="H263" t="n">
         <v>210500</v>
@@ -8054,7 +8054,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G265" t="n">
-        <v>6.92784070968628</v>
+        <v>6.92784118652344</v>
       </c>
       <c r="H265" t="n">
         <v>10500</v>
@@ -8112,7 +8112,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G267" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49599933624268</v>
       </c>
       <c r="H267" t="n">
         <v>18000</v>
@@ -8170,7 +8170,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>6.55112886428833</v>
+        <v>6.55112791061401</v>
       </c>
       <c r="H269" t="n">
         <v>7500</v>
@@ -8199,7 +8199,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G270" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49599933624268</v>
       </c>
       <c r="H270" t="n">
         <v>11500</v>
@@ -8257,7 +8257,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G272" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49599933624268</v>
       </c>
       <c r="H272" t="n">
         <v>5500</v>
@@ -8315,7 +8315,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>6.44087076187134</v>
+        <v>6.44087171554565</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8489,7 +8489,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H280" t="n">
         <v>26500</v>
@@ -8547,7 +8547,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73338508605957</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H282" t="n">
         <v>18500</v>
@@ -8663,7 +8663,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H286" t="n">
         <v>39500</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526683807373</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8895,7 +8895,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330575942993</v>
+        <v>6.41330623626709</v>
       </c>
       <c r="H294" t="n">
         <v>23500</v>
@@ -8924,7 +8924,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H295" t="n">
         <v>12500</v>
@@ -8953,7 +8953,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>6.55112886428833</v>
+        <v>6.55112791061401</v>
       </c>
       <c r="H296" t="n">
         <v>10000</v>
@@ -8982,7 +8982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H297" t="n">
         <v>14500</v>
@@ -9069,7 +9069,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H300" t="n">
         <v>39500</v>
@@ -9156,7 +9156,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386043548584</v>
       </c>
       <c r="H303" t="n">
         <v>18000</v>
@@ -9214,7 +9214,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386043548584</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9330,7 +9330,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>6.06415843963623</v>
+        <v>6.06415796279907</v>
       </c>
       <c r="H309" t="n">
         <v>4500</v>
@@ -9359,7 +9359,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H310" t="n">
         <v>7500</v>
@@ -9388,7 +9388,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9417,7 +9417,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G312" t="n">
-        <v>6.11009836196899</v>
+        <v>6.11009883880615</v>
       </c>
       <c r="H312" t="n">
         <v>10000</v>
@@ -9446,7 +9446,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05496978759766</v>
+        <v>6.05497026443481</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9504,7 +9504,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G315" t="n">
-        <v>6.11009836196899</v>
+        <v>6.11009883880615</v>
       </c>
       <c r="H315" t="n">
         <v>5000</v>
@@ -9562,7 +9562,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>6.09172296524048</v>
+        <v>6.09172201156616</v>
       </c>
       <c r="H317" t="n">
         <v>1500</v>
@@ -9620,7 +9620,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H319" t="n">
         <v>15000</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526683807373</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9794,7 +9794,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H325" t="n">
         <v>13000</v>
@@ -9881,7 +9881,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770231246948</v>
+        <v>5.79770278930664</v>
       </c>
       <c r="H328" t="n">
         <v>8871</v>
@@ -9939,7 +9939,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364318847656</v>
+        <v>5.8436427116394</v>
       </c>
       <c r="H330" t="n">
         <v>2311</v>
@@ -9997,7 +9997,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H332" t="n">
         <v>4456</v>
@@ -10026,7 +10026,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H333" t="n">
         <v>2022</v>
@@ -10113,7 +10113,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G336" t="n">
-        <v>6.11009836196899</v>
+        <v>6.11009883880615</v>
       </c>
       <c r="H336" t="n">
         <v>17470</v>
@@ -10142,7 +10142,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H337" t="n">
         <v>15456</v>
@@ -10171,7 +10171,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H338" t="n">
         <v>7965</v>
@@ -10287,7 +10287,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330575942993</v>
+        <v>6.41330623626709</v>
       </c>
       <c r="H342" t="n">
         <v>2560</v>
@@ -10345,7 +10345,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H344" t="n">
         <v>13218</v>
@@ -10403,7 +10403,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G346" t="n">
-        <v>6.10091018676758</v>
+        <v>6.10091066360474</v>
       </c>
       <c r="H346" t="n">
         <v>5191</v>
@@ -10432,7 +10432,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H347" t="n">
         <v>510</v>
@@ -10461,7 +10461,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H348" t="n">
         <v>1520</v>
@@ -10490,7 +10490,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G349" t="n">
-        <v>6.07334613800049</v>
+        <v>6.07334661483765</v>
       </c>
       <c r="H349" t="n">
         <v>8810</v>
@@ -10548,7 +10548,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H351" t="n">
         <v>2077</v>
@@ -10606,7 +10606,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G353" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H353" t="n">
         <v>14359</v>
@@ -10635,7 +10635,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27397966384888</v>
+        <v>5.27398014068604</v>
       </c>
       <c r="H354" t="n">
         <v>17836</v>
@@ -10664,7 +10664,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342546463013</v>
+        <v>5.39342594146729</v>
       </c>
       <c r="H355" t="n">
         <v>1874</v>
@@ -10722,7 +10722,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H357" t="n">
         <v>2284</v>
@@ -10809,7 +10809,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287031173706</v>
       </c>
       <c r="H360" t="n">
         <v>2285</v>
@@ -10896,7 +10896,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718849182129</v>
+        <v>5.57718801498413</v>
       </c>
       <c r="H363" t="n">
         <v>1392</v>
@@ -10925,7 +10925,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H364" t="n">
         <v>1105</v>
@@ -10983,7 +10983,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G366" t="n">
-        <v>5.65069246292114</v>
+        <v>5.6506929397583</v>
       </c>
       <c r="H366" t="n">
         <v>6216</v>
@@ -11099,7 +11099,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H370" t="n">
         <v>3154</v>
@@ -11186,7 +11186,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.07334613800049</v>
+        <v>6.07334661483765</v>
       </c>
       <c r="H374" t="n">
         <v>4630</v>
@@ -11302,7 +11302,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G377" t="n">
-        <v>5.73338508605957</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H377" t="n">
         <v>6848</v>
@@ -11389,7 +11389,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H380" t="n">
         <v>352</v>
@@ -11447,7 +11447,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H382" t="n">
         <v>7014</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.59556436538696</v>
+        <v>5.59556484222412</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11592,7 +11592,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>5.70582151412964</v>
+        <v>5.70582103729248</v>
       </c>
       <c r="H387" t="n">
         <v>2675</v>
@@ -11621,7 +11621,7 @@
         <v>6.25</v>
       </c>
       <c r="G388" t="n">
-        <v>5.7425742149353</v>
+        <v>5.74257373809814</v>
       </c>
       <c r="H388" t="n">
         <v>1978</v>
@@ -11853,7 +11853,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G396" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H396" t="n">
         <v>2491</v>
@@ -11882,7 +11882,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H397" t="n">
         <v>1264</v>
@@ -11940,7 +11940,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.11928653717041</v>
+        <v>6.11928701400757</v>
       </c>
       <c r="H399" t="n">
         <v>1503</v>
@@ -11998,7 +11998,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.99065256118774</v>
+        <v>5.9906530380249</v>
       </c>
       <c r="H401" t="n">
         <v>4770</v>
@@ -12027,7 +12027,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G402" t="n">
-        <v>5.90795993804932</v>
+        <v>5.90795946121216</v>
       </c>
       <c r="H402" t="n">
         <v>2037</v>
@@ -12056,7 +12056,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364318847656</v>
+        <v>5.8436427116394</v>
       </c>
       <c r="H403" t="n">
         <v>2709</v>
@@ -12085,7 +12085,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G404" t="n">
-        <v>5.85283088684082</v>
+        <v>5.85283136367798</v>
       </c>
       <c r="H404" t="n">
         <v>2104</v>
@@ -12201,7 +12201,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G408" t="n">
-        <v>5.73338508605957</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H408" t="n">
         <v>4978</v>
@@ -12230,7 +12230,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H409" t="n">
         <v>529</v>
@@ -12346,7 +12346,7 @@
         <v>6.25</v>
       </c>
       <c r="G413" t="n">
-        <v>5.7425742149353</v>
+        <v>5.74257373809814</v>
       </c>
       <c r="H413" t="n">
         <v>2441</v>
@@ -12404,7 +12404,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>5.63231658935547</v>
+        <v>5.63231611251831</v>
       </c>
       <c r="H415" t="n">
         <v>4705</v>
@@ -12433,7 +12433,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H416" t="n">
         <v>3751</v>
@@ -12462,7 +12462,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124666213989</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H417" t="n">
         <v>1848</v>
@@ -12520,7 +12520,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H419" t="n">
         <v>1068</v>
@@ -12549,7 +12549,7 @@
         <v>6</v>
       </c>
       <c r="G420" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287031173706</v>
       </c>
       <c r="H420" t="n">
         <v>2335</v>
@@ -12636,7 +12636,7 @@
         <v>6</v>
       </c>
       <c r="G423" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287031173706</v>
       </c>
       <c r="H423" t="n">
         <v>3401</v>
@@ -12694,7 +12694,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>5.41180181503296</v>
+        <v>5.4118013381958</v>
       </c>
       <c r="H425" t="n">
         <v>3167</v>
@@ -12752,7 +12752,7 @@
         <v>5.75</v>
       </c>
       <c r="G427" t="n">
-        <v>5.28316831588745</v>
+        <v>5.28316783905029</v>
       </c>
       <c r="H427" t="n">
         <v>6854</v>
@@ -12781,7 +12781,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27397966384888</v>
+        <v>5.27398014068604</v>
       </c>
       <c r="H428" t="n">
         <v>3146</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H434" t="n">
         <v>3264</v>
@@ -12984,7 +12984,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346488952637</v>
+        <v>5.05346536636353</v>
       </c>
       <c r="H435" t="n">
         <v>15369</v>
@@ -13042,7 +13042,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73188066482544</v>
+        <v>4.73188161849976</v>
       </c>
       <c r="H437" t="n">
         <v>15638</v>
@@ -13071,7 +13071,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.67675256729126</v>
+        <v>4.6767520904541</v>
       </c>
       <c r="H438" t="n">
         <v>13127</v>
@@ -13129,7 +13129,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>4.57568311691284</v>
+        <v>4.57568264007568</v>
       </c>
       <c r="H440" t="n">
         <v>3846</v>
@@ -13158,7 +13158,7 @@
         <v>4.97499990463257</v>
       </c>
       <c r="G441" t="n">
-        <v>4.5710883140564</v>
+        <v>4.57108879089355</v>
       </c>
       <c r="H441" t="n">
         <v>2599</v>
@@ -13187,7 +13187,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H442" t="n">
         <v>3292</v>
@@ -13216,7 +13216,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>4.58946466445923</v>
+        <v>4.58946514129639</v>
       </c>
       <c r="H443" t="n">
         <v>3808</v>
@@ -13245,7 +13245,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H444" t="n">
         <v>14966</v>
@@ -13274,7 +13274,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760381698608</v>
       </c>
       <c r="H445" t="n">
         <v>10951</v>
@@ -13303,7 +13303,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H446" t="n">
         <v>2659</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H448" t="n">
         <v>24980</v>
@@ -13390,7 +13390,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H449" t="n">
         <v>13181</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352521896362</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13448,7 +13448,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>4.64000034332275</v>
+        <v>4.6399998664856</v>
       </c>
       <c r="H451" t="n">
         <v>15337</v>
@@ -13506,7 +13506,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760381698608</v>
       </c>
       <c r="H453" t="n">
         <v>24237</v>
@@ -13535,7 +13535,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.4516429901123</v>
+        <v>4.45164346694946</v>
       </c>
       <c r="H454" t="n">
         <v>13974</v>
@@ -13564,7 +13564,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>4.38273286819458</v>
+        <v>4.38273239135742</v>
       </c>
       <c r="H455" t="n">
         <v>13871</v>
@@ -13593,7 +13593,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G456" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H456" t="n">
         <v>10262</v>
@@ -13622,7 +13622,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G457" t="n">
-        <v>4.48839616775513</v>
+        <v>4.48839569091797</v>
       </c>
       <c r="H457" t="n">
         <v>11036</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13680,7 +13680,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47461318969727</v>
+        <v>4.47461366653442</v>
       </c>
       <c r="H459" t="n">
         <v>11746</v>
@@ -13796,7 +13796,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.52974224090576</v>
+        <v>4.52974271774292</v>
       </c>
       <c r="H463" t="n">
         <v>15140</v>
@@ -13825,7 +13825,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G464" t="n">
-        <v>4.60324716567993</v>
+        <v>4.60324764251709</v>
       </c>
       <c r="H464" t="n">
         <v>5765</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352521896362</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -13941,7 +13941,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G468" t="n">
-        <v>4.4286732673645</v>
+        <v>4.42867374420166</v>
       </c>
       <c r="H468" t="n">
         <v>600</v>
@@ -14028,7 +14028,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34598016738892</v>
+        <v>4.34597969055176</v>
       </c>
       <c r="H471" t="n">
         <v>3835</v>
@@ -14057,7 +14057,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>4.39651441574097</v>
+        <v>4.39651393890381</v>
       </c>
       <c r="H472" t="n">
         <v>2289</v>
@@ -14144,7 +14144,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.39651441574097</v>
+        <v>4.39651393890381</v>
       </c>
       <c r="H475" t="n">
         <v>1381</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14202,7 +14202,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G477" t="n">
-        <v>4.49299001693726</v>
+        <v>4.4929895401001</v>
       </c>
       <c r="H477" t="n">
         <v>1400</v>
@@ -14231,7 +14231,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H478" t="n">
         <v>4551</v>
@@ -14260,7 +14260,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H479" t="n">
         <v>3457</v>
@@ -14289,7 +14289,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H480" t="n">
         <v>8400</v>
@@ -14318,7 +14318,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22194051742554</v>
+        <v>4.22194004058838</v>
       </c>
       <c r="H481" t="n">
         <v>10620</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332625389099</v>
+        <v>3.92332649230957</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14405,7 +14405,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G484" t="n">
-        <v>3.91413879394531</v>
+        <v>3.91413855552673</v>
       </c>
       <c r="H484" t="n">
         <v>16325</v>
@@ -14434,7 +14434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251538276672</v>
+        <v>3.93251490592957</v>
       </c>
       <c r="H485" t="n">
         <v>4207</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845482826233</v>
+        <v>3.97845506668091</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14492,7 +14492,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.97386074066162</v>
+        <v>3.9738609790802</v>
       </c>
       <c r="H487" t="n">
         <v>7176</v>
@@ -14608,7 +14608,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G491" t="n">
-        <v>3.82225704193115</v>
+        <v>3.82225680351257</v>
       </c>
       <c r="H491" t="n">
         <v>2924</v>
@@ -14637,7 +14637,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H492" t="n">
         <v>2046</v>
@@ -14666,7 +14666,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>3.84522747993469</v>
+        <v>3.84522724151611</v>
       </c>
       <c r="H493" t="n">
         <v>1926</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144569396973</v>
+        <v>3.83144545555115</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251538276672</v>
+        <v>3.93251490592957</v>
       </c>
       <c r="H497" t="n">
         <v>8274</v>
@@ -14811,7 +14811,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.95089077949524</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H498" t="n">
         <v>7416</v>
@@ -14840,7 +14840,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.95089077949524</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H499" t="n">
         <v>12304</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520729064941</v>
+        <v>4.01520776748657</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14956,7 +14956,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061344146729</v>
+        <v>4.01061296463013</v>
       </c>
       <c r="H503" t="n">
         <v>31005</v>
@@ -14985,7 +14985,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>4.3505744934082</v>
+        <v>4.35057401657104</v>
       </c>
       <c r="H504" t="n">
         <v>35126</v>
@@ -15014,7 +15014,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H505" t="n">
         <v>17677</v>
@@ -15043,7 +15043,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>4.32300996780396</v>
+        <v>4.3230094909668</v>
       </c>
       <c r="H506" t="n">
         <v>4619</v>
@@ -15072,7 +15072,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H507" t="n">
         <v>9121</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H508" t="n">
         <v>3615</v>
@@ -15159,7 +15159,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H510" t="n">
         <v>6857</v>
@@ -15188,7 +15188,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326663970947</v>
+        <v>4.43326711654663</v>
       </c>
       <c r="H511" t="n">
         <v>4220</v>
@@ -15217,7 +15217,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G512" t="n">
-        <v>4.30003881454468</v>
+        <v>4.30003929138184</v>
       </c>
       <c r="H512" t="n">
         <v>5794</v>
@@ -15246,7 +15246,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463314056396</v>
+        <v>4.30463361740112</v>
       </c>
       <c r="H513" t="n">
         <v>1902</v>
@@ -15275,7 +15275,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>4.40570259094238</v>
+        <v>4.40570306777954</v>
       </c>
       <c r="H514" t="n">
         <v>4889</v>
@@ -15304,7 +15304,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H515" t="n">
         <v>1906</v>
@@ -15391,7 +15391,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H518" t="n">
         <v>5744</v>
@@ -15420,7 +15420,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H519" t="n">
         <v>11351</v>
@@ -15449,7 +15449,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.73188066482544</v>
+        <v>4.73188161849976</v>
       </c>
       <c r="H520" t="n">
         <v>62686</v>
@@ -15710,7 +15710,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>4.89726734161377</v>
+        <v>4.89726686477661</v>
       </c>
       <c r="H529" t="n">
         <v>14250</v>
@@ -15739,7 +15739,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H530" t="n">
         <v>3028</v>
@@ -16029,7 +16029,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G540" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H540" t="n">
         <v>5649</v>
@@ -16058,7 +16058,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G541" t="n">
-        <v>4.8880786895752</v>
+        <v>4.88807916641235</v>
       </c>
       <c r="H541" t="n">
         <v>3175</v>
@@ -16116,7 +16116,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619741439819</v>
+        <v>4.79619789123535</v>
       </c>
       <c r="H543" t="n">
         <v>1688</v>
@@ -16145,7 +16145,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G544" t="n">
-        <v>4.69512891769409</v>
+        <v>4.69512844085693</v>
       </c>
       <c r="H544" t="n">
         <v>7711</v>
@@ -16232,7 +16232,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H547" t="n">
         <v>6999</v>
@@ -16261,7 +16261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H548" t="n">
         <v>5791</v>
@@ -16319,7 +16319,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.40570259094238</v>
+        <v>4.40570306777954</v>
       </c>
       <c r="H550" t="n">
         <v>4930</v>
@@ -16406,7 +16406,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H553" t="n">
         <v>1650</v>
@@ -16522,7 +16522,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546491622925</v>
+        <v>4.12546443939209</v>
       </c>
       <c r="H557" t="n">
         <v>7122</v>
@@ -16580,7 +16580,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H559" t="n">
         <v>22855</v>
@@ -16609,7 +16609,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>3.73497009277344</v>
+        <v>3.73497033119202</v>
       </c>
       <c r="H560" t="n">
         <v>18999</v>
@@ -16638,7 +16638,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631688117981</v>
+        <v>3.77631664276123</v>
       </c>
       <c r="H561" t="n">
         <v>14097</v>
@@ -16667,7 +16667,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>3.74875211715698</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H562" t="n">
         <v>4463</v>
@@ -16696,7 +16696,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H563" t="n">
         <v>7862</v>
@@ -16870,7 +16870,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G569" t="n">
-        <v>3.39041590690613</v>
+        <v>3.39041566848755</v>
       </c>
       <c r="H569" t="n">
         <v>51722</v>
@@ -16899,7 +16899,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H570" t="n">
         <v>38613</v>
@@ -16928,7 +16928,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G571" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H571" t="n">
         <v>7214</v>
@@ -17015,7 +17015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H574" t="n">
         <v>22621</v>
@@ -17189,7 +17189,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G580" t="n">
-        <v>3.03207921981812</v>
+        <v>3.03207898139954</v>
       </c>
       <c r="H580" t="n">
         <v>4602</v>
@@ -17218,7 +17218,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>3.05964326858521</v>
+        <v>3.05964350700378</v>
       </c>
       <c r="H581" t="n">
         <v>5248</v>
@@ -17305,7 +17305,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G584" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H584" t="n">
         <v>25151</v>
@@ -17334,7 +17334,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H585" t="n">
         <v>5627</v>
@@ -17363,7 +17363,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H586" t="n">
         <v>4755</v>
@@ -17392,7 +17392,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H587" t="n">
         <v>4318</v>
@@ -17595,7 +17595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904916763306</v>
+        <v>3.51904940605164</v>
       </c>
       <c r="H594" t="n">
         <v>20677</v>
@@ -17653,7 +17653,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H596" t="n">
         <v>1150</v>
@@ -17827,7 +17827,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H602" t="n">
         <v>23557</v>
@@ -18001,7 +18001,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178216934204</v>
+        <v>3.26178193092346</v>
       </c>
       <c r="H608" t="n">
         <v>18506</v>
@@ -18030,7 +18030,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178216934204</v>
+        <v>3.26178193092346</v>
       </c>
       <c r="H609" t="n">
         <v>2325</v>
@@ -18233,7 +18233,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H616" t="n">
         <v>4300</v>
@@ -18291,7 +18291,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.1147723197937</v>
+        <v>3.11477208137512</v>
       </c>
       <c r="H618" t="n">
         <v>1345</v>
@@ -18668,7 +18668,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G631" t="n">
-        <v>3.05137395858765</v>
+        <v>3.05137419700623</v>
       </c>
       <c r="H631" t="n">
         <v>3255</v>
@@ -19016,7 +19016,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H643" t="n">
         <v>60892</v>
@@ -19074,7 +19074,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040766716003</v>
+        <v>2.53040790557861</v>
       </c>
       <c r="H645" t="n">
         <v>12711</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761956214905</v>
+        <v>2.56761980056763</v>
       </c>
       <c r="H646" t="n">
         <v>8131</v>
@@ -19132,7 +19132,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901361465454</v>
+        <v>2.54901385307312</v>
       </c>
       <c r="H647" t="n">
         <v>4920</v>
@@ -19248,7 +19248,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H651" t="n">
         <v>18483</v>
@@ -19306,7 +19306,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G653" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H653" t="n">
         <v>9491</v>
@@ -19335,7 +19335,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H654" t="n">
         <v>19145</v>
@@ -19364,7 +19364,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H655" t="n">
         <v>11634</v>
@@ -19451,7 +19451,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G658" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H658" t="n">
         <v>3245</v>
@@ -19480,7 +19480,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G659" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H659" t="n">
         <v>1275</v>
@@ -19509,7 +19509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H660" t="n">
         <v>4896</v>
@@ -19596,7 +19596,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G663" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H663" t="n">
         <v>9545</v>
@@ -19625,7 +19625,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G664" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H664" t="n">
         <v>6580</v>
@@ -19654,7 +19654,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G665" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H665" t="n">
         <v>3700</v>
@@ -19770,7 +19770,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180171966553</v>
+        <v>2.51180195808411</v>
       </c>
       <c r="H669" t="n">
         <v>22344</v>
@@ -19799,7 +19799,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H670" t="n">
         <v>10500</v>
@@ -19828,7 +19828,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G671" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H671" t="n">
         <v>10911</v>
@@ -19857,7 +19857,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G672" t="n">
-        <v>2.37225699424744</v>
+        <v>2.37225723266602</v>
       </c>
       <c r="H672" t="n">
         <v>5885</v>
@@ -19886,7 +19886,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H673" t="n">
         <v>536</v>
@@ -20060,7 +20060,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H679" t="n">
         <v>10826</v>
@@ -20089,7 +20089,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20118,7 +20118,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H681" t="n">
         <v>3858</v>
@@ -20205,7 +20205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.4931960105896</v>
+        <v>2.49319577217102</v>
       </c>
       <c r="H684" t="n">
         <v>12276</v>
@@ -20350,7 +20350,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G689" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H689" t="n">
         <v>73294</v>
@@ -20379,7 +20379,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G690" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H690" t="n">
         <v>18911</v>
@@ -20437,7 +20437,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G692" t="n">
-        <v>1.1675226688385</v>
+        <v>1.16752278804779</v>
       </c>
       <c r="H692" t="n">
         <v>88258</v>
@@ -20466,7 +20466,7 @@
         <v>1.5</v>
       </c>
       <c r="G693" t="n">
-        <v>1.39544546604156</v>
+        <v>1.39544534683228</v>
       </c>
       <c r="H693" t="n">
         <v>126661</v>
@@ -20553,7 +20553,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H696" t="n">
         <v>232613</v>
@@ -20611,7 +20611,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>1.58150494098663</v>
+        <v>1.58150482177734</v>
       </c>
       <c r="H698" t="n">
         <v>54891</v>
@@ -20640,7 +20640,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G699" t="n">
-        <v>1.54429292678833</v>
+        <v>1.54429304599762</v>
       </c>
       <c r="H699" t="n">
         <v>36020</v>
@@ -20843,7 +20843,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G706" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H706" t="n">
         <v>26720</v>
@@ -20872,7 +20872,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G707" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H707" t="n">
         <v>1656</v>
@@ -20901,7 +20901,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G708" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H708" t="n">
         <v>9870</v>
@@ -20930,7 +20930,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G709" t="n">
-        <v>1.69314062595367</v>
+        <v>1.69314050674438</v>
       </c>
       <c r="H709" t="n">
         <v>21031</v>
@@ -20959,7 +20959,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>1.69779205322266</v>
+        <v>1.69779193401337</v>
       </c>
       <c r="H710" t="n">
         <v>5655</v>
@@ -21075,7 +21075,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.58150494098663</v>
+        <v>1.58150482177734</v>
       </c>
       <c r="H714" t="n">
         <v>5490</v>
@@ -21104,7 +21104,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G715" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H715" t="n">
         <v>9473</v>
@@ -21162,7 +21162,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G717" t="n">
-        <v>1.69314062595367</v>
+        <v>1.69314050674438</v>
       </c>
       <c r="H717" t="n">
         <v>5800</v>
@@ -21191,7 +21191,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G718" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H718" t="n">
         <v>5148</v>
@@ -21220,7 +21220,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G719" t="n">
-        <v>1.59545934200287</v>
+        <v>1.59545946121216</v>
       </c>
       <c r="H719" t="n">
         <v>9455</v>
@@ -21365,7 +21365,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="n">
-        <v>2.02804756164551</v>
+        <v>2.02804732322693</v>
       </c>
       <c r="H724" t="n">
         <v>114000</v>
@@ -21452,7 +21452,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H727" t="n">
         <v>67002</v>
@@ -21684,7 +21684,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H735" t="n">
         <v>53817</v>
@@ -21713,7 +21713,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H736" t="n">
         <v>25550</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H738" t="n">
         <v>41345</v>
@@ -21800,7 +21800,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550061225891</v>
+        <v>2.19550085067749</v>
       </c>
       <c r="H739" t="n">
         <v>13585</v>
@@ -21945,7 +21945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.1117742061615</v>
+        <v>2.11177396774292</v>
       </c>
       <c r="H744" t="n">
         <v>19716</v>
@@ -21974,7 +21974,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.009441614151</v>
+        <v>2.00944185256958</v>
       </c>
       <c r="H745" t="n">
         <v>22944</v>
@@ -22003,7 +22003,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>2.01874470710754</v>
+        <v>2.01874446868896</v>
       </c>
       <c r="H746" t="n">
         <v>7492</v>
@@ -22090,7 +22090,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>2.335045337677</v>
+        <v>2.33504557609558</v>
       </c>
       <c r="H749" t="n">
         <v>46515</v>
@@ -22177,7 +22177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.21410703659058</v>
+        <v>2.214106798172</v>
       </c>
       <c r="H752" t="n">
         <v>18450</v>
@@ -22293,7 +22293,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H756" t="n">
         <v>6173</v>
@@ -22322,7 +22322,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H757" t="n">
         <v>9025</v>
@@ -22351,7 +22351,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G758" t="n">
-        <v>2.22341012954712</v>
+        <v>2.22340989112854</v>
       </c>
       <c r="H758" t="n">
         <v>6613</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H760" t="n">
         <v>6602</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H761" t="n">
         <v>2731</v>
@@ -22525,7 +22525,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H764" t="n">
         <v>5171</v>
@@ -22554,7 +22554,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.1768946647644</v>
+        <v>2.17689490318298</v>
       </c>
       <c r="H765" t="n">
         <v>4690</v>
@@ -22699,7 +22699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H770" t="n">
         <v>1304</v>
@@ -22728,7 +22728,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H771" t="n">
         <v>5621</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.13968276977539</v>
+        <v>2.13968300819397</v>
       </c>
       <c r="H776" t="n">
         <v>3302</v>
@@ -22902,7 +22902,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>2.01874470710754</v>
+        <v>2.01874446868896</v>
       </c>
       <c r="H777" t="n">
         <v>30407</v>
@@ -22931,7 +22931,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G778" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H778" t="n">
         <v>10623</v>
@@ -23047,7 +23047,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H782" t="n">
         <v>7820</v>
@@ -23105,7 +23105,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.99083578586578</v>
+        <v>1.99083566665649</v>
       </c>
       <c r="H784" t="n">
         <v>1181</v>
@@ -23192,7 +23192,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H787" t="n">
         <v>19192</v>
@@ -23250,7 +23250,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G789" t="n">
-        <v>2.02804756164551</v>
+        <v>2.02804732322693</v>
       </c>
       <c r="H789" t="n">
         <v>2761</v>
@@ -23308,7 +23308,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.009441614151</v>
+        <v>2.00944185256958</v>
       </c>
       <c r="H791" t="n">
         <v>2800</v>
@@ -23366,7 +23366,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H793" t="n">
         <v>8905</v>
@@ -23395,7 +23395,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H794" t="n">
         <v>13577</v>
@@ -23569,7 +23569,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G800" t="n">
-        <v>1.90710878372192</v>
+        <v>1.90710866451263</v>
       </c>
       <c r="H800" t="n">
         <v>3251</v>
@@ -23772,7 +23772,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G807" t="n">
-        <v>1.69314062595367</v>
+        <v>1.69314050674438</v>
       </c>
       <c r="H807" t="n">
         <v>9403</v>
@@ -23801,7 +23801,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G808" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H808" t="n">
         <v>8701</v>
@@ -24004,7 +24004,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G815" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H815" t="n">
         <v>5716</v>
@@ -24033,7 +24033,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G816" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H816" t="n">
         <v>14593</v>
@@ -24120,7 +24120,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011088848114</v>
+        <v>1.60011076927185</v>
       </c>
       <c r="H819" t="n">
         <v>13128</v>
@@ -24265,7 +24265,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G824" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H824" t="n">
         <v>17867</v>
@@ -24352,7 +24352,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G827" t="n">
-        <v>1.52568697929382</v>
+        <v>1.52568709850311</v>
       </c>
       <c r="H827" t="n">
         <v>9611</v>
@@ -24381,7 +24381,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G828" t="n">
-        <v>1.56289875507355</v>
+        <v>1.56289887428284</v>
       </c>
       <c r="H828" t="n">
         <v>2401</v>
@@ -24439,7 +24439,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.83268511295319</v>
+        <v>1.83268523216248</v>
       </c>
       <c r="H830" t="n">
         <v>53960</v>
@@ -24700,7 +24700,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G839" t="n">
-        <v>1.84663939476013</v>
+        <v>1.84663951396942</v>
       </c>
       <c r="H839" t="n">
         <v>9860</v>
@@ -25106,7 +25106,7 @@
         <v>1.98500001430511</v>
       </c>
       <c r="G853" t="n">
-        <v>1.84663939476013</v>
+        <v>1.84663951396942</v>
       </c>
       <c r="H853" t="n">
         <v>17051</v>
@@ -25135,7 +25135,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.93501758575439</v>
+        <v>1.9350174665451</v>
       </c>
       <c r="H854" t="n">
         <v>16193</v>
@@ -25164,7 +25164,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G855" t="n">
-        <v>1.88850283622742</v>
+        <v>1.88850271701813</v>
       </c>
       <c r="H855" t="n">
         <v>15602</v>
@@ -25251,7 +25251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.8698970079422</v>
+        <v>1.86989688873291</v>
       </c>
       <c r="H858" t="n">
         <v>2711</v>
@@ -25280,7 +25280,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432044029236</v>
+        <v>1.94432055950165</v>
       </c>
       <c r="H859" t="n">
         <v>23244</v>
@@ -25338,7 +25338,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G861" t="n">
-        <v>2.02804756164551</v>
+        <v>2.02804732322693</v>
       </c>
       <c r="H861" t="n">
         <v>34243</v>
@@ -42657,6 +42657,64 @@
         <v>0</v>
       </c>
       <c r="I1458" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1459" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>0.665000021457672</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>830</v>
+      </c>
+      <c r="I1459" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1460" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>710</v>
+      </c>
+      <c r="I1460" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>2.83344316482544</v>
+        <v>2.83344292640686</v>
       </c>
       <c r="H2" t="n">
         <v>1050000</v>
@@ -485,7 +485,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6414999961853</v>
+        <v>2.64150023460388</v>
       </c>
       <c r="H4" t="n">
         <v>186000</v>
@@ -572,7 +572,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G7" t="n">
-        <v>3.53357768058777</v>
+        <v>3.53357791900635</v>
       </c>
       <c r="H7" t="n">
         <v>623000</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H11" t="n">
         <v>296000</v>
@@ -717,7 +717,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.60121488571167</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H12" t="n">
         <v>96000</v>
@@ -804,7 +804,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H15" t="n">
         <v>85000</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583201408386</v>
+        <v>3.44583249092102</v>
       </c>
       <c r="H16" t="n">
         <v>29000</v>
@@ -978,7 +978,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.26302933692932</v>
+        <v>3.2630295753479</v>
       </c>
       <c r="H21" t="n">
         <v>78000</v>
@@ -1007,7 +1007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30872988700867</v>
+        <v>3.30873036384583</v>
       </c>
       <c r="H22" t="n">
         <v>17000</v>
@@ -1036,7 +1036,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>3.40927171707153</v>
+        <v>3.40927195549011</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1094,7 +1094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.37271165847778</v>
+        <v>3.37271118164062</v>
       </c>
       <c r="H25" t="n">
         <v>11000</v>
@@ -1152,7 +1152,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248822212219</v>
+        <v>3.16248798370361</v>
       </c>
       <c r="H27" t="n">
         <v>62000</v>
@@ -1181,7 +1181,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764741897583</v>
+        <v>3.10764718055725</v>
       </c>
       <c r="H28" t="n">
         <v>52000</v>
@@ -1210,7 +1210,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.01624584197998</v>
+        <v>3.0162456035614</v>
       </c>
       <c r="H29" t="n">
         <v>41000</v>
@@ -1239,7 +1239,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15334796905518</v>
+        <v>3.1533477306366</v>
       </c>
       <c r="H30" t="n">
         <v>145000</v>
@@ -1268,7 +1268,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15334796905518</v>
+        <v>3.1533477306366</v>
       </c>
       <c r="H31" t="n">
         <v>36000</v>
@@ -1297,7 +1297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076825141907</v>
+        <v>3.18076801300049</v>
       </c>
       <c r="H32" t="n">
         <v>40000</v>
@@ -1384,7 +1384,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0893669128418</v>
+        <v>3.08936715126038</v>
       </c>
       <c r="H35" t="n">
         <v>9000</v>
@@ -1413,7 +1413,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818901062012</v>
+        <v>3.20818877220154</v>
       </c>
       <c r="H36" t="n">
         <v>50000</v>
@@ -1442,7 +1442,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443091392517</v>
+        <v>3.35443115234375</v>
       </c>
       <c r="H37" t="n">
         <v>264000</v>
@@ -1471,7 +1471,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G38" t="n">
-        <v>3.41841197013855</v>
+        <v>3.41841220855713</v>
       </c>
       <c r="H38" t="n">
         <v>54000</v>
@@ -1558,7 +1558,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H41" t="n">
         <v>172000</v>
@@ -1587,7 +1587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057785987854</v>
+        <v>3.82057809829712</v>
       </c>
       <c r="H42" t="n">
         <v>202000</v>
@@ -1616,7 +1616,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71089601516724</v>
+        <v>3.71089649200439</v>
       </c>
       <c r="H43" t="n">
         <v>172000</v>
@@ -1674,7 +1674,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>3.67433595657349</v>
+        <v>3.67433547973633</v>
       </c>
       <c r="H45" t="n">
         <v>29000</v>
@@ -1703,7 +1703,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72003674507141</v>
+        <v>3.72003698348999</v>
       </c>
       <c r="H46" t="n">
         <v>44000</v>
@@ -1732,7 +1732,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175623893738</v>
+        <v>3.7017560005188</v>
       </c>
       <c r="H47" t="n">
         <v>30000</v>
@@ -1761,7 +1761,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>3.67433595657349</v>
+        <v>3.67433547973633</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1819,7 +1819,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519594192505</v>
+        <v>3.66519570350647</v>
       </c>
       <c r="H50" t="n">
         <v>11000</v>
@@ -1877,7 +1877,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H52" t="n">
         <v>35000</v>
@@ -1906,7 +1906,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H53" t="n">
         <v>35000</v>
@@ -1935,7 +1935,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46411275863647</v>
+        <v>3.4641125202179</v>
       </c>
       <c r="H54" t="n">
         <v>65000</v>
@@ -1964,7 +1964,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -2051,7 +2051,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H58" t="n">
         <v>49000</v>
@@ -2080,7 +2080,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949467658997</v>
+        <v>3.61949491500854</v>
       </c>
       <c r="H59" t="n">
         <v>20000</v>
@@ -2109,7 +2109,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G60" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H60" t="n">
         <v>23000</v>
@@ -2138,7 +2138,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293461799622</v>
+        <v>3.58293485641479</v>
       </c>
       <c r="H61" t="n">
         <v>16000</v>
@@ -2225,7 +2225,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G64" t="n">
-        <v>3.60121488571167</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H64" t="n">
         <v>13000</v>
@@ -2254,7 +2254,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H65" t="n">
         <v>9000</v>
@@ -2283,7 +2283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H67" t="n">
         <v>24000</v>
@@ -2341,7 +2341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011909484863</v>
+        <v>3.62011861801147</v>
       </c>
       <c r="H68" t="n">
         <v>10000</v>
@@ -2544,7 +2544,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4179801940918</v>
+        <v>3.41797995567322</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2892,7 +2892,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G87" t="n">
-        <v>3.62930655479431</v>
+        <v>3.62930679321289</v>
       </c>
       <c r="H87" t="n">
         <v>36000</v>
@@ -2950,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524719238281</v>
+        <v>3.67524743080139</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524719238281</v>
+        <v>3.67524743080139</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3008,7 +3008,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.63849472999573</v>
+        <v>3.63849496841431</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3066,7 +3066,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>3.74875235557556</v>
+        <v>3.74875259399414</v>
       </c>
       <c r="H93" t="n">
         <v>51500</v>
@@ -3095,7 +3095,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H94" t="n">
         <v>132500</v>
@@ -3124,7 +3124,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G95" t="n">
-        <v>3.8957622051239</v>
+        <v>3.89576148986816</v>
       </c>
       <c r="H95" t="n">
         <v>105500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3211,7 +3211,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>5.09021759033203</v>
+        <v>5.09021711349487</v>
       </c>
       <c r="H98" t="n">
         <v>576000</v>
@@ -3269,7 +3269,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910871505737</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H100" t="n">
         <v>243500</v>
@@ -3385,7 +3385,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G104" t="n">
-        <v>5.31073188781738</v>
+        <v>5.31073236465454</v>
       </c>
       <c r="H104" t="n">
         <v>68500</v>
@@ -3530,7 +3530,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>5.49449491500854</v>
+        <v>5.49449443817139</v>
       </c>
       <c r="H109" t="n">
         <v>40500</v>
@@ -3559,7 +3559,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124761581421</v>
       </c>
       <c r="H110" t="n">
         <v>38500</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3704,7 +3704,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H115" t="n">
         <v>297500</v>
@@ -3733,7 +3733,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G116" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H116" t="n">
         <v>89000</v>
@@ -3791,7 +3791,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>7.49750471115112</v>
+        <v>7.49750518798828</v>
       </c>
       <c r="H118" t="n">
         <v>22500</v>
@@ -3820,7 +3820,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>7.38724708557129</v>
+        <v>7.38724660873413</v>
       </c>
       <c r="H119" t="n">
         <v>101000</v>
@@ -3849,7 +3849,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G120" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H120" t="n">
         <v>58500</v>
@@ -3878,7 +3878,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G121" t="n">
-        <v>7.36887168884277</v>
+        <v>7.36887073516846</v>
       </c>
       <c r="H121" t="n">
         <v>22000</v>
@@ -4023,7 +4023,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H126" t="n">
         <v>17500</v>
@@ -4052,7 +4052,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G127" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H127" t="n">
         <v>23000</v>
@@ -4081,7 +4081,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H128" t="n">
         <v>18500</v>
@@ -4226,7 +4226,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G133" t="n">
-        <v>7.27698945999146</v>
+        <v>7.27698993682861</v>
       </c>
       <c r="H133" t="n">
         <v>58000</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4313,7 +4313,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>7.38724708557129</v>
+        <v>7.38724660873413</v>
       </c>
       <c r="H136" t="n">
         <v>68000</v>
@@ -4342,7 +4342,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>7.25861310958862</v>
+        <v>7.25861358642578</v>
       </c>
       <c r="H137" t="n">
         <v>30500</v>
@@ -4371,7 +4371,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G138" t="n">
-        <v>7.4607515335083</v>
+        <v>7.46075248718262</v>
       </c>
       <c r="H138" t="n">
         <v>29000</v>
@@ -4400,7 +4400,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G139" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H139" t="n">
         <v>19500</v>
@@ -4429,7 +4429,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H140" t="n">
         <v>13000</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366283416748</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4603,7 +4603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08554363250732</v>
+        <v>8.08554458618164</v>
       </c>
       <c r="H146" t="n">
         <v>55500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366283416748</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4690,7 +4690,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G149" t="n">
-        <v>8.14067363739014</v>
+        <v>8.14067268371582</v>
       </c>
       <c r="H149" t="n">
         <v>53500</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4748,7 +4748,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178298950195</v>
+        <v>7.90178203582764</v>
       </c>
       <c r="H151" t="n">
         <v>20500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4835,7 +4835,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639583587646</v>
+        <v>7.73639631271362</v>
       </c>
       <c r="H154" t="n">
         <v>8500</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015743255615</v>
+        <v>7.92015790939331</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4893,7 +4893,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314758300781</v>
       </c>
       <c r="H156" t="n">
         <v>12500</v>
@@ -4951,7 +4951,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G158" t="n">
-        <v>7.7915244102478</v>
+        <v>7.79152297973633</v>
       </c>
       <c r="H158" t="n">
         <v>15500</v>
@@ -4980,7 +4980,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G159" t="n">
-        <v>7.7915244102478</v>
+        <v>7.79152297973633</v>
       </c>
       <c r="H159" t="n">
         <v>5500</v>
@@ -5009,7 +5009,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G160" t="n">
-        <v>7.64451360702515</v>
+        <v>7.6445140838623</v>
       </c>
       <c r="H160" t="n">
         <v>19000</v>
@@ -5067,7 +5067,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G162" t="n">
-        <v>7.68126630783081</v>
+        <v>7.68126726150513</v>
       </c>
       <c r="H162" t="n">
         <v>9500</v>
@@ -5096,7 +5096,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>7.49750471115112</v>
+        <v>7.49750518798828</v>
       </c>
       <c r="H163" t="n">
         <v>21000</v>
@@ -5125,7 +5125,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H164" t="n">
         <v>19000</v>
@@ -5154,7 +5154,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H165" t="n">
         <v>25000</v>
@@ -5183,7 +5183,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H166" t="n">
         <v>25500</v>
@@ -5212,7 +5212,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>7.27698945999146</v>
+        <v>7.27698993682861</v>
       </c>
       <c r="H167" t="n">
         <v>11500</v>
@@ -5241,7 +5241,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023818969727</v>
+        <v>7.24023723602295</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5357,7 +5357,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G172" t="n">
-        <v>8.14067363739014</v>
+        <v>8.14067268371582</v>
       </c>
       <c r="H172" t="n">
         <v>81500</v>
@@ -5386,7 +5386,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.36118793487549</v>
+        <v>8.36118698120117</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84665298461914</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5444,7 +5444,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801853179932</v>
+        <v>7.71801948547363</v>
       </c>
       <c r="H175" t="n">
         <v>33500</v>
@@ -5502,7 +5502,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G177" t="n">
-        <v>7.68126630783081</v>
+        <v>7.68126726150513</v>
       </c>
       <c r="H177" t="n">
         <v>11500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.84665298461914</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.84665298461914</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5618,7 +5618,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314758300781</v>
       </c>
       <c r="H181" t="n">
         <v>18500</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5821,7 +5821,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G188" t="n">
-        <v>7.4607515335083</v>
+        <v>7.46075248718262</v>
       </c>
       <c r="H188" t="n">
         <v>20500</v>
@@ -5850,7 +5850,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>7.4607515335083</v>
+        <v>7.46075248718262</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5908,7 +5908,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801853179932</v>
+        <v>7.71801948547363</v>
       </c>
       <c r="H191" t="n">
         <v>28000</v>
@@ -5937,7 +5937,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G192" t="n">
-        <v>7.68126630783081</v>
+        <v>7.68126726150513</v>
       </c>
       <c r="H192" t="n">
         <v>32000</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912931442261</v>
       </c>
       <c r="H197" t="n">
         <v>15000</v>
@@ -6169,7 +6169,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38724708557129</v>
+        <v>7.38724660873413</v>
       </c>
       <c r="H200" t="n">
         <v>9500</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H203" t="n">
         <v>17500</v>
@@ -6401,7 +6401,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G208" t="n">
-        <v>7.20348501205444</v>
+        <v>7.2034854888916</v>
       </c>
       <c r="H208" t="n">
         <v>15000</v>
@@ -6459,7 +6459,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023818969727</v>
+        <v>7.24023723602295</v>
       </c>
       <c r="H210" t="n">
         <v>10500</v>
@@ -6575,7 +6575,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83596038818359</v>
+        <v>6.83595991134644</v>
       </c>
       <c r="H214" t="n">
         <v>29500</v>
@@ -6633,7 +6633,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>6.8175835609436</v>
+        <v>6.81758403778076</v>
       </c>
       <c r="H216" t="n">
         <v>17500</v>
@@ -6691,7 +6691,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H218" t="n">
         <v>22500</v>
@@ -6720,7 +6720,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H219" t="n">
         <v>7500</v>
@@ -6778,7 +6778,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>6.46843528747559</v>
+        <v>6.46843481063843</v>
       </c>
       <c r="H221" t="n">
         <v>18500</v>
@@ -6836,7 +6836,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H223" t="n">
         <v>9000</v>
@@ -6923,7 +6923,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>7.16673278808594</v>
+        <v>7.16673231124878</v>
       </c>
       <c r="H226" t="n">
         <v>34500</v>
@@ -6981,7 +6981,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>7.16673278808594</v>
+        <v>7.16673231124878</v>
       </c>
       <c r="H228" t="n">
         <v>22000</v>
@@ -7010,7 +7010,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G229" t="n">
-        <v>7.23104906082153</v>
+        <v>7.23104858398438</v>
       </c>
       <c r="H229" t="n">
         <v>51500</v>
@@ -7068,7 +7068,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>7.13916778564453</v>
+        <v>7.13916826248169</v>
       </c>
       <c r="H231" t="n">
         <v>11500</v>
@@ -7213,7 +7213,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G236" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H236" t="n">
         <v>4500</v>
@@ -7300,7 +7300,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G239" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H239" t="n">
         <v>8000</v>
@@ -7329,7 +7329,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G240" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H240" t="n">
         <v>10000</v>
@@ -7387,7 +7387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G242" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H242" t="n">
         <v>21500</v>
@@ -7474,7 +7474,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76245546340942</v>
+        <v>6.76245498657227</v>
       </c>
       <c r="H245" t="n">
         <v>4500</v>
@@ -7561,7 +7561,7 @@
         <v>7</v>
       </c>
       <c r="G248" t="n">
-        <v>6.43168258666992</v>
+        <v>6.43168306350708</v>
       </c>
       <c r="H248" t="n">
         <v>15000</v>
@@ -7764,7 +7764,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>6.33061361312866</v>
+        <v>6.3306131362915</v>
       </c>
       <c r="H255" t="n">
         <v>17000</v>
@@ -7793,7 +7793,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>6.15603923797607</v>
+        <v>6.15603876113892</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>6.23873233795166</v>
+        <v>6.23873281478882</v>
       </c>
       <c r="H257" t="n">
         <v>3500</v>
@@ -7909,7 +7909,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G260" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H260" t="n">
         <v>5000</v>
@@ -7938,7 +7938,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H261" t="n">
         <v>25000</v>
@@ -7967,7 +7967,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H262" t="n">
         <v>104000</v>
@@ -7996,7 +7996,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322690963745</v>
+        <v>7.09322643280029</v>
       </c>
       <c r="H263" t="n">
         <v>210500</v>
@@ -8141,7 +8141,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H268" t="n">
         <v>11000</v>
@@ -8170,7 +8170,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>6.55112791061401</v>
+        <v>6.55112838745117</v>
       </c>
       <c r="H269" t="n">
         <v>7500</v>
@@ -8228,7 +8228,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>6.46843528747559</v>
+        <v>6.46843481063843</v>
       </c>
       <c r="H271" t="n">
         <v>20500</v>
@@ -8286,7 +8286,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G273" t="n">
-        <v>6.40411853790283</v>
+        <v>6.40411806106567</v>
       </c>
       <c r="H273" t="n">
         <v>10000</v>
@@ -8344,7 +8344,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G275" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8489,7 +8489,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H280" t="n">
         <v>26500</v>
@@ -8518,7 +8518,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H281" t="n">
         <v>27500</v>
@@ -8663,7 +8663,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910871505737</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H286" t="n">
         <v>39500</v>
@@ -8721,7 +8721,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G288" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H288" t="n">
         <v>11000</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526779174805</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8837,7 +8837,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G292" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H292" t="n">
         <v>3500</v>
@@ -8895,7 +8895,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H294" t="n">
         <v>23500</v>
@@ -8924,7 +8924,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H295" t="n">
         <v>12500</v>
@@ -8953,7 +8953,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>6.55112791061401</v>
+        <v>6.55112838745117</v>
       </c>
       <c r="H296" t="n">
         <v>10000</v>
@@ -8982,7 +8982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H297" t="n">
         <v>14500</v>
@@ -9011,7 +9011,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H298" t="n">
         <v>9000</v>
@@ -9040,7 +9040,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>6.56950426101685</v>
+        <v>6.569504737854</v>
       </c>
       <c r="H299" t="n">
         <v>6000</v>
@@ -9069,7 +9069,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H300" t="n">
         <v>39500</v>
@@ -9098,7 +9098,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G301" t="n">
-        <v>6.45924758911133</v>
+        <v>6.45924711227417</v>
       </c>
       <c r="H301" t="n">
         <v>43000</v>
@@ -9127,7 +9127,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H302" t="n">
         <v>17500</v>
@@ -9156,7 +9156,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>6.29386043548584</v>
+        <v>6.293860912323</v>
       </c>
       <c r="H303" t="n">
         <v>18000</v>
@@ -9185,7 +9185,7 @@
         <v>6.75</v>
       </c>
       <c r="G304" t="n">
-        <v>6.20198011398315</v>
+        <v>6.201979637146</v>
       </c>
       <c r="H304" t="n">
         <v>16000</v>
@@ -9214,7 +9214,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>6.29386043548584</v>
+        <v>6.293860912323</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9272,7 +9272,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548408508301</v>
+        <v>6.27548456192017</v>
       </c>
       <c r="H307" t="n">
         <v>9000</v>
@@ -9359,7 +9359,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H310" t="n">
         <v>7500</v>
@@ -9388,7 +9388,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05497026443481</v>
+        <v>6.05496978759766</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9562,7 +9562,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>6.09172201156616</v>
+        <v>6.09172248840332</v>
       </c>
       <c r="H317" t="n">
         <v>1500</v>
@@ -9678,7 +9678,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G321" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9736,7 +9736,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714859008789</v>
+        <v>5.91714811325073</v>
       </c>
       <c r="H323" t="n">
         <v>7000</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526779174805</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9794,7 +9794,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H325" t="n">
         <v>13000</v>
@@ -9852,7 +9852,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607866287231</v>
+        <v>5.81607913970947</v>
       </c>
       <c r="H327" t="n">
         <v>14080</v>
@@ -9881,7 +9881,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770278930664</v>
+        <v>5.79770231246948</v>
       </c>
       <c r="H328" t="n">
         <v>8871</v>
@@ -9939,7 +9939,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.8436427116394</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H330" t="n">
         <v>2311</v>
@@ -9997,7 +9997,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H332" t="n">
         <v>4456</v>
@@ -10026,7 +10026,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H333" t="n">
         <v>2022</v>
@@ -10055,7 +10055,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G334" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H334" t="n">
         <v>1801</v>
@@ -10142,7 +10142,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H337" t="n">
         <v>15456</v>
@@ -10258,7 +10258,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H341" t="n">
         <v>12887</v>
@@ -10287,7 +10287,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H342" t="n">
         <v>2560</v>
@@ -10316,7 +10316,7 @@
         <v>7</v>
       </c>
       <c r="G343" t="n">
-        <v>6.43168258666992</v>
+        <v>6.43168306350708</v>
       </c>
       <c r="H343" t="n">
         <v>3966</v>
@@ -10432,7 +10432,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H347" t="n">
         <v>510</v>
@@ -10461,7 +10461,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H348" t="n">
         <v>1520</v>
@@ -10490,7 +10490,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G349" t="n">
-        <v>6.07334661483765</v>
+        <v>6.07334613800049</v>
       </c>
       <c r="H349" t="n">
         <v>8810</v>
@@ -10548,7 +10548,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H351" t="n">
         <v>2077</v>
@@ -10606,7 +10606,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G353" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H353" t="n">
         <v>14359</v>
@@ -10635,7 +10635,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27398014068604</v>
+        <v>5.27397918701172</v>
       </c>
       <c r="H354" t="n">
         <v>17836</v>
@@ -10664,7 +10664,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342594146729</v>
+        <v>5.39342546463013</v>
       </c>
       <c r="H355" t="n">
         <v>1874</v>
@@ -10693,7 +10693,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.5588116645813</v>
+        <v>5.55881118774414</v>
       </c>
       <c r="H356" t="n">
         <v>2401</v>
@@ -10809,7 +10809,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="n">
-        <v>5.51287031173706</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H360" t="n">
         <v>2285</v>
@@ -10896,7 +10896,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718801498413</v>
+        <v>5.57718753814697</v>
       </c>
       <c r="H363" t="n">
         <v>1392</v>
@@ -10954,7 +10954,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>5.5588116645813</v>
+        <v>5.55881118774414</v>
       </c>
       <c r="H365" t="n">
         <v>2304</v>
@@ -11099,7 +11099,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H370" t="n">
         <v>3154</v>
@@ -11186,7 +11186,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.07334661483765</v>
+        <v>6.07334613800049</v>
       </c>
       <c r="H374" t="n">
         <v>4630</v>
@@ -11360,7 +11360,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>5.68744516372681</v>
+        <v>5.68744564056396</v>
       </c>
       <c r="H379" t="n">
         <v>2986</v>
@@ -11447,7 +11447,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H382" t="n">
         <v>7014</v>
@@ -11476,7 +11476,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H383" t="n">
         <v>1054</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.59556484222412</v>
+        <v>5.5955638885498</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11534,7 +11534,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H385" t="n">
         <v>1810</v>
@@ -11621,7 +11621,7 @@
         <v>6.25</v>
       </c>
       <c r="G388" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H388" t="n">
         <v>1978</v>
@@ -11650,7 +11650,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932691574097</v>
+        <v>5.77932643890381</v>
       </c>
       <c r="H389" t="n">
         <v>6221</v>
@@ -11766,7 +11766,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G393" t="n">
-        <v>5.96308851242065</v>
+        <v>5.96308898925781</v>
       </c>
       <c r="H393" t="n">
         <v>4882</v>
@@ -11795,7 +11795,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>6.14685106277466</v>
+        <v>6.14685153961182</v>
       </c>
       <c r="H394" t="n">
         <v>4839</v>
@@ -11824,7 +11824,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>6.14685106277466</v>
+        <v>6.14685153961182</v>
       </c>
       <c r="H395" t="n">
         <v>6355</v>
@@ -11853,7 +11853,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G396" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H396" t="n">
         <v>2491</v>
@@ -11882,7 +11882,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H397" t="n">
         <v>1264</v>
@@ -11969,7 +11969,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>6.00902938842773</v>
+        <v>6.00902891159058</v>
       </c>
       <c r="H400" t="n">
         <v>2189</v>
@@ -12056,7 +12056,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.8436427116394</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H403" t="n">
         <v>2709</v>
@@ -12085,7 +12085,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G404" t="n">
-        <v>5.85283136367798</v>
+        <v>5.85283088684082</v>
       </c>
       <c r="H404" t="n">
         <v>2104</v>
@@ -12114,7 +12114,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>5.95390033721924</v>
+        <v>5.9539008140564</v>
       </c>
       <c r="H405" t="n">
         <v>1670</v>
@@ -12259,7 +12259,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.89877223968506</v>
+        <v>5.8987717628479</v>
       </c>
       <c r="H410" t="n">
         <v>1853</v>
@@ -12317,7 +12317,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607866287231</v>
+        <v>5.81607913970947</v>
       </c>
       <c r="H412" t="n">
         <v>2753</v>
@@ -12346,7 +12346,7 @@
         <v>6.25</v>
       </c>
       <c r="G413" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H413" t="n">
         <v>2441</v>
@@ -12404,7 +12404,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>5.63231611251831</v>
+        <v>5.63231658935547</v>
       </c>
       <c r="H415" t="n">
         <v>4705</v>
@@ -12433,7 +12433,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H416" t="n">
         <v>3751</v>
@@ -12462,7 +12462,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124761581421</v>
       </c>
       <c r="H417" t="n">
         <v>1848</v>
@@ -12520,7 +12520,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H419" t="n">
         <v>1068</v>
@@ -12549,7 +12549,7 @@
         <v>6</v>
       </c>
       <c r="G420" t="n">
-        <v>5.51287031173706</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H420" t="n">
         <v>2335</v>
@@ -12578,7 +12578,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H421" t="n">
         <v>4496</v>
@@ -12607,7 +12607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G422" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H422" t="n">
         <v>3644</v>
@@ -12636,7 +12636,7 @@
         <v>6</v>
       </c>
       <c r="G423" t="n">
-        <v>5.51287031173706</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H423" t="n">
         <v>3401</v>
@@ -12781,7 +12781,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27398014068604</v>
+        <v>5.27397918701172</v>
       </c>
       <c r="H428" t="n">
         <v>3146</v>
@@ -12839,7 +12839,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>5.31992101669312</v>
+        <v>5.31992053985596</v>
       </c>
       <c r="H430" t="n">
         <v>4924</v>
@@ -12897,7 +12897,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423728942871</v>
+        <v>5.38423776626587</v>
       </c>
       <c r="H432" t="n">
         <v>3519</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910871505737</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H434" t="n">
         <v>3264</v>
@@ -13042,7 +13042,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73188161849976</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H437" t="n">
         <v>15638</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.58487033843994</v>
+        <v>4.5848708152771</v>
       </c>
       <c r="H439" t="n">
         <v>4452</v>
@@ -13187,7 +13187,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H442" t="n">
         <v>3292</v>
@@ -13216,7 +13216,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>4.58946514129639</v>
+        <v>4.58946466445923</v>
       </c>
       <c r="H443" t="n">
         <v>3808</v>
@@ -13245,7 +13245,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H444" t="n">
         <v>14966</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H448" t="n">
         <v>24980</v>
@@ -13535,7 +13535,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.45164346694946</v>
+        <v>4.4516429901123</v>
       </c>
       <c r="H454" t="n">
         <v>13974</v>
@@ -13622,7 +13622,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G457" t="n">
-        <v>4.48839569091797</v>
+        <v>4.48839616775513</v>
       </c>
       <c r="H457" t="n">
         <v>11036</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13738,7 +13738,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G461" t="n">
-        <v>4.46542549133301</v>
+        <v>4.46542596817017</v>
       </c>
       <c r="H461" t="n">
         <v>5481</v>
@@ -13796,7 +13796,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.52974271774292</v>
+        <v>4.52974224090576</v>
       </c>
       <c r="H463" t="n">
         <v>15140</v>
@@ -13854,7 +13854,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>4.49758386611938</v>
+        <v>4.49758434295654</v>
       </c>
       <c r="H465" t="n">
         <v>9324</v>
@@ -13999,7 +13999,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>4.49758386611938</v>
+        <v>4.49758434295654</v>
       </c>
       <c r="H470" t="n">
         <v>305</v>
@@ -14028,7 +14028,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34597969055176</v>
+        <v>4.34598016738892</v>
       </c>
       <c r="H471" t="n">
         <v>3835</v>
@@ -14057,7 +14057,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>4.39651393890381</v>
+        <v>4.39651489257812</v>
       </c>
       <c r="H472" t="n">
         <v>2289</v>
@@ -14144,7 +14144,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.39651393890381</v>
+        <v>4.39651489257812</v>
       </c>
       <c r="H475" t="n">
         <v>1381</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14318,7 +14318,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22194004058838</v>
+        <v>4.22194051742554</v>
       </c>
       <c r="H481" t="n">
         <v>10620</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332649230957</v>
+        <v>3.92332625389099</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14405,7 +14405,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G484" t="n">
-        <v>3.91413855552673</v>
+        <v>3.91413831710815</v>
       </c>
       <c r="H484" t="n">
         <v>16325</v>
@@ -14434,7 +14434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H485" t="n">
         <v>4207</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845506668091</v>
+        <v>3.97845530509949</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14521,7 +14521,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G488" t="n">
-        <v>3.84063315391541</v>
+        <v>3.84063363075256</v>
       </c>
       <c r="H488" t="n">
         <v>15203</v>
@@ -14550,7 +14550,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G489" t="n">
-        <v>3.84063315391541</v>
+        <v>3.84063363075256</v>
       </c>
       <c r="H489" t="n">
         <v>5714</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469275474548</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14608,7 +14608,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G491" t="n">
-        <v>3.82225680351257</v>
+        <v>3.82225704193115</v>
       </c>
       <c r="H491" t="n">
         <v>2924</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144545555115</v>
+        <v>3.83144569396973</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14724,7 +14724,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.85900926589966</v>
+        <v>3.85900974273682</v>
       </c>
       <c r="H495" t="n">
         <v>5373</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469275474548</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H497" t="n">
         <v>8274</v>
@@ -14811,7 +14811,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.95089149475098</v>
+        <v>3.95089101791382</v>
       </c>
       <c r="H498" t="n">
         <v>7416</v>
@@ -14840,7 +14840,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.95089149475098</v>
+        <v>3.95089101791382</v>
       </c>
       <c r="H499" t="n">
         <v>12304</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14956,7 +14956,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061296463013</v>
+        <v>4.01061344146729</v>
       </c>
       <c r="H503" t="n">
         <v>31005</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H508" t="n">
         <v>3615</v>
@@ -15159,7 +15159,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H510" t="n">
         <v>6857</v>
@@ -15217,7 +15217,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G512" t="n">
-        <v>4.30003929138184</v>
+        <v>4.30003881454468</v>
       </c>
       <c r="H512" t="n">
         <v>5794</v>
@@ -15246,7 +15246,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463361740112</v>
+        <v>4.30463314056396</v>
       </c>
       <c r="H513" t="n">
         <v>1902</v>
@@ -15275,7 +15275,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>4.40570306777954</v>
+        <v>4.40570259094238</v>
       </c>
       <c r="H514" t="n">
         <v>4889</v>
@@ -15362,7 +15362,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G517" t="n">
-        <v>4.391921043396</v>
+        <v>4.39192056655884</v>
       </c>
       <c r="H517" t="n">
         <v>7436</v>
@@ -15449,7 +15449,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.73188161849976</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H520" t="n">
         <v>62686</v>
@@ -15478,7 +15478,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>4.62162351608276</v>
+        <v>4.62162399291992</v>
       </c>
       <c r="H521" t="n">
         <v>14852</v>
@@ -15507,7 +15507,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G522" t="n">
-        <v>4.95239591598511</v>
+        <v>4.95239543914795</v>
       </c>
       <c r="H522" t="n">
         <v>39061</v>
@@ -15536,7 +15536,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H523" t="n">
         <v>16347</v>
@@ -15594,7 +15594,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H525" t="n">
         <v>6708</v>
@@ -15652,7 +15652,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>4.81457376480103</v>
+        <v>4.81457328796387</v>
       </c>
       <c r="H527" t="n">
         <v>9827</v>
@@ -15797,7 +15797,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G532" t="n">
-        <v>4.95239591598511</v>
+        <v>4.95239543914795</v>
       </c>
       <c r="H532" t="n">
         <v>12268</v>
@@ -15826,7 +15826,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.90645503997803</v>
+        <v>4.90645551681519</v>
       </c>
       <c r="H533" t="n">
         <v>5784</v>
@@ -15855,7 +15855,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H534" t="n">
         <v>5758</v>
@@ -15884,7 +15884,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>5.09021759033203</v>
+        <v>5.09021711349487</v>
       </c>
       <c r="H535" t="n">
         <v>24385</v>
@@ -16116,7 +16116,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619789123535</v>
+        <v>4.79619693756104</v>
       </c>
       <c r="H543" t="n">
         <v>1688</v>
@@ -16174,7 +16174,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G545" t="n">
-        <v>4.72269248962402</v>
+        <v>4.72269296646118</v>
       </c>
       <c r="H545" t="n">
         <v>18159</v>
@@ -16261,7 +16261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H548" t="n">
         <v>5791</v>
@@ -16290,7 +16290,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>4.26328659057617</v>
+        <v>4.26328706741333</v>
       </c>
       <c r="H549" t="n">
         <v>8198</v>
@@ -16319,7 +16319,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.40570306777954</v>
+        <v>4.40570259094238</v>
       </c>
       <c r="H550" t="n">
         <v>4930</v>
@@ -16348,7 +16348,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.20815849304199</v>
+        <v>4.20815801620483</v>
       </c>
       <c r="H551" t="n">
         <v>18005</v>
@@ -16464,7 +16464,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>4.09790086746216</v>
+        <v>4.097900390625</v>
       </c>
       <c r="H555" t="n">
         <v>11397</v>
@@ -16522,7 +16522,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546443939209</v>
+        <v>4.12546539306641</v>
       </c>
       <c r="H557" t="n">
         <v>7122</v>
@@ -16609,7 +16609,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>3.73497033119202</v>
+        <v>3.73497009277344</v>
       </c>
       <c r="H560" t="n">
         <v>18999</v>
@@ -16667,7 +16667,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>3.74875235557556</v>
+        <v>3.74875259399414</v>
       </c>
       <c r="H562" t="n">
         <v>4463</v>
@@ -16725,7 +16725,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>3.69362354278564</v>
+        <v>3.69362330436707</v>
       </c>
       <c r="H564" t="n">
         <v>10513</v>
@@ -16899,7 +16899,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>3.38122773170471</v>
+        <v>3.38122749328613</v>
       </c>
       <c r="H570" t="n">
         <v>38613</v>
@@ -16928,7 +16928,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G571" t="n">
-        <v>3.38122773170471</v>
+        <v>3.38122749328613</v>
       </c>
       <c r="H571" t="n">
         <v>7214</v>
@@ -16957,7 +16957,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H572" t="n">
         <v>40710</v>
@@ -17044,7 +17044,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G575" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H575" t="n">
         <v>2675</v>
@@ -17073,7 +17073,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G576" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H576" t="n">
         <v>1539</v>
@@ -17102,7 +17102,7 @@
         <v>3.5</v>
       </c>
       <c r="G577" t="n">
-        <v>3.21584129333496</v>
+        <v>3.21584153175354</v>
       </c>
       <c r="H577" t="n">
         <v>7340</v>
@@ -17160,7 +17160,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09639573097229</v>
+        <v>3.09639549255371</v>
       </c>
       <c r="H579" t="n">
         <v>10888</v>
@@ -17247,7 +17247,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>3.07801961898804</v>
+        <v>3.07801938056946</v>
       </c>
       <c r="H582" t="n">
         <v>2310</v>
@@ -17276,7 +17276,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H583" t="n">
         <v>18949</v>
@@ -17334,7 +17334,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.54661345481873</v>
+        <v>3.54661321640015</v>
       </c>
       <c r="H585" t="n">
         <v>5627</v>
@@ -17363,7 +17363,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.54661345481873</v>
+        <v>3.54661321640015</v>
       </c>
       <c r="H586" t="n">
         <v>4755</v>
@@ -17479,7 +17479,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.94170236587524</v>
+        <v>3.94170308113098</v>
       </c>
       <c r="H590" t="n">
         <v>70490</v>
@@ -17653,7 +17653,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.54661345481873</v>
+        <v>3.54661321640015</v>
       </c>
       <c r="H596" t="n">
         <v>1150</v>
@@ -17798,7 +17798,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G601" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H601" t="n">
         <v>18937</v>
@@ -17856,7 +17856,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H603" t="n">
         <v>2415</v>
@@ -17885,7 +17885,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H604" t="n">
         <v>8247</v>
@@ -18001,7 +18001,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H608" t="n">
         <v>18506</v>
@@ -18030,7 +18030,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H609" t="n">
         <v>2325</v>
@@ -18059,7 +18059,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>3.18827724456787</v>
+        <v>3.18827700614929</v>
       </c>
       <c r="H610" t="n">
         <v>6723</v>
@@ -18117,7 +18117,7 @@
         <v>3.5</v>
       </c>
       <c r="G612" t="n">
-        <v>3.21584129333496</v>
+        <v>3.21584153175354</v>
       </c>
       <c r="H612" t="n">
         <v>1010</v>
@@ -18262,7 +18262,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.07801961898804</v>
+        <v>3.07801938056946</v>
       </c>
       <c r="H617" t="n">
         <v>10279</v>
@@ -18291,7 +18291,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.11477208137512</v>
+        <v>3.1147723197937</v>
       </c>
       <c r="H618" t="n">
         <v>1345</v>
@@ -18320,7 +18320,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>3.00451469421387</v>
+        <v>3.00451445579529</v>
       </c>
       <c r="H619" t="n">
         <v>10299</v>
@@ -18349,7 +18349,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H620" t="n">
         <v>26152</v>
@@ -18407,7 +18407,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>2.84831666946411</v>
+        <v>2.84831643104553</v>
       </c>
       <c r="H622" t="n">
         <v>13986</v>
@@ -18523,7 +18523,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H626" t="n">
         <v>14381</v>
@@ -18581,7 +18581,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>2.97695016860962</v>
+        <v>2.9769504070282</v>
       </c>
       <c r="H628" t="n">
         <v>1810</v>
@@ -18813,7 +18813,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>2.87461757659912</v>
+        <v>2.8746178150177</v>
       </c>
       <c r="H636" t="n">
         <v>10336</v>
@@ -18900,7 +18900,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G639" t="n">
-        <v>2.87461757659912</v>
+        <v>2.8746178150177</v>
       </c>
       <c r="H639" t="n">
         <v>14548</v>
@@ -18958,7 +18958,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>2.64204335212708</v>
+        <v>2.64204359054565</v>
       </c>
       <c r="H641" t="n">
         <v>86139</v>
@@ -18987,7 +18987,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110481262207</v>
+        <v>2.52110505104065</v>
       </c>
       <c r="H642" t="n">
         <v>95598</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761980056763</v>
+        <v>2.56761956214905</v>
       </c>
       <c r="H646" t="n">
         <v>8131</v>
@@ -19190,7 +19190,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>2.48389291763306</v>
+        <v>2.48389315605164</v>
       </c>
       <c r="H649" t="n">
         <v>18231</v>
@@ -19248,7 +19248,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H651" t="n">
         <v>18483</v>
@@ -19277,7 +19277,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.39086294174194</v>
+        <v>2.39086318016052</v>
       </c>
       <c r="H652" t="n">
         <v>8591</v>
@@ -19335,7 +19335,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H654" t="n">
         <v>19145</v>
@@ -19364,7 +19364,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H655" t="n">
         <v>11634</v>
@@ -19422,7 +19422,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G657" t="n">
-        <v>2.39086294174194</v>
+        <v>2.39086318016052</v>
       </c>
       <c r="H657" t="n">
         <v>4696</v>
@@ -19509,7 +19509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H660" t="n">
         <v>4896</v>
@@ -19683,7 +19683,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H666" t="n">
         <v>5645</v>
@@ -19712,7 +19712,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H667" t="n">
         <v>3080</v>
@@ -19741,7 +19741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G668" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H668" t="n">
         <v>2684</v>
@@ -19886,7 +19886,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H673" t="n">
         <v>536</v>
@@ -20002,7 +20002,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H677" t="n">
         <v>13195</v>
@@ -20089,7 +20089,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20118,7 +20118,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H681" t="n">
         <v>3858</v>
@@ -20147,7 +20147,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H682" t="n">
         <v>8637</v>
@@ -20176,7 +20176,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.29783344268799</v>
+        <v>2.29783368110657</v>
       </c>
       <c r="H683" t="n">
         <v>7367</v>
@@ -20205,7 +20205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.49319577217102</v>
+        <v>2.4931960105896</v>
       </c>
       <c r="H684" t="n">
         <v>12276</v>
@@ -20234,7 +20234,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35365104675293</v>
+        <v>2.35365152359009</v>
       </c>
       <c r="H685" t="n">
         <v>24371</v>
@@ -20350,7 +20350,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G689" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H689" t="n">
         <v>73294</v>
@@ -20379,7 +20379,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G690" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H690" t="n">
         <v>18911</v>
@@ -20437,7 +20437,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G692" t="n">
-        <v>1.16752278804779</v>
+        <v>1.1675226688385</v>
       </c>
       <c r="H692" t="n">
         <v>88258</v>
@@ -20466,7 +20466,7 @@
         <v>1.5</v>
       </c>
       <c r="G693" t="n">
-        <v>1.39544534683228</v>
+        <v>1.39544546604156</v>
       </c>
       <c r="H693" t="n">
         <v>126661</v>
@@ -20495,7 +20495,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G694" t="n">
-        <v>1.74895823001862</v>
+        <v>1.74895834922791</v>
       </c>
       <c r="H694" t="n">
         <v>231606</v>
@@ -20524,7 +20524,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H695" t="n">
         <v>235716</v>
@@ -20640,7 +20640,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G699" t="n">
-        <v>1.54429304599762</v>
+        <v>1.54429292678833</v>
       </c>
       <c r="H699" t="n">
         <v>36020</v>
@@ -20988,7 +20988,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H711" t="n">
         <v>6528</v>
@@ -21017,7 +21017,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H712" t="n">
         <v>2874</v>
@@ -21104,7 +21104,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G715" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H715" t="n">
         <v>9473</v>
@@ -21191,7 +21191,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G718" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H718" t="n">
         <v>5148</v>
@@ -21220,7 +21220,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G719" t="n">
-        <v>1.59545946121216</v>
+        <v>1.59545934200287</v>
       </c>
       <c r="H719" t="n">
         <v>9455</v>
@@ -21249,7 +21249,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.63267111778259</v>
+        <v>1.63267123699188</v>
       </c>
       <c r="H720" t="n">
         <v>7920</v>
@@ -21365,7 +21365,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="n">
-        <v>2.02804732322693</v>
+        <v>2.02804756164551</v>
       </c>
       <c r="H724" t="n">
         <v>114000</v>
@@ -21423,7 +21423,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H726" t="n">
         <v>75327</v>
@@ -21481,7 +21481,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H728" t="n">
         <v>18194</v>
@@ -21742,7 +21742,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>2.18619775772095</v>
+        <v>2.18619799613953</v>
       </c>
       <c r="H737" t="n">
         <v>12209</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H738" t="n">
         <v>41345</v>
@@ -21945,7 +21945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.11177396774292</v>
+        <v>2.1117742061615</v>
       </c>
       <c r="H744" t="n">
         <v>19716</v>
@@ -21974,7 +21974,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.00944185256958</v>
+        <v>2.009441614151</v>
       </c>
       <c r="H745" t="n">
         <v>22944</v>
@@ -22003,7 +22003,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>2.01874446868896</v>
+        <v>2.01874470710754</v>
       </c>
       <c r="H746" t="n">
         <v>7492</v>
@@ -22090,7 +22090,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>2.33504557609558</v>
+        <v>2.335045337677</v>
       </c>
       <c r="H749" t="n">
         <v>46515</v>
@@ -22148,7 +22148,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H751" t="n">
         <v>7609</v>
@@ -22206,7 +22206,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.24201607704163</v>
+        <v>2.24201583862305</v>
       </c>
       <c r="H753" t="n">
         <v>7610</v>
@@ -22235,7 +22235,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H754" t="n">
         <v>54449</v>
@@ -22264,7 +22264,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H755" t="n">
         <v>13384</v>
@@ -22293,7 +22293,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H756" t="n">
         <v>6173</v>
@@ -22322,7 +22322,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H757" t="n">
         <v>9025</v>
@@ -22351,7 +22351,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G758" t="n">
-        <v>2.22340989112854</v>
+        <v>2.22341012954712</v>
       </c>
       <c r="H758" t="n">
         <v>6613</v>
@@ -22467,7 +22467,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16759181022644</v>
+        <v>2.16759204864502</v>
       </c>
       <c r="H762" t="n">
         <v>4601</v>
@@ -22496,7 +22496,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>2.1582887172699</v>
+        <v>2.15828895568848</v>
       </c>
       <c r="H763" t="n">
         <v>5178</v>
@@ -22786,7 +22786,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.12107706069946</v>
+        <v>2.12107729911804</v>
       </c>
       <c r="H773" t="n">
         <v>19252</v>
@@ -22844,7 +22844,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12107706069946</v>
+        <v>2.12107729911804</v>
       </c>
       <c r="H775" t="n">
         <v>1852</v>
@@ -22902,7 +22902,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>2.01874446868896</v>
+        <v>2.01874470710754</v>
       </c>
       <c r="H777" t="n">
         <v>30407</v>
@@ -22931,7 +22931,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G778" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H778" t="n">
         <v>10623</v>
@@ -22989,7 +22989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>2.04665327072144</v>
+        <v>2.04665350914001</v>
       </c>
       <c r="H780" t="n">
         <v>3975</v>
@@ -23047,7 +23047,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H782" t="n">
         <v>7820</v>
@@ -23076,7 +23076,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G783" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292662620544</v>
       </c>
       <c r="H783" t="n">
         <v>12163</v>
@@ -23105,7 +23105,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.99083566665649</v>
+        <v>1.99083578586578</v>
       </c>
       <c r="H784" t="n">
         <v>1181</v>
@@ -23163,7 +23163,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H786" t="n">
         <v>22188</v>
@@ -23221,7 +23221,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.05595636367798</v>
+        <v>2.05595660209656</v>
       </c>
       <c r="H788" t="n">
         <v>13900</v>
@@ -23250,7 +23250,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G789" t="n">
-        <v>2.02804732322693</v>
+        <v>2.02804756164551</v>
       </c>
       <c r="H789" t="n">
         <v>2761</v>
@@ -23308,7 +23308,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00944185256958</v>
+        <v>2.009441614151</v>
       </c>
       <c r="H791" t="n">
         <v>2800</v>
@@ -23337,7 +23337,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>2.04665327072144</v>
+        <v>2.04665350914001</v>
       </c>
       <c r="H792" t="n">
         <v>7172</v>
@@ -23366,7 +23366,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H793" t="n">
         <v>8905</v>
@@ -23395,7 +23395,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H794" t="n">
         <v>13577</v>
@@ -23424,7 +23424,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H795" t="n">
         <v>8911</v>
@@ -23453,7 +23453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H796" t="n">
         <v>3170</v>
@@ -23482,7 +23482,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362377166748</v>
       </c>
       <c r="H797" t="n">
         <v>15172</v>
@@ -23511,7 +23511,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G798" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H798" t="n">
         <v>16878</v>
@@ -23540,7 +23540,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H799" t="n">
         <v>9805</v>
@@ -23569,7 +23569,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G800" t="n">
-        <v>1.90710866451263</v>
+        <v>1.90710878372192</v>
       </c>
       <c r="H800" t="n">
         <v>3251</v>
@@ -23598,7 +23598,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H801" t="n">
         <v>1502</v>
@@ -23714,7 +23714,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G805" t="n">
-        <v>1.77686727046967</v>
+        <v>1.77686715126038</v>
       </c>
       <c r="H805" t="n">
         <v>1</v>
@@ -23801,7 +23801,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G808" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H808" t="n">
         <v>8701</v>
@@ -23917,7 +23917,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H812" t="n">
         <v>17120</v>
@@ -23946,7 +23946,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G813" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H813" t="n">
         <v>3750</v>
@@ -24091,7 +24091,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H818" t="n">
         <v>26987</v>
@@ -24120,7 +24120,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011076927185</v>
+        <v>1.60011088848114</v>
       </c>
       <c r="H819" t="n">
         <v>13128</v>
@@ -24149,7 +24149,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G820" t="n">
-        <v>1.60941386222839</v>
+        <v>1.6094137430191</v>
       </c>
       <c r="H820" t="n">
         <v>7001</v>
@@ -24178,7 +24178,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G821" t="n">
-        <v>1.63267111778259</v>
+        <v>1.63267123699188</v>
       </c>
       <c r="H821" t="n">
         <v>16193</v>
@@ -24265,7 +24265,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G824" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H824" t="n">
         <v>17867</v>
@@ -24410,7 +24410,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H829" t="n">
         <v>19930</v>
@@ -24439,7 +24439,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.83268523216248</v>
+        <v>1.83268511295319</v>
       </c>
       <c r="H830" t="n">
         <v>53960</v>
@@ -24613,7 +24613,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G836" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571473121643</v>
       </c>
       <c r="H836" t="n">
         <v>55529</v>
@@ -24642,7 +24642,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H837" t="n">
         <v>17650</v>
@@ -24671,7 +24671,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G838" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H838" t="n">
         <v>5154</v>
@@ -24729,7 +24729,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H840" t="n">
         <v>6246</v>
@@ -24758,7 +24758,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H841" t="n">
         <v>5347</v>
@@ -24787,7 +24787,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H842" t="n">
         <v>3510</v>
@@ -24816,7 +24816,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G843" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H843" t="n">
         <v>3897</v>
@@ -24845,7 +24845,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G844" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H844" t="n">
         <v>3634</v>
@@ -25077,7 +25077,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G852" t="n">
-        <v>1.8094277381897</v>
+        <v>1.80942761898041</v>
       </c>
       <c r="H852" t="n">
         <v>6250</v>
@@ -25135,7 +25135,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.9350174665451</v>
+        <v>1.93501770496368</v>
       </c>
       <c r="H854" t="n">
         <v>16193</v>
@@ -25164,7 +25164,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G855" t="n">
-        <v>1.88850271701813</v>
+        <v>1.88850283622742</v>
       </c>
       <c r="H855" t="n">
         <v>15602</v>
@@ -25193,7 +25193,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G856" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H856" t="n">
         <v>7440</v>
@@ -25222,7 +25222,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G857" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H857" t="n">
         <v>12741</v>
@@ -25280,7 +25280,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432055950165</v>
+        <v>1.94432067871094</v>
       </c>
       <c r="H859" t="n">
         <v>23244</v>
@@ -25309,7 +25309,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G860" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292662620544</v>
       </c>
       <c r="H860" t="n">
         <v>19342</v>
@@ -25338,7 +25338,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G861" t="n">
-        <v>2.02804732322693</v>
+        <v>2.02804756164551</v>
       </c>
       <c r="H861" t="n">
         <v>34243</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.18991017341614</v>
+        <v>2.18991041183472</v>
       </c>
       <c r="H864" t="n">
         <v>29824</v>
@@ -25454,7 +25454,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>2.1803891658783</v>
+        <v>2.18038892745972</v>
       </c>
       <c r="H865" t="n">
         <v>18169</v>
@@ -25541,7 +25541,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G868" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H868" t="n">
         <v>12463</v>
@@ -25599,7 +25599,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H870" t="n">
         <v>14204</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H871" t="n">
         <v>10741</v>
@@ -25686,7 +25686,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H873" t="n">
         <v>1780</v>
@@ -25715,7 +25715,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H874" t="n">
         <v>11963</v>
@@ -25860,7 +25860,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H879" t="n">
         <v>9646</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H881" t="n">
         <v>4363</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H882" t="n">
         <v>3757</v>
@@ -26005,7 +26005,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H884" t="n">
         <v>3933</v>
@@ -26092,7 +26092,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H887" t="n">
         <v>1502</v>
@@ -26121,7 +26121,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H888" t="n">
         <v>2991</v>
@@ -26150,7 +26150,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H889" t="n">
         <v>500</v>
@@ -26179,7 +26179,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H891" t="n">
         <v>1750</v>
@@ -26237,7 +26237,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H892" t="n">
         <v>3562</v>
@@ -26295,7 +26295,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H894" t="n">
         <v>2771</v>
@@ -27542,7 +27542,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H937" t="n">
         <v>12954</v>
@@ -27716,7 +27716,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G943" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H943" t="n">
         <v>13769</v>
@@ -27745,7 +27745,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.61862945556641</v>
+        <v>1.6186295747757</v>
       </c>
       <c r="H944" t="n">
         <v>22282</v>
@@ -27774,7 +27774,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G945" t="n">
-        <v>1.54245853424072</v>
+        <v>1.54245865345001</v>
       </c>
       <c r="H945" t="n">
         <v>13946</v>
@@ -27890,7 +27890,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.35679233074188</v>
+        <v>1.35679221153259</v>
       </c>
       <c r="H949" t="n">
         <v>12733</v>
@@ -27948,7 +27948,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G951" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H951" t="n">
         <v>18171</v>
@@ -28006,7 +28006,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G953" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H953" t="n">
         <v>17476</v>
@@ -28122,7 +28122,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>1.34727096557617</v>
+        <v>1.34727084636688</v>
       </c>
       <c r="H957" t="n">
         <v>10390</v>
@@ -28151,7 +28151,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H958" t="n">
         <v>120160</v>
@@ -28296,7 +28296,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G963" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H963" t="n">
         <v>70383</v>
@@ -28354,7 +28354,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H965" t="n">
         <v>11079</v>
@@ -28470,7 +28470,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G969" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H969" t="n">
         <v>5589</v>
@@ -28644,7 +28644,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G975" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H975" t="n">
         <v>16278</v>
@@ -28876,7 +28876,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G983" t="n">
-        <v>0.8474001288414</v>
+        <v>0.847400069236755</v>
       </c>
       <c r="H983" t="n">
         <v>11888</v>
@@ -28934,7 +28934,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G985" t="n">
-        <v>0.934996545314789</v>
+        <v>0.934996485710144</v>
       </c>
       <c r="H985" t="n">
         <v>22093</v>
@@ -28963,7 +28963,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G986" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H986" t="n">
         <v>24435</v>
@@ -29108,7 +29108,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H991" t="n">
         <v>4904</v>
@@ -29137,7 +29137,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H992" t="n">
         <v>18073</v>
@@ -29253,7 +29253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G996" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H996" t="n">
         <v>11904</v>
@@ -29282,7 +29282,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H997" t="n">
         <v>4540</v>
@@ -29427,7 +29427,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1002" t="n">
         <v>2974</v>
@@ -29485,7 +29485,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H1004" t="n">
         <v>11264</v>
@@ -29630,7 +29630,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1009" t="n">
         <v>18426</v>
@@ -29659,7 +29659,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1010" t="n">
         <v>2505</v>
@@ -29978,7 +29978,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1021" t="n">
         <v>5361</v>
@@ -30036,7 +30036,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1026" t="n">
         <v>3669</v>
@@ -30152,7 +30152,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1027" t="n">
         <v>8946</v>
@@ -30268,7 +30268,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1031" t="n">
         <v>6700</v>
@@ -30326,7 +30326,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1033" t="n">
         <v>2860</v>
@@ -30384,7 +30384,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1035" t="n">
         <v>7202</v>
@@ -30413,7 +30413,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1036" t="n">
         <v>3000</v>
@@ -30442,7 +30442,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1037" t="n">
         <v>3042</v>
@@ -30558,7 +30558,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1041" t="n">
         <v>702</v>
@@ -30616,7 +30616,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1043" t="n">
         <v>5703</v>
@@ -30674,7 +30674,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1045" t="n">
         <v>3810</v>
@@ -30703,7 +30703,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1046" t="n">
         <v>3045</v>
@@ -30732,7 +30732,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1047" t="n">
         <v>4337</v>
@@ -30993,7 +30993,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1056" t="n">
         <v>15939</v>
@@ -31138,7 +31138,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1061" t="n">
         <v>5653</v>
@@ -31225,7 +31225,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1064" t="n">
         <v>7815</v>
@@ -31254,7 +31254,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.01878452301025</v>
+        <v>1.01878440380096</v>
       </c>
       <c r="H1065" t="n">
         <v>2000</v>
@@ -31312,7 +31312,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1067" t="n">
         <v>2310</v>
@@ -31341,7 +31341,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1068" t="n">
         <v>8960</v>
@@ -31370,7 +31370,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1069" t="n">
         <v>9201</v>
@@ -31428,7 +31428,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.885485470294952</v>
+        <v>0.885485529899597</v>
       </c>
       <c r="H1071" t="n">
         <v>7123</v>
@@ -31834,7 +31834,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1085" t="n">
         <v>14616</v>
@@ -31863,7 +31863,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1086" t="n">
         <v>7925</v>
@@ -31979,7 +31979,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1090" t="n">
         <v>1503</v>
@@ -32008,7 +32008,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.990220308303833</v>
+        <v>0.990220367908478</v>
       </c>
       <c r="H1091" t="n">
         <v>4143</v>
@@ -32037,7 +32037,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1092" t="n">
         <v>4779</v>
@@ -32095,7 +32095,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1094" t="n">
         <v>8025</v>
@@ -32182,7 +32182,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.940709292888641</v>
+        <v>0.940709352493286</v>
       </c>
       <c r="H1097" t="n">
         <v>7780</v>
@@ -32327,7 +32327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1102" t="n">
         <v>114066</v>
@@ -32356,7 +32356,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1103" t="n">
         <v>155001</v>
@@ -32414,7 +32414,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1105" t="n">
         <v>9642</v>
@@ -32443,7 +32443,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14732277393341</v>
+        <v>1.14732265472412</v>
       </c>
       <c r="H1106" t="n">
         <v>29380</v>
@@ -32501,7 +32501,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1108" t="n">
         <v>51439</v>
@@ -32559,7 +32559,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1110" t="n">
         <v>7650</v>
@@ -32588,7 +32588,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1111" t="n">
         <v>5770</v>
@@ -32646,7 +32646,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1113" t="n">
         <v>10113</v>
@@ -32704,7 +32704,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1115" t="n">
         <v>12644</v>
@@ -32733,7 +32733,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1116" t="n">
         <v>8938</v>
@@ -32849,7 +32849,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1120" t="n">
         <v>9373</v>
@@ -32878,7 +32878,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1121" t="n">
         <v>12172</v>
@@ -33023,7 +33023,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1126" t="n">
         <v>6943</v>
@@ -33052,7 +33052,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.2092113494873</v>
+        <v>1.20921146869659</v>
       </c>
       <c r="H1127" t="n">
         <v>7459</v>
@@ -33139,7 +33139,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1130" t="n">
         <v>7350</v>
@@ -33197,7 +33197,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1132" t="n">
         <v>14474</v>
@@ -42715,6 +42715,35 @@
         <v>710</v>
       </c>
       <c r="I1460" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1461" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>430</v>
+      </c>
+      <c r="I1461" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74249863624573</v>
+        <v>2.74249839782715</v>
       </c>
       <c r="H3" t="n">
         <v>611000</v>
@@ -514,7 +514,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66892075538635</v>
+        <v>2.66892051696777</v>
       </c>
       <c r="H5" t="n">
         <v>100000</v>
@@ -543,7 +543,7 @@
         <v>3.53049993515015</v>
       </c>
       <c r="G6" t="n">
-        <v>3.22692584991455</v>
+        <v>3.22692608833313</v>
       </c>
       <c r="H6" t="n">
         <v>588000</v>
@@ -601,7 +601,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.79315757751465</v>
+        <v>3.79315781593323</v>
       </c>
       <c r="H8" t="n">
         <v>726000</v>
@@ -630,7 +630,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79315757751465</v>
+        <v>3.79315781593323</v>
       </c>
       <c r="H9" t="n">
         <v>550000</v>
@@ -717,7 +717,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.60121464729309</v>
+        <v>3.60121488571167</v>
       </c>
       <c r="H12" t="n">
         <v>96000</v>
@@ -775,7 +775,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45497250556946</v>
+        <v>3.45497226715088</v>
       </c>
       <c r="H14" t="n">
         <v>116000</v>
@@ -804,7 +804,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153304100037</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H15" t="n">
         <v>85000</v>
@@ -862,7 +862,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50981330871582</v>
+        <v>3.50981307029724</v>
       </c>
       <c r="H17" t="n">
         <v>74000</v>
@@ -920,7 +920,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G19" t="n">
-        <v>3.47325277328491</v>
+        <v>3.47325253486633</v>
       </c>
       <c r="H19" t="n">
         <v>32000</v>
@@ -1036,7 +1036,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>3.40927195549011</v>
+        <v>3.40927171707153</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.32701063156128</v>
+        <v>3.32701086997986</v>
       </c>
       <c r="H24" t="n">
         <v>30000</v>
@@ -1123,7 +1123,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H26" t="n">
         <v>34000</v>
@@ -1152,7 +1152,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248798370361</v>
+        <v>3.16248822212219</v>
       </c>
       <c r="H27" t="n">
         <v>62000</v>
@@ -1210,7 +1210,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G29" t="n">
-        <v>3.0162456035614</v>
+        <v>3.01624584197998</v>
       </c>
       <c r="H29" t="n">
         <v>41000</v>
@@ -1297,7 +1297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076801300049</v>
+        <v>3.18076825141907</v>
       </c>
       <c r="H32" t="n">
         <v>40000</v>
@@ -1326,7 +1326,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420771598816</v>
+        <v>3.14420795440674</v>
       </c>
       <c r="H33" t="n">
         <v>53000</v>
@@ -1355,7 +1355,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.13506770133972</v>
+        <v>3.13506746292114</v>
       </c>
       <c r="H34" t="n">
         <v>13000</v>
@@ -1413,7 +1413,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818877220154</v>
+        <v>3.20818853378296</v>
       </c>
       <c r="H36" t="n">
         <v>50000</v>
@@ -1442,7 +1442,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443115234375</v>
+        <v>3.35443091392517</v>
       </c>
       <c r="H37" t="n">
         <v>264000</v>
@@ -1500,7 +1500,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>3.32701063156128</v>
+        <v>3.32701086997986</v>
       </c>
       <c r="H39" t="n">
         <v>52000</v>
@@ -1529,7 +1529,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H40" t="n">
         <v>48000</v>
@@ -1558,7 +1558,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H41" t="n">
         <v>172000</v>
@@ -1587,7 +1587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057809829712</v>
+        <v>3.82057762145996</v>
       </c>
       <c r="H42" t="n">
         <v>202000</v>
@@ -1616,7 +1616,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71089649200439</v>
+        <v>3.71089625358582</v>
       </c>
       <c r="H43" t="n">
         <v>172000</v>
@@ -1645,7 +1645,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.65605568885803</v>
+        <v>3.65605545043945</v>
       </c>
       <c r="H44" t="n">
         <v>80000</v>
@@ -1674,7 +1674,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>3.67433547973633</v>
+        <v>3.67433571815491</v>
       </c>
       <c r="H45" t="n">
         <v>29000</v>
@@ -1703,7 +1703,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72003698348999</v>
+        <v>3.72003674507141</v>
       </c>
       <c r="H46" t="n">
         <v>44000</v>
@@ -1732,7 +1732,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.7017560005188</v>
+        <v>3.70175623893738</v>
       </c>
       <c r="H47" t="n">
         <v>30000</v>
@@ -1761,7 +1761,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>3.67433547973633</v>
+        <v>3.67433571815491</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1819,7 +1819,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519570350647</v>
+        <v>3.66519594192505</v>
       </c>
       <c r="H50" t="n">
         <v>11000</v>
@@ -1935,7 +1935,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.4641125202179</v>
+        <v>3.46411275863647</v>
       </c>
       <c r="H54" t="n">
         <v>65000</v>
@@ -1964,7 +1964,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153304100037</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55551433563232</v>
+        <v>3.55551409721375</v>
       </c>
       <c r="H56" t="n">
         <v>14000</v>
@@ -2138,7 +2138,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293485641479</v>
+        <v>3.58293437957764</v>
       </c>
       <c r="H61" t="n">
         <v>16000</v>
@@ -2167,7 +2167,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.62863516807556</v>
+        <v>3.62863492965698</v>
       </c>
       <c r="H62" t="n">
         <v>25000</v>
@@ -2225,7 +2225,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G64" t="n">
-        <v>3.60121464729309</v>
+        <v>3.60121488571167</v>
       </c>
       <c r="H64" t="n">
         <v>13000</v>
@@ -2283,7 +2283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H67" t="n">
         <v>24000</v>
@@ -2341,7 +2341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011861801147</v>
+        <v>3.62011885643005</v>
       </c>
       <c r="H68" t="n">
         <v>10000</v>
@@ -2486,7 +2486,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.50986123085022</v>
+        <v>3.5098614692688</v>
       </c>
       <c r="H73" t="n">
         <v>17000</v>
@@ -2544,7 +2544,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.41797995567322</v>
+        <v>3.4179801940918</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2776,7 +2776,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>3.50986123085022</v>
+        <v>3.5098614692688</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.49148488044739</v>
+        <v>3.49148511886597</v>
       </c>
       <c r="H84" t="n">
         <v>13000</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.49148488044739</v>
+        <v>3.49148511886597</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3037,7 +3037,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G92" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H92" t="n">
         <v>18000</v>
@@ -3066,7 +3066,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>3.74875259399414</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H93" t="n">
         <v>51500</v>
@@ -3095,7 +3095,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251466751099</v>
       </c>
       <c r="H94" t="n">
         <v>132500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520729064941</v>
+        <v>4.01520776748657</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3211,7 +3211,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>5.09021711349487</v>
+        <v>5.09021759033203</v>
       </c>
       <c r="H98" t="n">
         <v>576000</v>
@@ -3269,7 +3269,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H100" t="n">
         <v>243500</v>
@@ -3298,7 +3298,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H101" t="n">
         <v>184500</v>
@@ -3559,7 +3559,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124761581421</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H110" t="n">
         <v>38500</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3704,7 +3704,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237565994263</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H115" t="n">
         <v>297500</v>
@@ -3733,7 +3733,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G116" t="n">
-        <v>7.47912931442261</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H116" t="n">
         <v>89000</v>
@@ -3791,7 +3791,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>7.49750518798828</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H118" t="n">
         <v>22500</v>
@@ -3820,7 +3820,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>7.38724660873413</v>
+        <v>7.38724708557129</v>
       </c>
       <c r="H119" t="n">
         <v>101000</v>
@@ -3849,7 +3849,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G120" t="n">
-        <v>7.47912931442261</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H120" t="n">
         <v>58500</v>
@@ -3994,7 +3994,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>6.79920768737793</v>
+        <v>6.79920816421509</v>
       </c>
       <c r="H125" t="n">
         <v>45500</v>
@@ -4023,7 +4023,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.8727126121521</v>
+        <v>6.87271213531494</v>
       </c>
       <c r="H126" t="n">
         <v>17500</v>
@@ -4052,7 +4052,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G127" t="n">
-        <v>6.8727126121521</v>
+        <v>6.87271213531494</v>
       </c>
       <c r="H127" t="n">
         <v>23000</v>
@@ -4081,7 +4081,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.8727126121521</v>
+        <v>6.87271213531494</v>
       </c>
       <c r="H128" t="n">
         <v>18500</v>
@@ -4139,7 +4139,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>6.79920768737793</v>
+        <v>6.79920816421509</v>
       </c>
       <c r="H130" t="n">
         <v>7500</v>
@@ -4168,7 +4168,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G131" t="n">
-        <v>6.79920768737793</v>
+        <v>6.79920816421509</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4313,7 +4313,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>7.38724660873413</v>
+        <v>7.38724708557129</v>
       </c>
       <c r="H136" t="n">
         <v>68000</v>
@@ -4371,7 +4371,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G138" t="n">
-        <v>7.46075248718262</v>
+        <v>7.46075201034546</v>
       </c>
       <c r="H138" t="n">
         <v>29000</v>
@@ -4400,7 +4400,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G139" t="n">
-        <v>7.47912931442261</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H139" t="n">
         <v>19500</v>
@@ -4429,7 +4429,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237565994263</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H140" t="n">
         <v>13000</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938550949097</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4516,7 +4516,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>8.15904903411865</v>
+        <v>8.15904808044434</v>
       </c>
       <c r="H143" t="n">
         <v>145500</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366188049316</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366188049316</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4748,7 +4748,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178203582764</v>
+        <v>7.90178298950195</v>
       </c>
       <c r="H151" t="n">
         <v>20500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4806,7 +4806,7 @@
         <v>8.5</v>
       </c>
       <c r="G153" t="n">
-        <v>7.80989980697632</v>
+        <v>7.80990076065063</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4835,7 +4835,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639631271362</v>
+        <v>7.73639583587646</v>
       </c>
       <c r="H154" t="n">
         <v>8500</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015790939331</v>
+        <v>7.92015695571899</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4893,7 +4893,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314758300781</v>
+        <v>7.77314853668213</v>
       </c>
       <c r="H156" t="n">
         <v>12500</v>
@@ -4922,7 +4922,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.69964408874512</v>
+        <v>7.69964361190796</v>
       </c>
       <c r="H157" t="n">
         <v>22500</v>
@@ -5009,7 +5009,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G160" t="n">
-        <v>7.6445140838623</v>
+        <v>7.64451456069946</v>
       </c>
       <c r="H160" t="n">
         <v>19000</v>
@@ -5067,7 +5067,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G162" t="n">
-        <v>7.68126726150513</v>
+        <v>7.68126678466797</v>
       </c>
       <c r="H162" t="n">
         <v>9500</v>
@@ -5096,7 +5096,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>7.49750518798828</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H163" t="n">
         <v>21000</v>
@@ -5125,7 +5125,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237565994263</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H164" t="n">
         <v>19000</v>
@@ -5154,7 +5154,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H165" t="n">
         <v>25000</v>
@@ -5183,7 +5183,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H166" t="n">
         <v>25500</v>
@@ -5241,7 +5241,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5270,7 +5270,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G169" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938550949097</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5444,7 +5444,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H175" t="n">
         <v>33500</v>
@@ -5502,7 +5502,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G177" t="n">
-        <v>7.68126726150513</v>
+        <v>7.68126678466797</v>
       </c>
       <c r="H177" t="n">
         <v>11500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5560,7 +5560,7 @@
         <v>8.5</v>
       </c>
       <c r="G179" t="n">
-        <v>7.80989980697632</v>
+        <v>7.80990076065063</v>
       </c>
       <c r="H179" t="n">
         <v>16500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5618,7 +5618,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314758300781</v>
+        <v>7.77314853668213</v>
       </c>
       <c r="H181" t="n">
         <v>18500</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5705,7 +5705,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263328552246</v>
+        <v>7.5526328086853</v>
       </c>
       <c r="H184" t="n">
         <v>12000</v>
@@ -5763,7 +5763,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425645828247</v>
+        <v>7.53425693511963</v>
       </c>
       <c r="H186" t="n">
         <v>13000</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938550949097</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5821,7 +5821,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G188" t="n">
-        <v>7.46075248718262</v>
+        <v>7.46075201034546</v>
       </c>
       <c r="H188" t="n">
         <v>20500</v>
@@ -5850,7 +5850,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>7.46075248718262</v>
+        <v>7.46075201034546</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5879,7 +5879,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263328552246</v>
+        <v>7.5526328086853</v>
       </c>
       <c r="H190" t="n">
         <v>36500</v>
@@ -5908,7 +5908,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H191" t="n">
         <v>28000</v>
@@ -5937,7 +5937,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G192" t="n">
-        <v>7.68126726150513</v>
+        <v>7.68126678466797</v>
       </c>
       <c r="H192" t="n">
         <v>32000</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.47912931442261</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H197" t="n">
         <v>15000</v>
@@ -6169,7 +6169,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38724660873413</v>
+        <v>7.38724708557129</v>
       </c>
       <c r="H200" t="n">
         <v>9500</v>
@@ -6227,7 +6227,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G202" t="n">
-        <v>7.40562391281128</v>
+        <v>7.40562343597412</v>
       </c>
       <c r="H202" t="n">
         <v>14000</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H203" t="n">
         <v>17500</v>
@@ -6343,7 +6343,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H206" t="n">
         <v>10000</v>
@@ -6401,7 +6401,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G208" t="n">
-        <v>7.2034854888916</v>
+        <v>7.20348501205444</v>
       </c>
       <c r="H208" t="n">
         <v>15000</v>
@@ -6430,7 +6430,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H209" t="n">
         <v>21500</v>
@@ -6459,7 +6459,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H210" t="n">
         <v>10500</v>
@@ -6575,7 +6575,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83595991134644</v>
+        <v>6.83596038818359</v>
       </c>
       <c r="H214" t="n">
         <v>29500</v>
@@ -6662,7 +6662,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H217" t="n">
         <v>63000</v>
@@ -6691,7 +6691,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H218" t="n">
         <v>22500</v>
@@ -6749,7 +6749,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>6.57869291305542</v>
+        <v>6.57869243621826</v>
       </c>
       <c r="H220" t="n">
         <v>12000</v>
@@ -6807,7 +6807,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H222" t="n">
         <v>18500</v>
@@ -6836,7 +6836,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H223" t="n">
         <v>9000</v>
@@ -6894,7 +6894,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>6.98296976089478</v>
+        <v>6.98297023773193</v>
       </c>
       <c r="H225" t="n">
         <v>27000</v>
@@ -6923,7 +6923,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H226" t="n">
         <v>34500</v>
@@ -6981,7 +6981,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H228" t="n">
         <v>22000</v>
@@ -7010,7 +7010,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G229" t="n">
-        <v>7.23104858398438</v>
+        <v>7.23104906082153</v>
       </c>
       <c r="H229" t="n">
         <v>51500</v>
@@ -7068,7 +7068,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G231" t="n">
-        <v>7.13916826248169</v>
+        <v>7.13916778564453</v>
       </c>
       <c r="H231" t="n">
         <v>11500</v>
@@ -7184,7 +7184,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G235" t="n">
-        <v>6.90027713775635</v>
+        <v>6.90027761459351</v>
       </c>
       <c r="H235" t="n">
         <v>29000</v>
@@ -7271,7 +7271,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>6.98296976089478</v>
+        <v>6.98297023773193</v>
       </c>
       <c r="H238" t="n">
         <v>13000</v>
@@ -7387,7 +7387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G242" t="n">
-        <v>6.79001903533936</v>
+        <v>6.79001951217651</v>
       </c>
       <c r="H242" t="n">
         <v>21500</v>
@@ -7445,7 +7445,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>6.90027713775635</v>
+        <v>6.90027761459351</v>
       </c>
       <c r="H244" t="n">
         <v>2500</v>
@@ -7474,7 +7474,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76245498657227</v>
+        <v>6.76245546340942</v>
       </c>
       <c r="H245" t="n">
         <v>4500</v>
@@ -7532,7 +7532,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G247" t="n">
-        <v>6.49599933624268</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H247" t="n">
         <v>19000</v>
@@ -7561,7 +7561,7 @@
         <v>7</v>
       </c>
       <c r="G248" t="n">
-        <v>6.43168306350708</v>
+        <v>6.43168258666992</v>
       </c>
       <c r="H248" t="n">
         <v>15000</v>
@@ -7619,7 +7619,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>6.51437616348267</v>
+        <v>6.51437568664551</v>
       </c>
       <c r="H250" t="n">
         <v>5000</v>
@@ -7648,7 +7648,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G251" t="n">
-        <v>6.57869291305542</v>
+        <v>6.57869243621826</v>
       </c>
       <c r="H251" t="n">
         <v>5000</v>
@@ -7677,7 +7677,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>6.51437616348267</v>
+        <v>6.51437568664551</v>
       </c>
       <c r="H252" t="n">
         <v>2000</v>
@@ -7793,7 +7793,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>6.15603876113892</v>
+        <v>6.15603923797607</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7938,7 +7938,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H261" t="n">
         <v>25000</v>
@@ -7967,7 +7967,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>6.79001903533936</v>
+        <v>6.79001951217651</v>
       </c>
       <c r="H262" t="n">
         <v>104000</v>
@@ -7996,7 +7996,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322643280029</v>
+        <v>7.09322690963745</v>
       </c>
       <c r="H263" t="n">
         <v>210500</v>
@@ -8112,7 +8112,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G267" t="n">
-        <v>6.49599933624268</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H267" t="n">
         <v>18000</v>
@@ -8199,7 +8199,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G270" t="n">
-        <v>6.49599933624268</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H270" t="n">
         <v>11500</v>
@@ -8257,7 +8257,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G272" t="n">
-        <v>6.49599933624268</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H272" t="n">
         <v>5500</v>
@@ -8286,7 +8286,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G273" t="n">
-        <v>6.40411806106567</v>
+        <v>6.40411853790283</v>
       </c>
       <c r="H273" t="n">
         <v>10000</v>
@@ -8315,7 +8315,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>6.44087171554565</v>
+        <v>6.4408712387085</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8605,7 +8605,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>5.72419786453247</v>
+        <v>5.72419738769531</v>
       </c>
       <c r="H284" t="n">
         <v>12000</v>
@@ -8663,7 +8663,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H286" t="n">
         <v>39500</v>
@@ -8721,7 +8721,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G288" t="n">
-        <v>5.64150476455688</v>
+        <v>5.64150428771973</v>
       </c>
       <c r="H288" t="n">
         <v>11000</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526779174805</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8866,7 +8866,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H293" t="n">
         <v>64000</v>
@@ -8895,7 +8895,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330671310425</v>
+        <v>6.41330623626709</v>
       </c>
       <c r="H294" t="n">
         <v>23500</v>
@@ -9098,7 +9098,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G301" t="n">
-        <v>6.45924711227417</v>
+        <v>6.45924806594849</v>
       </c>
       <c r="H301" t="n">
         <v>43000</v>
@@ -9127,7 +9127,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H302" t="n">
         <v>17500</v>
@@ -9185,7 +9185,7 @@
         <v>6.75</v>
       </c>
       <c r="G304" t="n">
-        <v>6.201979637146</v>
+        <v>6.20198011398315</v>
       </c>
       <c r="H304" t="n">
         <v>16000</v>
@@ -9272,7 +9272,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548456192017</v>
+        <v>6.27548503875732</v>
       </c>
       <c r="H307" t="n">
         <v>9000</v>
@@ -9301,7 +9301,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H308" t="n">
         <v>4500</v>
@@ -9388,7 +9388,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9475,7 +9475,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>6.16522741317749</v>
+        <v>6.16522693634033</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9533,7 +9533,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G316" t="n">
-        <v>6.13766288757324</v>
+        <v>6.13766241073608</v>
       </c>
       <c r="H316" t="n">
         <v>5500</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526779174805</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9794,7 +9794,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H325" t="n">
         <v>13000</v>
@@ -9823,7 +9823,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H326" t="n">
         <v>1450</v>
@@ -9852,7 +9852,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607913970947</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H327" t="n">
         <v>14080</v>
@@ -9997,7 +9997,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H332" t="n">
         <v>4456</v>
@@ -10026,7 +10026,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H333" t="n">
         <v>2022</v>
@@ -10084,7 +10084,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H335" t="n">
         <v>25940</v>
@@ -10142,7 +10142,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H337" t="n">
         <v>15456</v>
@@ -10287,7 +10287,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330671310425</v>
+        <v>6.41330623626709</v>
       </c>
       <c r="H342" t="n">
         <v>2560</v>
@@ -10316,7 +10316,7 @@
         <v>7</v>
       </c>
       <c r="G343" t="n">
-        <v>6.43168306350708</v>
+        <v>6.43168258666992</v>
       </c>
       <c r="H343" t="n">
         <v>3966</v>
@@ -10374,7 +10374,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H345" t="n">
         <v>2764</v>
@@ -10403,7 +10403,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G346" t="n">
-        <v>6.10091066360474</v>
+        <v>6.10091018676758</v>
       </c>
       <c r="H346" t="n">
         <v>5191</v>
@@ -10432,7 +10432,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H347" t="n">
         <v>510</v>
@@ -10461,7 +10461,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H348" t="n">
         <v>1520</v>
@@ -10548,7 +10548,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H351" t="n">
         <v>2077</v>
@@ -10606,7 +10606,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G353" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H353" t="n">
         <v>14359</v>
@@ -10635,7 +10635,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H354" t="n">
         <v>17836</v>
@@ -10664,7 +10664,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342546463013</v>
+        <v>5.39342498779297</v>
       </c>
       <c r="H355" t="n">
         <v>1874</v>
@@ -10693,7 +10693,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.55881118774414</v>
+        <v>5.5588116645813</v>
       </c>
       <c r="H356" t="n">
         <v>2401</v>
@@ -10722,7 +10722,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936586380005</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H357" t="n">
         <v>2284</v>
@@ -10751,7 +10751,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530626296997</v>
+        <v>5.48530673980713</v>
       </c>
       <c r="H358" t="n">
         <v>3234</v>
@@ -10780,7 +10780,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H359" t="n">
         <v>3097</v>
@@ -10809,7 +10809,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="n">
-        <v>5.51287126541138</v>
+        <v>5.51287078857422</v>
       </c>
       <c r="H360" t="n">
         <v>2285</v>
@@ -10925,7 +10925,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936586380005</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H364" t="n">
         <v>1105</v>
@@ -10954,7 +10954,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>5.55881118774414</v>
+        <v>5.5588116645813</v>
       </c>
       <c r="H365" t="n">
         <v>2304</v>
@@ -11041,7 +11041,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H368" t="n">
         <v>11426</v>
@@ -11186,7 +11186,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H375" t="n">
         <v>9545</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H376" t="n">
         <v>7667</v>
@@ -11360,7 +11360,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>5.68744564056396</v>
+        <v>5.68744516372681</v>
       </c>
       <c r="H379" t="n">
         <v>2986</v>
@@ -11447,7 +11447,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H382" t="n">
         <v>7014</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.5955638885498</v>
+        <v>5.59556436538696</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11563,7 +11563,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>5.58637571334839</v>
+        <v>5.58637619018555</v>
       </c>
       <c r="H386" t="n">
         <v>2950</v>
@@ -11592,7 +11592,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>5.70582103729248</v>
+        <v>5.70582151412964</v>
       </c>
       <c r="H387" t="n">
         <v>2675</v>
@@ -11650,7 +11650,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932643890381</v>
+        <v>5.77932691574097</v>
       </c>
       <c r="H389" t="n">
         <v>6221</v>
@@ -11708,7 +11708,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G391" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H391" t="n">
         <v>4247</v>
@@ -11911,7 +11911,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>6.16522741317749</v>
+        <v>6.16522693634033</v>
       </c>
       <c r="H398" t="n">
         <v>1789</v>
@@ -11969,7 +11969,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G400" t="n">
-        <v>6.00902891159058</v>
+        <v>6.00902938842773</v>
       </c>
       <c r="H400" t="n">
         <v>2189</v>
@@ -12027,7 +12027,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G402" t="n">
-        <v>5.90795946121216</v>
+        <v>5.90795993804932</v>
       </c>
       <c r="H402" t="n">
         <v>2037</v>
@@ -12114,7 +12114,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>5.9539008140564</v>
+        <v>5.95390033721924</v>
       </c>
       <c r="H405" t="n">
         <v>1670</v>
@@ -12172,7 +12172,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H407" t="n">
         <v>1611</v>
@@ -12259,7 +12259,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.8987717628479</v>
+        <v>5.89877223968506</v>
       </c>
       <c r="H410" t="n">
         <v>1853</v>
@@ -12317,7 +12317,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607913970947</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H412" t="n">
         <v>2753</v>
@@ -12433,7 +12433,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H416" t="n">
         <v>3751</v>
@@ -12462,7 +12462,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124761581421</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H417" t="n">
         <v>1848</v>
@@ -12520,7 +12520,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H419" t="n">
         <v>1068</v>
@@ -12549,7 +12549,7 @@
         <v>6</v>
       </c>
       <c r="G420" t="n">
-        <v>5.51287126541138</v>
+        <v>5.51287078857422</v>
       </c>
       <c r="H420" t="n">
         <v>2335</v>
@@ -12607,7 +12607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G422" t="n">
-        <v>5.64150476455688</v>
+        <v>5.64150428771973</v>
       </c>
       <c r="H422" t="n">
         <v>3644</v>
@@ -12636,7 +12636,7 @@
         <v>6</v>
       </c>
       <c r="G423" t="n">
-        <v>5.51287126541138</v>
+        <v>5.51287078857422</v>
       </c>
       <c r="H423" t="n">
         <v>3401</v>
@@ -12694,7 +12694,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>5.4118013381958</v>
+        <v>5.41180181503296</v>
       </c>
       <c r="H425" t="n">
         <v>3167</v>
@@ -12752,7 +12752,7 @@
         <v>5.75</v>
       </c>
       <c r="G427" t="n">
-        <v>5.28316783905029</v>
+        <v>5.28316831588745</v>
       </c>
       <c r="H427" t="n">
         <v>6854</v>
@@ -12781,7 +12781,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H428" t="n">
         <v>3146</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H429" t="n">
         <v>4856</v>
@@ -12897,7 +12897,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423776626587</v>
+        <v>5.38423728942871</v>
       </c>
       <c r="H432" t="n">
         <v>3519</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910871505737</v>
       </c>
       <c r="H434" t="n">
         <v>3264</v>
@@ -12984,7 +12984,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346536636353</v>
+        <v>5.05346488952637</v>
       </c>
       <c r="H435" t="n">
         <v>15369</v>
@@ -13216,7 +13216,7 @@
         <v>4.99499988555908</v>
       </c>
       <c r="G443" t="n">
-        <v>4.58946466445923</v>
+        <v>4.58946514129639</v>
       </c>
       <c r="H443" t="n">
         <v>3808</v>
@@ -13332,7 +13332,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>4.29544544219971</v>
+        <v>4.29544591903687</v>
       </c>
       <c r="H447" t="n">
         <v>15587</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13448,7 +13448,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>4.6399998664856</v>
+        <v>4.63999938964844</v>
       </c>
       <c r="H451" t="n">
         <v>15337</v>
@@ -13477,7 +13477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948461532593</v>
+        <v>4.41948509216309</v>
       </c>
       <c r="H452" t="n">
         <v>45286</v>
@@ -13535,7 +13535,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.4516429901123</v>
+        <v>4.45164346694946</v>
       </c>
       <c r="H454" t="n">
         <v>13974</v>
@@ -13564,7 +13564,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>4.38273239135742</v>
+        <v>4.38273286819458</v>
       </c>
       <c r="H455" t="n">
         <v>13871</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13709,7 +13709,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.45623731613159</v>
+        <v>4.45623683929443</v>
       </c>
       <c r="H460" t="n">
         <v>2411</v>
@@ -13854,7 +13854,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>4.49758434295654</v>
+        <v>4.49758338928223</v>
       </c>
       <c r="H465" t="n">
         <v>9324</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -13941,7 +13941,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G468" t="n">
-        <v>4.42867374420166</v>
+        <v>4.4286732673645</v>
       </c>
       <c r="H468" t="n">
         <v>600</v>
@@ -13970,7 +13970,7 @@
         <v>4.875</v>
       </c>
       <c r="G469" t="n">
-        <v>4.47920799255371</v>
+        <v>4.47920751571655</v>
       </c>
       <c r="H469" t="n">
         <v>1653</v>
@@ -13999,7 +13999,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>4.49758434295654</v>
+        <v>4.49758338928223</v>
       </c>
       <c r="H470" t="n">
         <v>305</v>
@@ -14057,7 +14057,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H472" t="n">
         <v>2289</v>
@@ -14086,7 +14086,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>4.38732671737671</v>
+        <v>4.38732624053955</v>
       </c>
       <c r="H473" t="n">
         <v>3916</v>
@@ -14115,7 +14115,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435604095459</v>
+        <v>4.36435651779175</v>
       </c>
       <c r="H474" t="n">
         <v>5067</v>
@@ -14144,7 +14144,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H475" t="n">
         <v>1381</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14289,7 +14289,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H480" t="n">
         <v>8400</v>
@@ -14318,7 +14318,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22194051742554</v>
+        <v>4.22194004058838</v>
       </c>
       <c r="H481" t="n">
         <v>10620</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332625389099</v>
+        <v>3.92332673072815</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14405,7 +14405,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G484" t="n">
-        <v>3.91413831710815</v>
+        <v>3.91413879394531</v>
       </c>
       <c r="H484" t="n">
         <v>16325</v>
@@ -14434,7 +14434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251466751099</v>
       </c>
       <c r="H485" t="n">
         <v>4207</v>
@@ -14492,7 +14492,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.9738609790802</v>
+        <v>3.97386050224304</v>
       </c>
       <c r="H487" t="n">
         <v>7176</v>
@@ -14521,7 +14521,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G488" t="n">
-        <v>3.84063363075256</v>
+        <v>3.84063339233398</v>
       </c>
       <c r="H488" t="n">
         <v>15203</v>
@@ -14550,7 +14550,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G489" t="n">
-        <v>3.84063363075256</v>
+        <v>3.84063339233398</v>
       </c>
       <c r="H489" t="n">
         <v>5714</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469275474548</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14608,7 +14608,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G491" t="n">
-        <v>3.82225704193115</v>
+        <v>3.82225728034973</v>
       </c>
       <c r="H491" t="n">
         <v>2924</v>
@@ -14666,7 +14666,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>3.84522724151611</v>
+        <v>3.84522771835327</v>
       </c>
       <c r="H493" t="n">
         <v>1926</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144569396973</v>
+        <v>3.83144521713257</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14724,7 +14724,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.85900974273682</v>
+        <v>3.8590099811554</v>
       </c>
       <c r="H495" t="n">
         <v>5373</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469275474548</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251466751099</v>
       </c>
       <c r="H497" t="n">
         <v>8274</v>
@@ -14811,7 +14811,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.95089101791382</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H498" t="n">
         <v>7416</v>
@@ -14840,7 +14840,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.95089101791382</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H499" t="n">
         <v>12304</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520729064941</v>
+        <v>4.01520776748657</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14956,7 +14956,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061344146729</v>
+        <v>4.01061296463013</v>
       </c>
       <c r="H503" t="n">
         <v>31005</v>
@@ -14985,7 +14985,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>4.35057401657104</v>
+        <v>4.35057353973389</v>
       </c>
       <c r="H504" t="n">
         <v>35126</v>
@@ -15014,7 +15014,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H505" t="n">
         <v>17677</v>
@@ -15072,7 +15072,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>4.31841516494751</v>
+        <v>4.31841564178467</v>
       </c>
       <c r="H507" t="n">
         <v>9121</v>
@@ -15246,7 +15246,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463314056396</v>
+        <v>4.30463361740112</v>
       </c>
       <c r="H513" t="n">
         <v>1902</v>
@@ -15333,7 +15333,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>4.34138584136963</v>
+        <v>4.34138631820679</v>
       </c>
       <c r="H516" t="n">
         <v>12696</v>
@@ -15391,7 +15391,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31841516494751</v>
+        <v>4.31841564178467</v>
       </c>
       <c r="H518" t="n">
         <v>5744</v>
@@ -15565,7 +15565,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H524" t="n">
         <v>11142</v>
@@ -15623,7 +15623,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>4.75025749206543</v>
+        <v>4.75025701522827</v>
       </c>
       <c r="H526" t="n">
         <v>7054</v>
@@ -15652,7 +15652,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>4.81457328796387</v>
+        <v>4.81457424163818</v>
       </c>
       <c r="H527" t="n">
         <v>9827</v>
@@ -15681,7 +15681,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H528" t="n">
         <v>7274</v>
@@ -15739,7 +15739,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85132646560669</v>
+        <v>4.85132694244385</v>
       </c>
       <c r="H530" t="n">
         <v>3028</v>
@@ -15768,7 +15768,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H531" t="n">
         <v>4381</v>
@@ -15884,7 +15884,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>5.09021711349487</v>
+        <v>5.09021759033203</v>
       </c>
       <c r="H535" t="n">
         <v>24385</v>
@@ -15913,7 +15913,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G536" t="n">
-        <v>5.11778211593628</v>
+        <v>5.11778163909912</v>
       </c>
       <c r="H536" t="n">
         <v>8803</v>
@@ -15942,7 +15942,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>5.01671266555786</v>
+        <v>5.0167121887207</v>
       </c>
       <c r="H537" t="n">
         <v>6975</v>
@@ -16000,7 +16000,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>4.87889051437378</v>
+        <v>4.87889099121094</v>
       </c>
       <c r="H539" t="n">
         <v>6892</v>
@@ -16029,7 +16029,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G540" t="n">
-        <v>4.85132646560669</v>
+        <v>4.85132694244385</v>
       </c>
       <c r="H540" t="n">
         <v>5649</v>
@@ -16116,7 +16116,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619693756104</v>
+        <v>4.79619741439819</v>
       </c>
       <c r="H543" t="n">
         <v>1688</v>
@@ -16145,7 +16145,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G544" t="n">
-        <v>4.69512844085693</v>
+        <v>4.69512891769409</v>
       </c>
       <c r="H544" t="n">
         <v>7711</v>
@@ -16377,7 +16377,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G552" t="n">
-        <v>4.31382179260254</v>
+        <v>4.31382131576538</v>
       </c>
       <c r="H552" t="n">
         <v>11658</v>
@@ -16406,7 +16406,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H553" t="n">
         <v>1650</v>
@@ -16464,7 +16464,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>4.097900390625</v>
+        <v>4.09790086746216</v>
       </c>
       <c r="H555" t="n">
         <v>11397</v>
@@ -16493,7 +16493,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.15302991867065</v>
+        <v>4.1530294418335</v>
       </c>
       <c r="H556" t="n">
         <v>3648</v>
@@ -16522,7 +16522,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546539306641</v>
+        <v>4.12546491622925</v>
       </c>
       <c r="H557" t="n">
         <v>7122</v>
@@ -16638,7 +16638,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631664276123</v>
+        <v>3.77631640434265</v>
       </c>
       <c r="H561" t="n">
         <v>14097</v>
@@ -16667,7 +16667,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>3.74875259399414</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H562" t="n">
         <v>4463</v>
@@ -16725,7 +16725,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>3.69362330436707</v>
+        <v>3.69362354278564</v>
       </c>
       <c r="H564" t="n">
         <v>10513</v>
@@ -16899,7 +16899,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H570" t="n">
         <v>38613</v>
@@ -16928,7 +16928,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G571" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H571" t="n">
         <v>7214</v>
@@ -16957,7 +16957,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H572" t="n">
         <v>40710</v>
@@ -17044,7 +17044,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G575" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H575" t="n">
         <v>2675</v>
@@ -17102,7 +17102,7 @@
         <v>3.5</v>
       </c>
       <c r="G577" t="n">
-        <v>3.21584153175354</v>
+        <v>3.21584129333496</v>
       </c>
       <c r="H577" t="n">
         <v>7340</v>
@@ -17131,7 +17131,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G578" t="n">
-        <v>3.06883144378662</v>
+        <v>3.06883120536804</v>
       </c>
       <c r="H578" t="n">
         <v>17701</v>
@@ -17160,7 +17160,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09639549255371</v>
+        <v>3.09639573097229</v>
       </c>
       <c r="H579" t="n">
         <v>10888</v>
@@ -17247,7 +17247,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>3.07801938056946</v>
+        <v>3.07801961898804</v>
       </c>
       <c r="H582" t="n">
         <v>2310</v>
@@ -17334,7 +17334,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.54661321640015</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H585" t="n">
         <v>5627</v>
@@ -17363,7 +17363,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.54661321640015</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H586" t="n">
         <v>4755</v>
@@ -17450,7 +17450,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G589" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H589" t="n">
         <v>11400</v>
@@ -17508,7 +17508,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712822914124</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H591" t="n">
         <v>12175</v>
@@ -17537,7 +17537,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712822914124</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H592" t="n">
         <v>9692</v>
@@ -17566,7 +17566,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G593" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H593" t="n">
         <v>11590</v>
@@ -17595,7 +17595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904940605164</v>
+        <v>3.51904916763306</v>
       </c>
       <c r="H594" t="n">
         <v>20677</v>
@@ -17653,7 +17653,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.54661321640015</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H596" t="n">
         <v>1150</v>
@@ -17711,7 +17711,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H598" t="n">
         <v>3630</v>
@@ -17740,7 +17740,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G599" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H599" t="n">
         <v>8376</v>
@@ -17885,7 +17885,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H604" t="n">
         <v>8247</v>
@@ -17943,7 +17943,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015828132629</v>
+        <v>3.28015804290771</v>
       </c>
       <c r="H606" t="n">
         <v>4093</v>
@@ -18088,7 +18088,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990089416504</v>
+        <v>3.16990113258362</v>
       </c>
       <c r="H611" t="n">
         <v>4629</v>
@@ -18117,7 +18117,7 @@
         <v>3.5</v>
       </c>
       <c r="G612" t="n">
-        <v>3.21584153175354</v>
+        <v>3.21584129333496</v>
       </c>
       <c r="H612" t="n">
         <v>1010</v>
@@ -18146,7 +18146,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233660697937</v>
+        <v>3.14233636856079</v>
       </c>
       <c r="H613" t="n">
         <v>1790</v>
@@ -18262,7 +18262,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.07801938056946</v>
+        <v>3.07801961898804</v>
       </c>
       <c r="H617" t="n">
         <v>10279</v>
@@ -18320,7 +18320,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G619" t="n">
-        <v>3.00451445579529</v>
+        <v>3.00451469421387</v>
       </c>
       <c r="H619" t="n">
         <v>10299</v>
@@ -18552,7 +18552,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G627" t="n">
-        <v>2.9310097694397</v>
+        <v>2.93101000785828</v>
       </c>
       <c r="H627" t="n">
         <v>10185</v>
@@ -18581,7 +18581,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>2.9769504070282</v>
+        <v>2.97695016860962</v>
       </c>
       <c r="H628" t="n">
         <v>1810</v>
@@ -18813,7 +18813,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G636" t="n">
-        <v>2.8746178150177</v>
+        <v>2.87461757659912</v>
       </c>
       <c r="H636" t="n">
         <v>10336</v>
@@ -18900,7 +18900,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G639" t="n">
-        <v>2.8746178150177</v>
+        <v>2.87461757659912</v>
       </c>
       <c r="H639" t="n">
         <v>14548</v>
@@ -18958,7 +18958,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G641" t="n">
-        <v>2.64204359054565</v>
+        <v>2.64204335212708</v>
       </c>
       <c r="H641" t="n">
         <v>86139</v>
@@ -18987,7 +18987,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110505104065</v>
+        <v>2.52110481262207</v>
       </c>
       <c r="H642" t="n">
         <v>95598</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761956214905</v>
+        <v>2.56761932373047</v>
       </c>
       <c r="H646" t="n">
         <v>8131</v>
@@ -19161,7 +19161,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G648" t="n">
-        <v>2.42807507514954</v>
+        <v>2.42807483673096</v>
       </c>
       <c r="H648" t="n">
         <v>23503</v>
@@ -19335,7 +19335,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H654" t="n">
         <v>19145</v>
@@ -19364,7 +19364,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H655" t="n">
         <v>11634</v>
@@ -19393,7 +19393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H656" t="n">
         <v>10081</v>
@@ -19509,7 +19509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H660" t="n">
         <v>4896</v>
@@ -19770,7 +19770,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180195808411</v>
+        <v>2.51180171966553</v>
       </c>
       <c r="H669" t="n">
         <v>22344</v>
@@ -19915,7 +19915,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H674" t="n">
         <v>1569</v>
@@ -20118,7 +20118,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H681" t="n">
         <v>3858</v>
@@ -20205,7 +20205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.4931960105896</v>
+        <v>2.49319577217102</v>
       </c>
       <c r="H684" t="n">
         <v>12276</v>
@@ -20234,7 +20234,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35365152359009</v>
+        <v>2.35365128517151</v>
       </c>
       <c r="H685" t="n">
         <v>24371</v>
@@ -20495,7 +20495,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G694" t="n">
-        <v>1.74895834922791</v>
+        <v>1.74895823001862</v>
       </c>
       <c r="H694" t="n">
         <v>231606</v>
@@ -20524,7 +20524,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362377166748</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H695" t="n">
         <v>235716</v>
@@ -20611,7 +20611,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>1.58150482177734</v>
+        <v>1.58150494098663</v>
       </c>
       <c r="H698" t="n">
         <v>54891</v>
@@ -20698,7 +20698,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.4884752035141</v>
+        <v>1.48847508430481</v>
       </c>
       <c r="H701" t="n">
         <v>13536</v>
@@ -20814,7 +20814,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.44196033477783</v>
+        <v>1.44196021556854</v>
       </c>
       <c r="H705" t="n">
         <v>12919</v>
@@ -20959,7 +20959,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>1.69779193401337</v>
+        <v>1.69779205322266</v>
       </c>
       <c r="H710" t="n">
         <v>5655</v>
@@ -20988,7 +20988,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H711" t="n">
         <v>6528</v>
@@ -21017,7 +21017,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H712" t="n">
         <v>2874</v>
@@ -21075,7 +21075,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.58150482177734</v>
+        <v>1.58150494098663</v>
       </c>
       <c r="H714" t="n">
         <v>5490</v>
@@ -21133,7 +21133,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G716" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H716" t="n">
         <v>14629</v>
@@ -21249,7 +21249,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.63267123699188</v>
+        <v>1.63267111778259</v>
       </c>
       <c r="H720" t="n">
         <v>7920</v>
@@ -21307,7 +21307,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.55359590053558</v>
+        <v>1.55359578132629</v>
       </c>
       <c r="H722" t="n">
         <v>2574</v>
@@ -21336,7 +21336,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H723" t="n">
         <v>5633</v>
@@ -21423,7 +21423,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H726" t="n">
         <v>75327</v>
@@ -21510,7 +21510,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G729" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H729" t="n">
         <v>21650</v>
@@ -21568,7 +21568,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H731" t="n">
         <v>2155</v>
@@ -21626,7 +21626,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G733" t="n">
-        <v>2.42807507514954</v>
+        <v>2.42807483673096</v>
       </c>
       <c r="H733" t="n">
         <v>201386</v>
@@ -21742,7 +21742,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>2.18619799613953</v>
+        <v>2.18619775772095</v>
       </c>
       <c r="H737" t="n">
         <v>12209</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H738" t="n">
         <v>41345</v>
@@ -21800,7 +21800,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550085067749</v>
+        <v>2.19550061225891</v>
       </c>
       <c r="H739" t="n">
         <v>13585</v>
@@ -21887,7 +21887,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H742" t="n">
         <v>4041</v>
@@ -21916,7 +21916,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H743" t="n">
         <v>27715</v>
@@ -22003,7 +22003,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G746" t="n">
-        <v>2.01874470710754</v>
+        <v>2.01874446868896</v>
       </c>
       <c r="H746" t="n">
         <v>7492</v>
@@ -22148,7 +22148,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H751" t="n">
         <v>7609</v>
@@ -22235,7 +22235,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H754" t="n">
         <v>54449</v>
@@ -22264,7 +22264,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H755" t="n">
         <v>13384</v>
@@ -22293,7 +22293,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H756" t="n">
         <v>6173</v>
@@ -22322,7 +22322,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H757" t="n">
         <v>9025</v>
@@ -22351,7 +22351,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G758" t="n">
-        <v>2.22341012954712</v>
+        <v>2.22340989112854</v>
       </c>
       <c r="H758" t="n">
         <v>6613</v>
@@ -22583,7 +22583,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.26992464065552</v>
+        <v>2.26992440223694</v>
       </c>
       <c r="H766" t="n">
         <v>6724</v>
@@ -22757,7 +22757,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H772" t="n">
         <v>12685</v>
@@ -22786,7 +22786,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G773" t="n">
-        <v>2.12107729911804</v>
+        <v>2.12107706069946</v>
       </c>
       <c r="H773" t="n">
         <v>19252</v>
@@ -22844,7 +22844,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G775" t="n">
-        <v>2.12107729911804</v>
+        <v>2.12107706069946</v>
       </c>
       <c r="H775" t="n">
         <v>1852</v>
@@ -22902,7 +22902,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G777" t="n">
-        <v>2.01874470710754</v>
+        <v>2.01874446868896</v>
       </c>
       <c r="H777" t="n">
         <v>30407</v>
@@ -22960,7 +22960,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H779" t="n">
         <v>6646</v>
@@ -23076,7 +23076,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G783" t="n">
-        <v>1.96292662620544</v>
+        <v>1.96292638778687</v>
       </c>
       <c r="H783" t="n">
         <v>12163</v>
@@ -23105,7 +23105,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.99083578586578</v>
+        <v>1.9908355474472</v>
       </c>
       <c r="H784" t="n">
         <v>1181</v>
@@ -23134,7 +23134,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H785" t="n">
         <v>4151</v>
@@ -23163,7 +23163,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H786" t="n">
         <v>22188</v>
@@ -23221,7 +23221,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.05595660209656</v>
+        <v>2.05595636367798</v>
       </c>
       <c r="H788" t="n">
         <v>13900</v>
@@ -23279,7 +23279,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03735041618347</v>
+        <v>2.03735017776489</v>
       </c>
       <c r="H790" t="n">
         <v>6918</v>
@@ -23424,7 +23424,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362377166748</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H795" t="n">
         <v>8911</v>
@@ -23453,7 +23453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362377166748</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H796" t="n">
         <v>3170</v>
@@ -23482,7 +23482,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362377166748</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H797" t="n">
         <v>15172</v>
@@ -23511,7 +23511,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G798" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H798" t="n">
         <v>16878</v>
@@ -23598,7 +23598,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H801" t="n">
         <v>1502</v>
@@ -23656,7 +23656,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G803" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H803" t="n">
         <v>3999</v>
@@ -23714,7 +23714,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G805" t="n">
-        <v>1.77686715126038</v>
+        <v>1.77686727046967</v>
       </c>
       <c r="H805" t="n">
         <v>1</v>
@@ -23917,7 +23917,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H812" t="n">
         <v>17120</v>
@@ -24062,7 +24062,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G817" t="n">
-        <v>1.4884752035141</v>
+        <v>1.48847508430481</v>
       </c>
       <c r="H817" t="n">
         <v>14735</v>
@@ -24091,7 +24091,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H818" t="n">
         <v>26987</v>
@@ -24120,7 +24120,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011088848114</v>
+        <v>1.60011076927185</v>
       </c>
       <c r="H819" t="n">
         <v>13128</v>
@@ -24178,7 +24178,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G821" t="n">
-        <v>1.63267123699188</v>
+        <v>1.63267111778259</v>
       </c>
       <c r="H821" t="n">
         <v>16193</v>
@@ -24294,7 +24294,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H825" t="n">
         <v>2580</v>
@@ -24468,7 +24468,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G831" t="n">
-        <v>1.81873059272766</v>
+        <v>1.81873047351837</v>
       </c>
       <c r="H831" t="n">
         <v>14506</v>
@@ -24584,7 +24584,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G835" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H835" t="n">
         <v>50956</v>
@@ -24613,7 +24613,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G836" t="n">
-        <v>1.92571473121643</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H836" t="n">
         <v>55529</v>
@@ -24961,7 +24961,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G848" t="n">
-        <v>1.81873059272766</v>
+        <v>1.81873047351837</v>
       </c>
       <c r="H848" t="n">
         <v>1500</v>
@@ -25019,7 +25019,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G850" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H850" t="n">
         <v>10425</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H851" t="n">
         <v>616</v>
@@ -25077,7 +25077,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G852" t="n">
-        <v>1.80942761898041</v>
+        <v>1.8094277381897</v>
       </c>
       <c r="H852" t="n">
         <v>6250</v>
@@ -25135,7 +25135,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.93501770496368</v>
+        <v>1.93501758575439</v>
       </c>
       <c r="H854" t="n">
         <v>16193</v>
@@ -25280,7 +25280,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432067871094</v>
+        <v>1.94432055950165</v>
       </c>
       <c r="H859" t="n">
         <v>23244</v>
@@ -25309,7 +25309,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G860" t="n">
-        <v>1.96292662620544</v>
+        <v>1.96292638778687</v>
       </c>
       <c r="H860" t="n">
         <v>19342</v>
@@ -42744,6 +42744,35 @@
         <v>430</v>
       </c>
       <c r="I1461" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1462" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>0.639999985694885</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>3937</v>
+      </c>
+      <c r="I1462" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74249839782715</v>
+        <v>2.74249863624573</v>
       </c>
       <c r="H3" t="n">
         <v>611000</v>
@@ -485,7 +485,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64150023460388</v>
+        <v>2.6414999961853</v>
       </c>
       <c r="H4" t="n">
         <v>186000</v>
@@ -543,7 +543,7 @@
         <v>3.53049993515015</v>
       </c>
       <c r="G6" t="n">
-        <v>3.22692608833313</v>
+        <v>3.22692584991455</v>
       </c>
       <c r="H6" t="n">
         <v>588000</v>
@@ -572,7 +572,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G7" t="n">
-        <v>3.53357791900635</v>
+        <v>3.53357768058777</v>
       </c>
       <c r="H7" t="n">
         <v>623000</v>
@@ -601,7 +601,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G8" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H8" t="n">
         <v>726000</v>
@@ -630,7 +630,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G9" t="n">
-        <v>3.79315781593323</v>
+        <v>3.79315757751465</v>
       </c>
       <c r="H9" t="n">
         <v>550000</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H11" t="n">
         <v>296000</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583249092102</v>
+        <v>3.44583225250244</v>
       </c>
       <c r="H16" t="n">
         <v>29000</v>
@@ -949,7 +949,7 @@
         <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.42755198478699</v>
+        <v>3.42755222320557</v>
       </c>
       <c r="H20" t="n">
         <v>37000</v>
@@ -978,7 +978,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2630295753479</v>
+        <v>3.26302933692932</v>
       </c>
       <c r="H21" t="n">
         <v>78000</v>
@@ -1007,7 +1007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30873036384583</v>
+        <v>3.30873012542725</v>
       </c>
       <c r="H22" t="n">
         <v>17000</v>
@@ -1036,7 +1036,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>3.40927171707153</v>
+        <v>3.40927195549011</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1094,7 +1094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.37271118164062</v>
+        <v>3.3727114200592</v>
       </c>
       <c r="H25" t="n">
         <v>11000</v>
@@ -1239,7 +1239,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G30" t="n">
-        <v>3.1533477306366</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H30" t="n">
         <v>145000</v>
@@ -1268,7 +1268,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>3.1533477306366</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H31" t="n">
         <v>36000</v>
@@ -1326,7 +1326,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420795440674</v>
+        <v>3.14420771598816</v>
       </c>
       <c r="H33" t="n">
         <v>53000</v>
@@ -1384,7 +1384,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G35" t="n">
-        <v>3.08936715126038</v>
+        <v>3.0893669128418</v>
       </c>
       <c r="H35" t="n">
         <v>9000</v>
@@ -1413,7 +1413,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818853378296</v>
+        <v>3.20818877220154</v>
       </c>
       <c r="H36" t="n">
         <v>50000</v>
@@ -1587,7 +1587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057762145996</v>
+        <v>3.82057785987854</v>
       </c>
       <c r="H42" t="n">
         <v>202000</v>
@@ -1645,7 +1645,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.65605545043945</v>
+        <v>3.65605568885803</v>
       </c>
       <c r="H44" t="n">
         <v>80000</v>
@@ -1732,7 +1732,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175623893738</v>
+        <v>3.70175647735596</v>
       </c>
       <c r="H47" t="n">
         <v>30000</v>
@@ -1819,7 +1819,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519594192505</v>
+        <v>3.66519570350647</v>
       </c>
       <c r="H50" t="n">
         <v>11000</v>
@@ -1877,7 +1877,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H52" t="n">
         <v>35000</v>
@@ -1906,7 +1906,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H53" t="n">
         <v>35000</v>
@@ -1935,7 +1935,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G54" t="n">
-        <v>3.46411275863647</v>
+        <v>3.4641125202179</v>
       </c>
       <c r="H54" t="n">
         <v>65000</v>
@@ -2051,7 +2051,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H58" t="n">
         <v>49000</v>
@@ -2080,7 +2080,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949491500854</v>
+        <v>3.61949467658997</v>
       </c>
       <c r="H59" t="n">
         <v>20000</v>
@@ -2109,7 +2109,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G60" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H60" t="n">
         <v>23000</v>
@@ -2138,7 +2138,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293437957764</v>
+        <v>3.58293461799622</v>
       </c>
       <c r="H61" t="n">
         <v>16000</v>
@@ -2254,7 +2254,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.61035490036011</v>
+        <v>3.61035466194153</v>
       </c>
       <c r="H65" t="n">
         <v>9000</v>
@@ -2370,7 +2370,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2399,7 +2399,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H70" t="n">
         <v>14000</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H71" t="n">
         <v>9000</v>
@@ -2457,7 +2457,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H72" t="n">
         <v>23000</v>
@@ -2486,7 +2486,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.5098614692688</v>
+        <v>3.50986123085022</v>
       </c>
       <c r="H73" t="n">
         <v>17000</v>
@@ -2631,7 +2631,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H78" t="n">
         <v>10500</v>
@@ -2689,7 +2689,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>3.48229670524597</v>
+        <v>3.48229646682739</v>
       </c>
       <c r="H80" t="n">
         <v>11500</v>
@@ -2747,7 +2747,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.47310876846313</v>
+        <v>3.47310853004456</v>
       </c>
       <c r="H82" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>3.5098614692688</v>
+        <v>3.50986123085022</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2805,7 +2805,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G84" t="n">
-        <v>3.49148511886597</v>
+        <v>3.49148488044739</v>
       </c>
       <c r="H84" t="n">
         <v>13000</v>
@@ -2834,7 +2834,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G85" t="n">
-        <v>3.49148511886597</v>
+        <v>3.49148488044739</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.63849496841431</v>
+        <v>3.63849472999573</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G92" t="n">
-        <v>3.70281171798706</v>
+        <v>3.70281195640564</v>
       </c>
       <c r="H92" t="n">
         <v>18000</v>
@@ -3124,7 +3124,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G95" t="n">
-        <v>3.89576148986816</v>
+        <v>3.89576172828674</v>
       </c>
       <c r="H95" t="n">
         <v>105500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520824432373</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3182,7 +3182,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H97" t="n">
         <v>373000</v>
@@ -3211,7 +3211,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>5.09021759033203</v>
+        <v>5.09021711349487</v>
       </c>
       <c r="H98" t="n">
         <v>576000</v>
@@ -3298,7 +3298,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>5.4026141166687</v>
+        <v>5.40261363983154</v>
       </c>
       <c r="H101" t="n">
         <v>184500</v>
@@ -3443,7 +3443,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>5.36586141586304</v>
+        <v>5.36586093902588</v>
       </c>
       <c r="H106" t="n">
         <v>15000</v>
@@ -3501,7 +3501,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>5.36586141586304</v>
+        <v>5.36586093902588</v>
       </c>
       <c r="H108" t="n">
         <v>19000</v>
@@ -3530,7 +3530,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>5.49449443817139</v>
+        <v>5.49449491500854</v>
       </c>
       <c r="H109" t="n">
         <v>40500</v>
@@ -3559,7 +3559,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124761581421</v>
       </c>
       <c r="H110" t="n">
         <v>38500</v>
@@ -3588,7 +3588,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>6.96459341049194</v>
+        <v>6.96459293365479</v>
       </c>
       <c r="H111" t="n">
         <v>293500</v>
@@ -3646,7 +3646,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>6.94621753692627</v>
+        <v>6.94621706008911</v>
       </c>
       <c r="H113" t="n">
         <v>117500</v>
@@ -3704,7 +3704,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237661361694</v>
       </c>
       <c r="H115" t="n">
         <v>297500</v>
@@ -3820,7 +3820,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>7.38724708557129</v>
+        <v>7.38724756240845</v>
       </c>
       <c r="H119" t="n">
         <v>101000</v>
@@ -3878,7 +3878,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G121" t="n">
-        <v>7.36887073516846</v>
+        <v>7.36887121200562</v>
       </c>
       <c r="H121" t="n">
         <v>22000</v>
@@ -3936,7 +3936,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>6.94621753692627</v>
+        <v>6.94621706008911</v>
       </c>
       <c r="H123" t="n">
         <v>106000</v>
@@ -3994,7 +3994,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>6.79920816421509</v>
+        <v>6.79920768737793</v>
       </c>
       <c r="H125" t="n">
         <v>45500</v>
@@ -4139,7 +4139,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G130" t="n">
-        <v>6.79920816421509</v>
+        <v>6.79920768737793</v>
       </c>
       <c r="H130" t="n">
         <v>7500</v>
@@ -4168,7 +4168,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G131" t="n">
-        <v>6.79920816421509</v>
+        <v>6.79920768737793</v>
       </c>
       <c r="H131" t="n">
         <v>7000</v>
@@ -4226,7 +4226,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G133" t="n">
-        <v>7.27698993682861</v>
+        <v>7.27698945999146</v>
       </c>
       <c r="H133" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H135" t="n">
         <v>150000</v>
@@ -4313,7 +4313,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>7.38724708557129</v>
+        <v>7.38724756240845</v>
       </c>
       <c r="H136" t="n">
         <v>68000</v>
@@ -4429,7 +4429,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237661361694</v>
       </c>
       <c r="H140" t="n">
         <v>13000</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4516,7 +4516,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>8.15904808044434</v>
+        <v>8.15904903411865</v>
       </c>
       <c r="H143" t="n">
         <v>145500</v>
@@ -4545,7 +4545,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G144" t="n">
-        <v>8.06716728210449</v>
+        <v>8.06716823577881</v>
       </c>
       <c r="H144" t="n">
         <v>182000</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366188049316</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366188049316</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4661,7 +4661,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G148" t="n">
-        <v>8.06716728210449</v>
+        <v>8.06716823577881</v>
       </c>
       <c r="H148" t="n">
         <v>31000</v>
@@ -4690,7 +4690,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G149" t="n">
-        <v>8.14067268371582</v>
+        <v>8.14067363739014</v>
       </c>
       <c r="H149" t="n">
         <v>53500</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95691108703613</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4748,7 +4748,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178298950195</v>
+        <v>7.90178203582764</v>
       </c>
       <c r="H151" t="n">
         <v>20500</v>
@@ -4835,7 +4835,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639583587646</v>
+        <v>7.73639535903931</v>
       </c>
       <c r="H154" t="n">
         <v>8500</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015695571899</v>
+        <v>7.92015743255615</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4893,7 +4893,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314901351929</v>
       </c>
       <c r="H156" t="n">
         <v>12500</v>
@@ -4951,7 +4951,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G158" t="n">
-        <v>7.79152297973633</v>
+        <v>7.79152345657349</v>
       </c>
       <c r="H158" t="n">
         <v>15500</v>
@@ -4980,7 +4980,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G159" t="n">
-        <v>7.79152297973633</v>
+        <v>7.79152345657349</v>
       </c>
       <c r="H159" t="n">
         <v>5500</v>
@@ -5067,7 +5067,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G162" t="n">
-        <v>7.68126678466797</v>
+        <v>7.68126630783081</v>
       </c>
       <c r="H162" t="n">
         <v>9500</v>
@@ -5125,7 +5125,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237661361694</v>
       </c>
       <c r="H164" t="n">
         <v>19000</v>
@@ -5212,7 +5212,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>7.27698993682861</v>
+        <v>7.27698945999146</v>
       </c>
       <c r="H167" t="n">
         <v>11500</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95691108703613</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5357,7 +5357,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G172" t="n">
-        <v>8.14067268371582</v>
+        <v>8.14067363739014</v>
       </c>
       <c r="H172" t="n">
         <v>81500</v>
@@ -5386,7 +5386,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.36118698120117</v>
+        <v>8.36118793487549</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665393829346</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5444,7 +5444,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801996231079</v>
+        <v>7.71801948547363</v>
       </c>
       <c r="H175" t="n">
         <v>33500</v>
@@ -5473,7 +5473,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5502,7 +5502,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G177" t="n">
-        <v>7.68126678466797</v>
+        <v>7.68126630783081</v>
       </c>
       <c r="H177" t="n">
         <v>11500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665393829346</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665393829346</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5618,7 +5618,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314901351929</v>
       </c>
       <c r="H181" t="n">
         <v>18500</v>
@@ -5676,7 +5676,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H183" t="n">
         <v>33500</v>
@@ -5705,7 +5705,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.5526328086853</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H184" t="n">
         <v>12000</v>
@@ -5734,7 +5734,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588106155396</v>
+        <v>7.51588153839111</v>
       </c>
       <c r="H185" t="n">
         <v>12500</v>
@@ -5763,7 +5763,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425693511963</v>
+        <v>7.53425741195679</v>
       </c>
       <c r="H186" t="n">
         <v>13000</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5879,7 +5879,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.5526328086853</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H190" t="n">
         <v>36500</v>
@@ -5908,7 +5908,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801996231079</v>
+        <v>7.71801948547363</v>
       </c>
       <c r="H191" t="n">
         <v>28000</v>
@@ -5937,7 +5937,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G192" t="n">
-        <v>7.68126678466797</v>
+        <v>7.68126630783081</v>
       </c>
       <c r="H192" t="n">
         <v>32000</v>
@@ -6053,7 +6053,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6169,7 +6169,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38724708557129</v>
+        <v>7.38724756240845</v>
       </c>
       <c r="H200" t="n">
         <v>9500</v>
@@ -6227,7 +6227,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G202" t="n">
-        <v>7.40562343597412</v>
+        <v>7.40562391281128</v>
       </c>
       <c r="H202" t="n">
         <v>14000</v>
@@ -6372,7 +6372,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.07485055923462</v>
+        <v>7.07485103607178</v>
       </c>
       <c r="H207" t="n">
         <v>32500</v>
@@ -6633,7 +6633,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>6.81758403778076</v>
+        <v>6.8175835609436</v>
       </c>
       <c r="H216" t="n">
         <v>17500</v>
@@ -6662,7 +6662,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H217" t="n">
         <v>63000</v>
@@ -6720,7 +6720,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H219" t="n">
         <v>7500</v>
@@ -6807,7 +6807,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H222" t="n">
         <v>18500</v>
@@ -6894,7 +6894,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G225" t="n">
-        <v>6.98297023773193</v>
+        <v>6.98296976089478</v>
       </c>
       <c r="H225" t="n">
         <v>27000</v>
@@ -7097,7 +7097,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G232" t="n">
-        <v>7.04728698730469</v>
+        <v>7.04728746414185</v>
       </c>
       <c r="H232" t="n">
         <v>25500</v>
@@ -7184,7 +7184,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G235" t="n">
-        <v>6.90027761459351</v>
+        <v>6.90027713775635</v>
       </c>
       <c r="H235" t="n">
         <v>29000</v>
@@ -7271,7 +7271,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G238" t="n">
-        <v>6.98297023773193</v>
+        <v>6.98296976089478</v>
       </c>
       <c r="H238" t="n">
         <v>13000</v>
@@ -7358,7 +7358,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>6.94621753692627</v>
+        <v>6.94621706008911</v>
       </c>
       <c r="H241" t="n">
         <v>18500</v>
@@ -7445,7 +7445,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G244" t="n">
-        <v>6.90027761459351</v>
+        <v>6.90027713775635</v>
       </c>
       <c r="H244" t="n">
         <v>2500</v>
@@ -7474,7 +7474,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76245546340942</v>
+        <v>6.76245498657227</v>
       </c>
       <c r="H245" t="n">
         <v>4500</v>
@@ -7619,7 +7619,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G250" t="n">
-        <v>6.51437568664551</v>
+        <v>6.51437616348267</v>
       </c>
       <c r="H250" t="n">
         <v>5000</v>
@@ -7677,7 +7677,7 @@
         <v>7.09000015258789</v>
       </c>
       <c r="G252" t="n">
-        <v>6.51437568664551</v>
+        <v>6.51437616348267</v>
       </c>
       <c r="H252" t="n">
         <v>2000</v>
@@ -7764,7 +7764,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>6.3306131362915</v>
+        <v>6.33061361312866</v>
       </c>
       <c r="H255" t="n">
         <v>17000</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>6.23873281478882</v>
+        <v>6.2387318611145</v>
       </c>
       <c r="H257" t="n">
         <v>3500</v>
@@ -7851,7 +7851,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G258" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H258" t="n">
         <v>11000</v>
@@ -7880,7 +7880,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H259" t="n">
         <v>2000</v>
@@ -7909,7 +7909,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G260" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H260" t="n">
         <v>5000</v>
@@ -8025,7 +8025,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.07485055923462</v>
+        <v>7.07485103607178</v>
       </c>
       <c r="H264" t="n">
         <v>31000</v>
@@ -8083,7 +8083,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>6.65219736099243</v>
+        <v>6.65219783782959</v>
       </c>
       <c r="H266" t="n">
         <v>20500</v>
@@ -8141,7 +8141,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H268" t="n">
         <v>11000</v>
@@ -8344,7 +8344,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G275" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8373,7 +8373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G276" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H276" t="n">
         <v>8000</v>
@@ -8489,7 +8489,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H280" t="n">
         <v>26500</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8837,7 +8837,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G292" t="n">
-        <v>5.96308898925781</v>
+        <v>5.96308851242065</v>
       </c>
       <c r="H292" t="n">
         <v>3500</v>
@@ -8924,7 +8924,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H295" t="n">
         <v>12500</v>
@@ -8982,7 +8982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H297" t="n">
         <v>14500</v>
@@ -9011,7 +9011,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H298" t="n">
         <v>9000</v>
@@ -9040,7 +9040,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>6.569504737854</v>
+        <v>6.56950426101685</v>
       </c>
       <c r="H299" t="n">
         <v>6000</v>
@@ -9069,7 +9069,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H300" t="n">
         <v>39500</v>
@@ -9098,7 +9098,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G301" t="n">
-        <v>6.45924806594849</v>
+        <v>6.45924758911133</v>
       </c>
       <c r="H301" t="n">
         <v>43000</v>
@@ -9185,7 +9185,7 @@
         <v>6.75</v>
       </c>
       <c r="G304" t="n">
-        <v>6.20198011398315</v>
+        <v>6.201979637146</v>
       </c>
       <c r="H304" t="n">
         <v>16000</v>
@@ -9359,7 +9359,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H310" t="n">
         <v>7500</v>
@@ -9446,7 +9446,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05496978759766</v>
+        <v>6.05497026443481</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9533,7 +9533,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G316" t="n">
-        <v>6.13766241073608</v>
+        <v>6.13766288757324</v>
       </c>
       <c r="H316" t="n">
         <v>5500</v>
@@ -9620,7 +9620,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.83445501327515</v>
+        <v>5.83445453643799</v>
       </c>
       <c r="H319" t="n">
         <v>15000</v>
@@ -9678,7 +9678,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G321" t="n">
-        <v>5.96308898925781</v>
+        <v>5.96308851242065</v>
       </c>
       <c r="H321" t="n">
         <v>4000</v>
@@ -9736,7 +9736,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714811325073</v>
+        <v>5.91714859008789</v>
       </c>
       <c r="H323" t="n">
         <v>7000</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9852,7 +9852,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607866287231</v>
+        <v>5.81607818603516</v>
       </c>
       <c r="H327" t="n">
         <v>14080</v>
@@ -9910,7 +9910,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>5.76095008850098</v>
+        <v>5.76094961166382</v>
       </c>
       <c r="H329" t="n">
         <v>5878</v>
@@ -9939,7 +9939,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H330" t="n">
         <v>2311</v>
@@ -10055,7 +10055,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G334" t="n">
-        <v>5.96308898925781</v>
+        <v>5.96308851242065</v>
       </c>
       <c r="H334" t="n">
         <v>1801</v>
@@ -10171,7 +10171,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.32142543792725</v>
+        <v>6.3214259147644</v>
       </c>
       <c r="H338" t="n">
         <v>7965</v>
@@ -10229,7 +10229,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>6.54194021224976</v>
+        <v>6.5419397354126</v>
       </c>
       <c r="H340" t="n">
         <v>13709</v>
@@ -10258,7 +10258,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H341" t="n">
         <v>12887</v>
@@ -10345,7 +10345,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.32142543792725</v>
+        <v>6.3214259147644</v>
       </c>
       <c r="H344" t="n">
         <v>13218</v>
@@ -10374,7 +10374,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H345" t="n">
         <v>2764</v>
@@ -10606,7 +10606,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G353" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H353" t="n">
         <v>14359</v>
@@ -10664,7 +10664,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342498779297</v>
+        <v>5.39342546463013</v>
       </c>
       <c r="H355" t="n">
         <v>1874</v>
@@ -10693,7 +10693,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.5588116645813</v>
+        <v>5.55881214141846</v>
       </c>
       <c r="H356" t="n">
         <v>2401</v>
@@ -10722,7 +10722,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H357" t="n">
         <v>2284</v>
@@ -10751,7 +10751,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530673980713</v>
+        <v>5.48530626296997</v>
       </c>
       <c r="H358" t="n">
         <v>3234</v>
@@ -10780,7 +10780,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>5.4026141166687</v>
+        <v>5.40261363983154</v>
       </c>
       <c r="H359" t="n">
         <v>3097</v>
@@ -10896,7 +10896,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718753814697</v>
+        <v>5.57718801498413</v>
       </c>
       <c r="H363" t="n">
         <v>1392</v>
@@ -10925,7 +10925,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H364" t="n">
         <v>1105</v>
@@ -10954,7 +10954,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>5.5588116645813</v>
+        <v>5.55881214141846</v>
       </c>
       <c r="H365" t="n">
         <v>2304</v>
@@ -11041,7 +11041,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H368" t="n">
         <v>11426</v>
@@ -11099,7 +11099,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H370" t="n">
         <v>3154</v>
@@ -11244,7 +11244,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H375" t="n">
         <v>9545</v>
@@ -11389,7 +11389,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.83445501327515</v>
+        <v>5.83445453643799</v>
       </c>
       <c r="H380" t="n">
         <v>352</v>
@@ -11447,7 +11447,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H382" t="n">
         <v>7014</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.59556436538696</v>
+        <v>5.59556484222412</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11592,7 +11592,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>5.70582151412964</v>
+        <v>5.70582103729248</v>
       </c>
       <c r="H387" t="n">
         <v>2675</v>
@@ -11621,7 +11621,7 @@
         <v>6.25</v>
       </c>
       <c r="G388" t="n">
-        <v>5.7425742149353</v>
+        <v>5.74257373809814</v>
       </c>
       <c r="H388" t="n">
         <v>1978</v>
@@ -11650,7 +11650,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932691574097</v>
+        <v>5.77932643890381</v>
       </c>
       <c r="H389" t="n">
         <v>6221</v>
@@ -11708,7 +11708,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G391" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H391" t="n">
         <v>4247</v>
@@ -11766,7 +11766,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G393" t="n">
-        <v>5.96308898925781</v>
+        <v>5.96308851242065</v>
       </c>
       <c r="H393" t="n">
         <v>4882</v>
@@ -11795,7 +11795,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>6.14685153961182</v>
+        <v>6.14685106277466</v>
       </c>
       <c r="H394" t="n">
         <v>4839</v>
@@ -11824,7 +11824,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>6.14685153961182</v>
+        <v>6.14685106277466</v>
       </c>
       <c r="H395" t="n">
         <v>6355</v>
@@ -11853,7 +11853,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G396" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H396" t="n">
         <v>2491</v>
@@ -11882,7 +11882,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H397" t="n">
         <v>1264</v>
@@ -11998,7 +11998,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.9906530380249</v>
+        <v>5.99065351486206</v>
       </c>
       <c r="H401" t="n">
         <v>4770</v>
@@ -12056,7 +12056,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H403" t="n">
         <v>2709</v>
@@ -12114,7 +12114,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>5.95390033721924</v>
+        <v>5.9539008140564</v>
       </c>
       <c r="H405" t="n">
         <v>1670</v>
@@ -12172,7 +12172,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H407" t="n">
         <v>1611</v>
@@ -12230,7 +12230,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.83445501327515</v>
+        <v>5.83445453643799</v>
       </c>
       <c r="H409" t="n">
         <v>529</v>
@@ -12317,7 +12317,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607866287231</v>
+        <v>5.81607818603516</v>
       </c>
       <c r="H412" t="n">
         <v>2753</v>
@@ -12346,7 +12346,7 @@
         <v>6.25</v>
       </c>
       <c r="G413" t="n">
-        <v>5.7425742149353</v>
+        <v>5.74257373809814</v>
       </c>
       <c r="H413" t="n">
         <v>2441</v>
@@ -12433,7 +12433,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H416" t="n">
         <v>3751</v>
@@ -12462,7 +12462,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124761581421</v>
       </c>
       <c r="H417" t="n">
         <v>1848</v>
@@ -12520,7 +12520,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="n">
-        <v>5.61394023895264</v>
+        <v>5.61394071578979</v>
       </c>
       <c r="H419" t="n">
         <v>1068</v>
@@ -12723,7 +12723,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>5.42098999023438</v>
+        <v>5.42098951339722</v>
       </c>
       <c r="H426" t="n">
         <v>2060</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.4026141166687</v>
+        <v>5.40261363983154</v>
       </c>
       <c r="H429" t="n">
         <v>4856</v>
@@ -13013,7 +13013,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>4.86970281600952</v>
+        <v>4.86970329284668</v>
       </c>
       <c r="H436" t="n">
         <v>13180</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.5848708152771</v>
+        <v>4.58487033843994</v>
       </c>
       <c r="H439" t="n">
         <v>4452</v>
@@ -13187,7 +13187,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H442" t="n">
         <v>3292</v>
@@ -13245,7 +13245,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H444" t="n">
         <v>14966</v>
@@ -13274,7 +13274,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>4.32760381698608</v>
+        <v>4.32760334014893</v>
       </c>
       <c r="H445" t="n">
         <v>10951</v>
@@ -13303,7 +13303,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H446" t="n">
         <v>2659</v>
@@ -13332,7 +13332,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>4.29544591903687</v>
+        <v>4.29544544219971</v>
       </c>
       <c r="H447" t="n">
         <v>15587</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H448" t="n">
         <v>24980</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13506,7 +13506,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>4.32760381698608</v>
+        <v>4.32760334014893</v>
       </c>
       <c r="H453" t="n">
         <v>24237</v>
@@ -13564,7 +13564,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>4.38273286819458</v>
+        <v>4.38273239135742</v>
       </c>
       <c r="H455" t="n">
         <v>13871</v>
@@ -13593,7 +13593,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G456" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H456" t="n">
         <v>10262</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13854,7 +13854,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>4.49758338928223</v>
+        <v>4.49758386611938</v>
       </c>
       <c r="H465" t="n">
         <v>9324</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -13999,7 +13999,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>4.49758338928223</v>
+        <v>4.49758386611938</v>
       </c>
       <c r="H470" t="n">
         <v>305</v>
@@ -14028,7 +14028,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34598016738892</v>
+        <v>4.34597969055176</v>
       </c>
       <c r="H471" t="n">
         <v>3835</v>
@@ -14057,7 +14057,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>4.39651441574097</v>
+        <v>4.39651489257812</v>
       </c>
       <c r="H472" t="n">
         <v>2289</v>
@@ -14086,7 +14086,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>4.38732624053955</v>
+        <v>4.38732671737671</v>
       </c>
       <c r="H473" t="n">
         <v>3916</v>
@@ -14115,7 +14115,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435651779175</v>
+        <v>4.36435604095459</v>
       </c>
       <c r="H474" t="n">
         <v>5067</v>
@@ -14144,7 +14144,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.39651441574097</v>
+        <v>4.39651489257812</v>
       </c>
       <c r="H475" t="n">
         <v>1381</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14231,7 +14231,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H478" t="n">
         <v>4551</v>
@@ -14260,7 +14260,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H479" t="n">
         <v>3457</v>
@@ -14318,7 +14318,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22194004058838</v>
+        <v>4.22193956375122</v>
       </c>
       <c r="H481" t="n">
         <v>10620</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332673072815</v>
+        <v>3.92332696914673</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845530509949</v>
+        <v>3.97845554351807</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14492,7 +14492,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.97386050224304</v>
+        <v>3.9738609790802</v>
       </c>
       <c r="H487" t="n">
         <v>7176</v>
@@ -14521,7 +14521,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G488" t="n">
-        <v>3.84063339233398</v>
+        <v>3.84063315391541</v>
       </c>
       <c r="H488" t="n">
         <v>15203</v>
@@ -14550,7 +14550,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G489" t="n">
-        <v>3.84063339233398</v>
+        <v>3.84063315391541</v>
       </c>
       <c r="H489" t="n">
         <v>5714</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14666,7 +14666,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>3.84522771835327</v>
+        <v>3.84522747993469</v>
       </c>
       <c r="H493" t="n">
         <v>1926</v>
@@ -14724,7 +14724,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.8590099811554</v>
+        <v>3.85900974273682</v>
       </c>
       <c r="H495" t="n">
         <v>5373</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -14811,7 +14811,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.95089149475098</v>
+        <v>3.95089101791382</v>
       </c>
       <c r="H498" t="n">
         <v>7416</v>
@@ -14840,7 +14840,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.95089149475098</v>
+        <v>3.95089101791382</v>
       </c>
       <c r="H499" t="n">
         <v>12304</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520824432373</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14956,7 +14956,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061296463013</v>
+        <v>4.01061344146729</v>
       </c>
       <c r="H503" t="n">
         <v>31005</v>
@@ -15072,7 +15072,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H507" t="n">
         <v>9121</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H508" t="n">
         <v>3615</v>
@@ -15159,7 +15159,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H510" t="n">
         <v>6857</v>
@@ -15188,7 +15188,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326711654663</v>
+        <v>4.43326759338379</v>
       </c>
       <c r="H511" t="n">
         <v>4220</v>
@@ -15304,7 +15304,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H515" t="n">
         <v>1906</v>
@@ -15333,7 +15333,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>4.34138631820679</v>
+        <v>4.34138584136963</v>
       </c>
       <c r="H516" t="n">
         <v>12696</v>
@@ -15362,7 +15362,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G517" t="n">
-        <v>4.39192056655884</v>
+        <v>4.391921043396</v>
       </c>
       <c r="H517" t="n">
         <v>7436</v>
@@ -15391,7 +15391,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H518" t="n">
         <v>5744</v>
@@ -15420,7 +15420,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>4.37354421615601</v>
+        <v>4.37354469299316</v>
       </c>
       <c r="H519" t="n">
         <v>11351</v>
@@ -15478,7 +15478,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>4.62162399291992</v>
+        <v>4.62162351608276</v>
       </c>
       <c r="H521" t="n">
         <v>14852</v>
@@ -15536,7 +15536,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>4.84213876724243</v>
+        <v>4.84213829040527</v>
       </c>
       <c r="H523" t="n">
         <v>16347</v>
@@ -15594,7 +15594,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>4.84213876724243</v>
+        <v>4.84213829040527</v>
       </c>
       <c r="H525" t="n">
         <v>6708</v>
@@ -15623,7 +15623,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>4.75025701522827</v>
+        <v>4.75025749206543</v>
       </c>
       <c r="H526" t="n">
         <v>7054</v>
@@ -15855,7 +15855,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>4.84213876724243</v>
+        <v>4.84213829040527</v>
       </c>
       <c r="H534" t="n">
         <v>5758</v>
@@ -15884,7 +15884,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>5.09021759033203</v>
+        <v>5.09021711349487</v>
       </c>
       <c r="H535" t="n">
         <v>24385</v>
@@ -15913,7 +15913,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G536" t="n">
-        <v>5.11778163909912</v>
+        <v>5.11778211593628</v>
       </c>
       <c r="H536" t="n">
         <v>8803</v>
@@ -15971,7 +15971,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>5.03508901596069</v>
+        <v>5.03508853912354</v>
       </c>
       <c r="H538" t="n">
         <v>4031</v>
@@ -16087,7 +16087,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86970281600952</v>
+        <v>4.86970329284668</v>
       </c>
       <c r="H542" t="n">
         <v>3105</v>
@@ -16116,7 +16116,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619741439819</v>
+        <v>4.79619789123535</v>
       </c>
       <c r="H543" t="n">
         <v>1688</v>
@@ -16145,7 +16145,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G544" t="n">
-        <v>4.69512891769409</v>
+        <v>4.69512844085693</v>
       </c>
       <c r="H544" t="n">
         <v>7711</v>
@@ -16203,7 +16203,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G546" t="n">
-        <v>4.53893041610718</v>
+        <v>4.53893089294434</v>
       </c>
       <c r="H546" t="n">
         <v>4076</v>
@@ -16261,7 +16261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H548" t="n">
         <v>5791</v>
@@ -16638,7 +16638,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631640434265</v>
+        <v>3.77631664276123</v>
       </c>
       <c r="H561" t="n">
         <v>14097</v>
@@ -16725,7 +16725,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>3.69362354278564</v>
+        <v>3.69362378120422</v>
       </c>
       <c r="H564" t="n">
         <v>10513</v>
@@ -16841,7 +16841,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G568" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H568" t="n">
         <v>8477</v>
@@ -16899,7 +16899,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>3.38122773170471</v>
+        <v>3.38122749328613</v>
       </c>
       <c r="H570" t="n">
         <v>38613</v>
@@ -16928,7 +16928,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G571" t="n">
-        <v>3.38122773170471</v>
+        <v>3.38122749328613</v>
       </c>
       <c r="H571" t="n">
         <v>7214</v>
@@ -16957,7 +16957,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H572" t="n">
         <v>40710</v>
@@ -16986,7 +16986,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H573" t="n">
         <v>28469</v>
@@ -17044,7 +17044,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G575" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H575" t="n">
         <v>2675</v>
@@ -17131,7 +17131,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G578" t="n">
-        <v>3.06883120536804</v>
+        <v>3.06883144378662</v>
       </c>
       <c r="H578" t="n">
         <v>17701</v>
@@ -17479,7 +17479,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.94170308113098</v>
+        <v>3.9417028427124</v>
       </c>
       <c r="H590" t="n">
         <v>70490</v>
@@ -17508,7 +17508,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712846755981</v>
+        <v>3.76712870597839</v>
       </c>
       <c r="H591" t="n">
         <v>12175</v>
@@ -17537,7 +17537,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712846755981</v>
+        <v>3.76712870597839</v>
       </c>
       <c r="H592" t="n">
         <v>9692</v>
@@ -17566,7 +17566,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G593" t="n">
-        <v>3.70281171798706</v>
+        <v>3.70281195640564</v>
       </c>
       <c r="H593" t="n">
         <v>11590</v>
@@ -17595,7 +17595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904916763306</v>
+        <v>3.51904940605164</v>
       </c>
       <c r="H594" t="n">
         <v>20677</v>
@@ -17624,7 +17624,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H595" t="n">
         <v>9575</v>
@@ -17682,7 +17682,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H597" t="n">
         <v>7488</v>
@@ -17885,7 +17885,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H604" t="n">
         <v>8247</v>
@@ -17943,7 +17943,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015804290771</v>
+        <v>3.28015780448914</v>
       </c>
       <c r="H606" t="n">
         <v>4093</v>
@@ -17972,7 +17972,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>3.32609868049622</v>
+        <v>3.32609891891479</v>
       </c>
       <c r="H607" t="n">
         <v>1705</v>
@@ -18001,7 +18001,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178216934204</v>
+        <v>3.26178193092346</v>
       </c>
       <c r="H608" t="n">
         <v>18506</v>
@@ -18030,7 +18030,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178216934204</v>
+        <v>3.26178193092346</v>
       </c>
       <c r="H609" t="n">
         <v>2325</v>
@@ -18059,7 +18059,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>3.18827700614929</v>
+        <v>3.18827724456787</v>
       </c>
       <c r="H610" t="n">
         <v>6723</v>
@@ -18146,7 +18146,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233636856079</v>
+        <v>3.14233660697937</v>
       </c>
       <c r="H613" t="n">
         <v>1790</v>
@@ -18175,7 +18175,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H614" t="n">
         <v>18656</v>
@@ -18204,7 +18204,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H615" t="n">
         <v>1399</v>
@@ -18291,7 +18291,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.1147723197937</v>
+        <v>3.11477208137512</v>
       </c>
       <c r="H618" t="n">
         <v>1345</v>
@@ -18349,7 +18349,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H620" t="n">
         <v>26152</v>
@@ -18523,7 +18523,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H626" t="n">
         <v>14381</v>
@@ -18552,7 +18552,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G627" t="n">
-        <v>2.93101000785828</v>
+        <v>2.9310097694397</v>
       </c>
       <c r="H627" t="n">
         <v>10185</v>
@@ -18581,7 +18581,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>2.97695016860962</v>
+        <v>2.9769504070282</v>
       </c>
       <c r="H628" t="n">
         <v>1810</v>
@@ -18639,7 +18639,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G630" t="n">
-        <v>3.03276801109314</v>
+        <v>3.03276824951172</v>
       </c>
       <c r="H630" t="n">
         <v>1951</v>
@@ -18987,7 +18987,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110481262207</v>
+        <v>2.52110457420349</v>
       </c>
       <c r="H642" t="n">
         <v>95598</v>
@@ -19016,7 +19016,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H643" t="n">
         <v>60892</v>
@@ -19074,7 +19074,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040790557861</v>
+        <v>2.53040766716003</v>
       </c>
       <c r="H645" t="n">
         <v>12711</v>
@@ -19132,7 +19132,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901385307312</v>
+        <v>2.54901361465454</v>
       </c>
       <c r="H647" t="n">
         <v>4920</v>
@@ -19161,7 +19161,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G648" t="n">
-        <v>2.42807483673096</v>
+        <v>2.42807507514954</v>
       </c>
       <c r="H648" t="n">
         <v>23503</v>
@@ -19335,7 +19335,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H654" t="n">
         <v>19145</v>
@@ -19364,7 +19364,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H655" t="n">
         <v>11634</v>
@@ -19509,7 +19509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H660" t="n">
         <v>4896</v>
@@ -19799,7 +19799,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H670" t="n">
         <v>10500</v>
@@ -20060,7 +20060,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H679" t="n">
         <v>10826</v>
@@ -20118,7 +20118,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H681" t="n">
         <v>3858</v>
@@ -20205,7 +20205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.49319577217102</v>
+        <v>2.4931960105896</v>
       </c>
       <c r="H684" t="n">
         <v>12276</v>
@@ -20524,7 +20524,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.9536235332489</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H695" t="n">
         <v>235716</v>
@@ -20553,7 +20553,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H696" t="n">
         <v>232613</v>
@@ -20669,7 +20669,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.51638400554657</v>
+        <v>1.51638412475586</v>
       </c>
       <c r="H700" t="n">
         <v>7380</v>
@@ -20698,7 +20698,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.48847508430481</v>
+        <v>1.4884752035141</v>
       </c>
       <c r="H701" t="n">
         <v>13536</v>
@@ -20988,7 +20988,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H711" t="n">
         <v>6528</v>
@@ -21017,7 +21017,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H712" t="n">
         <v>2874</v>
@@ -21046,7 +21046,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G713" t="n">
-        <v>1.51638400554657</v>
+        <v>1.51638412475586</v>
       </c>
       <c r="H713" t="n">
         <v>7640</v>
@@ -21220,7 +21220,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G719" t="n">
-        <v>1.59545934200287</v>
+        <v>1.59545946121216</v>
       </c>
       <c r="H719" t="n">
         <v>9455</v>
@@ -21278,7 +21278,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G721" t="n">
-        <v>1.60476231575012</v>
+        <v>1.60476243495941</v>
       </c>
       <c r="H721" t="n">
         <v>5640</v>
@@ -21307,7 +21307,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.55359578132629</v>
+        <v>1.55359590053558</v>
       </c>
       <c r="H722" t="n">
         <v>2574</v>
@@ -21452,7 +21452,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H727" t="n">
         <v>67002</v>
@@ -21481,7 +21481,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.85129106044769</v>
+        <v>1.8512909412384</v>
       </c>
       <c r="H728" t="n">
         <v>18194</v>
@@ -21510,7 +21510,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G729" t="n">
-        <v>1.89780569076538</v>
+        <v>1.89780580997467</v>
       </c>
       <c r="H729" t="n">
         <v>21650</v>
@@ -21568,7 +21568,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>1.89780569076538</v>
+        <v>1.89780580997467</v>
       </c>
       <c r="H731" t="n">
         <v>2155</v>
@@ -21626,7 +21626,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G733" t="n">
-        <v>2.42807483673096</v>
+        <v>2.42807507514954</v>
       </c>
       <c r="H733" t="n">
         <v>201386</v>
@@ -21684,7 +21684,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H735" t="n">
         <v>53817</v>
@@ -21713,7 +21713,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H736" t="n">
         <v>25550</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H738" t="n">
         <v>41345</v>
@@ -21974,7 +21974,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.009441614151</v>
+        <v>2.00944137573242</v>
       </c>
       <c r="H745" t="n">
         <v>22944</v>
@@ -22177,7 +22177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.214106798172</v>
+        <v>2.21410703659058</v>
       </c>
       <c r="H752" t="n">
         <v>18450</v>
@@ -22293,7 +22293,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H756" t="n">
         <v>6173</v>
@@ -22322,7 +22322,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H757" t="n">
         <v>9025</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H760" t="n">
         <v>6602</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H761" t="n">
         <v>2731</v>
@@ -22467,7 +22467,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16759204864502</v>
+        <v>2.16759181022644</v>
       </c>
       <c r="H762" t="n">
         <v>4601</v>
@@ -22525,7 +22525,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H764" t="n">
         <v>5171</v>
@@ -22554,7 +22554,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.17689490318298</v>
+        <v>2.1768946647644</v>
       </c>
       <c r="H765" t="n">
         <v>4690</v>
@@ -22583,7 +22583,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.26992440223694</v>
+        <v>2.26992464065552</v>
       </c>
       <c r="H766" t="n">
         <v>6724</v>
@@ -22699,7 +22699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H770" t="n">
         <v>1304</v>
@@ -22728,7 +22728,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H771" t="n">
         <v>5621</v>
@@ -23076,7 +23076,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G783" t="n">
-        <v>1.96292638778687</v>
+        <v>1.96292650699615</v>
       </c>
       <c r="H783" t="n">
         <v>12163</v>
@@ -23134,7 +23134,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.89780569076538</v>
+        <v>1.89780580997467</v>
       </c>
       <c r="H785" t="n">
         <v>4151</v>
@@ -23192,7 +23192,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H787" t="n">
         <v>19192</v>
@@ -23279,7 +23279,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03735017776489</v>
+        <v>2.03735041618347</v>
       </c>
       <c r="H790" t="n">
         <v>6918</v>
@@ -23308,7 +23308,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.009441614151</v>
+        <v>2.00944137573242</v>
       </c>
       <c r="H791" t="n">
         <v>2800</v>
@@ -23424,7 +23424,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.9536235332489</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H795" t="n">
         <v>8911</v>
@@ -23453,7 +23453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.9536235332489</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H796" t="n">
         <v>3170</v>
@@ -23482,7 +23482,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.9536235332489</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H797" t="n">
         <v>15172</v>
@@ -23540,7 +23540,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H799" t="n">
         <v>9805</v>
@@ -23569,7 +23569,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G800" t="n">
-        <v>1.90710878372192</v>
+        <v>1.90710890293121</v>
       </c>
       <c r="H800" t="n">
         <v>3251</v>
@@ -23656,7 +23656,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G803" t="n">
-        <v>1.78617000579834</v>
+        <v>1.78617012500763</v>
       </c>
       <c r="H803" t="n">
         <v>3999</v>
@@ -23859,7 +23859,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.64662563800812</v>
+        <v>1.64662551879883</v>
       </c>
       <c r="H810" t="n">
         <v>3970</v>
@@ -23917,7 +23917,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H812" t="n">
         <v>17120</v>
@@ -23946,7 +23946,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G813" t="n">
-        <v>1.67453455924988</v>
+        <v>1.67453444004059</v>
       </c>
       <c r="H813" t="n">
         <v>3750</v>
@@ -24062,7 +24062,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G817" t="n">
-        <v>1.48847508430481</v>
+        <v>1.4884752035141</v>
       </c>
       <c r="H817" t="n">
         <v>14735</v>
@@ -24091,7 +24091,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H818" t="n">
         <v>26987</v>
@@ -24120,7 +24120,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011076927185</v>
+        <v>1.60011088848114</v>
       </c>
       <c r="H819" t="n">
         <v>13128</v>
@@ -24149,7 +24149,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G820" t="n">
-        <v>1.6094137430191</v>
+        <v>1.60941386222839</v>
       </c>
       <c r="H820" t="n">
         <v>7001</v>
@@ -24410,7 +24410,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.67453455924988</v>
+        <v>1.67453444004059</v>
       </c>
       <c r="H829" t="n">
         <v>19930</v>
@@ -24468,7 +24468,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G831" t="n">
-        <v>1.81873047351837</v>
+        <v>1.81873059272766</v>
       </c>
       <c r="H831" t="n">
         <v>14506</v>
@@ -24642,7 +24642,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H837" t="n">
         <v>17650</v>
@@ -24671,7 +24671,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G838" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H838" t="n">
         <v>5154</v>
@@ -24729,7 +24729,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H840" t="n">
         <v>6246</v>
@@ -24758,7 +24758,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>1.87919986248016</v>
+        <v>1.87919998168945</v>
       </c>
       <c r="H841" t="n">
         <v>5347</v>
@@ -24787,7 +24787,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.85129106044769</v>
+        <v>1.8512909412384</v>
       </c>
       <c r="H842" t="n">
         <v>3510</v>
@@ -24961,7 +24961,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G848" t="n">
-        <v>1.81873047351837</v>
+        <v>1.81873059272766</v>
       </c>
       <c r="H848" t="n">
         <v>1500</v>
@@ -25019,7 +25019,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G850" t="n">
-        <v>1.78617000579834</v>
+        <v>1.78617012500763</v>
       </c>
       <c r="H850" t="n">
         <v>10425</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.78617000579834</v>
+        <v>1.78617012500763</v>
       </c>
       <c r="H851" t="n">
         <v>616</v>
@@ -25135,7 +25135,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.93501758575439</v>
+        <v>1.93501770496368</v>
       </c>
       <c r="H854" t="n">
         <v>16193</v>
@@ -25193,7 +25193,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G856" t="n">
-        <v>1.85129106044769</v>
+        <v>1.8512909412384</v>
       </c>
       <c r="H856" t="n">
         <v>7440</v>
@@ -25251,7 +25251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.86989688873291</v>
+        <v>1.8698970079422</v>
       </c>
       <c r="H858" t="n">
         <v>2711</v>
@@ -25309,7 +25309,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G860" t="n">
-        <v>1.96292638778687</v>
+        <v>1.96292650699615</v>
       </c>
       <c r="H860" t="n">
         <v>19342</v>
@@ -42773,6 +42773,35 @@
         <v>3937</v>
       </c>
       <c r="I1462" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1463" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1463" t="n">
+        <v>0.620000004768372</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>0.584999978542328</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>0.660000026226044</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>28895</v>
+      </c>
+      <c r="I1463" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -514,7 +514,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66892051696777</v>
+        <v>2.66892075538635</v>
       </c>
       <c r="H5" t="n">
         <v>100000</v>
@@ -659,7 +659,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.81143808364868</v>
+        <v>3.8114378452301</v>
       </c>
       <c r="H10" t="n">
         <v>389000</v>
@@ -717,7 +717,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.60121488571167</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H12" t="n">
         <v>96000</v>
@@ -804,7 +804,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H15" t="n">
         <v>85000</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583225250244</v>
+        <v>3.44583249092102</v>
       </c>
       <c r="H16" t="n">
         <v>29000</v>
@@ -862,7 +862,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50981307029724</v>
+        <v>3.50981283187866</v>
       </c>
       <c r="H17" t="n">
         <v>74000</v>
@@ -920,7 +920,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G19" t="n">
-        <v>3.47325253486633</v>
+        <v>3.47325277328491</v>
       </c>
       <c r="H19" t="n">
         <v>32000</v>
@@ -949,7 +949,7 @@
         <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.42755222320557</v>
+        <v>3.42755198478699</v>
       </c>
       <c r="H20" t="n">
         <v>37000</v>
@@ -978,7 +978,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.26302933692932</v>
+        <v>3.2630295753479</v>
       </c>
       <c r="H21" t="n">
         <v>78000</v>
@@ -1094,7 +1094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3727114200592</v>
+        <v>3.37271118164062</v>
       </c>
       <c r="H25" t="n">
         <v>11000</v>
@@ -1152,7 +1152,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248822212219</v>
+        <v>3.16248798370361</v>
       </c>
       <c r="H27" t="n">
         <v>62000</v>
@@ -1326,7 +1326,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420771598816</v>
+        <v>3.14420795440674</v>
       </c>
       <c r="H33" t="n">
         <v>53000</v>
@@ -1355,7 +1355,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.13506746292114</v>
+        <v>3.1350679397583</v>
       </c>
       <c r="H34" t="n">
         <v>13000</v>
@@ -1413,7 +1413,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818877220154</v>
+        <v>3.20818853378296</v>
       </c>
       <c r="H36" t="n">
         <v>50000</v>
@@ -1442,7 +1442,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443091392517</v>
+        <v>3.35443115234375</v>
       </c>
       <c r="H37" t="n">
         <v>264000</v>
@@ -1471,7 +1471,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G38" t="n">
-        <v>3.41841220855713</v>
+        <v>3.41841173171997</v>
       </c>
       <c r="H38" t="n">
         <v>54000</v>
@@ -1558,7 +1558,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H41" t="n">
         <v>172000</v>
@@ -1587,7 +1587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057785987854</v>
+        <v>3.82057809829712</v>
       </c>
       <c r="H42" t="n">
         <v>202000</v>
@@ -1790,7 +1790,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H49" t="n">
         <v>51000</v>
@@ -1848,7 +1848,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H51" t="n">
         <v>21000</v>
@@ -1877,7 +1877,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G52" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H52" t="n">
         <v>35000</v>
@@ -1964,7 +1964,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -2022,7 +2022,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>3.5280933380127</v>
+        <v>3.52809357643127</v>
       </c>
       <c r="H57" t="n">
         <v>4000</v>
@@ -2051,7 +2051,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H58" t="n">
         <v>49000</v>
@@ -2080,7 +2080,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949467658997</v>
+        <v>3.61949515342712</v>
       </c>
       <c r="H59" t="n">
         <v>20000</v>
@@ -2109,7 +2109,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G60" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H60" t="n">
         <v>23000</v>
@@ -2138,7 +2138,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293461799622</v>
+        <v>3.58293437957764</v>
       </c>
       <c r="H61" t="n">
         <v>16000</v>
@@ -2167,7 +2167,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.62863492965698</v>
+        <v>3.62863516807556</v>
       </c>
       <c r="H62" t="n">
         <v>25000</v>
@@ -2196,7 +2196,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207463264465</v>
+        <v>3.59207439422607</v>
       </c>
       <c r="H63" t="n">
         <v>11000</v>
@@ -2225,7 +2225,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G64" t="n">
-        <v>3.60121488571167</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H64" t="n">
         <v>13000</v>
@@ -2254,7 +2254,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G65" t="n">
-        <v>3.61035466194153</v>
+        <v>3.61035490036011</v>
       </c>
       <c r="H65" t="n">
         <v>9000</v>
@@ -2283,7 +2283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H67" t="n">
         <v>24000</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H71" t="n">
         <v>9000</v>
@@ -2544,7 +2544,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4179801940918</v>
+        <v>3.41797995567322</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2631,7 +2631,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H78" t="n">
         <v>10500</v>
@@ -2660,7 +2660,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H79" t="n">
         <v>11000</v>
@@ -2689,7 +2689,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G80" t="n">
-        <v>3.48229646682739</v>
+        <v>3.48229670524597</v>
       </c>
       <c r="H80" t="n">
         <v>11500</v>
@@ -2718,7 +2718,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G81" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H81" t="n">
         <v>4500</v>
@@ -2747,7 +2747,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G82" t="n">
-        <v>3.47310853004456</v>
+        <v>3.47310876846313</v>
       </c>
       <c r="H82" t="n">
         <v>4500</v>
@@ -2921,7 +2921,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.65687108039856</v>
+        <v>3.65687131881714</v>
       </c>
       <c r="H88" t="n">
         <v>31500</v>
@@ -2950,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524719238281</v>
+        <v>3.67524743080139</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524719238281</v>
+        <v>3.67524743080139</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3037,7 +3037,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G92" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H92" t="n">
         <v>18000</v>
@@ -3095,7 +3095,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251466751099</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H94" t="n">
         <v>132500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520824432373</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3211,7 +3211,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>5.09021711349487</v>
+        <v>5.09021759033203</v>
       </c>
       <c r="H98" t="n">
         <v>576000</v>
@@ -3269,7 +3269,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910871505737</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H100" t="n">
         <v>243500</v>
@@ -3327,7 +3327,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>5.14534616470337</v>
+        <v>5.14534664154053</v>
       </c>
       <c r="H102" t="n">
         <v>73000</v>
@@ -3385,7 +3385,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G104" t="n">
-        <v>5.31073236465454</v>
+        <v>5.31073188781738</v>
       </c>
       <c r="H104" t="n">
         <v>68500</v>
@@ -3530,7 +3530,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>5.49449491500854</v>
+        <v>5.49449443817139</v>
       </c>
       <c r="H109" t="n">
         <v>40500</v>
@@ -3588,7 +3588,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>6.96459293365479</v>
+        <v>6.96459341049194</v>
       </c>
       <c r="H111" t="n">
         <v>293500</v>
@@ -3617,7 +3617,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.00134611129761</v>
+        <v>7.00134563446045</v>
       </c>
       <c r="H112" t="n">
         <v>689000</v>
@@ -3646,7 +3646,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G113" t="n">
-        <v>6.94621706008911</v>
+        <v>6.94621753692627</v>
       </c>
       <c r="H113" t="n">
         <v>117500</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3704,7 +3704,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237661361694</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H115" t="n">
         <v>297500</v>
@@ -3820,7 +3820,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>7.38724756240845</v>
+        <v>7.38724660873413</v>
       </c>
       <c r="H119" t="n">
         <v>101000</v>
@@ -3936,7 +3936,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>6.94621706008911</v>
+        <v>6.94621753692627</v>
       </c>
       <c r="H123" t="n">
         <v>106000</v>
@@ -4110,7 +4110,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433578491211</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4197,7 +4197,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>6.74407911300659</v>
+        <v>6.74407958984375</v>
       </c>
       <c r="H132" t="n">
         <v>13000</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4284,7 +4284,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H135" t="n">
         <v>150000</v>
@@ -4313,7 +4313,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>7.38724756240845</v>
+        <v>7.38724660873413</v>
       </c>
       <c r="H136" t="n">
         <v>68000</v>
@@ -4429,7 +4429,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237661361694</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H140" t="n">
         <v>13000</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366188049316</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4603,7 +4603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08554458618164</v>
+        <v>8.08554553985596</v>
       </c>
       <c r="H146" t="n">
         <v>55500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366188049316</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4690,7 +4690,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G149" t="n">
-        <v>8.14067363739014</v>
+        <v>8.14067268371582</v>
       </c>
       <c r="H149" t="n">
         <v>53500</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691108703613</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4806,7 +4806,7 @@
         <v>8.5</v>
       </c>
       <c r="G153" t="n">
-        <v>7.80990076065063</v>
+        <v>7.80990028381348</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015743255615</v>
+        <v>7.92015790939331</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4893,7 +4893,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314901351929</v>
+        <v>7.77314853668213</v>
       </c>
       <c r="H156" t="n">
         <v>12500</v>
@@ -5009,7 +5009,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G160" t="n">
-        <v>7.64451456069946</v>
+        <v>7.64451360702515</v>
       </c>
       <c r="H160" t="n">
         <v>19000</v>
@@ -5125,7 +5125,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237661361694</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H164" t="n">
         <v>19000</v>
@@ -5154,7 +5154,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H165" t="n">
         <v>25000</v>
@@ -5183,7 +5183,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H166" t="n">
         <v>25500</v>
@@ -5270,7 +5270,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G169" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691108703613</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5357,7 +5357,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G172" t="n">
-        <v>8.14067363739014</v>
+        <v>8.14067268371582</v>
       </c>
       <c r="H172" t="n">
         <v>81500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84665393829346</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5473,7 +5473,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.84665393829346</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5560,7 +5560,7 @@
         <v>8.5</v>
       </c>
       <c r="G179" t="n">
-        <v>7.80990076065063</v>
+        <v>7.80990028381348</v>
       </c>
       <c r="H179" t="n">
         <v>16500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.84665393829346</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5618,7 +5618,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314901351929</v>
+        <v>7.77314853668213</v>
       </c>
       <c r="H181" t="n">
         <v>18500</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H183" t="n">
         <v>33500</v>
@@ -5734,7 +5734,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588153839111</v>
+        <v>7.51588106155396</v>
       </c>
       <c r="H185" t="n">
         <v>12500</v>
@@ -5763,7 +5763,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425741195679</v>
+        <v>7.53425645828247</v>
       </c>
       <c r="H186" t="n">
         <v>13000</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -6053,7 +6053,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6169,7 +6169,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38724756240845</v>
+        <v>7.38724660873413</v>
       </c>
       <c r="H200" t="n">
         <v>9500</v>
@@ -6227,7 +6227,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G202" t="n">
-        <v>7.40562391281128</v>
+        <v>7.40562343597412</v>
       </c>
       <c r="H202" t="n">
         <v>14000</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049438476562</v>
+        <v>7.35049486160278</v>
       </c>
       <c r="H203" t="n">
         <v>17500</v>
@@ -6314,7 +6314,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>7.31374216079712</v>
+        <v>7.31374263763428</v>
       </c>
       <c r="H205" t="n">
         <v>14500</v>
@@ -6343,7 +6343,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H206" t="n">
         <v>10000</v>
@@ -6372,7 +6372,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H207" t="n">
         <v>32500</v>
@@ -6430,7 +6430,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H209" t="n">
         <v>21500</v>
@@ -6575,7 +6575,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83596038818359</v>
+        <v>6.83595991134644</v>
       </c>
       <c r="H214" t="n">
         <v>29500</v>
@@ -6633,7 +6633,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>6.8175835609436</v>
+        <v>6.81758403778076</v>
       </c>
       <c r="H216" t="n">
         <v>17500</v>
@@ -6662,7 +6662,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H217" t="n">
         <v>63000</v>
@@ -6807,7 +6807,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H222" t="n">
         <v>18500</v>
@@ -6865,7 +6865,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433578491211</v>
       </c>
       <c r="H224" t="n">
         <v>31500</v>
@@ -6952,7 +6952,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G227" t="n">
-        <v>6.74407911300659</v>
+        <v>6.74407958984375</v>
       </c>
       <c r="H227" t="n">
         <v>34000</v>
@@ -7097,7 +7097,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G232" t="n">
-        <v>7.04728746414185</v>
+        <v>7.04728698730469</v>
       </c>
       <c r="H232" t="n">
         <v>25500</v>
@@ -7126,7 +7126,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813776016235</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7155,7 +7155,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H234" t="n">
         <v>37500</v>
@@ -7242,7 +7242,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433578491211</v>
       </c>
       <c r="H237" t="n">
         <v>14500</v>
@@ -7358,7 +7358,7 @@
         <v>7.55999994277954</v>
       </c>
       <c r="G241" t="n">
-        <v>6.94621706008911</v>
+        <v>6.94621753692627</v>
       </c>
       <c r="H241" t="n">
         <v>18500</v>
@@ -7387,7 +7387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G242" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H242" t="n">
         <v>21500</v>
@@ -7474,7 +7474,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76245498657227</v>
+        <v>6.76245546340942</v>
       </c>
       <c r="H245" t="n">
         <v>4500</v>
@@ -7503,7 +7503,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H246" t="n">
         <v>14000</v>
@@ -7561,7 +7561,7 @@
         <v>7</v>
       </c>
       <c r="G248" t="n">
-        <v>6.43168258666992</v>
+        <v>6.43168306350708</v>
       </c>
       <c r="H248" t="n">
         <v>15000</v>
@@ -7590,7 +7590,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>6.3857421875</v>
+        <v>6.38574171066284</v>
       </c>
       <c r="H249" t="n">
         <v>26000</v>
@@ -7706,7 +7706,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>6.3857421875</v>
+        <v>6.38574171066284</v>
       </c>
       <c r="H253" t="n">
         <v>14500</v>
@@ -7735,7 +7735,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H254" t="n">
         <v>14500</v>
@@ -7764,7 +7764,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>6.33061361312866</v>
+        <v>6.3306131362915</v>
       </c>
       <c r="H255" t="n">
         <v>17000</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>6.2387318611145</v>
+        <v>6.23873233795166</v>
       </c>
       <c r="H257" t="n">
         <v>3500</v>
@@ -7851,7 +7851,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G258" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H258" t="n">
         <v>11000</v>
@@ -7880,7 +7880,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H259" t="n">
         <v>2000</v>
@@ -7909,7 +7909,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G260" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H260" t="n">
         <v>5000</v>
@@ -7938,7 +7938,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H261" t="n">
         <v>25000</v>
@@ -7967,7 +7967,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H262" t="n">
         <v>104000</v>
@@ -8025,7 +8025,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H264" t="n">
         <v>31000</v>
@@ -8083,7 +8083,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>6.65219783782959</v>
+        <v>6.65219736099243</v>
       </c>
       <c r="H266" t="n">
         <v>20500</v>
@@ -8141,7 +8141,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H268" t="n">
         <v>11000</v>
@@ -8344,7 +8344,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G275" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8373,7 +8373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G276" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H276" t="n">
         <v>8000</v>
@@ -8402,7 +8402,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G277" t="n">
-        <v>6.21116828918457</v>
+        <v>6.21116876602173</v>
       </c>
       <c r="H277" t="n">
         <v>20000</v>
@@ -8431,7 +8431,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G278" t="n">
-        <v>6.21116828918457</v>
+        <v>6.21116876602173</v>
       </c>
       <c r="H278" t="n">
         <v>7000</v>
@@ -8518,7 +8518,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>5.69663286209106</v>
+        <v>5.69663333892822</v>
       </c>
       <c r="H281" t="n">
         <v>27500</v>
@@ -8576,7 +8576,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.80689096450806</v>
+        <v>5.8068904876709</v>
       </c>
       <c r="H283" t="n">
         <v>10500</v>
@@ -8605,7 +8605,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>5.72419738769531</v>
+        <v>5.72419786453247</v>
       </c>
       <c r="H284" t="n">
         <v>12000</v>
@@ -8663,7 +8663,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910871505737</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H286" t="n">
         <v>39500</v>
@@ -8721,7 +8721,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G288" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H288" t="n">
         <v>11000</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526683807373</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8866,7 +8866,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H293" t="n">
         <v>64000</v>
@@ -8895,7 +8895,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H294" t="n">
         <v>23500</v>
@@ -9011,7 +9011,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H298" t="n">
         <v>9000</v>
@@ -9243,7 +9243,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G306" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H306" t="n">
         <v>8000</v>
@@ -9301,7 +9301,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>6.0457820892334</v>
+        <v>6.04578161239624</v>
       </c>
       <c r="H308" t="n">
         <v>4500</v>
@@ -9330,7 +9330,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>6.06415796279907</v>
+        <v>6.06415843963623</v>
       </c>
       <c r="H309" t="n">
         <v>4500</v>
@@ -9359,7 +9359,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H310" t="n">
         <v>7500</v>
@@ -9388,7 +9388,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9446,7 +9446,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05497026443481</v>
+        <v>6.05496978759766</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9475,7 +9475,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>6.16522693634033</v>
+        <v>6.16522741317749</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9533,7 +9533,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G316" t="n">
-        <v>6.13766288757324</v>
+        <v>6.1376633644104</v>
       </c>
       <c r="H316" t="n">
         <v>5500</v>
@@ -9620,7 +9620,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.83445453643799</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H319" t="n">
         <v>15000</v>
@@ -9736,7 +9736,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714859008789</v>
+        <v>5.91714811325073</v>
       </c>
       <c r="H323" t="n">
         <v>7000</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526683807373</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9794,7 +9794,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H325" t="n">
         <v>13000</v>
@@ -9823,7 +9823,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>6.0457820892334</v>
+        <v>6.04578161239624</v>
       </c>
       <c r="H326" t="n">
         <v>1450</v>
@@ -9852,7 +9852,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607913970947</v>
       </c>
       <c r="H327" t="n">
         <v>14080</v>
@@ -9881,7 +9881,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770231246948</v>
+        <v>5.79770278930664</v>
       </c>
       <c r="H328" t="n">
         <v>8871</v>
@@ -9910,7 +9910,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>5.76094961166382</v>
+        <v>5.76095008850098</v>
       </c>
       <c r="H329" t="n">
         <v>5878</v>
@@ -9997,7 +9997,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H332" t="n">
         <v>4456</v>
@@ -10026,7 +10026,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H333" t="n">
         <v>2022</v>
@@ -10084,7 +10084,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H335" t="n">
         <v>25940</v>
@@ -10142,7 +10142,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H337" t="n">
         <v>15456</v>
@@ -10171,7 +10171,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H338" t="n">
         <v>7965</v>
@@ -10200,7 +10200,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813776016235</v>
       </c>
       <c r="H339" t="n">
         <v>40701</v>
@@ -10229,7 +10229,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>6.5419397354126</v>
+        <v>6.54194021224976</v>
       </c>
       <c r="H340" t="n">
         <v>13709</v>
@@ -10258,7 +10258,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H341" t="n">
         <v>12887</v>
@@ -10287,7 +10287,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H342" t="n">
         <v>2560</v>
@@ -10316,7 +10316,7 @@
         <v>7</v>
       </c>
       <c r="G343" t="n">
-        <v>6.43168258666992</v>
+        <v>6.43168306350708</v>
       </c>
       <c r="H343" t="n">
         <v>3966</v>
@@ -10345,7 +10345,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H344" t="n">
         <v>13218</v>
@@ -10374,7 +10374,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H345" t="n">
         <v>2764</v>
@@ -10432,7 +10432,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H347" t="n">
         <v>510</v>
@@ -10461,7 +10461,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H348" t="n">
         <v>1520</v>
@@ -10519,7 +10519,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G350" t="n">
-        <v>6.21116828918457</v>
+        <v>6.21116876602173</v>
       </c>
       <c r="H350" t="n">
         <v>500</v>
@@ -10548,7 +10548,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360376358032</v>
+        <v>6.18360328674316</v>
       </c>
       <c r="H351" t="n">
         <v>2077</v>
@@ -10693,7 +10693,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G356" t="n">
-        <v>5.55881214141846</v>
+        <v>5.5588116645813</v>
       </c>
       <c r="H356" t="n">
         <v>2401</v>
@@ -10809,7 +10809,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H360" t="n">
         <v>2285</v>
@@ -10838,7 +10838,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>5.4669303894043</v>
+        <v>5.46692991256714</v>
       </c>
       <c r="H361" t="n">
         <v>1880</v>
@@ -10896,7 +10896,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718801498413</v>
+        <v>5.57718753814697</v>
       </c>
       <c r="H363" t="n">
         <v>1392</v>
@@ -10954,7 +10954,7 @@
         <v>6.05000019073486</v>
       </c>
       <c r="G365" t="n">
-        <v>5.55881214141846</v>
+        <v>5.5588116645813</v>
       </c>
       <c r="H365" t="n">
         <v>2304</v>
@@ -10983,7 +10983,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G366" t="n">
-        <v>5.6506929397583</v>
+        <v>5.65069246292114</v>
       </c>
       <c r="H366" t="n">
         <v>6216</v>
@@ -11012,7 +11012,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>5.4669303894043</v>
+        <v>5.46692991256714</v>
       </c>
       <c r="H367" t="n">
         <v>3574</v>
@@ -11070,7 +11070,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G369" t="n">
-        <v>5.80689096450806</v>
+        <v>5.8068904876709</v>
       </c>
       <c r="H369" t="n">
         <v>4280</v>
@@ -11128,7 +11128,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>5.80689096450806</v>
+        <v>5.8068904876709</v>
       </c>
       <c r="H371" t="n">
         <v>6334</v>
@@ -11186,7 +11186,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H375" t="n">
         <v>9545</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.0457820892334</v>
+        <v>6.04578161239624</v>
       </c>
       <c r="H376" t="n">
         <v>7667</v>
@@ -11331,7 +11331,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>5.56799936294556</v>
+        <v>5.56799983978271</v>
       </c>
       <c r="H378" t="n">
         <v>9532</v>
@@ -11389,7 +11389,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.83445453643799</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H380" t="n">
         <v>352</v>
@@ -11418,7 +11418,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H381" t="n">
         <v>5665</v>
@@ -11476,7 +11476,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.69663286209106</v>
+        <v>5.69663333892822</v>
       </c>
       <c r="H383" t="n">
         <v>1054</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.59556484222412</v>
+        <v>5.5955638885498</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11534,7 +11534,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.69663286209106</v>
+        <v>5.69663333892822</v>
       </c>
       <c r="H385" t="n">
         <v>1810</v>
@@ -11563,7 +11563,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>5.58637619018555</v>
+        <v>5.58637571334839</v>
       </c>
       <c r="H386" t="n">
         <v>2950</v>
@@ -11621,7 +11621,7 @@
         <v>6.25</v>
       </c>
       <c r="G388" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H388" t="n">
         <v>1978</v>
@@ -11650,7 +11650,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932643890381</v>
+        <v>5.77932596206665</v>
       </c>
       <c r="H389" t="n">
         <v>6221</v>
@@ -11679,7 +11679,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H390" t="n">
         <v>5008</v>
@@ -11737,7 +11737,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G392" t="n">
-        <v>5.80689096450806</v>
+        <v>5.8068904876709</v>
       </c>
       <c r="H392" t="n">
         <v>2786</v>
@@ -11853,7 +11853,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G396" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H396" t="n">
         <v>2491</v>
@@ -11882,7 +11882,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H397" t="n">
         <v>1264</v>
@@ -11911,7 +11911,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>6.16522693634033</v>
+        <v>6.16522741317749</v>
       </c>
       <c r="H398" t="n">
         <v>1789</v>
@@ -11940,7 +11940,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.11928701400757</v>
+        <v>6.11928653717041</v>
       </c>
       <c r="H399" t="n">
         <v>1503</v>
@@ -11998,7 +11998,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.99065351486206</v>
+        <v>5.99065256118774</v>
       </c>
       <c r="H401" t="n">
         <v>4770</v>
@@ -12085,7 +12085,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G404" t="n">
-        <v>5.85283088684082</v>
+        <v>5.85283136367798</v>
       </c>
       <c r="H404" t="n">
         <v>2104</v>
@@ -12230,7 +12230,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.83445453643799</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H409" t="n">
         <v>529</v>
@@ -12259,7 +12259,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.89877223968506</v>
+        <v>5.8987717628479</v>
       </c>
       <c r="H410" t="n">
         <v>1853</v>
@@ -12317,7 +12317,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607913970947</v>
       </c>
       <c r="H412" t="n">
         <v>2753</v>
@@ -12346,7 +12346,7 @@
         <v>6.25</v>
       </c>
       <c r="G413" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H413" t="n">
         <v>2441</v>
@@ -12375,7 +12375,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H414" t="n">
         <v>7162</v>
@@ -12549,7 +12549,7 @@
         <v>6</v>
       </c>
       <c r="G420" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H420" t="n">
         <v>2335</v>
@@ -12578,7 +12578,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>5.69663286209106</v>
+        <v>5.69663333892822</v>
       </c>
       <c r="H421" t="n">
         <v>4496</v>
@@ -12607,7 +12607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G422" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H422" t="n">
         <v>3644</v>
@@ -12636,7 +12636,7 @@
         <v>6</v>
       </c>
       <c r="G423" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H423" t="n">
         <v>3401</v>
@@ -12723,7 +12723,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>5.42098951339722</v>
+        <v>5.42098999023438</v>
       </c>
       <c r="H426" t="n">
         <v>2060</v>
@@ -12752,7 +12752,7 @@
         <v>5.75</v>
       </c>
       <c r="G427" t="n">
-        <v>5.28316831588745</v>
+        <v>5.28316783905029</v>
       </c>
       <c r="H427" t="n">
         <v>6854</v>
@@ -12839,7 +12839,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>5.31992053985596</v>
+        <v>5.31992101669312</v>
       </c>
       <c r="H430" t="n">
         <v>4924</v>
@@ -12868,7 +12868,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>5.35667276382446</v>
+        <v>5.35667324066162</v>
       </c>
       <c r="H431" t="n">
         <v>2160</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910871505737</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H434" t="n">
         <v>3264</v>
@@ -12984,7 +12984,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346488952637</v>
+        <v>5.05346536636353</v>
       </c>
       <c r="H435" t="n">
         <v>15369</v>
@@ -13013,7 +13013,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>4.86970329284668</v>
+        <v>4.86970281600952</v>
       </c>
       <c r="H436" t="n">
         <v>13180</v>
@@ -13071,7 +13071,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.6767520904541</v>
+        <v>4.67675256729126</v>
       </c>
       <c r="H438" t="n">
         <v>13127</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.58487033843994</v>
+        <v>4.5848708152771</v>
       </c>
       <c r="H439" t="n">
         <v>4452</v>
@@ -13129,7 +13129,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>4.57568264007568</v>
+        <v>4.57568311691284</v>
       </c>
       <c r="H440" t="n">
         <v>3846</v>
@@ -13245,7 +13245,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H444" t="n">
         <v>14966</v>
@@ -13274,7 +13274,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760429382324</v>
       </c>
       <c r="H445" t="n">
         <v>10951</v>
@@ -13303,7 +13303,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H446" t="n">
         <v>2659</v>
@@ -13390,7 +13390,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H449" t="n">
         <v>13181</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13448,7 +13448,7 @@
         <v>5.05000019073486</v>
       </c>
       <c r="G451" t="n">
-        <v>4.63999938964844</v>
+        <v>4.6399998664856</v>
       </c>
       <c r="H451" t="n">
         <v>15337</v>
@@ -13477,7 +13477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948509216309</v>
+        <v>4.41948413848877</v>
       </c>
       <c r="H452" t="n">
         <v>45286</v>
@@ -13506,7 +13506,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760429382324</v>
       </c>
       <c r="H453" t="n">
         <v>24237</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001981735229</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13680,7 +13680,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47461366653442</v>
+        <v>4.47461318969727</v>
       </c>
       <c r="H459" t="n">
         <v>11746</v>
@@ -13709,7 +13709,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.45623683929443</v>
+        <v>4.45623731613159</v>
       </c>
       <c r="H460" t="n">
         <v>2411</v>
@@ -13825,7 +13825,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G464" t="n">
-        <v>4.60324764251709</v>
+        <v>4.60324716567993</v>
       </c>
       <c r="H464" t="n">
         <v>5765</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -13970,7 +13970,7 @@
         <v>4.875</v>
       </c>
       <c r="G469" t="n">
-        <v>4.47920751571655</v>
+        <v>4.47920799255371</v>
       </c>
       <c r="H469" t="n">
         <v>1653</v>
@@ -14028,7 +14028,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34597969055176</v>
+        <v>4.34598016738892</v>
       </c>
       <c r="H471" t="n">
         <v>3835</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001981735229</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14260,7 +14260,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H479" t="n">
         <v>3457</v>
@@ -14289,7 +14289,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H480" t="n">
         <v>8400</v>
@@ -14318,7 +14318,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22193956375122</v>
+        <v>4.22194004058838</v>
       </c>
       <c r="H481" t="n">
         <v>10620</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332696914673</v>
+        <v>3.92332625389099</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14434,7 +14434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251466751099</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H485" t="n">
         <v>4207</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845554351807</v>
+        <v>3.97845506668091</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14492,7 +14492,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.9738609790802</v>
+        <v>3.97386145591736</v>
       </c>
       <c r="H487" t="n">
         <v>7176</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469275474548</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14608,7 +14608,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G491" t="n">
-        <v>3.82225728034973</v>
+        <v>3.82225680351257</v>
       </c>
       <c r="H491" t="n">
         <v>2924</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144521713257</v>
+        <v>3.83144569396973</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469275474548</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251466751099</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H497" t="n">
         <v>8274</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520824432373</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14956,7 +14956,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061344146729</v>
+        <v>4.01061296463013</v>
       </c>
       <c r="H503" t="n">
         <v>31005</v>
@@ -15014,7 +15014,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H505" t="n">
         <v>17677</v>
@@ -15043,7 +15043,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>4.3230094909668</v>
+        <v>4.32300996780396</v>
       </c>
       <c r="H506" t="n">
         <v>4619</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H508" t="n">
         <v>3615</v>
@@ -15159,7 +15159,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H510" t="n">
         <v>6857</v>
@@ -15188,7 +15188,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326759338379</v>
+        <v>4.43326663970947</v>
       </c>
       <c r="H511" t="n">
         <v>4220</v>
@@ -15304,7 +15304,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H515" t="n">
         <v>1906</v>
@@ -15362,7 +15362,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G517" t="n">
-        <v>4.391921043396</v>
+        <v>4.39192056655884</v>
       </c>
       <c r="H517" t="n">
         <v>7436</v>
@@ -15478,7 +15478,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>4.62162351608276</v>
+        <v>4.62162399291992</v>
       </c>
       <c r="H521" t="n">
         <v>14852</v>
@@ -15652,7 +15652,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>4.81457424163818</v>
+        <v>4.81457328796387</v>
       </c>
       <c r="H527" t="n">
         <v>9827</v>
@@ -15826,7 +15826,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.90645551681519</v>
+        <v>4.90645503997803</v>
       </c>
       <c r="H533" t="n">
         <v>5784</v>
@@ -15884,7 +15884,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>5.09021711349487</v>
+        <v>5.09021759033203</v>
       </c>
       <c r="H535" t="n">
         <v>24385</v>
@@ -15913,7 +15913,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G536" t="n">
-        <v>5.11778211593628</v>
+        <v>5.11778259277344</v>
       </c>
       <c r="H536" t="n">
         <v>8803</v>
@@ -15942,7 +15942,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>5.0167121887207</v>
+        <v>5.01671314239502</v>
       </c>
       <c r="H537" t="n">
         <v>6975</v>
@@ -15971,7 +15971,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G538" t="n">
-        <v>5.03508853912354</v>
+        <v>5.03508901596069</v>
       </c>
       <c r="H538" t="n">
         <v>4031</v>
@@ -16058,7 +16058,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G541" t="n">
-        <v>4.88807916641235</v>
+        <v>4.8880786895752</v>
       </c>
       <c r="H541" t="n">
         <v>3175</v>
@@ -16087,7 +16087,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86970329284668</v>
+        <v>4.86970281600952</v>
       </c>
       <c r="H542" t="n">
         <v>3105</v>
@@ -16116,7 +16116,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619789123535</v>
+        <v>4.79619741439819</v>
       </c>
       <c r="H543" t="n">
         <v>1688</v>
@@ -16232,7 +16232,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H547" t="n">
         <v>6999</v>
@@ -16261,7 +16261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029691696167</v>
       </c>
       <c r="H548" t="n">
         <v>5791</v>
@@ -16290,7 +16290,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>4.26328706741333</v>
+        <v>4.26328659057617</v>
       </c>
       <c r="H549" t="n">
         <v>8198</v>
@@ -16348,7 +16348,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.20815801620483</v>
+        <v>4.20815753936768</v>
       </c>
       <c r="H551" t="n">
         <v>18005</v>
@@ -16377,7 +16377,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G552" t="n">
-        <v>4.31382131576538</v>
+        <v>4.31382179260254</v>
       </c>
       <c r="H552" t="n">
         <v>11658</v>
@@ -16406,7 +16406,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247476577759</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H553" t="n">
         <v>1650</v>
@@ -16464,7 +16464,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>4.09790086746216</v>
+        <v>4.097900390625</v>
       </c>
       <c r="H555" t="n">
         <v>11397</v>
@@ -16522,7 +16522,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546491622925</v>
+        <v>4.12546539306641</v>
       </c>
       <c r="H557" t="n">
         <v>7122</v>
@@ -16725,7 +16725,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>3.69362378120422</v>
+        <v>3.69362330436707</v>
       </c>
       <c r="H564" t="n">
         <v>10513</v>
@@ -16754,7 +16754,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65687108039856</v>
+        <v>3.65687131881714</v>
       </c>
       <c r="H565" t="n">
         <v>350</v>
@@ -16841,7 +16841,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G568" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H568" t="n">
         <v>8477</v>
@@ -16899,7 +16899,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H570" t="n">
         <v>38613</v>
@@ -16928,7 +16928,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G571" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H571" t="n">
         <v>7214</v>
@@ -17015,7 +17015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152430534363</v>
       </c>
       <c r="H574" t="n">
         <v>22621</v>
@@ -17102,7 +17102,7 @@
         <v>3.5</v>
       </c>
       <c r="G577" t="n">
-        <v>3.21584129333496</v>
+        <v>3.21584153175354</v>
       </c>
       <c r="H577" t="n">
         <v>7340</v>
@@ -17131,7 +17131,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G578" t="n">
-        <v>3.06883144378662</v>
+        <v>3.0688316822052</v>
       </c>
       <c r="H578" t="n">
         <v>17701</v>
@@ -17189,7 +17189,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G580" t="n">
-        <v>3.03207898139954</v>
+        <v>3.03207921981812</v>
       </c>
       <c r="H580" t="n">
         <v>4602</v>
@@ -17218,7 +17218,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>3.05964350700378</v>
+        <v>3.05964326858521</v>
       </c>
       <c r="H581" t="n">
         <v>5248</v>
@@ -17305,7 +17305,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G584" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H584" t="n">
         <v>25151</v>
@@ -17392,7 +17392,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H587" t="n">
         <v>4318</v>
@@ -17450,7 +17450,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G589" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H589" t="n">
         <v>11400</v>
@@ -17479,7 +17479,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.9417028427124</v>
+        <v>3.94170308113098</v>
       </c>
       <c r="H590" t="n">
         <v>70490</v>
@@ -17508,7 +17508,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712822914124</v>
       </c>
       <c r="H591" t="n">
         <v>12175</v>
@@ -17537,7 +17537,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712822914124</v>
       </c>
       <c r="H592" t="n">
         <v>9692</v>
@@ -17566,7 +17566,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G593" t="n">
-        <v>3.70281195640564</v>
+        <v>3.70281171798706</v>
       </c>
       <c r="H593" t="n">
         <v>11590</v>
@@ -17595,7 +17595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904940605164</v>
+        <v>3.51904916763306</v>
       </c>
       <c r="H594" t="n">
         <v>20677</v>
@@ -17682,7 +17682,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H597" t="n">
         <v>7488</v>
@@ -17711,7 +17711,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H598" t="n">
         <v>3630</v>
@@ -17740,7 +17740,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G599" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H599" t="n">
         <v>8376</v>
@@ -17827,7 +17827,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152430534363</v>
       </c>
       <c r="H602" t="n">
         <v>23557</v>
@@ -17914,7 +17914,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>3.30772233009338</v>
+        <v>3.30772280693054</v>
       </c>
       <c r="H605" t="n">
         <v>3361</v>
@@ -17943,7 +17943,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015780448914</v>
+        <v>3.28015828132629</v>
       </c>
       <c r="H606" t="n">
         <v>4093</v>
@@ -17972,7 +17972,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>3.32609891891479</v>
+        <v>3.32609868049622</v>
       </c>
       <c r="H607" t="n">
         <v>1705</v>
@@ -18059,7 +18059,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>3.18827724456787</v>
+        <v>3.18827700614929</v>
       </c>
       <c r="H610" t="n">
         <v>6723</v>
@@ -18088,7 +18088,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990113258362</v>
+        <v>3.16990089416504</v>
       </c>
       <c r="H611" t="n">
         <v>4629</v>
@@ -18117,7 +18117,7 @@
         <v>3.5</v>
       </c>
       <c r="G612" t="n">
-        <v>3.21584129333496</v>
+        <v>3.21584153175354</v>
       </c>
       <c r="H612" t="n">
         <v>1010</v>
@@ -18146,7 +18146,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233660697937</v>
+        <v>3.14233636856079</v>
       </c>
       <c r="H613" t="n">
         <v>1790</v>
@@ -18233,7 +18233,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152430534363</v>
       </c>
       <c r="H616" t="n">
         <v>4300</v>
@@ -18291,7 +18291,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.11477208137512</v>
+        <v>3.1147723197937</v>
       </c>
       <c r="H618" t="n">
         <v>1345</v>
@@ -18349,7 +18349,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H620" t="n">
         <v>26152</v>
@@ -18407,7 +18407,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>2.84831643104553</v>
+        <v>2.84831666946411</v>
       </c>
       <c r="H622" t="n">
         <v>13986</v>
@@ -18436,7 +18436,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>2.89425730705261</v>
+        <v>2.89425706863403</v>
       </c>
       <c r="H623" t="n">
         <v>25740</v>
@@ -18523,7 +18523,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H626" t="n">
         <v>14381</v>
@@ -18639,7 +18639,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G630" t="n">
-        <v>3.03276824951172</v>
+        <v>3.03276801109314</v>
       </c>
       <c r="H630" t="n">
         <v>1951</v>
@@ -18987,7 +18987,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110457420349</v>
+        <v>2.52110481262207</v>
       </c>
       <c r="H642" t="n">
         <v>95598</v>
@@ -19016,7 +19016,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H643" t="n">
         <v>60892</v>
@@ -19074,7 +19074,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040766716003</v>
+        <v>2.53040790557861</v>
       </c>
       <c r="H645" t="n">
         <v>12711</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761932373047</v>
+        <v>2.56761980056763</v>
       </c>
       <c r="H646" t="n">
         <v>8131</v>
@@ -19132,7 +19132,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901361465454</v>
+        <v>2.54901385307312</v>
       </c>
       <c r="H647" t="n">
         <v>4920</v>
@@ -19190,7 +19190,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>2.48389315605164</v>
+        <v>2.48389291763306</v>
       </c>
       <c r="H649" t="n">
         <v>18231</v>
@@ -19248,7 +19248,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H651" t="n">
         <v>18483</v>
@@ -19277,7 +19277,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.39086318016052</v>
+        <v>2.39086294174194</v>
       </c>
       <c r="H652" t="n">
         <v>8591</v>
@@ -19335,7 +19335,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H654" t="n">
         <v>19145</v>
@@ -19364,7 +19364,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H655" t="n">
         <v>11634</v>
@@ -19393,7 +19393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>2.40946936607361</v>
+        <v>2.40946912765503</v>
       </c>
       <c r="H656" t="n">
         <v>10081</v>
@@ -19422,7 +19422,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G657" t="n">
-        <v>2.39086318016052</v>
+        <v>2.39086294174194</v>
       </c>
       <c r="H657" t="n">
         <v>4696</v>
@@ -19509,7 +19509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H660" t="n">
         <v>4896</v>
@@ -19683,7 +19683,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H666" t="n">
         <v>5645</v>
@@ -19712,7 +19712,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H667" t="n">
         <v>3080</v>
@@ -19741,7 +19741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G668" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H668" t="n">
         <v>2684</v>
@@ -19770,7 +19770,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180171966553</v>
+        <v>2.51180195808411</v>
       </c>
       <c r="H669" t="n">
         <v>22344</v>
@@ -19799,7 +19799,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H670" t="n">
         <v>10500</v>
@@ -19886,7 +19886,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H673" t="n">
         <v>536</v>
@@ -19915,7 +19915,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.40946936607361</v>
+        <v>2.40946912765503</v>
       </c>
       <c r="H674" t="n">
         <v>1569</v>
@@ -20002,7 +20002,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H677" t="n">
         <v>13195</v>
@@ -20060,7 +20060,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H679" t="n">
         <v>10826</v>
@@ -20089,7 +20089,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20118,7 +20118,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H681" t="n">
         <v>3858</v>
@@ -20147,7 +20147,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.46528720855713</v>
+        <v>2.46528697013855</v>
       </c>
       <c r="H682" t="n">
         <v>8637</v>
@@ -20176,7 +20176,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.29783368110657</v>
+        <v>2.29783344268799</v>
       </c>
       <c r="H683" t="n">
         <v>7367</v>
@@ -20205,7 +20205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.4931960105896</v>
+        <v>2.49319577217102</v>
       </c>
       <c r="H684" t="n">
         <v>12276</v>
@@ -20234,7 +20234,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35365128517151</v>
+        <v>2.35365104675293</v>
       </c>
       <c r="H685" t="n">
         <v>24371</v>
@@ -20350,7 +20350,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G689" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H689" t="n">
         <v>73294</v>
@@ -20379,7 +20379,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G690" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H690" t="n">
         <v>18911</v>
@@ -20437,7 +20437,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G692" t="n">
-        <v>1.1675226688385</v>
+        <v>1.16752278804779</v>
       </c>
       <c r="H692" t="n">
         <v>88258</v>
@@ -20466,7 +20466,7 @@
         <v>1.5</v>
       </c>
       <c r="G693" t="n">
-        <v>1.39544546604156</v>
+        <v>1.39544534683228</v>
       </c>
       <c r="H693" t="n">
         <v>126661</v>
@@ -20524,7 +20524,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H695" t="n">
         <v>235716</v>
@@ -20553,7 +20553,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H696" t="n">
         <v>232613</v>
@@ -20611,7 +20611,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>1.58150494098663</v>
+        <v>1.58150482177734</v>
       </c>
       <c r="H698" t="n">
         <v>54891</v>
@@ -20640,7 +20640,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G699" t="n">
-        <v>1.54429292678833</v>
+        <v>1.54429304599762</v>
       </c>
       <c r="H699" t="n">
         <v>36020</v>
@@ -20669,7 +20669,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.51638412475586</v>
+        <v>1.51638400554657</v>
       </c>
       <c r="H700" t="n">
         <v>7380</v>
@@ -20814,7 +20814,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.44196021556854</v>
+        <v>1.44196033477783</v>
       </c>
       <c r="H705" t="n">
         <v>12919</v>
@@ -20959,7 +20959,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>1.69779205322266</v>
+        <v>1.69779193401337</v>
       </c>
       <c r="H710" t="n">
         <v>5655</v>
@@ -20988,7 +20988,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H711" t="n">
         <v>6528</v>
@@ -21017,7 +21017,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H712" t="n">
         <v>2874</v>
@@ -21046,7 +21046,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G713" t="n">
-        <v>1.51638412475586</v>
+        <v>1.51638400554657</v>
       </c>
       <c r="H713" t="n">
         <v>7640</v>
@@ -21075,7 +21075,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.58150494098663</v>
+        <v>1.58150482177734</v>
       </c>
       <c r="H714" t="n">
         <v>5490</v>
@@ -21104,7 +21104,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G715" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H715" t="n">
         <v>9473</v>
@@ -21133,7 +21133,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G716" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H716" t="n">
         <v>14629</v>
@@ -21191,7 +21191,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G718" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H718" t="n">
         <v>5148</v>
@@ -21278,7 +21278,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G721" t="n">
-        <v>1.60476243495941</v>
+        <v>1.60476231575012</v>
       </c>
       <c r="H721" t="n">
         <v>5640</v>
@@ -21336,7 +21336,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H723" t="n">
         <v>5633</v>
@@ -21365,7 +21365,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="n">
-        <v>2.02804756164551</v>
+        <v>2.02804732322693</v>
       </c>
       <c r="H724" t="n">
         <v>114000</v>
@@ -21452,7 +21452,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H727" t="n">
         <v>67002</v>
@@ -21684,7 +21684,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H735" t="n">
         <v>53817</v>
@@ -21713,7 +21713,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H736" t="n">
         <v>25550</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H738" t="n">
         <v>41345</v>
@@ -21800,7 +21800,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550061225891</v>
+        <v>2.19550085067749</v>
       </c>
       <c r="H739" t="n">
         <v>13585</v>
@@ -21887,7 +21887,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H742" t="n">
         <v>4041</v>
@@ -21916,7 +21916,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H743" t="n">
         <v>27715</v>
@@ -21945,7 +21945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.1117742061615</v>
+        <v>2.11177396774292</v>
       </c>
       <c r="H744" t="n">
         <v>19716</v>
@@ -21974,7 +21974,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.00944137573242</v>
+        <v>2.00944185256958</v>
       </c>
       <c r="H745" t="n">
         <v>22944</v>
@@ -22090,7 +22090,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>2.335045337677</v>
+        <v>2.33504557609558</v>
       </c>
       <c r="H749" t="n">
         <v>46515</v>
@@ -22177,7 +22177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.21410703659058</v>
+        <v>2.214106798172</v>
       </c>
       <c r="H752" t="n">
         <v>18450</v>
@@ -22206,7 +22206,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.24201583862305</v>
+        <v>2.24201607704163</v>
       </c>
       <c r="H753" t="n">
         <v>7610</v>
@@ -22293,7 +22293,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H756" t="n">
         <v>6173</v>
@@ -22322,7 +22322,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H757" t="n">
         <v>9025</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H760" t="n">
         <v>6602</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H761" t="n">
         <v>2731</v>
@@ -22496,7 +22496,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>2.15828895568848</v>
+        <v>2.1582887172699</v>
       </c>
       <c r="H763" t="n">
         <v>5178</v>
@@ -22525,7 +22525,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H764" t="n">
         <v>5171</v>
@@ -22554,7 +22554,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.1768946647644</v>
+        <v>2.17689490318298</v>
       </c>
       <c r="H765" t="n">
         <v>4690</v>
@@ -22699,7 +22699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H770" t="n">
         <v>1304</v>
@@ -22728,7 +22728,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H771" t="n">
         <v>5621</v>
@@ -22757,7 +22757,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H772" t="n">
         <v>12685</v>
@@ -22931,7 +22931,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G778" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H778" t="n">
         <v>10623</v>
@@ -22960,7 +22960,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>1.97222936153412</v>
+        <v>1.9722295999527</v>
       </c>
       <c r="H779" t="n">
         <v>6646</v>
@@ -22989,7 +22989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>2.04665350914001</v>
+        <v>2.04665327072144</v>
       </c>
       <c r="H780" t="n">
         <v>3975</v>
@@ -23047,7 +23047,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H782" t="n">
         <v>7820</v>
@@ -23105,7 +23105,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.9908355474472</v>
+        <v>1.99083566665649</v>
       </c>
       <c r="H784" t="n">
         <v>1181</v>
@@ -23192,7 +23192,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H787" t="n">
         <v>19192</v>
@@ -23250,7 +23250,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G789" t="n">
-        <v>2.02804756164551</v>
+        <v>2.02804732322693</v>
       </c>
       <c r="H789" t="n">
         <v>2761</v>
@@ -23308,7 +23308,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00944137573242</v>
+        <v>2.00944185256958</v>
       </c>
       <c r="H791" t="n">
         <v>2800</v>
@@ -23337,7 +23337,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>2.04665350914001</v>
+        <v>2.04665327072144</v>
       </c>
       <c r="H792" t="n">
         <v>7172</v>
@@ -23366,7 +23366,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H793" t="n">
         <v>8905</v>
@@ -23395,7 +23395,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153257369995</v>
       </c>
       <c r="H794" t="n">
         <v>13577</v>
@@ -23424,7 +23424,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H795" t="n">
         <v>8911</v>
@@ -23453,7 +23453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H796" t="n">
         <v>3170</v>
@@ -23482,7 +23482,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362365245819</v>
+        <v>1.95362341403961</v>
       </c>
       <c r="H797" t="n">
         <v>15172</v>
@@ -23569,7 +23569,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G800" t="n">
-        <v>1.90710890293121</v>
+        <v>1.90710866451263</v>
       </c>
       <c r="H800" t="n">
         <v>3251</v>
@@ -23801,7 +23801,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G808" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H808" t="n">
         <v>8701</v>
@@ -23859,7 +23859,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.64662551879883</v>
+        <v>1.64662563800812</v>
       </c>
       <c r="H810" t="n">
         <v>3970</v>
@@ -23917,7 +23917,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H812" t="n">
         <v>17120</v>
@@ -24091,7 +24091,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H818" t="n">
         <v>26987</v>
@@ -24120,7 +24120,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011088848114</v>
+        <v>1.60011076927185</v>
       </c>
       <c r="H819" t="n">
         <v>13128</v>
@@ -24265,7 +24265,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G824" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H824" t="n">
         <v>17867</v>
@@ -24294,7 +24294,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H825" t="n">
         <v>2580</v>
@@ -24439,7 +24439,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.83268511295319</v>
+        <v>1.83268523216248</v>
       </c>
       <c r="H830" t="n">
         <v>53960</v>
@@ -24584,7 +24584,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97222936153412</v>
+        <v>1.9722295999527</v>
       </c>
       <c r="H835" t="n">
         <v>50956</v>
@@ -24816,7 +24816,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G843" t="n">
-        <v>1.83733654022217</v>
+        <v>1.83733642101288</v>
       </c>
       <c r="H843" t="n">
         <v>3897</v>
@@ -24845,7 +24845,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G844" t="n">
-        <v>1.83733654022217</v>
+        <v>1.83733642101288</v>
       </c>
       <c r="H844" t="n">
         <v>3634</v>
@@ -25135,7 +25135,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.93501770496368</v>
+        <v>1.9350174665451</v>
       </c>
       <c r="H854" t="n">
         <v>16193</v>
@@ -25164,7 +25164,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G855" t="n">
-        <v>1.88850283622742</v>
+        <v>1.88850271701813</v>
       </c>
       <c r="H855" t="n">
         <v>15602</v>
@@ -25222,7 +25222,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G857" t="n">
-        <v>1.83733654022217</v>
+        <v>1.83733642101288</v>
       </c>
       <c r="H857" t="n">
         <v>12741</v>
@@ -25251,7 +25251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.8698970079422</v>
+        <v>1.86989688873291</v>
       </c>
       <c r="H858" t="n">
         <v>2711</v>
@@ -25338,7 +25338,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G861" t="n">
-        <v>2.02804756164551</v>
+        <v>2.02804732322693</v>
       </c>
       <c r="H861" t="n">
         <v>34243</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.18991041183472</v>
+        <v>2.18991017341614</v>
       </c>
       <c r="H864" t="n">
         <v>29824</v>
@@ -25454,7 +25454,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>2.18038892745972</v>
+        <v>2.1803891658783</v>
       </c>
       <c r="H865" t="n">
         <v>18169</v>
@@ -25541,7 +25541,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G868" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H868" t="n">
         <v>12463</v>
@@ -25599,7 +25599,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H870" t="n">
         <v>14204</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.98044073581696</v>
+        <v>1.98044061660767</v>
       </c>
       <c r="H871" t="n">
         <v>10741</v>
@@ -25686,7 +25686,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H873" t="n">
         <v>1780</v>
@@ -25715,7 +25715,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H874" t="n">
         <v>11963</v>
@@ -25860,7 +25860,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H879" t="n">
         <v>9646</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H881" t="n">
         <v>4363</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98044073581696</v>
+        <v>1.98044061660767</v>
       </c>
       <c r="H882" t="n">
         <v>3757</v>
@@ -26005,7 +26005,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.99948346614838</v>
+        <v>1.9994832277298</v>
       </c>
       <c r="H884" t="n">
         <v>3933</v>
@@ -26092,7 +26092,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H887" t="n">
         <v>1502</v>
@@ -26121,7 +26121,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H888" t="n">
         <v>2991</v>
@@ -26150,7 +26150,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H889" t="n">
         <v>500</v>
@@ -26179,7 +26179,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H891" t="n">
         <v>1750</v>
@@ -26237,7 +26237,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>1.99948346614838</v>
+        <v>1.9994832277298</v>
       </c>
       <c r="H892" t="n">
         <v>3562</v>
@@ -26295,7 +26295,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H894" t="n">
         <v>2771</v>
@@ -27542,7 +27542,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.69480013847351</v>
+        <v>1.6948002576828</v>
       </c>
       <c r="H937" t="n">
         <v>12954</v>
@@ -27716,7 +27716,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G943" t="n">
-        <v>1.69480013847351</v>
+        <v>1.6948002576828</v>
       </c>
       <c r="H943" t="n">
         <v>13769</v>
@@ -27745,7 +27745,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.6186295747757</v>
+        <v>1.61862945556641</v>
       </c>
       <c r="H944" t="n">
         <v>22282</v>
@@ -27774,7 +27774,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G945" t="n">
-        <v>1.54245865345001</v>
+        <v>1.54245853424072</v>
       </c>
       <c r="H945" t="n">
         <v>13946</v>
@@ -27890,7 +27890,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.35679221153259</v>
+        <v>1.35679233074188</v>
       </c>
       <c r="H949" t="n">
         <v>12733</v>
@@ -27948,7 +27948,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G951" t="n">
-        <v>1.31394612789154</v>
+        <v>1.31394624710083</v>
       </c>
       <c r="H951" t="n">
         <v>18171</v>
@@ -28006,7 +28006,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G953" t="n">
-        <v>1.31394612789154</v>
+        <v>1.31394624710083</v>
       </c>
       <c r="H953" t="n">
         <v>17476</v>
@@ -28122,7 +28122,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>1.34727084636688</v>
+        <v>1.34727096557617</v>
       </c>
       <c r="H957" t="n">
         <v>10390</v>
@@ -28151,7 +28151,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H958" t="n">
         <v>120160</v>
@@ -28296,7 +28296,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G963" t="n">
-        <v>1.02830576896667</v>
+        <v>1.02830588817596</v>
       </c>
       <c r="H963" t="n">
         <v>70383</v>
@@ -28354,7 +28354,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H965" t="n">
         <v>11079</v>
@@ -28470,7 +28470,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G969" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H969" t="n">
         <v>5589</v>
@@ -28644,7 +28644,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G975" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H975" t="n">
         <v>16278</v>
@@ -28876,7 +28876,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G983" t="n">
-        <v>0.847400069236755</v>
+        <v>0.8474001288414</v>
       </c>
       <c r="H983" t="n">
         <v>11888</v>
@@ -28934,7 +28934,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G985" t="n">
-        <v>0.934996485710144</v>
+        <v>0.934996545314789</v>
       </c>
       <c r="H985" t="n">
         <v>22093</v>
@@ -28963,7 +28963,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G986" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H986" t="n">
         <v>24435</v>
@@ -29108,7 +29108,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H991" t="n">
         <v>4904</v>
@@ -29137,7 +29137,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H992" t="n">
         <v>18073</v>
@@ -29253,7 +29253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G996" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H996" t="n">
         <v>11904</v>
@@ -29282,7 +29282,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H997" t="n">
         <v>4540</v>
@@ -29427,7 +29427,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1002" t="n">
         <v>2974</v>
@@ -29485,7 +29485,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.02830576896667</v>
+        <v>1.02830588817596</v>
       </c>
       <c r="H1004" t="n">
         <v>11264</v>
@@ -29630,7 +29630,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1009" t="n">
         <v>18426</v>
@@ -29659,7 +29659,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1010" t="n">
         <v>2505</v>
@@ -29978,7 +29978,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1021" t="n">
         <v>5361</v>
@@ -30036,7 +30036,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1026" t="n">
         <v>3669</v>
@@ -30152,7 +30152,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1027" t="n">
         <v>8946</v>
@@ -30268,7 +30268,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1031" t="n">
         <v>6700</v>
@@ -30326,7 +30326,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1033" t="n">
         <v>2860</v>
@@ -30384,7 +30384,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1035" t="n">
         <v>7202</v>
@@ -30413,7 +30413,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1036" t="n">
         <v>3000</v>
@@ -30442,7 +30442,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1037" t="n">
         <v>3042</v>
@@ -30558,7 +30558,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1041" t="n">
         <v>702</v>
@@ -30616,7 +30616,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1043" t="n">
         <v>5703</v>
@@ -30674,7 +30674,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1045" t="n">
         <v>3810</v>
@@ -30703,7 +30703,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1046" t="n">
         <v>3045</v>
@@ -30732,7 +30732,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1047" t="n">
         <v>4337</v>
@@ -30993,7 +30993,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.0473484992981</v>
+        <v>1.04734838008881</v>
       </c>
       <c r="H1056" t="n">
         <v>15939</v>
@@ -31138,7 +31138,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.0473484992981</v>
+        <v>1.04734838008881</v>
       </c>
       <c r="H1061" t="n">
         <v>5653</v>
@@ -31225,7 +31225,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.999741733074188</v>
+        <v>0.999741613864899</v>
       </c>
       <c r="H1064" t="n">
         <v>7815</v>
@@ -31254,7 +31254,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.01878440380096</v>
+        <v>1.01878452301025</v>
       </c>
       <c r="H1065" t="n">
         <v>2000</v>
@@ -31312,7 +31312,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.00926291942596</v>
+        <v>1.00926303863525</v>
       </c>
       <c r="H1067" t="n">
         <v>2310</v>
@@ -31341,7 +31341,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00926291942596</v>
+        <v>1.00926303863525</v>
       </c>
       <c r="H1068" t="n">
         <v>8960</v>
@@ -31370,7 +31370,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1069" t="n">
         <v>9201</v>
@@ -31428,7 +31428,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.885485529899597</v>
+        <v>0.885485470294952</v>
       </c>
       <c r="H1071" t="n">
         <v>7123</v>
@@ -31834,7 +31834,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1085" t="n">
         <v>14616</v>
@@ -31863,7 +31863,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.999741733074188</v>
+        <v>0.999741613864899</v>
       </c>
       <c r="H1086" t="n">
         <v>7925</v>
@@ -31979,7 +31979,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.975938379764557</v>
+        <v>0.975938320159912</v>
       </c>
       <c r="H1090" t="n">
         <v>1503</v>
@@ -32008,7 +32008,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.990220367908478</v>
+        <v>0.990220308303833</v>
       </c>
       <c r="H1091" t="n">
         <v>4143</v>
@@ -32037,7 +32037,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.975938379764557</v>
+        <v>0.975938320159912</v>
       </c>
       <c r="H1092" t="n">
         <v>4779</v>
@@ -32095,7 +32095,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1094" t="n">
         <v>8025</v>
@@ -32182,7 +32182,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.940709352493286</v>
+        <v>0.940709292888641</v>
       </c>
       <c r="H1097" t="n">
         <v>7780</v>
@@ -32327,7 +32327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1102" t="n">
         <v>114066</v>
@@ -32356,7 +32356,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1103" t="n">
         <v>155001</v>
@@ -32414,7 +32414,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1105" t="n">
         <v>9642</v>
@@ -32443,7 +32443,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14732265472412</v>
+        <v>1.14732277393341</v>
       </c>
       <c r="H1106" t="n">
         <v>29380</v>
@@ -32501,7 +32501,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1108" t="n">
         <v>51439</v>
@@ -32559,7 +32559,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1110" t="n">
         <v>7650</v>
@@ -32588,7 +32588,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1111" t="n">
         <v>5770</v>
@@ -32646,7 +32646,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1113" t="n">
         <v>10113</v>
@@ -32704,7 +32704,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1115" t="n">
         <v>12644</v>
@@ -32733,7 +32733,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1116" t="n">
         <v>8938</v>
@@ -32849,7 +32849,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1120" t="n">
         <v>9373</v>
@@ -32878,7 +32878,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1121" t="n">
         <v>12172</v>
@@ -33023,7 +33023,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.20445072650909</v>
+        <v>1.2044506072998</v>
       </c>
       <c r="H1126" t="n">
         <v>6943</v>
@@ -33052,7 +33052,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.20921146869659</v>
+        <v>1.2092113494873</v>
       </c>
       <c r="H1127" t="n">
         <v>7459</v>
@@ -33139,7 +33139,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.20445072650909</v>
+        <v>1.2044506072998</v>
       </c>
       <c r="H1130" t="n">
         <v>7350</v>
@@ -33197,7 +33197,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1132" t="n">
         <v>14474</v>
@@ -42802,6 +42802,35 @@
         <v>28895</v>
       </c>
       <c r="I1463" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1464" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1464" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>0.720000028610229</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>15180</v>
+      </c>
+      <c r="I1464" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -572,7 +572,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G7" t="n">
-        <v>3.53357768058777</v>
+        <v>3.53357744216919</v>
       </c>
       <c r="H7" t="n">
         <v>623000</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H11" t="n">
         <v>296000</v>
@@ -717,7 +717,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.60121464729309</v>
+        <v>3.60121512413025</v>
       </c>
       <c r="H12" t="n">
         <v>96000</v>
@@ -746,7 +746,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5737943649292</v>
+        <v>3.57379412651062</v>
       </c>
       <c r="H13" t="n">
         <v>75000</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583249092102</v>
+        <v>3.44583225250244</v>
       </c>
       <c r="H16" t="n">
         <v>29000</v>
@@ -862,7 +862,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G17" t="n">
-        <v>3.50981283187866</v>
+        <v>3.50981307029724</v>
       </c>
       <c r="H17" t="n">
         <v>74000</v>
@@ -978,7 +978,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.2630295753479</v>
+        <v>3.26302933692932</v>
       </c>
       <c r="H21" t="n">
         <v>78000</v>
@@ -1036,7 +1036,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>3.40927195549011</v>
+        <v>3.40927171707153</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.32701086997986</v>
+        <v>3.3270103931427</v>
       </c>
       <c r="H24" t="n">
         <v>30000</v>
@@ -1123,7 +1123,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>3.31787061691284</v>
+        <v>3.31787037849426</v>
       </c>
       <c r="H26" t="n">
         <v>34000</v>
@@ -1152,7 +1152,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248798370361</v>
+        <v>3.16248822212219</v>
       </c>
       <c r="H27" t="n">
         <v>62000</v>
@@ -1181,7 +1181,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764718055725</v>
+        <v>3.10764741897583</v>
       </c>
       <c r="H28" t="n">
         <v>52000</v>
@@ -1239,7 +1239,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15334796905518</v>
+        <v>3.15334820747375</v>
       </c>
       <c r="H30" t="n">
         <v>145000</v>
@@ -1268,7 +1268,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15334796905518</v>
+        <v>3.15334820747375</v>
       </c>
       <c r="H31" t="n">
         <v>36000</v>
@@ -1384,7 +1384,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0893669128418</v>
+        <v>3.08936715126038</v>
       </c>
       <c r="H35" t="n">
         <v>9000</v>
@@ -1500,7 +1500,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>3.32701086997986</v>
+        <v>3.3270103931427</v>
       </c>
       <c r="H39" t="n">
         <v>52000</v>
@@ -1529,7 +1529,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.31787061691284</v>
+        <v>3.31787037849426</v>
       </c>
       <c r="H40" t="n">
         <v>48000</v>
@@ -1558,7 +1558,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.50067281723022</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H41" t="n">
         <v>172000</v>
@@ -1645,7 +1645,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.65605568885803</v>
+        <v>3.65605545043945</v>
       </c>
       <c r="H44" t="n">
         <v>80000</v>
@@ -1703,7 +1703,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72003674507141</v>
+        <v>3.72003698348999</v>
       </c>
       <c r="H46" t="n">
         <v>44000</v>
@@ -1732,7 +1732,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175647735596</v>
+        <v>3.70175671577454</v>
       </c>
       <c r="H47" t="n">
         <v>30000</v>
@@ -1790,7 +1790,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H49" t="n">
         <v>51000</v>
@@ -1848,7 +1848,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H51" t="n">
         <v>21000</v>
@@ -1906,7 +1906,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H53" t="n">
         <v>35000</v>
@@ -2022,7 +2022,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G57" t="n">
-        <v>3.52809357643127</v>
+        <v>3.5280933380127</v>
       </c>
       <c r="H57" t="n">
         <v>4000</v>
@@ -2138,7 +2138,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293437957764</v>
+        <v>3.58293485641479</v>
       </c>
       <c r="H61" t="n">
         <v>16000</v>
@@ -2196,7 +2196,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207439422607</v>
+        <v>3.59207463264465</v>
       </c>
       <c r="H63" t="n">
         <v>11000</v>
@@ -2225,7 +2225,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G64" t="n">
-        <v>3.60121464729309</v>
+        <v>3.60121512413025</v>
       </c>
       <c r="H64" t="n">
         <v>13000</v>
@@ -2283,7 +2283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.50067281723022</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.50067281723022</v>
+        <v>3.50067329406738</v>
       </c>
       <c r="H67" t="n">
         <v>24000</v>
@@ -2341,7 +2341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011885643005</v>
+        <v>3.62011861801147</v>
       </c>
       <c r="H68" t="n">
         <v>10000</v>
@@ -2370,7 +2370,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2399,7 +2399,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H70" t="n">
         <v>14000</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H71" t="n">
         <v>9000</v>
@@ -2457,7 +2457,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H72" t="n">
         <v>23000</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>3.44554424285889</v>
+        <v>3.44554448127747</v>
       </c>
       <c r="H74" t="n">
         <v>9000</v>
@@ -2544,7 +2544,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.41797995567322</v>
+        <v>3.4179801940918</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2631,7 +2631,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H78" t="n">
         <v>10500</v>
@@ -2660,7 +2660,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>3.50067281723022</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H79" t="n">
         <v>11000</v>
@@ -2718,7 +2718,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G81" t="n">
-        <v>3.50067281723022</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H81" t="n">
         <v>4500</v>
@@ -2921,7 +2921,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.65687131881714</v>
+        <v>3.65687108039856</v>
       </c>
       <c r="H88" t="n">
         <v>31500</v>
@@ -3037,7 +3037,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G92" t="n">
-        <v>3.70281171798706</v>
+        <v>3.70281195640564</v>
       </c>
       <c r="H92" t="n">
         <v>18000</v>
@@ -3066,7 +3066,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>3.74875235557556</v>
+        <v>3.74875211715698</v>
       </c>
       <c r="H93" t="n">
         <v>51500</v>
@@ -3095,7 +3095,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251490592957</v>
       </c>
       <c r="H94" t="n">
         <v>132500</v>
@@ -3124,7 +3124,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G95" t="n">
-        <v>3.89576172828674</v>
+        <v>3.89576148986816</v>
       </c>
       <c r="H95" t="n">
         <v>105500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520729064941</v>
+        <v>4.01520776748657</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3269,7 +3269,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910823822021</v>
       </c>
       <c r="H100" t="n">
         <v>243500</v>
@@ -3327,7 +3327,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>5.14534664154053</v>
+        <v>5.14534616470337</v>
       </c>
       <c r="H102" t="n">
         <v>73000</v>
@@ -3385,7 +3385,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G104" t="n">
-        <v>5.31073188781738</v>
+        <v>5.31073236465454</v>
       </c>
       <c r="H104" t="n">
         <v>68500</v>
@@ -3530,7 +3530,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>5.49449443817139</v>
+        <v>5.49449491500854</v>
       </c>
       <c r="H109" t="n">
         <v>40500</v>
@@ -3559,7 +3559,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124761581421</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H110" t="n">
         <v>38500</v>
@@ -3617,7 +3617,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.00134563446045</v>
+        <v>7.00134611129761</v>
       </c>
       <c r="H112" t="n">
         <v>689000</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3704,7 +3704,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237565994263</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H115" t="n">
         <v>297500</v>
@@ -3762,7 +3762,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>7.62613821029663</v>
+        <v>7.62613868713379</v>
       </c>
       <c r="H117" t="n">
         <v>118000</v>
@@ -3791,7 +3791,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>7.49750471115112</v>
+        <v>7.49750423431396</v>
       </c>
       <c r="H118" t="n">
         <v>22500</v>
@@ -3820,7 +3820,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G119" t="n">
-        <v>7.38724660873413</v>
+        <v>7.38724708557129</v>
       </c>
       <c r="H119" t="n">
         <v>101000</v>
@@ -4110,7 +4110,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>6.85433578491211</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4197,7 +4197,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G132" t="n">
-        <v>6.74407958984375</v>
+        <v>6.74407911300659</v>
       </c>
       <c r="H132" t="n">
         <v>13000</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4284,7 +4284,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H135" t="n">
         <v>150000</v>
@@ -4313,7 +4313,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G136" t="n">
-        <v>7.38724660873413</v>
+        <v>7.38724708557129</v>
       </c>
       <c r="H136" t="n">
         <v>68000</v>
@@ -4429,7 +4429,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237565994263</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H140" t="n">
         <v>13000</v>
@@ -4458,7 +4458,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>7.62613821029663</v>
+        <v>7.62613868713379</v>
       </c>
       <c r="H141" t="n">
         <v>64000</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938550949097</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4516,7 +4516,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>8.15904903411865</v>
+        <v>8.15904808044434</v>
       </c>
       <c r="H143" t="n">
         <v>145500</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366188049316</v>
+        <v>7.99366283416748</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4603,7 +4603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08554553985596</v>
+        <v>8.08554363250732</v>
       </c>
       <c r="H146" t="n">
         <v>55500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366188049316</v>
+        <v>7.99366283416748</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4748,7 +4748,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178203582764</v>
+        <v>7.90178251266479</v>
       </c>
       <c r="H151" t="n">
         <v>20500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4806,7 +4806,7 @@
         <v>8.5</v>
       </c>
       <c r="G153" t="n">
-        <v>7.80990028381348</v>
+        <v>7.80990076065063</v>
       </c>
       <c r="H153" t="n">
         <v>13500</v>
@@ -4951,7 +4951,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G158" t="n">
-        <v>7.79152345657349</v>
+        <v>7.79152297973633</v>
       </c>
       <c r="H158" t="n">
         <v>15500</v>
@@ -4980,7 +4980,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G159" t="n">
-        <v>7.79152345657349</v>
+        <v>7.79152297973633</v>
       </c>
       <c r="H159" t="n">
         <v>5500</v>
@@ -5009,7 +5009,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G160" t="n">
-        <v>7.64451360702515</v>
+        <v>7.64451456069946</v>
       </c>
       <c r="H160" t="n">
         <v>19000</v>
@@ -5038,7 +5038,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>7.62613821029663</v>
+        <v>7.62613868713379</v>
       </c>
       <c r="H161" t="n">
         <v>4000</v>
@@ -5067,7 +5067,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G162" t="n">
-        <v>7.68126630783081</v>
+        <v>7.68126678466797</v>
       </c>
       <c r="H162" t="n">
         <v>9500</v>
@@ -5096,7 +5096,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>7.49750471115112</v>
+        <v>7.49750423431396</v>
       </c>
       <c r="H163" t="n">
         <v>21000</v>
@@ -5125,7 +5125,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237565994263</v>
+        <v>7.44237613677979</v>
       </c>
       <c r="H164" t="n">
         <v>19000</v>
@@ -5241,7 +5241,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023771286011</v>
+        <v>7.24023723602295</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5270,7 +5270,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G169" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938550949097</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5386,7 +5386,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.36118793487549</v>
+        <v>8.3611888885498</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5473,7 +5473,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5502,7 +5502,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G177" t="n">
-        <v>7.68126630783081</v>
+        <v>7.68126678466797</v>
       </c>
       <c r="H177" t="n">
         <v>11500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5560,7 +5560,7 @@
         <v>8.5</v>
       </c>
       <c r="G179" t="n">
-        <v>7.80990028381348</v>
+        <v>7.80990076065063</v>
       </c>
       <c r="H179" t="n">
         <v>16500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.84665250778198</v>
+        <v>7.8466534614563</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H183" t="n">
         <v>33500</v>
@@ -5705,7 +5705,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263328552246</v>
+        <v>7.55263376235962</v>
       </c>
       <c r="H184" t="n">
         <v>12000</v>
@@ -5734,7 +5734,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588106155396</v>
+        <v>7.51588153839111</v>
       </c>
       <c r="H185" t="n">
         <v>12500</v>
@@ -5763,7 +5763,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425645828247</v>
+        <v>7.53425741195679</v>
       </c>
       <c r="H186" t="n">
         <v>13000</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938550949097</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5879,7 +5879,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263328552246</v>
+        <v>7.55263376235962</v>
       </c>
       <c r="H190" t="n">
         <v>36500</v>
@@ -5937,7 +5937,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G192" t="n">
-        <v>7.68126630783081</v>
+        <v>7.68126678466797</v>
       </c>
       <c r="H192" t="n">
         <v>32000</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -5995,7 +5995,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>7.62613821029663</v>
+        <v>7.62613868713379</v>
       </c>
       <c r="H194" t="n">
         <v>11500</v>
@@ -6024,7 +6024,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G195" t="n">
-        <v>7.60776138305664</v>
+        <v>7.6077618598938</v>
       </c>
       <c r="H195" t="n">
         <v>15000</v>
@@ -6053,7 +6053,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6169,7 +6169,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G200" t="n">
-        <v>7.38724660873413</v>
+        <v>7.38724708557129</v>
       </c>
       <c r="H200" t="n">
         <v>9500</v>
@@ -6227,7 +6227,7 @@
         <v>8.0600004196167</v>
       </c>
       <c r="G202" t="n">
-        <v>7.40562343597412</v>
+        <v>7.40562391281128</v>
       </c>
       <c r="H202" t="n">
         <v>14000</v>
@@ -6314,7 +6314,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>7.31374263763428</v>
+        <v>7.31374216079712</v>
       </c>
       <c r="H205" t="n">
         <v>14500</v>
@@ -6343,7 +6343,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H206" t="n">
         <v>10000</v>
@@ -6372,7 +6372,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.07485055923462</v>
+        <v>7.07485103607178</v>
       </c>
       <c r="H207" t="n">
         <v>32500</v>
@@ -6430,7 +6430,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>7.22186136245728</v>
+        <v>7.22186088562012</v>
       </c>
       <c r="H209" t="n">
         <v>21500</v>
@@ -6459,7 +6459,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023771286011</v>
+        <v>7.24023723602295</v>
       </c>
       <c r="H210" t="n">
         <v>10500</v>
@@ -6488,7 +6488,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G211" t="n">
-        <v>7.12998008728027</v>
+        <v>7.12997961044312</v>
       </c>
       <c r="H211" t="n">
         <v>10000</v>
@@ -6546,7 +6546,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="n">
-        <v>6.89108848571777</v>
+        <v>6.89108896255493</v>
       </c>
       <c r="H213" t="n">
         <v>14000</v>
@@ -6575,7 +6575,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83595991134644</v>
+        <v>6.83596038818359</v>
       </c>
       <c r="H214" t="n">
         <v>29500</v>
@@ -6604,7 +6604,7 @@
         <v>7.5</v>
       </c>
       <c r="G215" t="n">
-        <v>6.89108848571777</v>
+        <v>6.89108896255493</v>
       </c>
       <c r="H215" t="n">
         <v>9500</v>
@@ -6633,7 +6633,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>6.81758403778076</v>
+        <v>6.8175835609436</v>
       </c>
       <c r="H216" t="n">
         <v>17500</v>
@@ -6662,7 +6662,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H217" t="n">
         <v>63000</v>
@@ -6778,7 +6778,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>6.46843481063843</v>
+        <v>6.46843528747559</v>
       </c>
       <c r="H221" t="n">
         <v>18500</v>
@@ -6807,7 +6807,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H222" t="n">
         <v>18500</v>
@@ -6865,7 +6865,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.85433578491211</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H224" t="n">
         <v>31500</v>
@@ -6923,7 +6923,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>7.16673278808594</v>
+        <v>7.16673231124878</v>
       </c>
       <c r="H226" t="n">
         <v>34500</v>
@@ -6952,7 +6952,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G227" t="n">
-        <v>6.74407958984375</v>
+        <v>6.74407911300659</v>
       </c>
       <c r="H227" t="n">
         <v>34000</v>
@@ -6981,7 +6981,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>7.16673278808594</v>
+        <v>7.16673231124878</v>
       </c>
       <c r="H228" t="n">
         <v>22000</v>
@@ -7039,7 +7039,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>7.18510866165161</v>
+        <v>7.18510818481445</v>
       </c>
       <c r="H230" t="n">
         <v>11500</v>
@@ -7126,7 +7126,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69813776016235</v>
+        <v>6.69813823699951</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7155,7 +7155,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H234" t="n">
         <v>37500</v>
@@ -7242,7 +7242,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>6.85433578491211</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H237" t="n">
         <v>14500</v>
@@ -7387,7 +7387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G242" t="n">
-        <v>6.79001903533936</v>
+        <v>6.79001951217651</v>
       </c>
       <c r="H242" t="n">
         <v>21500</v>
@@ -7416,7 +7416,7 @@
         <v>7.5</v>
       </c>
       <c r="G243" t="n">
-        <v>6.89108848571777</v>
+        <v>6.89108896255493</v>
       </c>
       <c r="H243" t="n">
         <v>10500</v>
@@ -7474,7 +7474,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76245546340942</v>
+        <v>6.76245498657227</v>
       </c>
       <c r="H245" t="n">
         <v>4500</v>
@@ -7503,7 +7503,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H246" t="n">
         <v>14000</v>
@@ -7532,7 +7532,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G247" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49600028991699</v>
       </c>
       <c r="H247" t="n">
         <v>19000</v>
@@ -7735,7 +7735,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>6.35817766189575</v>
+        <v>6.35817813873291</v>
       </c>
       <c r="H254" t="n">
         <v>14500</v>
@@ -7851,7 +7851,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G258" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H258" t="n">
         <v>11000</v>
@@ -7880,7 +7880,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H259" t="n">
         <v>2000</v>
@@ -7909,7 +7909,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G260" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H260" t="n">
         <v>5000</v>
@@ -7938,7 +7938,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H261" t="n">
         <v>25000</v>
@@ -7967,7 +7967,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>6.79001903533936</v>
+        <v>6.79001951217651</v>
       </c>
       <c r="H262" t="n">
         <v>104000</v>
@@ -7996,7 +7996,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322690963745</v>
+        <v>7.09322738647461</v>
       </c>
       <c r="H263" t="n">
         <v>210500</v>
@@ -8025,7 +8025,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.07485055923462</v>
+        <v>7.07485103607178</v>
       </c>
       <c r="H264" t="n">
         <v>31000</v>
@@ -8112,7 +8112,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G267" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49600028991699</v>
       </c>
       <c r="H267" t="n">
         <v>18000</v>
@@ -8141,7 +8141,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H268" t="n">
         <v>11000</v>
@@ -8170,7 +8170,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>6.55112838745117</v>
+        <v>6.55112886428833</v>
       </c>
       <c r="H269" t="n">
         <v>7500</v>
@@ -8199,7 +8199,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G270" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49600028991699</v>
       </c>
       <c r="H270" t="n">
         <v>11500</v>
@@ -8228,7 +8228,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>6.46843481063843</v>
+        <v>6.46843528747559</v>
       </c>
       <c r="H271" t="n">
         <v>20500</v>
@@ -8257,7 +8257,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G272" t="n">
-        <v>6.49599981307983</v>
+        <v>6.49600028991699</v>
       </c>
       <c r="H272" t="n">
         <v>5500</v>
@@ -8315,7 +8315,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>6.4408712387085</v>
+        <v>6.44087076187134</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G275" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8373,7 +8373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G276" t="n">
-        <v>6.26629686355591</v>
+        <v>6.26629734039307</v>
       </c>
       <c r="H276" t="n">
         <v>8000</v>
@@ -8402,7 +8402,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G277" t="n">
-        <v>6.21116876602173</v>
+        <v>6.21116828918457</v>
       </c>
       <c r="H277" t="n">
         <v>20000</v>
@@ -8431,7 +8431,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G278" t="n">
-        <v>6.21116876602173</v>
+        <v>6.21116828918457</v>
       </c>
       <c r="H278" t="n">
         <v>7000</v>
@@ -8489,7 +8489,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H280" t="n">
         <v>26500</v>
@@ -8576,7 +8576,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.8068904876709</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H283" t="n">
         <v>10500</v>
@@ -8605,7 +8605,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>5.72419786453247</v>
+        <v>5.72419738769531</v>
       </c>
       <c r="H284" t="n">
         <v>12000</v>
@@ -8634,7 +8634,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G285" t="n">
-        <v>5.37504911422729</v>
+        <v>5.37504959106445</v>
       </c>
       <c r="H285" t="n">
         <v>28000</v>
@@ -8663,7 +8663,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910823822021</v>
       </c>
       <c r="H286" t="n">
         <v>39500</v>
@@ -8692,7 +8692,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.37504911422729</v>
+        <v>5.37504959106445</v>
       </c>
       <c r="H287" t="n">
         <v>22500</v>
@@ -8721,7 +8721,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G288" t="n">
-        <v>5.64150476455688</v>
+        <v>5.64150428771973</v>
       </c>
       <c r="H288" t="n">
         <v>11000</v>
@@ -8866,7 +8866,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H293" t="n">
         <v>64000</v>
@@ -8895,7 +8895,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330671310425</v>
+        <v>6.41330623626709</v>
       </c>
       <c r="H294" t="n">
         <v>23500</v>
@@ -8953,7 +8953,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>6.55112838745117</v>
+        <v>6.55112886428833</v>
       </c>
       <c r="H296" t="n">
         <v>10000</v>
@@ -9011,7 +9011,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H298" t="n">
         <v>9000</v>
@@ -9040,7 +9040,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>6.56950426101685</v>
+        <v>6.569504737854</v>
       </c>
       <c r="H299" t="n">
         <v>6000</v>
@@ -9243,7 +9243,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G306" t="n">
-        <v>6.35817766189575</v>
+        <v>6.35817813873291</v>
       </c>
       <c r="H306" t="n">
         <v>8000</v>
@@ -9272,7 +9272,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548503875732</v>
+        <v>6.27548456192017</v>
       </c>
       <c r="H307" t="n">
         <v>9000</v>
@@ -9330,7 +9330,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G309" t="n">
-        <v>6.06415843963623</v>
+        <v>6.06415796279907</v>
       </c>
       <c r="H309" t="n">
         <v>4500</v>
@@ -9359,7 +9359,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H310" t="n">
         <v>7500</v>
@@ -9446,7 +9446,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05496978759766</v>
+        <v>6.05497026443481</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9533,7 +9533,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G316" t="n">
-        <v>6.1376633644104</v>
+        <v>6.13766288757324</v>
       </c>
       <c r="H316" t="n">
         <v>5500</v>
@@ -9562,7 +9562,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>6.09172248840332</v>
+        <v>6.09172296524048</v>
       </c>
       <c r="H317" t="n">
         <v>1500</v>
@@ -9649,7 +9649,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>5.88039588928223</v>
+        <v>5.88039541244507</v>
       </c>
       <c r="H320" t="n">
         <v>43500</v>
@@ -9707,7 +9707,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.88039588928223</v>
+        <v>5.88039541244507</v>
       </c>
       <c r="H322" t="n">
         <v>1500</v>
@@ -9794,7 +9794,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H325" t="n">
         <v>13000</v>
@@ -9852,7 +9852,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607913970947</v>
+        <v>5.81607818603516</v>
       </c>
       <c r="H327" t="n">
         <v>14080</v>
@@ -9881,7 +9881,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770278930664</v>
+        <v>5.79770231246948</v>
       </c>
       <c r="H328" t="n">
         <v>8871</v>
@@ -9910,7 +9910,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>5.76095008850098</v>
+        <v>5.76094961166382</v>
       </c>
       <c r="H329" t="n">
         <v>5878</v>
@@ -9939,7 +9939,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364318847656</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H330" t="n">
         <v>2311</v>
@@ -9997,7 +9997,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H332" t="n">
         <v>4456</v>
@@ -10026,7 +10026,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H333" t="n">
         <v>2022</v>
@@ -10084,7 +10084,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H335" t="n">
         <v>25940</v>
@@ -10171,7 +10171,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.32142543792725</v>
+        <v>6.3214259147644</v>
       </c>
       <c r="H338" t="n">
         <v>7965</v>
@@ -10200,7 +10200,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>6.69813776016235</v>
+        <v>6.69813823699951</v>
       </c>
       <c r="H339" t="n">
         <v>40701</v>
@@ -10229,7 +10229,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>6.54194021224976</v>
+        <v>6.5419397354126</v>
       </c>
       <c r="H340" t="n">
         <v>13709</v>
@@ -10258,7 +10258,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>6.42249488830566</v>
+        <v>6.42249441146851</v>
       </c>
       <c r="H341" t="n">
         <v>12887</v>
@@ -10287,7 +10287,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330671310425</v>
+        <v>6.41330623626709</v>
       </c>
       <c r="H342" t="n">
         <v>2560</v>
@@ -10345,7 +10345,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.32142543792725</v>
+        <v>6.3214259147644</v>
       </c>
       <c r="H344" t="n">
         <v>13218</v>
@@ -10374,7 +10374,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H345" t="n">
         <v>2764</v>
@@ -10519,7 +10519,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G350" t="n">
-        <v>6.21116876602173</v>
+        <v>6.21116828918457</v>
       </c>
       <c r="H350" t="n">
         <v>500</v>
@@ -10606,7 +10606,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G353" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H353" t="n">
         <v>14359</v>
@@ -10635,7 +10635,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27397966384888</v>
+        <v>5.27397918701172</v>
       </c>
       <c r="H354" t="n">
         <v>17836</v>
@@ -10722,7 +10722,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936586380005</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H357" t="n">
         <v>2284</v>
@@ -10751,7 +10751,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530626296997</v>
+        <v>5.48530673980713</v>
       </c>
       <c r="H358" t="n">
         <v>3234</v>
@@ -10809,7 +10809,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="n">
-        <v>5.51287126541138</v>
+        <v>5.51287078857422</v>
       </c>
       <c r="H360" t="n">
         <v>2285</v>
@@ -10838,7 +10838,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>5.46692991256714</v>
+        <v>5.46693086624146</v>
       </c>
       <c r="H361" t="n">
         <v>1880</v>
@@ -10896,7 +10896,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718753814697</v>
+        <v>5.57718801498413</v>
       </c>
       <c r="H363" t="n">
         <v>1392</v>
@@ -10925,7 +10925,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936586380005</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H364" t="n">
         <v>1105</v>
@@ -11012,7 +11012,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>5.46692991256714</v>
+        <v>5.46693086624146</v>
       </c>
       <c r="H367" t="n">
         <v>3574</v>
@@ -11041,7 +11041,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H368" t="n">
         <v>11426</v>
@@ -11070,7 +11070,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G369" t="n">
-        <v>5.8068904876709</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H369" t="n">
         <v>4280</v>
@@ -11099,7 +11099,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H370" t="n">
         <v>3154</v>
@@ -11128,7 +11128,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>5.8068904876709</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H371" t="n">
         <v>6334</v>
@@ -11186,7 +11186,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11244,7 +11244,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H375" t="n">
         <v>9545</v>
@@ -11331,7 +11331,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G378" t="n">
-        <v>5.56799983978271</v>
+        <v>5.56799936294556</v>
       </c>
       <c r="H378" t="n">
         <v>9532</v>
@@ -11418,7 +11418,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.78851413726807</v>
+        <v>5.78851461410522</v>
       </c>
       <c r="H381" t="n">
         <v>5665</v>
@@ -11447,7 +11447,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G382" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H382" t="n">
         <v>7014</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.5955638885498</v>
+        <v>5.59556436538696</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11621,7 +11621,7 @@
         <v>6.25</v>
       </c>
       <c r="G388" t="n">
-        <v>5.7425742149353</v>
+        <v>5.74257373809814</v>
       </c>
       <c r="H388" t="n">
         <v>1978</v>
@@ -11650,7 +11650,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932596206665</v>
+        <v>5.77932643890381</v>
       </c>
       <c r="H389" t="n">
         <v>6221</v>
@@ -11679,7 +11679,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.78851413726807</v>
+        <v>5.78851461410522</v>
       </c>
       <c r="H390" t="n">
         <v>5008</v>
@@ -11708,7 +11708,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G391" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H391" t="n">
         <v>4247</v>
@@ -11737,7 +11737,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G392" t="n">
-        <v>5.8068904876709</v>
+        <v>5.80689144134521</v>
       </c>
       <c r="H392" t="n">
         <v>2786</v>
@@ -11795,7 +11795,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G394" t="n">
-        <v>6.14685106277466</v>
+        <v>6.14685153961182</v>
       </c>
       <c r="H394" t="n">
         <v>4839</v>
@@ -11824,7 +11824,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G395" t="n">
-        <v>6.14685106277466</v>
+        <v>6.14685153961182</v>
       </c>
       <c r="H395" t="n">
         <v>6355</v>
@@ -11853,7 +11853,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G396" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H396" t="n">
         <v>2491</v>
@@ -11882,7 +11882,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>6.17441511154175</v>
+        <v>6.17441558837891</v>
       </c>
       <c r="H397" t="n">
         <v>1264</v>
@@ -11940,7 +11940,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G399" t="n">
-        <v>6.11928653717041</v>
+        <v>6.11928701400757</v>
       </c>
       <c r="H399" t="n">
         <v>1503</v>
@@ -11998,7 +11998,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.99065256118774</v>
+        <v>5.9906530380249</v>
       </c>
       <c r="H401" t="n">
         <v>4770</v>
@@ -12056,7 +12056,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364318847656</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H403" t="n">
         <v>2709</v>
@@ -12085,7 +12085,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G404" t="n">
-        <v>5.85283136367798</v>
+        <v>5.85283088684082</v>
       </c>
       <c r="H404" t="n">
         <v>2104</v>
@@ -12143,7 +12143,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>5.88039588928223</v>
+        <v>5.88039541244507</v>
       </c>
       <c r="H406" t="n">
         <v>1830</v>
@@ -12172,7 +12172,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H407" t="n">
         <v>1611</v>
@@ -12317,7 +12317,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607913970947</v>
+        <v>5.81607818603516</v>
       </c>
       <c r="H412" t="n">
         <v>2753</v>
@@ -12346,7 +12346,7 @@
         <v>6.25</v>
       </c>
       <c r="G413" t="n">
-        <v>5.7425742149353</v>
+        <v>5.74257373809814</v>
       </c>
       <c r="H413" t="n">
         <v>2441</v>
@@ -12375,7 +12375,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.78851413726807</v>
+        <v>5.78851461410522</v>
       </c>
       <c r="H414" t="n">
         <v>7162</v>
@@ -12433,7 +12433,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G416" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H416" t="n">
         <v>3751</v>
@@ -12462,7 +12462,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124761581421</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H417" t="n">
         <v>1848</v>
@@ -12520,7 +12520,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G419" t="n">
-        <v>5.61394071578979</v>
+        <v>5.61394023895264</v>
       </c>
       <c r="H419" t="n">
         <v>1068</v>
@@ -12549,7 +12549,7 @@
         <v>6</v>
       </c>
       <c r="G420" t="n">
-        <v>5.51287126541138</v>
+        <v>5.51287078857422</v>
       </c>
       <c r="H420" t="n">
         <v>2335</v>
@@ -12607,7 +12607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G422" t="n">
-        <v>5.64150476455688</v>
+        <v>5.64150428771973</v>
       </c>
       <c r="H422" t="n">
         <v>3644</v>
@@ -12636,7 +12636,7 @@
         <v>6</v>
       </c>
       <c r="G423" t="n">
-        <v>5.51287126541138</v>
+        <v>5.51287078857422</v>
       </c>
       <c r="H423" t="n">
         <v>3401</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.37504911422729</v>
+        <v>5.37504959106445</v>
       </c>
       <c r="H424" t="n">
         <v>2411</v>
@@ -12723,7 +12723,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>5.42098999023438</v>
+        <v>5.42098951339722</v>
       </c>
       <c r="H426" t="n">
         <v>2060</v>
@@ -12752,7 +12752,7 @@
         <v>5.75</v>
       </c>
       <c r="G427" t="n">
-        <v>5.28316783905029</v>
+        <v>5.28316831588745</v>
       </c>
       <c r="H427" t="n">
         <v>6854</v>
@@ -12781,7 +12781,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27397966384888</v>
+        <v>5.27397918701172</v>
       </c>
       <c r="H428" t="n">
         <v>3146</v>
@@ -12839,7 +12839,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>5.31992101669312</v>
+        <v>5.31992053985596</v>
       </c>
       <c r="H430" t="n">
         <v>4924</v>
@@ -12868,7 +12868,7 @@
         <v>5.82999992370605</v>
       </c>
       <c r="G431" t="n">
-        <v>5.35667324066162</v>
+        <v>5.35667276382446</v>
       </c>
       <c r="H431" t="n">
         <v>2160</v>
@@ -12897,7 +12897,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423728942871</v>
+        <v>5.38423681259155</v>
       </c>
       <c r="H432" t="n">
         <v>3519</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910919189453</v>
+        <v>5.32910823822021</v>
       </c>
       <c r="H434" t="n">
         <v>3264</v>
@@ -12984,7 +12984,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346536636353</v>
+        <v>5.05346488952637</v>
       </c>
       <c r="H435" t="n">
         <v>15369</v>
@@ -13042,7 +13042,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.7318811416626</v>
+        <v>4.73188066482544</v>
       </c>
       <c r="H437" t="n">
         <v>15638</v>
@@ -13071,7 +13071,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.67675256729126</v>
+        <v>4.6767520904541</v>
       </c>
       <c r="H438" t="n">
         <v>13127</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.5848708152771</v>
+        <v>4.58487033843994</v>
       </c>
       <c r="H439" t="n">
         <v>4452</v>
@@ -13245,7 +13245,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H444" t="n">
         <v>14966</v>
@@ -13274,7 +13274,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>4.32760429382324</v>
+        <v>4.32760334014893</v>
       </c>
       <c r="H445" t="n">
         <v>10951</v>
@@ -13303,7 +13303,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H446" t="n">
         <v>2659</v>
@@ -13390,7 +13390,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H449" t="n">
         <v>13181</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13477,7 +13477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948413848877</v>
+        <v>4.41948461532593</v>
       </c>
       <c r="H452" t="n">
         <v>45286</v>
@@ -13506,7 +13506,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>4.32760429382324</v>
+        <v>4.32760334014893</v>
       </c>
       <c r="H453" t="n">
         <v>24237</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001981735229</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13709,7 +13709,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.45623731613159</v>
+        <v>4.45623683929443</v>
       </c>
       <c r="H460" t="n">
         <v>2411</v>
@@ -13796,7 +13796,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.52974224090576</v>
+        <v>4.5297417640686</v>
       </c>
       <c r="H463" t="n">
         <v>15140</v>
@@ -13825,7 +13825,7 @@
         <v>5.01000022888184</v>
       </c>
       <c r="G464" t="n">
-        <v>4.60324716567993</v>
+        <v>4.60324764251709</v>
       </c>
       <c r="H464" t="n">
         <v>5765</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -13970,7 +13970,7 @@
         <v>4.875</v>
       </c>
       <c r="G469" t="n">
-        <v>4.47920799255371</v>
+        <v>4.47920751571655</v>
       </c>
       <c r="H469" t="n">
         <v>1653</v>
@@ -14028,7 +14028,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34598016738892</v>
+        <v>4.34597969055176</v>
       </c>
       <c r="H471" t="n">
         <v>3835</v>
@@ -14086,7 +14086,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>4.38732671737671</v>
+        <v>4.38732624053955</v>
       </c>
       <c r="H473" t="n">
         <v>3916</v>
@@ -14115,7 +14115,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435604095459</v>
+        <v>4.36435556411743</v>
       </c>
       <c r="H474" t="n">
         <v>5067</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001981735229</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14260,7 +14260,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H479" t="n">
         <v>3457</v>
@@ -14289,7 +14289,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H480" t="n">
         <v>8400</v>
@@ -14318,7 +14318,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22194004058838</v>
+        <v>4.22193956375122</v>
       </c>
       <c r="H481" t="n">
         <v>10620</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332625389099</v>
+        <v>3.92332673072815</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14434,7 +14434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251490592957</v>
       </c>
       <c r="H485" t="n">
         <v>4207</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845506668091</v>
+        <v>3.97845530509949</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14492,7 +14492,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.97386145591736</v>
+        <v>3.97386074066162</v>
       </c>
       <c r="H487" t="n">
         <v>7176</v>
@@ -14521,7 +14521,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G488" t="n">
-        <v>3.84063315391541</v>
+        <v>3.84063339233398</v>
       </c>
       <c r="H488" t="n">
         <v>15203</v>
@@ -14550,7 +14550,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G489" t="n">
-        <v>3.84063315391541</v>
+        <v>3.84063339233398</v>
       </c>
       <c r="H489" t="n">
         <v>5714</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469275474548</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14608,7 +14608,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G491" t="n">
-        <v>3.82225680351257</v>
+        <v>3.82225728034973</v>
       </c>
       <c r="H491" t="n">
         <v>2924</v>
@@ -14637,7 +14637,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>3.81306910514832</v>
+        <v>3.81306934356689</v>
       </c>
       <c r="H492" t="n">
         <v>2046</v>
@@ -14666,7 +14666,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>3.84522747993469</v>
+        <v>3.84522771835327</v>
       </c>
       <c r="H493" t="n">
         <v>1926</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144569396973</v>
+        <v>3.83144545555115</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469275474548</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251514434814</v>
+        <v>3.93251490592957</v>
       </c>
       <c r="H497" t="n">
         <v>8274</v>
@@ -14811,7 +14811,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.95089101791382</v>
+        <v>3.9508912563324</v>
       </c>
       <c r="H498" t="n">
         <v>7416</v>
@@ -14840,7 +14840,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.95089101791382</v>
+        <v>3.9508912563324</v>
       </c>
       <c r="H499" t="n">
         <v>12304</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520729064941</v>
+        <v>4.01520776748657</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14956,7 +14956,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061296463013</v>
+        <v>4.01061344146729</v>
       </c>
       <c r="H503" t="n">
         <v>31005</v>
@@ -14985,7 +14985,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>4.35057353973389</v>
+        <v>4.35057401657104</v>
       </c>
       <c r="H504" t="n">
         <v>35126</v>
@@ -15014,7 +15014,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H505" t="n">
         <v>17677</v>
@@ -15072,7 +15072,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>4.31841516494751</v>
+        <v>4.31841564178467</v>
       </c>
       <c r="H507" t="n">
         <v>9121</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H508" t="n">
         <v>3615</v>
@@ -15159,7 +15159,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H510" t="n">
         <v>6857</v>
@@ -15188,7 +15188,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326663970947</v>
+        <v>4.43326759338379</v>
       </c>
       <c r="H511" t="n">
         <v>4220</v>
@@ -15304,7 +15304,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516786575317</v>
+        <v>4.35516834259033</v>
       </c>
       <c r="H515" t="n">
         <v>1906</v>
@@ -15333,7 +15333,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>4.34138584136963</v>
+        <v>4.34138631820679</v>
       </c>
       <c r="H516" t="n">
         <v>12696</v>
@@ -15391,7 +15391,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31841516494751</v>
+        <v>4.31841564178467</v>
       </c>
       <c r="H518" t="n">
         <v>5744</v>
@@ -15449,7 +15449,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.7318811416626</v>
+        <v>4.73188066482544</v>
       </c>
       <c r="H520" t="n">
         <v>62686</v>
@@ -15478,7 +15478,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>4.62162399291992</v>
+        <v>4.62162351608276</v>
       </c>
       <c r="H521" t="n">
         <v>14852</v>
@@ -15652,7 +15652,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G527" t="n">
-        <v>4.81457328796387</v>
+        <v>4.81457376480103</v>
       </c>
       <c r="H527" t="n">
         <v>9827</v>
@@ -15710,7 +15710,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>4.89726686477661</v>
+        <v>4.89726734161377</v>
       </c>
       <c r="H529" t="n">
         <v>14250</v>
@@ -15826,7 +15826,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.90645503997803</v>
+        <v>4.90645551681519</v>
       </c>
       <c r="H533" t="n">
         <v>5784</v>
@@ -15913,7 +15913,7 @@
         <v>5.57000017166138</v>
       </c>
       <c r="G536" t="n">
-        <v>5.11778259277344</v>
+        <v>5.11778211593628</v>
       </c>
       <c r="H536" t="n">
         <v>8803</v>
@@ -15942,7 +15942,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>5.01671314239502</v>
+        <v>5.0167121887207</v>
       </c>
       <c r="H537" t="n">
         <v>6975</v>
@@ -16058,7 +16058,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G541" t="n">
-        <v>4.8880786895752</v>
+        <v>4.88807916641235</v>
       </c>
       <c r="H541" t="n">
         <v>3175</v>
@@ -16145,7 +16145,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G544" t="n">
-        <v>4.69512844085693</v>
+        <v>4.69512891769409</v>
       </c>
       <c r="H544" t="n">
         <v>7711</v>
@@ -16232,7 +16232,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H547" t="n">
         <v>6999</v>
@@ -16261,7 +16261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029691696167</v>
+        <v>4.41029739379883</v>
       </c>
       <c r="H548" t="n">
         <v>5791</v>
@@ -16290,7 +16290,7 @@
         <v>4.6399998664856</v>
       </c>
       <c r="G549" t="n">
-        <v>4.26328659057617</v>
+        <v>4.26328706741333</v>
       </c>
       <c r="H549" t="n">
         <v>8198</v>
@@ -16348,7 +16348,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.20815753936768</v>
+        <v>4.20815801620483</v>
       </c>
       <c r="H551" t="n">
         <v>18005</v>
@@ -16377,7 +16377,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G552" t="n">
-        <v>4.31382179260254</v>
+        <v>4.31382131576538</v>
       </c>
       <c r="H552" t="n">
         <v>11658</v>
@@ -16406,7 +16406,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247524261475</v>
+        <v>4.27247476577759</v>
       </c>
       <c r="H553" t="n">
         <v>1650</v>
@@ -16464,7 +16464,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G555" t="n">
-        <v>4.097900390625</v>
+        <v>4.09790086746216</v>
       </c>
       <c r="H555" t="n">
         <v>11397</v>
@@ -16580,7 +16580,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>3.81306910514832</v>
+        <v>3.81306934356689</v>
       </c>
       <c r="H559" t="n">
         <v>22855</v>
@@ -16609,7 +16609,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>3.73497009277344</v>
+        <v>3.73496985435486</v>
       </c>
       <c r="H560" t="n">
         <v>18999</v>
@@ -16638,7 +16638,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631664276123</v>
+        <v>3.77631688117981</v>
       </c>
       <c r="H561" t="n">
         <v>14097</v>
@@ -16667,7 +16667,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>3.74875235557556</v>
+        <v>3.74875211715698</v>
       </c>
       <c r="H562" t="n">
         <v>4463</v>
@@ -16696,7 +16696,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.81306910514832</v>
+        <v>3.81306934356689</v>
       </c>
       <c r="H563" t="n">
         <v>7862</v>
@@ -16725,7 +16725,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>3.69362330436707</v>
+        <v>3.69362354278564</v>
       </c>
       <c r="H564" t="n">
         <v>10513</v>
@@ -16754,7 +16754,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65687131881714</v>
+        <v>3.65687108039856</v>
       </c>
       <c r="H565" t="n">
         <v>350</v>
@@ -16841,7 +16841,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G568" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H568" t="n">
         <v>8477</v>
@@ -16899,7 +16899,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>3.38122773170471</v>
+        <v>3.38122749328613</v>
       </c>
       <c r="H570" t="n">
         <v>38613</v>
@@ -16928,7 +16928,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G571" t="n">
-        <v>3.38122773170471</v>
+        <v>3.38122749328613</v>
       </c>
       <c r="H571" t="n">
         <v>7214</v>
@@ -17015,7 +17015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152430534363</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H574" t="n">
         <v>22621</v>
@@ -17073,7 +17073,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G576" t="n">
-        <v>3.23421740531921</v>
+        <v>3.23421764373779</v>
       </c>
       <c r="H576" t="n">
         <v>1539</v>
@@ -17131,7 +17131,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G578" t="n">
-        <v>3.0688316822052</v>
+        <v>3.06883144378662</v>
       </c>
       <c r="H578" t="n">
         <v>17701</v>
@@ -17189,7 +17189,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G580" t="n">
-        <v>3.03207921981812</v>
+        <v>3.03207898139954</v>
       </c>
       <c r="H580" t="n">
         <v>4602</v>
@@ -17218,7 +17218,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G581" t="n">
-        <v>3.05964326858521</v>
+        <v>3.05964350700378</v>
       </c>
       <c r="H581" t="n">
         <v>5248</v>
@@ -17276,7 +17276,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>3.23421740531921</v>
+        <v>3.23421764373779</v>
       </c>
       <c r="H583" t="n">
         <v>18949</v>
@@ -17305,7 +17305,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G584" t="n">
-        <v>3.50067281723022</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H584" t="n">
         <v>25151</v>
@@ -17334,7 +17334,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.54661345481873</v>
+        <v>3.5466136932373</v>
       </c>
       <c r="H585" t="n">
         <v>5627</v>
@@ -17363,7 +17363,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.54661345481873</v>
+        <v>3.5466136932373</v>
       </c>
       <c r="H586" t="n">
         <v>4755</v>
@@ -17392,7 +17392,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>3.50067281723022</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H587" t="n">
         <v>4318</v>
@@ -17421,7 +17421,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>3.56499004364014</v>
+        <v>3.56498980522156</v>
       </c>
       <c r="H588" t="n">
         <v>2735</v>
@@ -17450,7 +17450,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G589" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H589" t="n">
         <v>11400</v>
@@ -17479,7 +17479,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.94170308113098</v>
+        <v>3.9417028427124</v>
       </c>
       <c r="H590" t="n">
         <v>70490</v>
@@ -17508,7 +17508,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712822914124</v>
+        <v>3.76712870597839</v>
       </c>
       <c r="H591" t="n">
         <v>12175</v>
@@ -17537,7 +17537,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712822914124</v>
+        <v>3.76712870597839</v>
       </c>
       <c r="H592" t="n">
         <v>9692</v>
@@ -17566,7 +17566,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G593" t="n">
-        <v>3.70281171798706</v>
+        <v>3.70281195640564</v>
       </c>
       <c r="H593" t="n">
         <v>11590</v>
@@ -17595,7 +17595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904916763306</v>
+        <v>3.51904940605164</v>
       </c>
       <c r="H594" t="n">
         <v>20677</v>
@@ -17624,7 +17624,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H595" t="n">
         <v>9575</v>
@@ -17653,7 +17653,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.54661345481873</v>
+        <v>3.5466136932373</v>
       </c>
       <c r="H596" t="n">
         <v>1150</v>
@@ -17682,7 +17682,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.53742527961731</v>
+        <v>3.53742551803589</v>
       </c>
       <c r="H597" t="n">
         <v>7488</v>
@@ -17711,7 +17711,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H598" t="n">
         <v>3630</v>
@@ -17740,7 +17740,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G599" t="n">
-        <v>3.61093068122864</v>
+        <v>3.61093044281006</v>
       </c>
       <c r="H599" t="n">
         <v>8376</v>
@@ -17798,7 +17798,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G601" t="n">
-        <v>3.23421740531921</v>
+        <v>3.23421764373779</v>
       </c>
       <c r="H601" t="n">
         <v>18937</v>
@@ -17827,7 +17827,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152430534363</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H602" t="n">
         <v>23557</v>
@@ -17856,7 +17856,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>3.23421740531921</v>
+        <v>3.23421764373779</v>
       </c>
       <c r="H603" t="n">
         <v>2415</v>
@@ -17914,7 +17914,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>3.30772280693054</v>
+        <v>3.30772233009338</v>
       </c>
       <c r="H605" t="n">
         <v>3361</v>
@@ -17943,7 +17943,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015828132629</v>
+        <v>3.28015780448914</v>
       </c>
       <c r="H606" t="n">
         <v>4093</v>
@@ -18059,7 +18059,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>3.18827700614929</v>
+        <v>3.18827724456787</v>
       </c>
       <c r="H610" t="n">
         <v>6723</v>
@@ -18088,7 +18088,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990089416504</v>
+        <v>3.16990113258362</v>
       </c>
       <c r="H611" t="n">
         <v>4629</v>
@@ -18146,7 +18146,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233636856079</v>
+        <v>3.14233660697937</v>
       </c>
       <c r="H613" t="n">
         <v>1790</v>
@@ -18233,7 +18233,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152430534363</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H616" t="n">
         <v>4300</v>
@@ -18378,7 +18378,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G621" t="n">
-        <v>2.94019794464111</v>
+        <v>2.94019770622253</v>
       </c>
       <c r="H621" t="n">
         <v>5112</v>
@@ -18436,7 +18436,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>2.89425706863403</v>
+        <v>2.89425730705261</v>
       </c>
       <c r="H623" t="n">
         <v>25740</v>
@@ -18465,7 +18465,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G624" t="n">
-        <v>2.94019794464111</v>
+        <v>2.94019770622253</v>
       </c>
       <c r="H624" t="n">
         <v>2110</v>
@@ -18494,7 +18494,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>2.94019794464111</v>
+        <v>2.94019770622253</v>
       </c>
       <c r="H625" t="n">
         <v>6810</v>
@@ -18552,7 +18552,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G627" t="n">
-        <v>2.9310097694397</v>
+        <v>2.93101000785828</v>
       </c>
       <c r="H627" t="n">
         <v>10185</v>
@@ -18639,7 +18639,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G630" t="n">
-        <v>3.03276801109314</v>
+        <v>3.03276824951172</v>
       </c>
       <c r="H630" t="n">
         <v>1951</v>
@@ -18987,7 +18987,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110481262207</v>
+        <v>2.52110457420349</v>
       </c>
       <c r="H642" t="n">
         <v>95598</v>
@@ -19016,7 +19016,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H643" t="n">
         <v>60892</v>
@@ -19074,7 +19074,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040790557861</v>
+        <v>2.53040766716003</v>
       </c>
       <c r="H645" t="n">
         <v>12711</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761980056763</v>
+        <v>2.56761932373047</v>
       </c>
       <c r="H646" t="n">
         <v>8131</v>
@@ -19132,7 +19132,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901385307312</v>
+        <v>2.54901361465454</v>
       </c>
       <c r="H647" t="n">
         <v>4920</v>
@@ -19190,7 +19190,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G649" t="n">
-        <v>2.48389291763306</v>
+        <v>2.48389315605164</v>
       </c>
       <c r="H649" t="n">
         <v>18231</v>
@@ -19248,7 +19248,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H651" t="n">
         <v>18483</v>
@@ -19277,7 +19277,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="n">
-        <v>2.39086294174194</v>
+        <v>2.39086318016052</v>
       </c>
       <c r="H652" t="n">
         <v>8591</v>
@@ -19335,7 +19335,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H654" t="n">
         <v>19145</v>
@@ -19364,7 +19364,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H655" t="n">
         <v>11634</v>
@@ -19393,7 +19393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H656" t="n">
         <v>10081</v>
@@ -19422,7 +19422,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G657" t="n">
-        <v>2.39086294174194</v>
+        <v>2.39086318016052</v>
       </c>
       <c r="H657" t="n">
         <v>4696</v>
@@ -19509,7 +19509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H660" t="n">
         <v>4896</v>
@@ -19683,7 +19683,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G666" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H666" t="n">
         <v>5645</v>
@@ -19712,7 +19712,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H667" t="n">
         <v>3080</v>
@@ -19741,7 +19741,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G668" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H668" t="n">
         <v>2684</v>
@@ -19770,7 +19770,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180195808411</v>
+        <v>2.51180171966553</v>
       </c>
       <c r="H669" t="n">
         <v>22344</v>
@@ -19799,7 +19799,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H670" t="n">
         <v>10500</v>
@@ -19886,7 +19886,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H673" t="n">
         <v>536</v>
@@ -19915,7 +19915,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H674" t="n">
         <v>1569</v>
@@ -20002,7 +20002,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G677" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H677" t="n">
         <v>13195</v>
@@ -20060,7 +20060,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.4373779296875</v>
+        <v>2.43737816810608</v>
       </c>
       <c r="H679" t="n">
         <v>10826</v>
@@ -20089,7 +20089,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20118,7 +20118,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877198219299</v>
+        <v>2.41877222061157</v>
       </c>
       <c r="H681" t="n">
         <v>3858</v>
@@ -20147,7 +20147,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G682" t="n">
-        <v>2.46528697013855</v>
+        <v>2.46528720855713</v>
       </c>
       <c r="H682" t="n">
         <v>8637</v>
@@ -20176,7 +20176,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.29783344268799</v>
+        <v>2.29783368110657</v>
       </c>
       <c r="H683" t="n">
         <v>7367</v>
@@ -20205,7 +20205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.49319577217102</v>
+        <v>2.4931960105896</v>
       </c>
       <c r="H684" t="n">
         <v>12276</v>
@@ -20234,7 +20234,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>2.35365104675293</v>
+        <v>2.35365128517151</v>
       </c>
       <c r="H685" t="n">
         <v>24371</v>
@@ -20350,7 +20350,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G689" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H689" t="n">
         <v>73294</v>
@@ -20379,7 +20379,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G690" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H690" t="n">
         <v>18911</v>
@@ -20437,7 +20437,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G692" t="n">
-        <v>1.16752278804779</v>
+        <v>1.1675226688385</v>
       </c>
       <c r="H692" t="n">
         <v>88258</v>
@@ -20466,7 +20466,7 @@
         <v>1.5</v>
       </c>
       <c r="G693" t="n">
-        <v>1.39544534683228</v>
+        <v>1.39544546604156</v>
       </c>
       <c r="H693" t="n">
         <v>126661</v>
@@ -20524,7 +20524,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H695" t="n">
         <v>235716</v>
@@ -20553,7 +20553,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H696" t="n">
         <v>232613</v>
@@ -20611,7 +20611,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G698" t="n">
-        <v>1.58150482177734</v>
+        <v>1.58150494098663</v>
       </c>
       <c r="H698" t="n">
         <v>54891</v>
@@ -20640,7 +20640,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G699" t="n">
-        <v>1.54429304599762</v>
+        <v>1.54429292678833</v>
       </c>
       <c r="H699" t="n">
         <v>36020</v>
@@ -20669,7 +20669,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.51638400554657</v>
+        <v>1.51638412475586</v>
       </c>
       <c r="H700" t="n">
         <v>7380</v>
@@ -20814,7 +20814,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.44196033477783</v>
+        <v>1.44196021556854</v>
       </c>
       <c r="H705" t="n">
         <v>12919</v>
@@ -20959,7 +20959,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G710" t="n">
-        <v>1.69779193401337</v>
+        <v>1.69779205322266</v>
       </c>
       <c r="H710" t="n">
         <v>5655</v>
@@ -20988,7 +20988,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H711" t="n">
         <v>6528</v>
@@ -21017,7 +21017,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H712" t="n">
         <v>2874</v>
@@ -21046,7 +21046,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G713" t="n">
-        <v>1.51638400554657</v>
+        <v>1.51638412475586</v>
       </c>
       <c r="H713" t="n">
         <v>7640</v>
@@ -21075,7 +21075,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G714" t="n">
-        <v>1.58150482177734</v>
+        <v>1.58150494098663</v>
       </c>
       <c r="H714" t="n">
         <v>5490</v>
@@ -21104,7 +21104,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G715" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H715" t="n">
         <v>9473</v>
@@ -21133,7 +21133,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G716" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H716" t="n">
         <v>14629</v>
@@ -21191,7 +21191,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G718" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H718" t="n">
         <v>5148</v>
@@ -21278,7 +21278,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G721" t="n">
-        <v>1.60476231575012</v>
+        <v>1.60476243495941</v>
       </c>
       <c r="H721" t="n">
         <v>5640</v>
@@ -21336,7 +21336,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H723" t="n">
         <v>5633</v>
@@ -21365,7 +21365,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G724" t="n">
-        <v>2.02804732322693</v>
+        <v>2.02804756164551</v>
       </c>
       <c r="H724" t="n">
         <v>114000</v>
@@ -21452,7 +21452,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H727" t="n">
         <v>67002</v>
@@ -21684,7 +21684,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H735" t="n">
         <v>53817</v>
@@ -21713,7 +21713,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H736" t="n">
         <v>25550</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H738" t="n">
         <v>41345</v>
@@ -21800,7 +21800,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550085067749</v>
+        <v>2.19550061225891</v>
       </c>
       <c r="H739" t="n">
         <v>13585</v>
@@ -21887,7 +21887,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H742" t="n">
         <v>4041</v>
@@ -21916,7 +21916,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H743" t="n">
         <v>27715</v>
@@ -21945,7 +21945,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G744" t="n">
-        <v>2.11177396774292</v>
+        <v>2.1117742061615</v>
       </c>
       <c r="H744" t="n">
         <v>19716</v>
@@ -21974,7 +21974,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.00944185256958</v>
+        <v>2.00944137573242</v>
       </c>
       <c r="H745" t="n">
         <v>22944</v>
@@ -22090,7 +22090,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>2.33504557609558</v>
+        <v>2.335045337677</v>
       </c>
       <c r="H749" t="n">
         <v>46515</v>
@@ -22177,7 +22177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.214106798172</v>
+        <v>2.21410703659058</v>
       </c>
       <c r="H752" t="n">
         <v>18450</v>
@@ -22206,7 +22206,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.24201607704163</v>
+        <v>2.24201583862305</v>
       </c>
       <c r="H753" t="n">
         <v>7610</v>
@@ -22293,7 +22293,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H756" t="n">
         <v>6173</v>
@@ -22322,7 +22322,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062154769897</v>
+        <v>2.26062178611755</v>
       </c>
       <c r="H757" t="n">
         <v>9025</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H760" t="n">
         <v>6602</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H761" t="n">
         <v>2731</v>
@@ -22496,7 +22496,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G763" t="n">
-        <v>2.1582887172699</v>
+        <v>2.15828895568848</v>
       </c>
       <c r="H763" t="n">
         <v>5178</v>
@@ -22525,7 +22525,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H764" t="n">
         <v>5171</v>
@@ -22554,7 +22554,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.17689490318298</v>
+        <v>2.1768946647644</v>
       </c>
       <c r="H765" t="n">
         <v>4690</v>
@@ -22699,7 +22699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H770" t="n">
         <v>1304</v>
@@ -22728,7 +22728,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480370521545</v>
+        <v>2.20480394363403</v>
       </c>
       <c r="H771" t="n">
         <v>5621</v>
@@ -22757,7 +22757,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H772" t="n">
         <v>12685</v>
@@ -22931,7 +22931,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G778" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H778" t="n">
         <v>10623</v>
@@ -22960,7 +22960,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H779" t="n">
         <v>6646</v>
@@ -22989,7 +22989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>2.04665327072144</v>
+        <v>2.04665350914001</v>
       </c>
       <c r="H780" t="n">
         <v>3975</v>
@@ -23047,7 +23047,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H782" t="n">
         <v>7820</v>
@@ -23105,7 +23105,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.99083566665649</v>
+        <v>1.9908355474472</v>
       </c>
       <c r="H784" t="n">
         <v>1181</v>
@@ -23192,7 +23192,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013875961304</v>
+        <v>2.00013852119446</v>
       </c>
       <c r="H787" t="n">
         <v>19192</v>
@@ -23250,7 +23250,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G789" t="n">
-        <v>2.02804732322693</v>
+        <v>2.02804756164551</v>
       </c>
       <c r="H789" t="n">
         <v>2761</v>
@@ -23308,7 +23308,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00944185256958</v>
+        <v>2.00944137573242</v>
       </c>
       <c r="H791" t="n">
         <v>2800</v>
@@ -23337,7 +23337,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G792" t="n">
-        <v>2.04665327072144</v>
+        <v>2.04665350914001</v>
       </c>
       <c r="H792" t="n">
         <v>7172</v>
@@ -23366,7 +23366,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H793" t="n">
         <v>8905</v>
@@ -23395,7 +23395,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98153257369995</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H794" t="n">
         <v>13577</v>
@@ -23424,7 +23424,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H795" t="n">
         <v>8911</v>
@@ -23453,7 +23453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H796" t="n">
         <v>3170</v>
@@ -23482,7 +23482,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362341403961</v>
+        <v>1.95362365245819</v>
       </c>
       <c r="H797" t="n">
         <v>15172</v>
@@ -23569,7 +23569,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G800" t="n">
-        <v>1.90710866451263</v>
+        <v>1.90710890293121</v>
       </c>
       <c r="H800" t="n">
         <v>3251</v>
@@ -23801,7 +23801,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G808" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H808" t="n">
         <v>8701</v>
@@ -23859,7 +23859,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.64662563800812</v>
+        <v>1.64662551879883</v>
       </c>
       <c r="H810" t="n">
         <v>3970</v>
@@ -23917,7 +23917,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H812" t="n">
         <v>17120</v>
@@ -24091,7 +24091,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>1.66523158550262</v>
+        <v>1.66523146629333</v>
       </c>
       <c r="H818" t="n">
         <v>26987</v>
@@ -24120,7 +24120,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011076927185</v>
+        <v>1.60011088848114</v>
       </c>
       <c r="H819" t="n">
         <v>13128</v>
@@ -24265,7 +24265,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G824" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H824" t="n">
         <v>17867</v>
@@ -24294,7 +24294,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H825" t="n">
         <v>2580</v>
@@ -24439,7 +24439,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G830" t="n">
-        <v>1.83268523216248</v>
+        <v>1.83268511295319</v>
       </c>
       <c r="H830" t="n">
         <v>53960</v>
@@ -24584,7 +24584,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G835" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H835" t="n">
         <v>50956</v>
@@ -24816,7 +24816,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G843" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H843" t="n">
         <v>3897</v>
@@ -24845,7 +24845,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G844" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H844" t="n">
         <v>3634</v>
@@ -25135,7 +25135,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.9350174665451</v>
+        <v>1.93501770496368</v>
       </c>
       <c r="H854" t="n">
         <v>16193</v>
@@ -25164,7 +25164,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G855" t="n">
-        <v>1.88850271701813</v>
+        <v>1.88850283622742</v>
       </c>
       <c r="H855" t="n">
         <v>15602</v>
@@ -25222,7 +25222,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G857" t="n">
-        <v>1.83733642101288</v>
+        <v>1.83733654022217</v>
       </c>
       <c r="H857" t="n">
         <v>12741</v>
@@ -25251,7 +25251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.86989688873291</v>
+        <v>1.8698970079422</v>
       </c>
       <c r="H858" t="n">
         <v>2711</v>
@@ -25338,7 +25338,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G861" t="n">
-        <v>2.02804732322693</v>
+        <v>2.02804756164551</v>
       </c>
       <c r="H861" t="n">
         <v>34243</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.18991017341614</v>
+        <v>2.18991041183472</v>
       </c>
       <c r="H864" t="n">
         <v>29824</v>
@@ -25454,7 +25454,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>2.1803891658783</v>
+        <v>2.18038892745972</v>
       </c>
       <c r="H865" t="n">
         <v>18169</v>
@@ -25541,7 +25541,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G868" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H868" t="n">
         <v>12463</v>
@@ -25599,7 +25599,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H870" t="n">
         <v>14204</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H871" t="n">
         <v>10741</v>
@@ -25686,7 +25686,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H873" t="n">
         <v>1780</v>
@@ -25715,7 +25715,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H874" t="n">
         <v>11963</v>
@@ -25860,7 +25860,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H879" t="n">
         <v>9646</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H881" t="n">
         <v>4363</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H882" t="n">
         <v>3757</v>
@@ -26005,7 +26005,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H884" t="n">
         <v>3933</v>
@@ -26092,7 +26092,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H887" t="n">
         <v>1502</v>
@@ -26121,7 +26121,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H888" t="n">
         <v>2991</v>
@@ -26150,7 +26150,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H889" t="n">
         <v>500</v>
@@ -26179,7 +26179,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H891" t="n">
         <v>1750</v>
@@ -26237,7 +26237,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H892" t="n">
         <v>3562</v>
@@ -26295,7 +26295,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H894" t="n">
         <v>2771</v>
@@ -27542,7 +27542,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H937" t="n">
         <v>12954</v>
@@ -27716,7 +27716,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G943" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H943" t="n">
         <v>13769</v>
@@ -27745,7 +27745,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.61862945556641</v>
+        <v>1.6186295747757</v>
       </c>
       <c r="H944" t="n">
         <v>22282</v>
@@ -27774,7 +27774,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G945" t="n">
-        <v>1.54245853424072</v>
+        <v>1.54245865345001</v>
       </c>
       <c r="H945" t="n">
         <v>13946</v>
@@ -27890,7 +27890,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.35679233074188</v>
+        <v>1.35679221153259</v>
       </c>
       <c r="H949" t="n">
         <v>12733</v>
@@ -27948,7 +27948,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G951" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H951" t="n">
         <v>18171</v>
@@ -28006,7 +28006,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G953" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H953" t="n">
         <v>17476</v>
@@ -28122,7 +28122,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>1.34727096557617</v>
+        <v>1.34727084636688</v>
       </c>
       <c r="H957" t="n">
         <v>10390</v>
@@ -28151,7 +28151,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H958" t="n">
         <v>120160</v>
@@ -28296,7 +28296,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G963" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H963" t="n">
         <v>70383</v>
@@ -28354,7 +28354,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H965" t="n">
         <v>11079</v>
@@ -28470,7 +28470,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G969" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H969" t="n">
         <v>5589</v>
@@ -28644,7 +28644,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G975" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H975" t="n">
         <v>16278</v>
@@ -28876,7 +28876,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G983" t="n">
-        <v>0.8474001288414</v>
+        <v>0.847400069236755</v>
       </c>
       <c r="H983" t="n">
         <v>11888</v>
@@ -28934,7 +28934,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G985" t="n">
-        <v>0.934996545314789</v>
+        <v>0.934996485710144</v>
       </c>
       <c r="H985" t="n">
         <v>22093</v>
@@ -28963,7 +28963,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G986" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H986" t="n">
         <v>24435</v>
@@ -29108,7 +29108,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H991" t="n">
         <v>4904</v>
@@ -29137,7 +29137,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H992" t="n">
         <v>18073</v>
@@ -29253,7 +29253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G996" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H996" t="n">
         <v>11904</v>
@@ -29282,7 +29282,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H997" t="n">
         <v>4540</v>
@@ -29427,7 +29427,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1002" t="n">
         <v>2974</v>
@@ -29485,7 +29485,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H1004" t="n">
         <v>11264</v>
@@ -29630,7 +29630,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1009" t="n">
         <v>18426</v>
@@ -29659,7 +29659,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1010" t="n">
         <v>2505</v>
@@ -29978,7 +29978,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1021" t="n">
         <v>5361</v>
@@ -30036,7 +30036,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1026" t="n">
         <v>3669</v>
@@ -30152,7 +30152,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1027" t="n">
         <v>8946</v>
@@ -30268,7 +30268,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1031" t="n">
         <v>6700</v>
@@ -30326,7 +30326,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1033" t="n">
         <v>2860</v>
@@ -30384,7 +30384,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1035" t="n">
         <v>7202</v>
@@ -30413,7 +30413,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1036" t="n">
         <v>3000</v>
@@ -30442,7 +30442,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1037" t="n">
         <v>3042</v>
@@ -30558,7 +30558,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1041" t="n">
         <v>702</v>
@@ -30616,7 +30616,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1043" t="n">
         <v>5703</v>
@@ -30674,7 +30674,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1045" t="n">
         <v>3810</v>
@@ -30703,7 +30703,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1046" t="n">
         <v>3045</v>
@@ -30732,7 +30732,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1047" t="n">
         <v>4337</v>
@@ -30993,7 +30993,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1056" t="n">
         <v>15939</v>
@@ -31138,7 +31138,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1061" t="n">
         <v>5653</v>
@@ -31225,7 +31225,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1064" t="n">
         <v>7815</v>
@@ -31254,7 +31254,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.01878452301025</v>
+        <v>1.01878440380096</v>
       </c>
       <c r="H1065" t="n">
         <v>2000</v>
@@ -31312,7 +31312,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1067" t="n">
         <v>2310</v>
@@ -31341,7 +31341,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1068" t="n">
         <v>8960</v>
@@ -31370,7 +31370,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1069" t="n">
         <v>9201</v>
@@ -31428,7 +31428,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.885485470294952</v>
+        <v>0.885485529899597</v>
       </c>
       <c r="H1071" t="n">
         <v>7123</v>
@@ -31834,7 +31834,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1085" t="n">
         <v>14616</v>
@@ -31863,7 +31863,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1086" t="n">
         <v>7925</v>
@@ -31979,7 +31979,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1090" t="n">
         <v>1503</v>
@@ -32008,7 +32008,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.990220308303833</v>
+        <v>0.990220367908478</v>
       </c>
       <c r="H1091" t="n">
         <v>4143</v>
@@ -32037,7 +32037,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1092" t="n">
         <v>4779</v>
@@ -32095,7 +32095,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1094" t="n">
         <v>8025</v>
@@ -32182,7 +32182,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.940709292888641</v>
+        <v>0.940709352493286</v>
       </c>
       <c r="H1097" t="n">
         <v>7780</v>
@@ -32327,7 +32327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1102" t="n">
         <v>114066</v>
@@ -32356,7 +32356,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1103" t="n">
         <v>155001</v>
@@ -32414,7 +32414,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1105" t="n">
         <v>9642</v>
@@ -32443,7 +32443,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14732277393341</v>
+        <v>1.14732265472412</v>
       </c>
       <c r="H1106" t="n">
         <v>29380</v>
@@ -32501,7 +32501,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1108" t="n">
         <v>51439</v>
@@ -32559,7 +32559,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1110" t="n">
         <v>7650</v>
@@ -32588,7 +32588,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1111" t="n">
         <v>5770</v>
@@ -32646,7 +32646,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1113" t="n">
         <v>10113</v>
@@ -32704,7 +32704,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1115" t="n">
         <v>12644</v>
@@ -32733,7 +32733,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1116" t="n">
         <v>8938</v>
@@ -32849,7 +32849,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1120" t="n">
         <v>9373</v>
@@ -32878,7 +32878,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1121" t="n">
         <v>12172</v>
@@ -33023,7 +33023,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1126" t="n">
         <v>6943</v>
@@ -33052,7 +33052,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.2092113494873</v>
+        <v>1.20921146869659</v>
       </c>
       <c r="H1127" t="n">
         <v>7459</v>
@@ -33139,7 +33139,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1130" t="n">
         <v>7350</v>
@@ -33197,7 +33197,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1132" t="n">
         <v>14474</v>
@@ -42831,6 +42831,35 @@
         <v>15180</v>
       </c>
       <c r="I1464" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1465" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>0.709999978542328</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>0.735000014305115</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>0.689999997615814</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>12027</v>
+      </c>
+      <c r="I1465" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74249863624573</v>
+        <v>2.74249887466431</v>
       </c>
       <c r="H3" t="n">
         <v>611000</v>
@@ -485,7 +485,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6414999961853</v>
+        <v>2.64150023460388</v>
       </c>
       <c r="H4" t="n">
         <v>186000</v>
@@ -514,7 +514,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66892075538635</v>
+        <v>2.66892051696777</v>
       </c>
       <c r="H5" t="n">
         <v>100000</v>
@@ -543,7 +543,7 @@
         <v>3.53049993515015</v>
       </c>
       <c r="G6" t="n">
-        <v>3.22692584991455</v>
+        <v>3.22692632675171</v>
       </c>
       <c r="H6" t="n">
         <v>588000</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H11" t="n">
         <v>296000</v>
@@ -717,7 +717,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G12" t="n">
-        <v>3.60121512413025</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H12" t="n">
         <v>96000</v>
@@ -746,7 +746,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.57379412651062</v>
+        <v>3.5737943649292</v>
       </c>
       <c r="H13" t="n">
         <v>75000</v>
@@ -775,7 +775,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45497226715088</v>
+        <v>3.45497250556946</v>
       </c>
       <c r="H14" t="n">
         <v>116000</v>
@@ -891,7 +891,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>3.51895332336426</v>
+        <v>3.51895308494568</v>
       </c>
       <c r="H18" t="n">
         <v>36000</v>
@@ -949,7 +949,7 @@
         <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.42755198478699</v>
+        <v>3.42755222320557</v>
       </c>
       <c r="H20" t="n">
         <v>37000</v>
@@ -978,7 +978,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.26302933692932</v>
+        <v>3.26302909851074</v>
       </c>
       <c r="H21" t="n">
         <v>78000</v>
@@ -1007,7 +1007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30873012542725</v>
+        <v>3.30873036384583</v>
       </c>
       <c r="H22" t="n">
         <v>17000</v>
@@ -1065,7 +1065,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G24" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H24" t="n">
         <v>30000</v>
@@ -1123,7 +1123,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H26" t="n">
         <v>34000</v>
@@ -1152,7 +1152,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248822212219</v>
+        <v>3.16248798370361</v>
       </c>
       <c r="H27" t="n">
         <v>62000</v>
@@ -1181,7 +1181,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764741897583</v>
+        <v>3.10764718055725</v>
       </c>
       <c r="H28" t="n">
         <v>52000</v>
@@ -1239,7 +1239,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G30" t="n">
-        <v>3.15334820747375</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H30" t="n">
         <v>145000</v>
@@ -1268,7 +1268,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G31" t="n">
-        <v>3.15334820747375</v>
+        <v>3.15334796905518</v>
       </c>
       <c r="H31" t="n">
         <v>36000</v>
@@ -1297,7 +1297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076825141907</v>
+        <v>3.18076848983765</v>
       </c>
       <c r="H32" t="n">
         <v>40000</v>
@@ -1326,7 +1326,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420795440674</v>
+        <v>3.14420771598816</v>
       </c>
       <c r="H33" t="n">
         <v>53000</v>
@@ -1355,7 +1355,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.1350679397583</v>
+        <v>3.13506770133972</v>
       </c>
       <c r="H34" t="n">
         <v>13000</v>
@@ -1413,7 +1413,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818853378296</v>
+        <v>3.20818877220154</v>
       </c>
       <c r="H36" t="n">
         <v>50000</v>
@@ -1500,7 +1500,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G39" t="n">
-        <v>3.3270103931427</v>
+        <v>3.32701063156128</v>
       </c>
       <c r="H39" t="n">
         <v>52000</v>
@@ -1529,7 +1529,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H40" t="n">
         <v>48000</v>
@@ -1558,7 +1558,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H41" t="n">
         <v>172000</v>
@@ -1587,7 +1587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057809829712</v>
+        <v>3.82057785987854</v>
       </c>
       <c r="H42" t="n">
         <v>202000</v>
@@ -1703,7 +1703,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G46" t="n">
-        <v>3.72003698348999</v>
+        <v>3.72003674507141</v>
       </c>
       <c r="H46" t="n">
         <v>44000</v>
@@ -1732,7 +1732,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175671577454</v>
+        <v>3.70175647735596</v>
       </c>
       <c r="H47" t="n">
         <v>30000</v>
@@ -1819,7 +1819,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519570350647</v>
+        <v>3.66519594192505</v>
       </c>
       <c r="H50" t="n">
         <v>11000</v>
@@ -1906,7 +1906,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465411186218</v>
+        <v>3.56465435028076</v>
       </c>
       <c r="H53" t="n">
         <v>35000</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55551409721375</v>
+        <v>3.55551433563232</v>
       </c>
       <c r="H56" t="n">
         <v>14000</v>
@@ -2080,7 +2080,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949515342712</v>
+        <v>3.61949491500854</v>
       </c>
       <c r="H59" t="n">
         <v>20000</v>
@@ -2138,7 +2138,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293485641479</v>
+        <v>3.58293461799622</v>
       </c>
       <c r="H61" t="n">
         <v>16000</v>
@@ -2167,7 +2167,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.62863516807556</v>
+        <v>3.62863540649414</v>
       </c>
       <c r="H62" t="n">
         <v>25000</v>
@@ -2196,7 +2196,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207463264465</v>
+        <v>3.59207439422607</v>
       </c>
       <c r="H63" t="n">
         <v>11000</v>
@@ -2225,7 +2225,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G64" t="n">
-        <v>3.60121512413025</v>
+        <v>3.60121464729309</v>
       </c>
       <c r="H64" t="n">
         <v>13000</v>
@@ -2283,7 +2283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.50067329406738</v>
+        <v>3.5006730556488</v>
       </c>
       <c r="H67" t="n">
         <v>24000</v>
@@ -2428,7 +2428,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G71" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H71" t="n">
         <v>9000</v>
@@ -2602,7 +2602,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G77" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417845726013</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2631,7 +2631,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G78" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H78" t="n">
         <v>10500</v>
@@ -2863,7 +2863,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G86" t="n">
-        <v>3.52823734283447</v>
+        <v>3.52823710441589</v>
       </c>
       <c r="H86" t="n">
         <v>5000</v>
@@ -2950,7 +2950,7 @@
         <v>4</v>
       </c>
       <c r="G89" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H89" t="n">
         <v>9000</v>
@@ -2979,7 +2979,7 @@
         <v>4</v>
       </c>
       <c r="G90" t="n">
-        <v>3.67524743080139</v>
+        <v>3.67524719238281</v>
       </c>
       <c r="H90" t="n">
         <v>9000</v>
@@ -3298,7 +3298,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H101" t="n">
         <v>184500</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3762,7 +3762,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G117" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H117" t="n">
         <v>118000</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4284,7 +4284,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H135" t="n">
         <v>150000</v>
@@ -4458,7 +4458,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G141" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H141" t="n">
         <v>64000</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95690965652466</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015790939331</v>
+        <v>7.92015695571899</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4922,7 +4922,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.69964361190796</v>
+        <v>7.6996431350708</v>
       </c>
       <c r="H157" t="n">
         <v>22500</v>
@@ -5038,7 +5038,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G161" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H161" t="n">
         <v>4000</v>
@@ -5154,7 +5154,7 @@
         <v>8</v>
       </c>
       <c r="G165" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H165" t="n">
         <v>25000</v>
@@ -5183,7 +5183,7 @@
         <v>8</v>
       </c>
       <c r="G166" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H166" t="n">
         <v>25500</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691061019897</v>
+        <v>7.95690965652466</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5386,7 +5386,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.3611888885498</v>
+        <v>8.36118793487549</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5444,7 +5444,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H175" t="n">
         <v>33500</v>
@@ -5473,7 +5473,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H183" t="n">
         <v>33500</v>
@@ -5705,7 +5705,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H184" t="n">
         <v>12000</v>
@@ -5734,7 +5734,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588153839111</v>
+        <v>7.51588106155396</v>
       </c>
       <c r="H185" t="n">
         <v>12500</v>
@@ -5763,7 +5763,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G186" t="n">
-        <v>7.53425741195679</v>
+        <v>7.53425693511963</v>
       </c>
       <c r="H186" t="n">
         <v>13000</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938598632812</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5879,7 +5879,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H190" t="n">
         <v>36500</v>
@@ -5908,7 +5908,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801996231079</v>
       </c>
       <c r="H191" t="n">
         <v>28000</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289091110229</v>
+        <v>7.66289043426514</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -5995,7 +5995,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>7.62613868713379</v>
+        <v>7.62613821029663</v>
       </c>
       <c r="H194" t="n">
         <v>11500</v>
@@ -6024,7 +6024,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G195" t="n">
-        <v>7.6077618598938</v>
+        <v>7.60776138305664</v>
       </c>
       <c r="H195" t="n">
         <v>15000</v>
@@ -6053,7 +6053,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6256,7 +6256,7 @@
         <v>8</v>
       </c>
       <c r="G203" t="n">
-        <v>7.35049486160278</v>
+        <v>7.35049438476562</v>
       </c>
       <c r="H203" t="n">
         <v>17500</v>
@@ -6372,7 +6372,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G207" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H207" t="n">
         <v>32500</v>
@@ -6488,7 +6488,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G211" t="n">
-        <v>7.12997961044312</v>
+        <v>7.12998008728027</v>
       </c>
       <c r="H211" t="n">
         <v>10000</v>
@@ -6517,7 +6517,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G212" t="n">
-        <v>7.05647468566895</v>
+        <v>7.05647420883179</v>
       </c>
       <c r="H212" t="n">
         <v>19500</v>
@@ -6662,7 +6662,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H217" t="n">
         <v>63000</v>
@@ -6720,7 +6720,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H219" t="n">
         <v>7500</v>
@@ -6807,7 +6807,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H222" t="n">
         <v>18500</v>
@@ -6923,7 +6923,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H226" t="n">
         <v>34500</v>
@@ -6981,7 +6981,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>7.16673231124878</v>
+        <v>7.16673278808594</v>
       </c>
       <c r="H228" t="n">
         <v>22000</v>
@@ -7039,7 +7039,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G230" t="n">
-        <v>7.18510818481445</v>
+        <v>7.18510866165161</v>
       </c>
       <c r="H230" t="n">
         <v>11500</v>
@@ -7126,7 +7126,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813776016235</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7155,7 +7155,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H234" t="n">
         <v>37500</v>
@@ -7503,7 +7503,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.6889500617981</v>
+        <v>6.68895053863525</v>
       </c>
       <c r="H246" t="n">
         <v>14000</v>
@@ -7735,7 +7735,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H254" t="n">
         <v>14500</v>
@@ -7851,7 +7851,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G258" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H258" t="n">
         <v>11000</v>
@@ -7880,7 +7880,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G259" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H259" t="n">
         <v>2000</v>
@@ -7996,7 +7996,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G263" t="n">
-        <v>7.09322738647461</v>
+        <v>7.09322690963745</v>
       </c>
       <c r="H263" t="n">
         <v>210500</v>
@@ -8025,7 +8025,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G264" t="n">
-        <v>7.07485103607178</v>
+        <v>7.07485055923462</v>
       </c>
       <c r="H264" t="n">
         <v>31000</v>
@@ -8083,7 +8083,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>6.65219736099243</v>
+        <v>6.65219783782959</v>
       </c>
       <c r="H266" t="n">
         <v>20500</v>
@@ -8373,7 +8373,7 @@
         <v>6.82000017166138</v>
       </c>
       <c r="G276" t="n">
-        <v>6.26629734039307</v>
+        <v>6.26629686355591</v>
       </c>
       <c r="H276" t="n">
         <v>8000</v>
@@ -8576,7 +8576,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G283" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H283" t="n">
         <v>10500</v>
@@ -8634,7 +8634,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G285" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H285" t="n">
         <v>28000</v>
@@ -8692,7 +8692,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G287" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H287" t="n">
         <v>22500</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8808,7 +8808,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>6.0825343132019</v>
+        <v>6.08253383636475</v>
       </c>
       <c r="H291" t="n">
         <v>35000</v>
@@ -8866,7 +8866,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H293" t="n">
         <v>64000</v>
@@ -8924,7 +8924,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H295" t="n">
         <v>12500</v>
@@ -8982,7 +8982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H297" t="n">
         <v>14500</v>
@@ -9069,7 +9069,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H300" t="n">
         <v>39500</v>
@@ -9156,7 +9156,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386138916016</v>
       </c>
       <c r="H303" t="n">
         <v>18000</v>
@@ -9214,7 +9214,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386138916016</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9243,7 +9243,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G306" t="n">
-        <v>6.35817813873291</v>
+        <v>6.35817766189575</v>
       </c>
       <c r="H306" t="n">
         <v>8000</v>
@@ -9272,7 +9272,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548456192017</v>
+        <v>6.27548503875732</v>
       </c>
       <c r="H307" t="n">
         <v>9000</v>
@@ -9475,7 +9475,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>6.16522741317749</v>
+        <v>6.16522693634033</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9620,7 +9620,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H319" t="n">
         <v>15000</v>
@@ -9649,7 +9649,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G320" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H320" t="n">
         <v>43500</v>
@@ -9707,7 +9707,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G322" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H322" t="n">
         <v>1500</v>
@@ -9736,7 +9736,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714811325073</v>
+        <v>5.91714859008789</v>
       </c>
       <c r="H323" t="n">
         <v>7000</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526683807373</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9852,7 +9852,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H327" t="n">
         <v>14080</v>
@@ -9881,7 +9881,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770231246948</v>
+        <v>5.79770278930664</v>
       </c>
       <c r="H328" t="n">
         <v>8871</v>
@@ -9910,7 +9910,7 @@
         <v>6.26999998092651</v>
       </c>
       <c r="G329" t="n">
-        <v>5.76094961166382</v>
+        <v>5.76095008850098</v>
       </c>
       <c r="H329" t="n">
         <v>5878</v>
@@ -9939,7 +9939,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H330" t="n">
         <v>2311</v>
@@ -10084,7 +10084,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980226516724</v>
+        <v>6.33980178833008</v>
       </c>
       <c r="H335" t="n">
         <v>25940</v>
@@ -10171,7 +10171,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H338" t="n">
         <v>7965</v>
@@ -10200,7 +10200,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>6.69813823699951</v>
+        <v>6.69813776016235</v>
       </c>
       <c r="H339" t="n">
         <v>40701</v>
@@ -10229,7 +10229,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G340" t="n">
-        <v>6.5419397354126</v>
+        <v>6.54194021224976</v>
       </c>
       <c r="H340" t="n">
         <v>13709</v>
@@ -10345,7 +10345,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.3214259147644</v>
+        <v>6.32142543792725</v>
       </c>
       <c r="H344" t="n">
         <v>13218</v>
@@ -10374,7 +10374,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H345" t="n">
         <v>2764</v>
@@ -10403,7 +10403,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G346" t="n">
-        <v>6.10091018676758</v>
+        <v>6.10090970993042</v>
       </c>
       <c r="H346" t="n">
         <v>5191</v>
@@ -10635,7 +10635,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H354" t="n">
         <v>17836</v>
@@ -10664,7 +10664,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342546463013</v>
+        <v>5.39342498779297</v>
       </c>
       <c r="H355" t="n">
         <v>1874</v>
@@ -10722,7 +10722,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936681747437</v>
       </c>
       <c r="H357" t="n">
         <v>2284</v>
@@ -10751,7 +10751,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530673980713</v>
+        <v>5.48530626296997</v>
       </c>
       <c r="H358" t="n">
         <v>3234</v>
@@ -10780,7 +10780,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H359" t="n">
         <v>3097</v>
@@ -10838,7 +10838,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G361" t="n">
-        <v>5.46693086624146</v>
+        <v>5.4669303894043</v>
       </c>
       <c r="H361" t="n">
         <v>1880</v>
@@ -10925,7 +10925,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936681747437</v>
       </c>
       <c r="H364" t="n">
         <v>1105</v>
@@ -10983,7 +10983,7 @@
         <v>6.15000009536743</v>
       </c>
       <c r="G366" t="n">
-        <v>5.65069246292114</v>
+        <v>5.6506929397583</v>
       </c>
       <c r="H366" t="n">
         <v>6216</v>
@@ -11012,7 +11012,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G367" t="n">
-        <v>5.46693086624146</v>
+        <v>5.4669303894043</v>
       </c>
       <c r="H367" t="n">
         <v>3574</v>
@@ -11041,7 +11041,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H368" t="n">
         <v>11426</v>
@@ -11070,7 +11070,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G369" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H369" t="n">
         <v>4280</v>
@@ -11128,7 +11128,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G371" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H371" t="n">
         <v>6334</v>
@@ -11244,7 +11244,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H375" t="n">
         <v>9545</v>
@@ -11389,7 +11389,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H380" t="n">
         <v>352</v>
@@ -11418,7 +11418,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H381" t="n">
         <v>5665</v>
@@ -11650,7 +11650,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932643890381</v>
+        <v>5.77932691574097</v>
       </c>
       <c r="H389" t="n">
         <v>6221</v>
@@ -11679,7 +11679,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H390" t="n">
         <v>5008</v>
@@ -11708,7 +11708,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G391" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H391" t="n">
         <v>4247</v>
@@ -11737,7 +11737,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G392" t="n">
-        <v>5.80689144134521</v>
+        <v>5.80689096450806</v>
       </c>
       <c r="H392" t="n">
         <v>2786</v>
@@ -11911,7 +11911,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>6.16522741317749</v>
+        <v>6.16522693634033</v>
       </c>
       <c r="H398" t="n">
         <v>1789</v>
@@ -12056,7 +12056,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364366531372</v>
+        <v>5.84364318847656</v>
       </c>
       <c r="H403" t="n">
         <v>2709</v>
@@ -12143,7 +12143,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G406" t="n">
-        <v>5.88039541244507</v>
+        <v>5.88039588928223</v>
       </c>
       <c r="H406" t="n">
         <v>1830</v>
@@ -12172,7 +12172,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>5.86202001571655</v>
+        <v>5.86201953887939</v>
       </c>
       <c r="H407" t="n">
         <v>1611</v>
@@ -12230,7 +12230,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.83445501327515</v>
+        <v>5.8344554901123</v>
       </c>
       <c r="H409" t="n">
         <v>529</v>
@@ -12259,7 +12259,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.8987717628479</v>
+        <v>5.89877223968506</v>
       </c>
       <c r="H410" t="n">
         <v>1853</v>
@@ -12317,7 +12317,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607818603516</v>
+        <v>5.81607866287231</v>
       </c>
       <c r="H412" t="n">
         <v>2753</v>
@@ -12375,7 +12375,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.78851461410522</v>
+        <v>5.78851413726807</v>
       </c>
       <c r="H414" t="n">
         <v>7162</v>
@@ -12665,7 +12665,7 @@
         <v>5.84999990463257</v>
       </c>
       <c r="G424" t="n">
-        <v>5.37504959106445</v>
+        <v>5.37504911422729</v>
       </c>
       <c r="H424" t="n">
         <v>2411</v>
@@ -12723,7 +12723,7 @@
         <v>5.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>5.42098951339722</v>
+        <v>5.42098999023438</v>
       </c>
       <c r="H426" t="n">
         <v>2060</v>
@@ -12781,7 +12781,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27397918701172</v>
+        <v>5.27397966384888</v>
       </c>
       <c r="H428" t="n">
         <v>3146</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.40261363983154</v>
+        <v>5.4026141166687</v>
       </c>
       <c r="H429" t="n">
         <v>4856</v>
@@ -12897,7 +12897,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423681259155</v>
+        <v>5.38423728942871</v>
       </c>
       <c r="H432" t="n">
         <v>3519</v>
@@ -13129,7 +13129,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>4.57568311691284</v>
+        <v>4.57568264007568</v>
       </c>
       <c r="H440" t="n">
         <v>3846</v>
@@ -13187,7 +13187,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H442" t="n">
         <v>3292</v>
@@ -13303,7 +13303,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G446" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H446" t="n">
         <v>2659</v>
@@ -13332,7 +13332,7 @@
         <v>4.67500019073486</v>
       </c>
       <c r="G447" t="n">
-        <v>4.29544544219971</v>
+        <v>4.29544591903687</v>
       </c>
       <c r="H447" t="n">
         <v>15587</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H448" t="n">
         <v>24980</v>
@@ -13390,7 +13390,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H449" t="n">
         <v>13181</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13477,7 +13477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948461532593</v>
+        <v>4.41948509216309</v>
       </c>
       <c r="H452" t="n">
         <v>45286</v>
@@ -13535,7 +13535,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.45164346694946</v>
+        <v>4.4516429901123</v>
       </c>
       <c r="H454" t="n">
         <v>13974</v>
@@ -13564,7 +13564,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>4.38273239135742</v>
+        <v>4.38273286819458</v>
       </c>
       <c r="H455" t="n">
         <v>13871</v>
@@ -13796,7 +13796,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.5297417640686</v>
+        <v>4.52974224090576</v>
       </c>
       <c r="H463" t="n">
         <v>15140</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -14028,7 +14028,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G471" t="n">
-        <v>4.34597969055176</v>
+        <v>4.34598016738892</v>
       </c>
       <c r="H471" t="n">
         <v>3835</v>
@@ -14057,7 +14057,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G472" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H472" t="n">
         <v>2289</v>
@@ -14115,7 +14115,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435556411743</v>
+        <v>4.36435604095459</v>
       </c>
       <c r="H474" t="n">
         <v>5067</v>
@@ -14144,7 +14144,7 @@
         <v>4.78499984741211</v>
       </c>
       <c r="G475" t="n">
-        <v>4.39651489257812</v>
+        <v>4.39651441574097</v>
       </c>
       <c r="H475" t="n">
         <v>1381</v>
@@ -14202,7 +14202,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G477" t="n">
-        <v>4.4929895401001</v>
+        <v>4.49299001693726</v>
       </c>
       <c r="H477" t="n">
         <v>1400</v>
@@ -14260,7 +14260,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G479" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H479" t="n">
         <v>3457</v>
@@ -14318,7 +14318,7 @@
         <v>4.59499979019165</v>
       </c>
       <c r="G481" t="n">
-        <v>4.22193956375122</v>
+        <v>4.22194004058838</v>
       </c>
       <c r="H481" t="n">
         <v>10620</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845530509949</v>
+        <v>3.97845482826233</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14637,7 +14637,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G492" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H492" t="n">
         <v>2046</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144545555115</v>
+        <v>3.83144521713257</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14724,7 +14724,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.85900974273682</v>
+        <v>3.8590099811554</v>
       </c>
       <c r="H495" t="n">
         <v>5373</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469299316406</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -15188,7 +15188,7 @@
         <v>4.82499980926514</v>
       </c>
       <c r="G511" t="n">
-        <v>4.43326759338379</v>
+        <v>4.43326711654663</v>
       </c>
       <c r="H511" t="n">
         <v>4220</v>
@@ -15246,7 +15246,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463361740112</v>
+        <v>4.30463314056396</v>
       </c>
       <c r="H513" t="n">
         <v>1902</v>
@@ -15304,7 +15304,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G515" t="n">
-        <v>4.35516834259033</v>
+        <v>4.35516786575317</v>
       </c>
       <c r="H515" t="n">
         <v>1906</v>
@@ -15739,7 +15739,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H530" t="n">
         <v>3028</v>
@@ -16029,7 +16029,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G540" t="n">
-        <v>4.85132694244385</v>
+        <v>4.85132646560669</v>
       </c>
       <c r="H540" t="n">
         <v>5649</v>
@@ -16203,7 +16203,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G546" t="n">
-        <v>4.53893089294434</v>
+        <v>4.53893041610718</v>
       </c>
       <c r="H546" t="n">
         <v>4076</v>
@@ -16232,7 +16232,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217819213867</v>
+        <v>4.50217771530151</v>
       </c>
       <c r="H547" t="n">
         <v>6999</v>
@@ -16493,7 +16493,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.1530294418335</v>
+        <v>4.15302991867065</v>
       </c>
       <c r="H556" t="n">
         <v>3648</v>
@@ -16522,7 +16522,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546539306641</v>
+        <v>4.12546491622925</v>
       </c>
       <c r="H557" t="n">
         <v>7122</v>
@@ -16551,7 +16551,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>3.90035629272461</v>
+        <v>3.90035653114319</v>
       </c>
       <c r="H558" t="n">
         <v>78936</v>
@@ -16580,7 +16580,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G559" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H559" t="n">
         <v>22855</v>
@@ -16638,7 +16638,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631688117981</v>
+        <v>3.77631664276123</v>
       </c>
       <c r="H561" t="n">
         <v>14097</v>
@@ -16696,7 +16696,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>3.81306934356689</v>
+        <v>3.81306910514832</v>
       </c>
       <c r="H563" t="n">
         <v>7862</v>
@@ -16783,7 +16783,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G566" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417845726013</v>
       </c>
       <c r="H566" t="n">
         <v>6203</v>
@@ -16841,7 +16841,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G568" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H568" t="n">
         <v>8477</v>
@@ -16957,7 +16957,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H572" t="n">
         <v>40710</v>
@@ -16986,7 +16986,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H573" t="n">
         <v>28469</v>
@@ -17015,7 +17015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H574" t="n">
         <v>22621</v>
@@ -17044,7 +17044,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G575" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H575" t="n">
         <v>2675</v>
@@ -17334,7 +17334,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G585" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H585" t="n">
         <v>5627</v>
@@ -17363,7 +17363,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G586" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H586" t="n">
         <v>4755</v>
@@ -17421,7 +17421,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G588" t="n">
-        <v>3.56498980522156</v>
+        <v>3.56499004364014</v>
       </c>
       <c r="H588" t="n">
         <v>2735</v>
@@ -17508,7 +17508,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G591" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H591" t="n">
         <v>12175</v>
@@ -17537,7 +17537,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G592" t="n">
-        <v>3.76712870597839</v>
+        <v>3.76712846755981</v>
       </c>
       <c r="H592" t="n">
         <v>9692</v>
@@ -17595,7 +17595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904940605164</v>
+        <v>3.51904916763306</v>
       </c>
       <c r="H594" t="n">
         <v>20677</v>
@@ -17653,7 +17653,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>3.5466136932373</v>
+        <v>3.54661345481873</v>
       </c>
       <c r="H596" t="n">
         <v>1150</v>
@@ -17682,7 +17682,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G597" t="n">
-        <v>3.53742551803589</v>
+        <v>3.53742527961731</v>
       </c>
       <c r="H597" t="n">
         <v>7488</v>
@@ -17827,7 +17827,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H602" t="n">
         <v>23557</v>
@@ -17885,7 +17885,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.24340558052063</v>
+        <v>3.24340581893921</v>
       </c>
       <c r="H604" t="n">
         <v>8247</v>
@@ -17914,7 +17914,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>3.30772233009338</v>
+        <v>3.30772256851196</v>
       </c>
       <c r="H605" t="n">
         <v>3361</v>
@@ -17972,7 +17972,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>3.32609868049622</v>
+        <v>3.32609891891479</v>
       </c>
       <c r="H607" t="n">
         <v>1705</v>
@@ -18001,7 +18001,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H608" t="n">
         <v>18506</v>
@@ -18030,7 +18030,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H609" t="n">
         <v>2325</v>
@@ -18088,7 +18088,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990113258362</v>
+        <v>3.16990089416504</v>
       </c>
       <c r="H611" t="n">
         <v>4629</v>
@@ -18146,7 +18146,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233660697937</v>
+        <v>3.14233636856079</v>
       </c>
       <c r="H613" t="n">
         <v>1790</v>
@@ -18175,7 +18175,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H614" t="n">
         <v>18656</v>
@@ -18204,7 +18204,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H615" t="n">
         <v>1399</v>
@@ -18233,7 +18233,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H616" t="n">
         <v>4300</v>
@@ -18349,7 +18349,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H620" t="n">
         <v>26152</v>
@@ -18378,7 +18378,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G621" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H621" t="n">
         <v>5112</v>
@@ -18436,7 +18436,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>2.89425730705261</v>
+        <v>2.89425706863403</v>
       </c>
       <c r="H623" t="n">
         <v>25740</v>
@@ -18465,7 +18465,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G624" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H624" t="n">
         <v>2110</v>
@@ -18494,7 +18494,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G625" t="n">
-        <v>2.94019770622253</v>
+        <v>2.94019794464111</v>
       </c>
       <c r="H625" t="n">
         <v>6810</v>
@@ -18523,7 +18523,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857405662537</v>
+        <v>2.95857429504395</v>
       </c>
       <c r="H626" t="n">
         <v>14381</v>
@@ -18552,7 +18552,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G627" t="n">
-        <v>2.93101000785828</v>
+        <v>2.9310097694397</v>
       </c>
       <c r="H627" t="n">
         <v>10185</v>
@@ -42860,6 +42860,35 @@
         <v>12027</v>
       </c>
       <c r="I1465" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1466" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1466" t="n">
+        <v>0.685000002384186</v>
+      </c>
+      <c r="D1466" t="n">
+        <v>0.685000002384186</v>
+      </c>
+      <c r="E1466" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="F1466" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="G1466" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="H1466" t="n">
+        <v>6330</v>
+      </c>
+      <c r="I1466" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -485,7 +485,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.64150023460388</v>
+        <v>2.6414999961853</v>
       </c>
       <c r="H4" t="n">
         <v>186000</v>
@@ -514,7 +514,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66892051696777</v>
+        <v>2.66892075538635</v>
       </c>
       <c r="H5" t="n">
         <v>100000</v>
@@ -543,7 +543,7 @@
         <v>3.53049993515015</v>
       </c>
       <c r="G6" t="n">
-        <v>3.22692632675171</v>
+        <v>3.22692608833313</v>
       </c>
       <c r="H6" t="n">
         <v>588000</v>
@@ -572,7 +572,7 @@
         <v>3.8659999370575</v>
       </c>
       <c r="G7" t="n">
-        <v>3.53357744216919</v>
+        <v>3.53357768058777</v>
       </c>
       <c r="H7" t="n">
         <v>623000</v>
@@ -659,7 +659,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G10" t="n">
-        <v>3.8114378452301</v>
+        <v>3.81143808364868</v>
       </c>
       <c r="H10" t="n">
         <v>389000</v>
@@ -746,7 +746,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5737943649292</v>
+        <v>3.57379412651062</v>
       </c>
       <c r="H13" t="n">
         <v>75000</v>
@@ -804,7 +804,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153304100037</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H15" t="n">
         <v>85000</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583225250244</v>
+        <v>3.44583201408386</v>
       </c>
       <c r="H16" t="n">
         <v>29000</v>
@@ -891,7 +891,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G18" t="n">
-        <v>3.51895308494568</v>
+        <v>3.51895332336426</v>
       </c>
       <c r="H18" t="n">
         <v>36000</v>
@@ -949,7 +949,7 @@
         <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>3.42755222320557</v>
+        <v>3.42755198478699</v>
       </c>
       <c r="H20" t="n">
         <v>37000</v>
@@ -978,7 +978,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G21" t="n">
-        <v>3.26302909851074</v>
+        <v>3.26302933692932</v>
       </c>
       <c r="H21" t="n">
         <v>78000</v>
@@ -1007,7 +1007,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G22" t="n">
-        <v>3.30873036384583</v>
+        <v>3.30873012542725</v>
       </c>
       <c r="H22" t="n">
         <v>17000</v>
@@ -1094,7 +1094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.37271118164062</v>
+        <v>3.3727114200592</v>
       </c>
       <c r="H25" t="n">
         <v>11000</v>
@@ -1123,7 +1123,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>3.31787061691284</v>
+        <v>3.31787037849426</v>
       </c>
       <c r="H26" t="n">
         <v>34000</v>
@@ -1181,7 +1181,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764718055725</v>
+        <v>3.10764741897583</v>
       </c>
       <c r="H28" t="n">
         <v>52000</v>
@@ -1297,7 +1297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076848983765</v>
+        <v>3.18076825141907</v>
       </c>
       <c r="H32" t="n">
         <v>40000</v>
@@ -1355,7 +1355,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.13506770133972</v>
+        <v>3.13506746292114</v>
       </c>
       <c r="H34" t="n">
         <v>13000</v>
@@ -1384,7 +1384,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G35" t="n">
-        <v>3.08936715126038</v>
+        <v>3.0893669128418</v>
       </c>
       <c r="H35" t="n">
         <v>9000</v>
@@ -1442,7 +1442,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443115234375</v>
+        <v>3.35443067550659</v>
       </c>
       <c r="H37" t="n">
         <v>264000</v>
@@ -1471,7 +1471,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G38" t="n">
-        <v>3.41841173171997</v>
+        <v>3.41841197013855</v>
       </c>
       <c r="H38" t="n">
         <v>54000</v>
@@ -1529,7 +1529,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.31787061691284</v>
+        <v>3.31787037849426</v>
       </c>
       <c r="H40" t="n">
         <v>48000</v>
@@ -1587,7 +1587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057785987854</v>
+        <v>3.82057809829712</v>
       </c>
       <c r="H42" t="n">
         <v>202000</v>
@@ -1616,7 +1616,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71089625358582</v>
+        <v>3.71089601516724</v>
       </c>
       <c r="H43" t="n">
         <v>172000</v>
@@ -1645,7 +1645,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.65605545043945</v>
+        <v>3.65605568885803</v>
       </c>
       <c r="H44" t="n">
         <v>80000</v>
@@ -1732,7 +1732,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G47" t="n">
-        <v>3.70175647735596</v>
+        <v>3.70175623893738</v>
       </c>
       <c r="H47" t="n">
         <v>30000</v>
@@ -1790,7 +1790,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H49" t="n">
         <v>51000</v>
@@ -1819,7 +1819,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519594192505</v>
+        <v>3.66519570350647</v>
       </c>
       <c r="H50" t="n">
         <v>11000</v>
@@ -1848,7 +1848,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.6834762096405</v>
+        <v>3.68347597122192</v>
       </c>
       <c r="H51" t="n">
         <v>21000</v>
@@ -1964,7 +1964,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153304100037</v>
+        <v>3.49153280258179</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.55551433563232</v>
+        <v>3.55551409721375</v>
       </c>
       <c r="H56" t="n">
         <v>14000</v>
@@ -2080,7 +2080,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949491500854</v>
+        <v>3.61949467658997</v>
       </c>
       <c r="H59" t="n">
         <v>20000</v>
@@ -2138,7 +2138,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G61" t="n">
-        <v>3.58293461799622</v>
+        <v>3.58293437957764</v>
       </c>
       <c r="H61" t="n">
         <v>16000</v>
@@ -2167,7 +2167,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.62863540649414</v>
+        <v>3.62863516807556</v>
       </c>
       <c r="H62" t="n">
         <v>25000</v>
@@ -2196,7 +2196,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207439422607</v>
+        <v>3.59207463264465</v>
       </c>
       <c r="H63" t="n">
         <v>11000</v>
@@ -2341,7 +2341,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G68" t="n">
-        <v>3.62011861801147</v>
+        <v>3.62011885643005</v>
       </c>
       <c r="H68" t="n">
         <v>10000</v>
@@ -2370,7 +2370,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2399,7 +2399,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H70" t="n">
         <v>14000</v>
@@ -2457,7 +2457,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H72" t="n">
         <v>23000</v>
@@ -2486,7 +2486,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.50986123085022</v>
+        <v>3.50986099243164</v>
       </c>
       <c r="H73" t="n">
         <v>17000</v>
@@ -2515,7 +2515,7 @@
         <v>3.75</v>
       </c>
       <c r="G74" t="n">
-        <v>3.44554448127747</v>
+        <v>3.44554424285889</v>
       </c>
       <c r="H74" t="n">
         <v>9000</v>
@@ -2602,7 +2602,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G77" t="n">
-        <v>3.57417845726013</v>
+        <v>3.57417821884155</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2776,7 +2776,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>3.50986123085022</v>
+        <v>3.50986099243164</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G86" t="n">
-        <v>3.52823710441589</v>
+        <v>3.52823758125305</v>
       </c>
       <c r="H86" t="n">
         <v>5000</v>
@@ -2921,7 +2921,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.65687108039856</v>
+        <v>3.65687131881714</v>
       </c>
       <c r="H88" t="n">
         <v>31500</v>
@@ -3066,7 +3066,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G93" t="n">
-        <v>3.74875211715698</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H93" t="n">
         <v>51500</v>
@@ -3124,7 +3124,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G95" t="n">
-        <v>3.89576148986816</v>
+        <v>3.8957622051239</v>
       </c>
       <c r="H95" t="n">
         <v>105500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520824432373</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3269,7 +3269,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G100" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H100" t="n">
         <v>243500</v>
@@ -3298,7 +3298,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G101" t="n">
-        <v>5.4026141166687</v>
+        <v>5.40261363983154</v>
       </c>
       <c r="H101" t="n">
         <v>184500</v>
@@ -3443,7 +3443,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G106" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H106" t="n">
         <v>15000</v>
@@ -3501,7 +3501,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G108" t="n">
-        <v>5.36586093902588</v>
+        <v>5.36586141586304</v>
       </c>
       <c r="H108" t="n">
         <v>19000</v>
@@ -3559,7 +3559,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124761581421</v>
       </c>
       <c r="H110" t="n">
         <v>38500</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3733,7 +3733,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G116" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H116" t="n">
         <v>89000</v>
@@ -3791,7 +3791,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G118" t="n">
-        <v>7.49750423431396</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H118" t="n">
         <v>22500</v>
@@ -3849,7 +3849,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G120" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H120" t="n">
         <v>58500</v>
@@ -4110,7 +4110,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433673858643</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4284,7 +4284,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H135" t="n">
         <v>150000</v>
@@ -4400,7 +4400,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G139" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H139" t="n">
         <v>19500</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4516,7 +4516,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G143" t="n">
-        <v>8.15904808044434</v>
+        <v>8.15904903411865</v>
       </c>
       <c r="H143" t="n">
         <v>145500</v>
@@ -4545,7 +4545,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G144" t="n">
-        <v>8.06716823577881</v>
+        <v>8.06716728210449</v>
       </c>
       <c r="H144" t="n">
         <v>182000</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4603,7 +4603,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G146" t="n">
-        <v>8.08554363250732</v>
+        <v>8.08554458618164</v>
       </c>
       <c r="H146" t="n">
         <v>55500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366283416748</v>
+        <v>7.99366331100464</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4661,7 +4661,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G148" t="n">
-        <v>8.06716823577881</v>
+        <v>8.06716728210449</v>
       </c>
       <c r="H148" t="n">
         <v>31000</v>
@@ -4690,7 +4690,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G149" t="n">
-        <v>8.14067268371582</v>
+        <v>8.14067363739014</v>
       </c>
       <c r="H149" t="n">
         <v>53500</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95690965652466</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4748,7 +4748,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G151" t="n">
-        <v>7.90178251266479</v>
+        <v>7.90178298950195</v>
       </c>
       <c r="H151" t="n">
         <v>20500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4835,7 +4835,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G154" t="n">
-        <v>7.73639535903931</v>
+        <v>7.73639583587646</v>
       </c>
       <c r="H154" t="n">
         <v>8500</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015695571899</v>
+        <v>7.92015838623047</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4922,7 +4922,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.6996431350708</v>
+        <v>7.69964408874512</v>
       </c>
       <c r="H157" t="n">
         <v>22500</v>
@@ -4951,7 +4951,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G158" t="n">
-        <v>7.79152297973633</v>
+        <v>7.7915244102478</v>
       </c>
       <c r="H158" t="n">
         <v>15500</v>
@@ -4980,7 +4980,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G159" t="n">
-        <v>7.79152297973633</v>
+        <v>7.7915244102478</v>
       </c>
       <c r="H159" t="n">
         <v>5500</v>
@@ -5096,7 +5096,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G163" t="n">
-        <v>7.49750423431396</v>
+        <v>7.49750471115112</v>
       </c>
       <c r="H163" t="n">
         <v>21000</v>
@@ -5241,7 +5241,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G168" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H168" t="n">
         <v>26500</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95690965652466</v>
+        <v>7.95691013336182</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5357,7 +5357,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G172" t="n">
-        <v>8.14067268371582</v>
+        <v>8.14067363739014</v>
       </c>
       <c r="H172" t="n">
         <v>81500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665393829346</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5444,7 +5444,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801996231079</v>
+        <v>7.71801948547363</v>
       </c>
       <c r="H175" t="n">
         <v>33500</v>
@@ -5473,7 +5473,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665393829346</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.8466534614563</v>
+        <v>7.84665393829346</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H183" t="n">
         <v>33500</v>
@@ -5705,7 +5705,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263328552246</v>
+        <v>7.55263376235962</v>
       </c>
       <c r="H184" t="n">
         <v>12000</v>
@@ -5734,7 +5734,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588106155396</v>
+        <v>7.51588153839111</v>
       </c>
       <c r="H185" t="n">
         <v>12500</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938598632812</v>
+        <v>7.58938646316528</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5879,7 +5879,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263328552246</v>
+        <v>7.55263376235962</v>
       </c>
       <c r="H190" t="n">
         <v>36500</v>
@@ -5908,7 +5908,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801996231079</v>
+        <v>7.71801948547363</v>
       </c>
       <c r="H191" t="n">
         <v>28000</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289043426514</v>
+        <v>7.66289138793945</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -6024,7 +6024,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G195" t="n">
-        <v>7.60776138305664</v>
+        <v>7.60776233673096</v>
       </c>
       <c r="H195" t="n">
         <v>15000</v>
@@ -6053,7 +6053,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100915908813</v>
+        <v>7.57100963592529</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.47912883758545</v>
+        <v>7.47912836074829</v>
       </c>
       <c r="H197" t="n">
         <v>15000</v>
@@ -6111,7 +6111,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>7.42399978637695</v>
+        <v>7.42399930953979</v>
       </c>
       <c r="H198" t="n">
         <v>22500</v>
@@ -6140,7 +6140,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G199" t="n">
-        <v>7.42399978637695</v>
+        <v>7.42399930953979</v>
       </c>
       <c r="H199" t="n">
         <v>6500</v>
@@ -6314,7 +6314,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>7.31374216079712</v>
+        <v>7.31374263763428</v>
       </c>
       <c r="H205" t="n">
         <v>14500</v>
@@ -6459,7 +6459,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G210" t="n">
-        <v>7.24023723602295</v>
+        <v>7.24023771286011</v>
       </c>
       <c r="H210" t="n">
         <v>10500</v>
@@ -6517,7 +6517,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G212" t="n">
-        <v>7.05647420883179</v>
+        <v>7.0564751625061</v>
       </c>
       <c r="H212" t="n">
         <v>19500</v>
@@ -6546,7 +6546,7 @@
         <v>7.5</v>
       </c>
       <c r="G213" t="n">
-        <v>6.89108896255493</v>
+        <v>6.89108848571777</v>
       </c>
       <c r="H213" t="n">
         <v>14000</v>
@@ -6604,7 +6604,7 @@
         <v>7.5</v>
       </c>
       <c r="G215" t="n">
-        <v>6.89108896255493</v>
+        <v>6.89108848571777</v>
       </c>
       <c r="H215" t="n">
         <v>9500</v>
@@ -6662,7 +6662,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H217" t="n">
         <v>63000</v>
@@ -6691,7 +6691,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H218" t="n">
         <v>22500</v>
@@ -6720,7 +6720,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H219" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>6.57869243621826</v>
+        <v>6.57869291305542</v>
       </c>
       <c r="H220" t="n">
         <v>12000</v>
@@ -6807,7 +6807,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H222" t="n">
         <v>18500</v>
@@ -6836,7 +6836,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H223" t="n">
         <v>9000</v>
@@ -6865,7 +6865,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433673858643</v>
       </c>
       <c r="H224" t="n">
         <v>31500</v>
@@ -6923,7 +6923,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G226" t="n">
-        <v>7.16673278808594</v>
+        <v>7.16673231124878</v>
       </c>
       <c r="H226" t="n">
         <v>34500</v>
@@ -6981,7 +6981,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G228" t="n">
-        <v>7.16673278808594</v>
+        <v>7.16673231124878</v>
       </c>
       <c r="H228" t="n">
         <v>22000</v>
@@ -7126,7 +7126,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G233" t="n">
-        <v>6.69813776016235</v>
+        <v>6.69813823699951</v>
       </c>
       <c r="H233" t="n">
         <v>31500</v>
@@ -7155,7 +7155,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G234" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H234" t="n">
         <v>37500</v>
@@ -7213,7 +7213,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G236" t="n">
-        <v>6.91865348815918</v>
+        <v>6.91865301132202</v>
       </c>
       <c r="H236" t="n">
         <v>4500</v>
@@ -7242,7 +7242,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>6.85433626174927</v>
+        <v>6.85433673858643</v>
       </c>
       <c r="H237" t="n">
         <v>14500</v>
@@ -7300,7 +7300,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G239" t="n">
-        <v>6.91865348815918</v>
+        <v>6.91865301132202</v>
       </c>
       <c r="H239" t="n">
         <v>8000</v>
@@ -7329,7 +7329,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G240" t="n">
-        <v>6.91865348815918</v>
+        <v>6.91865301132202</v>
       </c>
       <c r="H240" t="n">
         <v>10000</v>
@@ -7416,7 +7416,7 @@
         <v>7.5</v>
       </c>
       <c r="G243" t="n">
-        <v>6.89108896255493</v>
+        <v>6.89108848571777</v>
       </c>
       <c r="H243" t="n">
         <v>10500</v>
@@ -7503,7 +7503,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G246" t="n">
-        <v>6.68895053863525</v>
+        <v>6.6889500617981</v>
       </c>
       <c r="H246" t="n">
         <v>14000</v>
@@ -7532,7 +7532,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G247" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H247" t="n">
         <v>19000</v>
@@ -7561,7 +7561,7 @@
         <v>7</v>
       </c>
       <c r="G248" t="n">
-        <v>6.43168306350708</v>
+        <v>6.43168258666992</v>
       </c>
       <c r="H248" t="n">
         <v>15000</v>
@@ -7590,7 +7590,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G249" t="n">
-        <v>6.38574171066284</v>
+        <v>6.3857421875</v>
       </c>
       <c r="H249" t="n">
         <v>26000</v>
@@ -7648,7 +7648,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G251" t="n">
-        <v>6.57869243621826</v>
+        <v>6.57869291305542</v>
       </c>
       <c r="H251" t="n">
         <v>5000</v>
@@ -7706,7 +7706,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G253" t="n">
-        <v>6.38574171066284</v>
+        <v>6.3857421875</v>
       </c>
       <c r="H253" t="n">
         <v>14500</v>
@@ -7764,7 +7764,7 @@
         <v>6.8899998664856</v>
       </c>
       <c r="G255" t="n">
-        <v>6.3306131362915</v>
+        <v>6.33061361312866</v>
       </c>
       <c r="H255" t="n">
         <v>17000</v>
@@ -7793,7 +7793,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>6.15603923797607</v>
+        <v>6.15603876113892</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7938,7 +7938,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H261" t="n">
         <v>25000</v>
@@ -8112,7 +8112,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G267" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H267" t="n">
         <v>18000</v>
@@ -8170,7 +8170,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G269" t="n">
-        <v>6.55112886428833</v>
+        <v>6.55112838745117</v>
       </c>
       <c r="H269" t="n">
         <v>7500</v>
@@ -8199,7 +8199,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G270" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H270" t="n">
         <v>11500</v>
@@ -8257,7 +8257,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G272" t="n">
-        <v>6.49600028991699</v>
+        <v>6.49599981307983</v>
       </c>
       <c r="H272" t="n">
         <v>5500</v>
@@ -8315,7 +8315,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>6.44087076187134</v>
+        <v>6.44087171554565</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8489,7 +8489,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H280" t="n">
         <v>26500</v>
@@ -8547,7 +8547,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73338556289673</v>
+        <v>5.73338603973389</v>
       </c>
       <c r="H282" t="n">
         <v>18500</v>
@@ -8605,7 +8605,7 @@
         <v>6.23000001907349</v>
       </c>
       <c r="G284" t="n">
-        <v>5.72419738769531</v>
+        <v>5.72419786453247</v>
       </c>
       <c r="H284" t="n">
         <v>12000</v>
@@ -8663,7 +8663,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G286" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H286" t="n">
         <v>39500</v>
@@ -8721,7 +8721,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G288" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H288" t="n">
         <v>11000</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526683807373</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8808,7 +8808,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G291" t="n">
-        <v>6.08253383636475</v>
+        <v>6.0825343132019</v>
       </c>
       <c r="H291" t="n">
         <v>35000</v>
@@ -8924,7 +8924,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H295" t="n">
         <v>12500</v>
@@ -8953,7 +8953,7 @@
         <v>7.13000011444092</v>
       </c>
       <c r="G296" t="n">
-        <v>6.55112886428833</v>
+        <v>6.55112838745117</v>
       </c>
       <c r="H296" t="n">
         <v>10000</v>
@@ -8982,7 +8982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H297" t="n">
         <v>14500</v>
@@ -9040,7 +9040,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>6.569504737854</v>
+        <v>6.56950426101685</v>
       </c>
       <c r="H299" t="n">
         <v>6000</v>
@@ -9069,7 +9069,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356433868408</v>
+        <v>6.52356386184692</v>
       </c>
       <c r="H300" t="n">
         <v>39500</v>
@@ -9098,7 +9098,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G301" t="n">
-        <v>6.45924758911133</v>
+        <v>6.45924711227417</v>
       </c>
       <c r="H301" t="n">
         <v>43000</v>
@@ -9127,7 +9127,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>6.45005893707275</v>
+        <v>6.45005941390991</v>
       </c>
       <c r="H302" t="n">
         <v>17500</v>
@@ -9156,7 +9156,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>6.29386138916016</v>
+        <v>6.293860912323</v>
       </c>
       <c r="H303" t="n">
         <v>18000</v>
@@ -9185,7 +9185,7 @@
         <v>6.75</v>
       </c>
       <c r="G304" t="n">
-        <v>6.201979637146</v>
+        <v>6.20198011398315</v>
       </c>
       <c r="H304" t="n">
         <v>16000</v>
@@ -9214,7 +9214,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>6.29386138916016</v>
+        <v>6.293860912323</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9272,7 +9272,7 @@
         <v>6.82999992370605</v>
       </c>
       <c r="G307" t="n">
-        <v>6.27548503875732</v>
+        <v>6.27548456192017</v>
       </c>
       <c r="H307" t="n">
         <v>9000</v>
@@ -9301,7 +9301,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G308" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H308" t="n">
         <v>4500</v>
@@ -9388,7 +9388,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G311" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H311" t="n">
         <v>500</v>
@@ -9475,7 +9475,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>6.16522693634033</v>
+        <v>6.16522741317749</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9562,7 +9562,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>6.09172296524048</v>
+        <v>6.09172248840332</v>
       </c>
       <c r="H317" t="n">
         <v>1500</v>
@@ -9620,7 +9620,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G319" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H319" t="n">
         <v>15000</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526683807373</v>
+        <v>5.82526731491089</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9794,7 +9794,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H325" t="n">
         <v>13000</v>
@@ -9823,7 +9823,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G326" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H326" t="n">
         <v>1450</v>
@@ -9997,7 +9997,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H332" t="n">
         <v>4456</v>
@@ -10026,7 +10026,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H333" t="n">
         <v>2022</v>
@@ -10142,7 +10142,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H337" t="n">
         <v>15456</v>
@@ -10200,7 +10200,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G339" t="n">
-        <v>6.69813776016235</v>
+        <v>6.69813823699951</v>
       </c>
       <c r="H339" t="n">
         <v>40701</v>
@@ -10316,7 +10316,7 @@
         <v>7</v>
       </c>
       <c r="G343" t="n">
-        <v>6.43168306350708</v>
+        <v>6.43168258666992</v>
       </c>
       <c r="H343" t="n">
         <v>3966</v>
@@ -10374,7 +10374,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H345" t="n">
         <v>2764</v>
@@ -10403,7 +10403,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G346" t="n">
-        <v>6.10090970993042</v>
+        <v>6.10091066360474</v>
       </c>
       <c r="H346" t="n">
         <v>5191</v>
@@ -10432,7 +10432,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G347" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H347" t="n">
         <v>510</v>
@@ -10461,7 +10461,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G348" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H348" t="n">
         <v>1520</v>
@@ -10490,7 +10490,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G349" t="n">
-        <v>6.07334613800049</v>
+        <v>6.07334661483765</v>
       </c>
       <c r="H349" t="n">
         <v>8810</v>
@@ -10548,7 +10548,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>6.18360328674316</v>
+        <v>6.18360376358032</v>
       </c>
       <c r="H351" t="n">
         <v>2077</v>
@@ -10635,7 +10635,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27397966384888</v>
+        <v>5.27398014068604</v>
       </c>
       <c r="H354" t="n">
         <v>17836</v>
@@ -10664,7 +10664,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342498779297</v>
+        <v>5.39342594146729</v>
       </c>
       <c r="H355" t="n">
         <v>1874</v>
@@ -10722,7 +10722,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936681747437</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H357" t="n">
         <v>2284</v>
@@ -10751,7 +10751,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G358" t="n">
-        <v>5.48530626296997</v>
+        <v>5.48530673980713</v>
       </c>
       <c r="H358" t="n">
         <v>3234</v>
@@ -10780,7 +10780,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G359" t="n">
-        <v>5.4026141166687</v>
+        <v>5.40261363983154</v>
       </c>
       <c r="H359" t="n">
         <v>3097</v>
@@ -10925,7 +10925,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936681747437</v>
+        <v>5.43936634063721</v>
       </c>
       <c r="H364" t="n">
         <v>1105</v>
@@ -11099,7 +11099,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120723724365</v>
+        <v>5.87120771408081</v>
       </c>
       <c r="H370" t="n">
         <v>3154</v>
@@ -11186,7 +11186,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471216201782</v>
+        <v>5.94471263885498</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.07334613800049</v>
+        <v>6.07334661483765</v>
       </c>
       <c r="H374" t="n">
         <v>4630</v>
@@ -11244,7 +11244,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467273712158</v>
+        <v>6.28467321395874</v>
       </c>
       <c r="H375" t="n">
         <v>9545</v>
@@ -11273,7 +11273,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G376" t="n">
-        <v>6.04578161239624</v>
+        <v>6.0457820892334</v>
       </c>
       <c r="H376" t="n">
         <v>7667</v>
@@ -11302,7 +11302,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G377" t="n">
-        <v>5.73338556289673</v>
+        <v>5.73338603973389</v>
       </c>
       <c r="H377" t="n">
         <v>6848</v>
@@ -11360,7 +11360,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>5.68744516372681</v>
+        <v>5.68744564056396</v>
       </c>
       <c r="H379" t="n">
         <v>2986</v>
@@ -11389,7 +11389,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G380" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H380" t="n">
         <v>352</v>
@@ -11418,7 +11418,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.78851413726807</v>
+        <v>5.78851509094238</v>
       </c>
       <c r="H381" t="n">
         <v>5665</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.59556436538696</v>
+        <v>5.59556484222412</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11563,7 +11563,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>5.58637571334839</v>
+        <v>5.58637619018555</v>
       </c>
       <c r="H386" t="n">
         <v>2950</v>
@@ -11621,7 +11621,7 @@
         <v>6.25</v>
       </c>
       <c r="G388" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H388" t="n">
         <v>1978</v>
@@ -11679,7 +11679,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.78851413726807</v>
+        <v>5.78851509094238</v>
       </c>
       <c r="H390" t="n">
         <v>5008</v>
@@ -11911,7 +11911,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G398" t="n">
-        <v>6.16522693634033</v>
+        <v>6.16522741317749</v>
       </c>
       <c r="H398" t="n">
         <v>1789</v>
@@ -11998,7 +11998,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.9906530380249</v>
+        <v>5.99065351486206</v>
       </c>
       <c r="H401" t="n">
         <v>4770</v>
@@ -12027,7 +12027,7 @@
         <v>6.42999982833862</v>
       </c>
       <c r="G402" t="n">
-        <v>5.90795993804932</v>
+        <v>5.90795946121216</v>
       </c>
       <c r="H402" t="n">
         <v>2037</v>
@@ -12085,7 +12085,7 @@
         <v>6.36999988555908</v>
       </c>
       <c r="G404" t="n">
-        <v>5.85283088684082</v>
+        <v>5.85283136367798</v>
       </c>
       <c r="H404" t="n">
         <v>2104</v>
@@ -12114,7 +12114,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G405" t="n">
-        <v>5.9539008140564</v>
+        <v>5.95390033721924</v>
       </c>
       <c r="H405" t="n">
         <v>1670</v>
@@ -12201,7 +12201,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G408" t="n">
-        <v>5.73338556289673</v>
+        <v>5.73338603973389</v>
       </c>
       <c r="H408" t="n">
         <v>4978</v>
@@ -12230,7 +12230,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G409" t="n">
-        <v>5.8344554901123</v>
+        <v>5.83445501327515</v>
       </c>
       <c r="H409" t="n">
         <v>529</v>
@@ -12346,7 +12346,7 @@
         <v>6.25</v>
       </c>
       <c r="G413" t="n">
-        <v>5.74257373809814</v>
+        <v>5.7425742149353</v>
       </c>
       <c r="H413" t="n">
         <v>2441</v>
@@ -12375,7 +12375,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.78851413726807</v>
+        <v>5.78851509094238</v>
       </c>
       <c r="H414" t="n">
         <v>7162</v>
@@ -12462,7 +12462,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124713897705</v>
+        <v>5.53124761581421</v>
       </c>
       <c r="H417" t="n">
         <v>1848</v>
@@ -12607,7 +12607,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G422" t="n">
-        <v>5.64150428771973</v>
+        <v>5.64150476455688</v>
       </c>
       <c r="H422" t="n">
         <v>3644</v>
@@ -12781,7 +12781,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27397966384888</v>
+        <v>5.27398014068604</v>
       </c>
       <c r="H428" t="n">
         <v>3146</v>
@@ -12810,7 +12810,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G429" t="n">
-        <v>5.4026141166687</v>
+        <v>5.40261363983154</v>
       </c>
       <c r="H429" t="n">
         <v>4856</v>
@@ -12839,7 +12839,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>5.31992053985596</v>
+        <v>5.31992101669312</v>
       </c>
       <c r="H430" t="n">
         <v>4924</v>
@@ -12897,7 +12897,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423728942871</v>
+        <v>5.38423776626587</v>
       </c>
       <c r="H432" t="n">
         <v>3519</v>
@@ -12955,7 +12955,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G434" t="n">
-        <v>5.32910823822021</v>
+        <v>5.32910919189453</v>
       </c>
       <c r="H434" t="n">
         <v>3264</v>
@@ -12984,7 +12984,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346488952637</v>
+        <v>5.05346536636353</v>
       </c>
       <c r="H435" t="n">
         <v>15369</v>
@@ -13013,7 +13013,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>4.86970281600952</v>
+        <v>4.86970329284668</v>
       </c>
       <c r="H436" t="n">
         <v>13180</v>
@@ -13042,7 +13042,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73188066482544</v>
+        <v>4.73188161849976</v>
       </c>
       <c r="H437" t="n">
         <v>15638</v>
@@ -13071,7 +13071,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.6767520904541</v>
+        <v>4.67675256729126</v>
       </c>
       <c r="H438" t="n">
         <v>13127</v>
@@ -13129,7 +13129,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>4.57568264007568</v>
+        <v>4.57568311691284</v>
       </c>
       <c r="H440" t="n">
         <v>3846</v>
@@ -13187,7 +13187,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H442" t="n">
         <v>3292</v>
@@ -13274,7 +13274,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G445" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760429382324</v>
       </c>
       <c r="H445" t="n">
         <v>10951</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405899047852</v>
+        <v>4.59405946731567</v>
       </c>
       <c r="H448" t="n">
         <v>24980</v>
@@ -13390,7 +13390,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G449" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H449" t="n">
         <v>13181</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13506,7 +13506,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G453" t="n">
-        <v>4.32760334014893</v>
+        <v>4.32760429382324</v>
       </c>
       <c r="H453" t="n">
         <v>24237</v>
@@ -13535,7 +13535,7 @@
         <v>4.84499979019165</v>
       </c>
       <c r="G454" t="n">
-        <v>4.4516429901123</v>
+        <v>4.45164346694946</v>
       </c>
       <c r="H454" t="n">
         <v>13974</v>
@@ -13564,7 +13564,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G455" t="n">
-        <v>4.38273286819458</v>
+        <v>4.38273239135742</v>
       </c>
       <c r="H455" t="n">
         <v>13871</v>
@@ -13622,7 +13622,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G457" t="n">
-        <v>4.48839616775513</v>
+        <v>4.48839569091797</v>
       </c>
       <c r="H457" t="n">
         <v>11036</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13680,7 +13680,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47461318969727</v>
+        <v>4.47461414337158</v>
       </c>
       <c r="H459" t="n">
         <v>11746</v>
@@ -13709,7 +13709,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.45623683929443</v>
+        <v>4.45623731613159</v>
       </c>
       <c r="H460" t="n">
         <v>2411</v>
@@ -13796,7 +13796,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.52974224090576</v>
+        <v>4.52974271774292</v>
       </c>
       <c r="H463" t="n">
         <v>15140</v>
@@ -13854,7 +13854,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>4.49758386611938</v>
+        <v>4.49758434295654</v>
       </c>
       <c r="H465" t="n">
         <v>9324</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352426528931</v>
+        <v>4.54352474212646</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -13941,7 +13941,7 @@
         <v>4.82000017166138</v>
       </c>
       <c r="G468" t="n">
-        <v>4.4286732673645</v>
+        <v>4.42867374420166</v>
       </c>
       <c r="H468" t="n">
         <v>600</v>
@@ -13999,7 +13999,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>4.49758386611938</v>
+        <v>4.49758434295654</v>
       </c>
       <c r="H470" t="n">
         <v>305</v>
@@ -14086,7 +14086,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>4.38732624053955</v>
+        <v>4.38732671737671</v>
       </c>
       <c r="H473" t="n">
         <v>3916</v>
@@ -14115,7 +14115,7 @@
         <v>4.75</v>
       </c>
       <c r="G474" t="n">
-        <v>4.36435604095459</v>
+        <v>4.36435651779175</v>
       </c>
       <c r="H474" t="n">
         <v>5067</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001934051514</v>
+        <v>4.47001886367798</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14202,7 +14202,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G477" t="n">
-        <v>4.49299001693726</v>
+        <v>4.4929895401001</v>
       </c>
       <c r="H477" t="n">
         <v>1400</v>
@@ -14289,7 +14289,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.27247476577759</v>
+        <v>4.2724757194519</v>
       </c>
       <c r="H480" t="n">
         <v>8400</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332673072815</v>
+        <v>3.92332696914673</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14405,7 +14405,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G484" t="n">
-        <v>3.91413879394531</v>
+        <v>3.91413903236389</v>
       </c>
       <c r="H484" t="n">
         <v>16325</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845482826233</v>
+        <v>3.97845506668091</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14492,7 +14492,7 @@
         <v>4.32499980926514</v>
       </c>
       <c r="G487" t="n">
-        <v>3.97386074066162</v>
+        <v>3.9738609790802</v>
       </c>
       <c r="H487" t="n">
         <v>7176</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14666,7 +14666,7 @@
         <v>4.18499994277954</v>
       </c>
       <c r="G493" t="n">
-        <v>3.84522771835327</v>
+        <v>3.84522724151611</v>
       </c>
       <c r="H493" t="n">
         <v>1926</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144521713257</v>
+        <v>3.83144569396973</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14724,7 +14724,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.8590099811554</v>
+        <v>3.85900974273682</v>
       </c>
       <c r="H495" t="n">
         <v>5373</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469299316406</v>
+        <v>3.79469323158264</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -14811,7 +14811,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G498" t="n">
-        <v>3.9508912563324</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H498" t="n">
         <v>7416</v>
@@ -14840,7 +14840,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G499" t="n">
-        <v>3.9508912563324</v>
+        <v>3.95089149475098</v>
       </c>
       <c r="H499" t="n">
         <v>12304</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520776748657</v>
+        <v>4.01520824432373</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14956,7 +14956,7 @@
         <v>4.36499977111816</v>
       </c>
       <c r="G503" t="n">
-        <v>4.01061344146729</v>
+        <v>4.01061296463013</v>
       </c>
       <c r="H503" t="n">
         <v>31005</v>
@@ -15014,7 +15014,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.27247476577759</v>
+        <v>4.2724757194519</v>
       </c>
       <c r="H505" t="n">
         <v>17677</v>
@@ -15043,7 +15043,7 @@
         <v>4.70499992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>4.32300996780396</v>
+        <v>4.3230094909668</v>
       </c>
       <c r="H506" t="n">
         <v>4619</v>
@@ -15217,7 +15217,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G512" t="n">
-        <v>4.30003881454468</v>
+        <v>4.30003929138184</v>
       </c>
       <c r="H512" t="n">
         <v>5794</v>
@@ -15246,7 +15246,7 @@
         <v>4.68499994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30463314056396</v>
+        <v>4.30463361740112</v>
       </c>
       <c r="H513" t="n">
         <v>1902</v>
@@ -15275,7 +15275,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>4.40570259094238</v>
+        <v>4.40570306777954</v>
       </c>
       <c r="H514" t="n">
         <v>4889</v>
@@ -15333,7 +15333,7 @@
         <v>4.72499990463257</v>
       </c>
       <c r="G516" t="n">
-        <v>4.34138631820679</v>
+        <v>4.34138584136963</v>
       </c>
       <c r="H516" t="n">
         <v>12696</v>
@@ -15362,7 +15362,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G517" t="n">
-        <v>4.39192056655884</v>
+        <v>4.391921043396</v>
       </c>
       <c r="H517" t="n">
         <v>7436</v>
@@ -15449,7 +15449,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.73188066482544</v>
+        <v>4.73188161849976</v>
       </c>
       <c r="H520" t="n">
         <v>62686</v>
@@ -15478,7 +15478,7 @@
         <v>5.03000020980835</v>
       </c>
       <c r="G521" t="n">
-        <v>4.62162351608276</v>
+        <v>4.62162399291992</v>
       </c>
       <c r="H521" t="n">
         <v>14852</v>
@@ -15507,7 +15507,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G522" t="n">
-        <v>4.95239543914795</v>
+        <v>4.95239591598511</v>
       </c>
       <c r="H522" t="n">
         <v>39061</v>
@@ -15565,7 +15565,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>4.78700971603394</v>
+        <v>4.78700923919678</v>
       </c>
       <c r="H524" t="n">
         <v>11142</v>
@@ -15681,7 +15681,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>4.78700971603394</v>
+        <v>4.78700923919678</v>
       </c>
       <c r="H528" t="n">
         <v>7274</v>
@@ -15710,7 +15710,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>4.89726734161377</v>
+        <v>4.89726686477661</v>
       </c>
       <c r="H529" t="n">
         <v>14250</v>
@@ -15768,7 +15768,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>4.78700971603394</v>
+        <v>4.78700923919678</v>
       </c>
       <c r="H531" t="n">
         <v>4381</v>
@@ -15797,7 +15797,7 @@
         <v>5.3899998664856</v>
       </c>
       <c r="G532" t="n">
-        <v>4.95239543914795</v>
+        <v>4.95239591598511</v>
       </c>
       <c r="H532" t="n">
         <v>12268</v>
@@ -15942,7 +15942,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G537" t="n">
-        <v>5.0167121887207</v>
+        <v>5.01671266555786</v>
       </c>
       <c r="H537" t="n">
         <v>6975</v>
@@ -16087,7 +16087,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86970281600952</v>
+        <v>4.86970329284668</v>
       </c>
       <c r="H542" t="n">
         <v>3105</v>
@@ -16116,7 +16116,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619741439819</v>
+        <v>4.79619789123535</v>
       </c>
       <c r="H543" t="n">
         <v>1688</v>
@@ -16145,7 +16145,7 @@
         <v>5.1100001335144</v>
       </c>
       <c r="G544" t="n">
-        <v>4.69512891769409</v>
+        <v>4.69512844085693</v>
       </c>
       <c r="H544" t="n">
         <v>7711</v>
@@ -16232,7 +16232,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G547" t="n">
-        <v>4.50217771530151</v>
+        <v>4.50217819213867</v>
       </c>
       <c r="H547" t="n">
         <v>6999</v>
@@ -16319,7 +16319,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.40570259094238</v>
+        <v>4.40570306777954</v>
       </c>
       <c r="H550" t="n">
         <v>4930</v>
@@ -16348,7 +16348,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.20815801620483</v>
+        <v>4.20815849304199</v>
       </c>
       <c r="H551" t="n">
         <v>18005</v>
@@ -16377,7 +16377,7 @@
         <v>4.69500017166138</v>
       </c>
       <c r="G552" t="n">
-        <v>4.31382131576538</v>
+        <v>4.31382179260254</v>
       </c>
       <c r="H552" t="n">
         <v>11658</v>
@@ -16406,7 +16406,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.27247476577759</v>
+        <v>4.2724757194519</v>
       </c>
       <c r="H553" t="n">
         <v>1650</v>
@@ -16435,7 +16435,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>4.22653436660767</v>
+        <v>4.22653484344482</v>
       </c>
       <c r="H554" t="n">
         <v>2710</v>
@@ -16551,7 +16551,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>3.90035653114319</v>
+        <v>3.90035581588745</v>
       </c>
       <c r="H558" t="n">
         <v>78936</v>
@@ -16609,7 +16609,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>3.73496985435486</v>
+        <v>3.73497033119202</v>
       </c>
       <c r="H560" t="n">
         <v>18999</v>
@@ -16638,7 +16638,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631664276123</v>
+        <v>3.77631688117981</v>
       </c>
       <c r="H561" t="n">
         <v>14097</v>
@@ -16667,7 +16667,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G562" t="n">
-        <v>3.74875211715698</v>
+        <v>3.74875235557556</v>
       </c>
       <c r="H562" t="n">
         <v>4463</v>
@@ -16754,7 +16754,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65687108039856</v>
+        <v>3.65687131881714</v>
       </c>
       <c r="H565" t="n">
         <v>350</v>
@@ -16783,7 +16783,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G566" t="n">
-        <v>3.57417845726013</v>
+        <v>3.57417821884155</v>
       </c>
       <c r="H566" t="n">
         <v>6203</v>
@@ -16986,7 +16986,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H573" t="n">
         <v>28469</v>
@@ -17015,7 +17015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H574" t="n">
         <v>22621</v>
@@ -17102,7 +17102,7 @@
         <v>3.5</v>
       </c>
       <c r="G577" t="n">
-        <v>3.21584153175354</v>
+        <v>3.21584129333496</v>
       </c>
       <c r="H577" t="n">
         <v>7340</v>
@@ -17160,7 +17160,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09639573097229</v>
+        <v>3.09639596939087</v>
       </c>
       <c r="H579" t="n">
         <v>10888</v>
@@ -17247,7 +17247,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>3.07801961898804</v>
+        <v>3.07801938056946</v>
       </c>
       <c r="H582" t="n">
         <v>2310</v>
@@ -17595,7 +17595,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G594" t="n">
-        <v>3.51904916763306</v>
+        <v>3.51904940605164</v>
       </c>
       <c r="H594" t="n">
         <v>20677</v>
@@ -17624,7 +17624,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55580163002014</v>
+        <v>3.55580186843872</v>
       </c>
       <c r="H595" t="n">
         <v>9575</v>
@@ -17769,7 +17769,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G600" t="n">
-        <v>3.4547324180603</v>
+        <v>3.45473265647888</v>
       </c>
       <c r="H600" t="n">
         <v>15455</v>
@@ -17827,7 +17827,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H602" t="n">
         <v>23557</v>
@@ -17914,7 +17914,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G605" t="n">
-        <v>3.30772256851196</v>
+        <v>3.30772233009338</v>
       </c>
       <c r="H605" t="n">
         <v>3361</v>
@@ -17943,7 +17943,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015780448914</v>
+        <v>3.28015804290771</v>
       </c>
       <c r="H606" t="n">
         <v>4093</v>
@@ -18001,7 +18001,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178216934204</v>
+        <v>3.26178193092346</v>
       </c>
       <c r="H608" t="n">
         <v>18506</v>
@@ -18030,7 +18030,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178216934204</v>
+        <v>3.26178193092346</v>
       </c>
       <c r="H609" t="n">
         <v>2325</v>
@@ -18117,7 +18117,7 @@
         <v>3.5</v>
       </c>
       <c r="G612" t="n">
-        <v>3.21584153175354</v>
+        <v>3.21584129333496</v>
       </c>
       <c r="H612" t="n">
         <v>1010</v>
@@ -18146,7 +18146,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233636856079</v>
+        <v>3.14233660697937</v>
       </c>
       <c r="H613" t="n">
         <v>1790</v>
@@ -18175,7 +18175,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H614" t="n">
         <v>18656</v>
@@ -18204,7 +18204,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.12396025657654</v>
+        <v>3.12396049499512</v>
       </c>
       <c r="H615" t="n">
         <v>1399</v>
@@ -18233,7 +18233,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152454376221</v>
+        <v>3.15152478218079</v>
       </c>
       <c r="H616" t="n">
         <v>4300</v>
@@ -18262,7 +18262,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.07801961898804</v>
+        <v>3.07801938056946</v>
       </c>
       <c r="H617" t="n">
         <v>10279</v>
@@ -18291,7 +18291,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.1147723197937</v>
+        <v>3.11477208137512</v>
       </c>
       <c r="H618" t="n">
         <v>1345</v>
@@ -18436,7 +18436,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>2.89425706863403</v>
+        <v>2.89425754547119</v>
       </c>
       <c r="H623" t="n">
         <v>25740</v>
@@ -18581,7 +18581,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G628" t="n">
-        <v>2.9769504070282</v>
+        <v>2.97695016860962</v>
       </c>
       <c r="H628" t="n">
         <v>1810</v>
@@ -18697,7 +18697,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>2.90252637863159</v>
+        <v>2.90252661705017</v>
       </c>
       <c r="H632" t="n">
         <v>10235</v>
@@ -18929,7 +18929,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.85601162910461</v>
+        <v>2.85601186752319</v>
       </c>
       <c r="H640" t="n">
         <v>11783</v>
@@ -18987,7 +18987,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110457420349</v>
+        <v>2.52110505104065</v>
       </c>
       <c r="H642" t="n">
         <v>95598</v>
@@ -19016,7 +19016,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G643" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H643" t="n">
         <v>60892</v>
@@ -19074,7 +19074,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G645" t="n">
-        <v>2.53040766716003</v>
+        <v>2.53040790557861</v>
       </c>
       <c r="H645" t="n">
         <v>12711</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761932373047</v>
+        <v>2.56761980056763</v>
       </c>
       <c r="H646" t="n">
         <v>8131</v>
@@ -19132,7 +19132,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G647" t="n">
-        <v>2.54901361465454</v>
+        <v>2.54901385307312</v>
       </c>
       <c r="H647" t="n">
         <v>4920</v>
@@ -19248,7 +19248,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H651" t="n">
         <v>18483</v>
@@ -19393,7 +19393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>2.40946936607361</v>
+        <v>2.40946912765503</v>
       </c>
       <c r="H656" t="n">
         <v>10081</v>
@@ -19770,7 +19770,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180171966553</v>
+        <v>2.51180195808411</v>
       </c>
       <c r="H669" t="n">
         <v>22344</v>
@@ -19799,7 +19799,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G670" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H670" t="n">
         <v>10500</v>
@@ -19886,7 +19886,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H673" t="n">
         <v>536</v>
@@ -19915,7 +19915,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.40946936607361</v>
+        <v>2.40946912765503</v>
       </c>
       <c r="H674" t="n">
         <v>1569</v>
@@ -20060,7 +20060,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G679" t="n">
-        <v>2.43737816810608</v>
+        <v>2.4373779296875</v>
       </c>
       <c r="H679" t="n">
         <v>10826</v>
@@ -20089,7 +20089,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>2.40016627311707</v>
+        <v>2.40016603469849</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20176,7 +20176,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.29783368110657</v>
+        <v>2.29783344268799</v>
       </c>
       <c r="H683" t="n">
         <v>7367</v>
@@ -20350,7 +20350,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G689" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H689" t="n">
         <v>73294</v>
@@ -20379,7 +20379,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G690" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H690" t="n">
         <v>18911</v>
@@ -20437,7 +20437,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G692" t="n">
-        <v>1.1675226688385</v>
+        <v>1.16752278804779</v>
       </c>
       <c r="H692" t="n">
         <v>88258</v>
@@ -20495,7 +20495,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G694" t="n">
-        <v>1.74895823001862</v>
+        <v>1.74895834922791</v>
       </c>
       <c r="H694" t="n">
         <v>231606</v>
@@ -20553,7 +20553,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G696" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H696" t="n">
         <v>232613</v>
@@ -20640,7 +20640,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G699" t="n">
-        <v>1.54429292678833</v>
+        <v>1.54429304599762</v>
       </c>
       <c r="H699" t="n">
         <v>36020</v>
@@ -20727,7 +20727,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G702" t="n">
-        <v>1.4512631893158</v>
+        <v>1.45126330852509</v>
       </c>
       <c r="H702" t="n">
         <v>19933</v>
@@ -20814,7 +20814,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.44196021556854</v>
+        <v>1.44196033477783</v>
       </c>
       <c r="H705" t="n">
         <v>12919</v>
@@ -20988,7 +20988,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G711" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H711" t="n">
         <v>6528</v>
@@ -21017,7 +21017,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H712" t="n">
         <v>2874</v>
@@ -21104,7 +21104,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G715" t="n">
-        <v>1.5861564874649</v>
+        <v>1.58615636825562</v>
       </c>
       <c r="H715" t="n">
         <v>9473</v>
@@ -21133,7 +21133,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G716" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H716" t="n">
         <v>14629</v>
@@ -21191,7 +21191,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G718" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H718" t="n">
         <v>5148</v>
@@ -21249,7 +21249,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.63267111778259</v>
+        <v>1.63267123699188</v>
       </c>
       <c r="H720" t="n">
         <v>7920</v>
@@ -21278,7 +21278,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G721" t="n">
-        <v>1.60476243495941</v>
+        <v>1.60476231575012</v>
       </c>
       <c r="H721" t="n">
         <v>5640</v>
@@ -21336,7 +21336,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H723" t="n">
         <v>5633</v>
@@ -21423,7 +21423,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571485042572</v>
       </c>
       <c r="H726" t="n">
         <v>75327</v>
@@ -21452,7 +21452,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G727" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H727" t="n">
         <v>67002</v>
@@ -21481,7 +21481,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G728" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H728" t="n">
         <v>18194</v>
@@ -21597,7 +21597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G732" t="n">
-        <v>2.14898586273193</v>
+        <v>2.14898610115051</v>
       </c>
       <c r="H732" t="n">
         <v>89764</v>
@@ -21684,7 +21684,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G735" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H735" t="n">
         <v>53817</v>
@@ -21713,7 +21713,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G736" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H736" t="n">
         <v>25550</v>
@@ -21742,7 +21742,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>2.18619775772095</v>
+        <v>2.18619799613953</v>
       </c>
       <c r="H737" t="n">
         <v>12209</v>
@@ -21800,7 +21800,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550061225891</v>
+        <v>2.19550085067749</v>
       </c>
       <c r="H739" t="n">
         <v>13585</v>
@@ -21887,7 +21887,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H742" t="n">
         <v>4041</v>
@@ -21916,7 +21916,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H743" t="n">
         <v>27715</v>
@@ -21974,7 +21974,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.00944137573242</v>
+        <v>2.00944185256958</v>
       </c>
       <c r="H745" t="n">
         <v>22944</v>
@@ -22090,7 +22090,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>2.335045337677</v>
+        <v>2.33504557609558</v>
       </c>
       <c r="H749" t="n">
         <v>46515</v>
@@ -22148,7 +22148,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H751" t="n">
         <v>7609</v>
@@ -22206,7 +22206,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.24201583862305</v>
+        <v>2.24201607704163</v>
       </c>
       <c r="H753" t="n">
         <v>7610</v>
@@ -22235,7 +22235,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H754" t="n">
         <v>54449</v>
@@ -22264,7 +22264,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.28853058815002</v>
+        <v>2.2885308265686</v>
       </c>
       <c r="H755" t="n">
         <v>13384</v>
@@ -22409,7 +22409,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G760" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H760" t="n">
         <v>6602</v>
@@ -22438,7 +22438,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G761" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H761" t="n">
         <v>2731</v>
@@ -22525,7 +22525,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G764" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H764" t="n">
         <v>5171</v>
@@ -22554,7 +22554,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G765" t="n">
-        <v>2.1768946647644</v>
+        <v>2.17689490318298</v>
       </c>
       <c r="H765" t="n">
         <v>4690</v>
@@ -22699,7 +22699,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G770" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H770" t="n">
         <v>1304</v>
@@ -22728,7 +22728,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G771" t="n">
-        <v>2.20480394363403</v>
+        <v>2.20480370521545</v>
       </c>
       <c r="H771" t="n">
         <v>5621</v>
@@ -22757,7 +22757,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>2.13037991523743</v>
+        <v>2.13038015365601</v>
       </c>
       <c r="H772" t="n">
         <v>12685</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.13968300819397</v>
+        <v>2.13968324661255</v>
       </c>
       <c r="H776" t="n">
         <v>3302</v>
@@ -22931,7 +22931,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G778" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153281211853</v>
       </c>
       <c r="H778" t="n">
         <v>10623</v>
@@ -22960,7 +22960,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>1.97222936153412</v>
+        <v>1.9722295999527</v>
       </c>
       <c r="H779" t="n">
         <v>6646</v>
@@ -23018,7 +23018,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G781" t="n">
-        <v>2.08386516571045</v>
+        <v>2.08386540412903</v>
       </c>
       <c r="H781" t="n">
         <v>400</v>
@@ -23047,7 +23047,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153281211853</v>
       </c>
       <c r="H782" t="n">
         <v>7820</v>
@@ -23105,7 +23105,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.9908355474472</v>
+        <v>1.99083566665649</v>
       </c>
       <c r="H784" t="n">
         <v>1181</v>
@@ -23163,7 +23163,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571485042572</v>
       </c>
       <c r="H786" t="n">
         <v>22188</v>
@@ -23192,7 +23192,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G787" t="n">
-        <v>2.00013852119446</v>
+        <v>2.00013875961304</v>
       </c>
       <c r="H787" t="n">
         <v>19192</v>
@@ -23221,7 +23221,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.05595636367798</v>
+        <v>2.05595660209656</v>
       </c>
       <c r="H788" t="n">
         <v>13900</v>
@@ -23279,7 +23279,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03735041618347</v>
+        <v>2.03735065460205</v>
       </c>
       <c r="H790" t="n">
         <v>6918</v>
@@ -23308,7 +23308,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00944137573242</v>
+        <v>2.00944185256958</v>
       </c>
       <c r="H791" t="n">
         <v>2800</v>
@@ -23366,7 +23366,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153281211853</v>
       </c>
       <c r="H793" t="n">
         <v>8905</v>
@@ -23395,7 +23395,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98153269290924</v>
+        <v>1.98153281211853</v>
       </c>
       <c r="H794" t="n">
         <v>13577</v>
@@ -23511,7 +23511,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G798" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571485042572</v>
       </c>
       <c r="H798" t="n">
         <v>16878</v>
@@ -23540,7 +23540,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G799" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H799" t="n">
         <v>9805</v>
@@ -23569,7 +23569,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G800" t="n">
-        <v>1.90710890293121</v>
+        <v>1.90710878372192</v>
       </c>
       <c r="H800" t="n">
         <v>3251</v>
@@ -23598,7 +23598,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571485042572</v>
       </c>
       <c r="H801" t="n">
         <v>1502</v>
@@ -23656,7 +23656,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G803" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617024421692</v>
       </c>
       <c r="H803" t="n">
         <v>3999</v>
@@ -23714,7 +23714,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G805" t="n">
-        <v>1.77686727046967</v>
+        <v>1.77686715126038</v>
       </c>
       <c r="H805" t="n">
         <v>1</v>
@@ -23801,7 +23801,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G808" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H808" t="n">
         <v>8701</v>
@@ -23859,7 +23859,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.64662551879883</v>
+        <v>1.64662563800812</v>
       </c>
       <c r="H810" t="n">
         <v>3970</v>
@@ -23917,7 +23917,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H812" t="n">
         <v>17120</v>
@@ -24091,7 +24091,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G818" t="n">
-        <v>1.66523146629333</v>
+        <v>1.66523158550262</v>
       </c>
       <c r="H818" t="n">
         <v>26987</v>
@@ -24120,7 +24120,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G819" t="n">
-        <v>1.60011088848114</v>
+        <v>1.60011076927185</v>
       </c>
       <c r="H819" t="n">
         <v>13128</v>
@@ -24149,7 +24149,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G820" t="n">
-        <v>1.60941386222839</v>
+        <v>1.6094137430191</v>
       </c>
       <c r="H820" t="n">
         <v>7001</v>
@@ -24178,7 +24178,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G821" t="n">
-        <v>1.63267111778259</v>
+        <v>1.63267123699188</v>
       </c>
       <c r="H821" t="n">
         <v>16193</v>
@@ -24265,7 +24265,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G824" t="n">
-        <v>1.64197409152985</v>
+        <v>1.64197421073914</v>
       </c>
       <c r="H824" t="n">
         <v>17867</v>
@@ -24294,7 +24294,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.63732254505157</v>
+        <v>1.63732266426086</v>
       </c>
       <c r="H825" t="n">
         <v>2580</v>
@@ -24584,7 +24584,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G835" t="n">
-        <v>1.97222936153412</v>
+        <v>1.9722295999527</v>
       </c>
       <c r="H835" t="n">
         <v>50956</v>
@@ -24613,7 +24613,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G836" t="n">
-        <v>1.92571461200714</v>
+        <v>1.92571485042572</v>
       </c>
       <c r="H836" t="n">
         <v>55529</v>
@@ -24642,7 +24642,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G837" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H837" t="n">
         <v>17650</v>
@@ -24671,7 +24671,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G838" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H838" t="n">
         <v>5154</v>
@@ -24729,7 +24729,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G840" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H840" t="n">
         <v>6246</v>
@@ -24758,7 +24758,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G841" t="n">
-        <v>1.87919998168945</v>
+        <v>1.87919986248016</v>
       </c>
       <c r="H841" t="n">
         <v>5347</v>
@@ -24787,7 +24787,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H842" t="n">
         <v>3510</v>
@@ -25019,7 +25019,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G850" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617024421692</v>
       </c>
       <c r="H850" t="n">
         <v>10425</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.78617012500763</v>
+        <v>1.78617024421692</v>
       </c>
       <c r="H851" t="n">
         <v>616</v>
@@ -25193,7 +25193,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G856" t="n">
-        <v>1.8512909412384</v>
+        <v>1.85129106044769</v>
       </c>
       <c r="H856" t="n">
         <v>7440</v>
@@ -25251,7 +25251,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G858" t="n">
-        <v>1.8698970079422</v>
+        <v>1.86989688873291</v>
       </c>
       <c r="H858" t="n">
         <v>2711</v>
@@ -25280,7 +25280,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432055950165</v>
+        <v>1.94432067871094</v>
       </c>
       <c r="H859" t="n">
         <v>23244</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.18991041183472</v>
+        <v>2.18991017341614</v>
       </c>
       <c r="H864" t="n">
         <v>29824</v>
@@ -25454,7 +25454,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>2.18038892745972</v>
+        <v>2.1803891658783</v>
       </c>
       <c r="H865" t="n">
         <v>18169</v>
@@ -25541,7 +25541,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G868" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H868" t="n">
         <v>12463</v>
@@ -25599,7 +25599,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H870" t="n">
         <v>14204</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.98044073581696</v>
+        <v>1.98044061660767</v>
       </c>
       <c r="H871" t="n">
         <v>10741</v>
@@ -25686,7 +25686,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H873" t="n">
         <v>1780</v>
@@ -25715,7 +25715,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H874" t="n">
         <v>11963</v>
@@ -25860,7 +25860,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H879" t="n">
         <v>9646</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>2.05661153793335</v>
+        <v>2.05661177635193</v>
       </c>
       <c r="H881" t="n">
         <v>4363</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98044073581696</v>
+        <v>1.98044061660767</v>
       </c>
       <c r="H882" t="n">
         <v>3757</v>
@@ -26005,7 +26005,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.99948346614838</v>
+        <v>1.9994832277298</v>
       </c>
       <c r="H884" t="n">
         <v>3933</v>
@@ -26092,7 +26092,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H887" t="n">
         <v>1502</v>
@@ -26121,7 +26121,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H888" t="n">
         <v>2991</v>
@@ -26150,7 +26150,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H889" t="n">
         <v>500</v>
@@ -26179,7 +26179,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.95187675952911</v>
+        <v>1.95187664031982</v>
       </c>
       <c r="H891" t="n">
         <v>1750</v>
@@ -26237,7 +26237,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>1.99948346614838</v>
+        <v>1.9994832277298</v>
       </c>
       <c r="H892" t="n">
         <v>3562</v>
@@ -26295,7 +26295,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>1.98996198177338</v>
+        <v>1.98996186256409</v>
       </c>
       <c r="H894" t="n">
         <v>2771</v>
@@ -27542,7 +27542,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.69480013847351</v>
+        <v>1.6948002576828</v>
       </c>
       <c r="H937" t="n">
         <v>12954</v>
@@ -27716,7 +27716,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G943" t="n">
-        <v>1.69480013847351</v>
+        <v>1.6948002576828</v>
       </c>
       <c r="H943" t="n">
         <v>13769</v>
@@ -27745,7 +27745,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.6186295747757</v>
+        <v>1.61862945556641</v>
       </c>
       <c r="H944" t="n">
         <v>22282</v>
@@ -27774,7 +27774,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G945" t="n">
-        <v>1.54245865345001</v>
+        <v>1.54245853424072</v>
       </c>
       <c r="H945" t="n">
         <v>13946</v>
@@ -27890,7 +27890,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.35679221153259</v>
+        <v>1.35679233074188</v>
       </c>
       <c r="H949" t="n">
         <v>12733</v>
@@ -27948,7 +27948,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G951" t="n">
-        <v>1.31394612789154</v>
+        <v>1.31394624710083</v>
       </c>
       <c r="H951" t="n">
         <v>18171</v>
@@ -28006,7 +28006,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G953" t="n">
-        <v>1.31394612789154</v>
+        <v>1.31394624710083</v>
       </c>
       <c r="H953" t="n">
         <v>17476</v>
@@ -28122,7 +28122,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>1.34727084636688</v>
+        <v>1.34727096557617</v>
       </c>
       <c r="H957" t="n">
         <v>10390</v>
@@ -28151,7 +28151,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H958" t="n">
         <v>120160</v>
@@ -28296,7 +28296,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G963" t="n">
-        <v>1.02830576896667</v>
+        <v>1.02830588817596</v>
       </c>
       <c r="H963" t="n">
         <v>70383</v>
@@ -28354,7 +28354,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H965" t="n">
         <v>11079</v>
@@ -28470,7 +28470,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G969" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H969" t="n">
         <v>5589</v>
@@ -28644,7 +28644,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G975" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H975" t="n">
         <v>16278</v>
@@ -28876,7 +28876,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G983" t="n">
-        <v>0.847400069236755</v>
+        <v>0.8474001288414</v>
       </c>
       <c r="H983" t="n">
         <v>11888</v>
@@ -28934,7 +28934,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G985" t="n">
-        <v>0.934996485710144</v>
+        <v>0.934996545314789</v>
       </c>
       <c r="H985" t="n">
         <v>22093</v>
@@ -28963,7 +28963,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G986" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H986" t="n">
         <v>24435</v>
@@ -29108,7 +29108,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.13780128955841</v>
+        <v>1.1378014087677</v>
       </c>
       <c r="H991" t="n">
         <v>4904</v>
@@ -29137,7 +29137,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H992" t="n">
         <v>18073</v>
@@ -29253,7 +29253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G996" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H996" t="n">
         <v>11904</v>
@@ -29282,7 +29282,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H997" t="n">
         <v>4540</v>
@@ -29427,7 +29427,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1002" t="n">
         <v>2974</v>
@@ -29485,7 +29485,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.02830576896667</v>
+        <v>1.02830588817596</v>
       </c>
       <c r="H1004" t="n">
         <v>11264</v>
@@ -29630,7 +29630,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1009" t="n">
         <v>18426</v>
@@ -29659,7 +29659,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1010" t="n">
         <v>2505</v>
@@ -29978,7 +29978,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1021" t="n">
         <v>5361</v>
@@ -30036,7 +30036,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1026" t="n">
         <v>3669</v>
@@ -30152,7 +30152,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1027" t="n">
         <v>8946</v>
@@ -30268,7 +30268,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1031" t="n">
         <v>6700</v>
@@ -30326,7 +30326,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1033" t="n">
         <v>2860</v>
@@ -30384,7 +30384,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.10447657108307</v>
+        <v>1.10447645187378</v>
       </c>
       <c r="H1035" t="n">
         <v>7202</v>
@@ -30413,7 +30413,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1036" t="n">
         <v>3000</v>
@@ -30442,7 +30442,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1037" t="n">
         <v>3042</v>
@@ -30558,7 +30558,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1041" t="n">
         <v>702</v>
@@ -30616,7 +30616,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1043" t="n">
         <v>5703</v>
@@ -30674,7 +30674,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1045" t="n">
         <v>3810</v>
@@ -30703,7 +30703,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1046" t="n">
         <v>3045</v>
@@ -30732,7 +30732,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.09019446372986</v>
+        <v>1.09019458293915</v>
       </c>
       <c r="H1047" t="n">
         <v>4337</v>
@@ -30993,7 +30993,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.0473484992981</v>
+        <v>1.04734838008881</v>
       </c>
       <c r="H1056" t="n">
         <v>15939</v>
@@ -31138,7 +31138,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.0473484992981</v>
+        <v>1.04734838008881</v>
       </c>
       <c r="H1061" t="n">
         <v>5653</v>
@@ -31225,7 +31225,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.999741733074188</v>
+        <v>0.999741613864899</v>
       </c>
       <c r="H1064" t="n">
         <v>7815</v>
@@ -31254,7 +31254,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.01878440380096</v>
+        <v>1.01878452301025</v>
       </c>
       <c r="H1065" t="n">
         <v>2000</v>
@@ -31312,7 +31312,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.00926291942596</v>
+        <v>1.00926303863525</v>
       </c>
       <c r="H1067" t="n">
         <v>2310</v>
@@ -31341,7 +31341,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00926291942596</v>
+        <v>1.00926303863525</v>
       </c>
       <c r="H1068" t="n">
         <v>8960</v>
@@ -31370,7 +31370,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1069" t="n">
         <v>9201</v>
@@ -31428,7 +31428,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.885485529899597</v>
+        <v>0.885485470294952</v>
       </c>
       <c r="H1071" t="n">
         <v>7123</v>
@@ -31834,7 +31834,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1085" t="n">
         <v>14616</v>
@@ -31863,7 +31863,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.999741733074188</v>
+        <v>0.999741613864899</v>
       </c>
       <c r="H1086" t="n">
         <v>7925</v>
@@ -31979,7 +31979,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.975938379764557</v>
+        <v>0.975938320159912</v>
       </c>
       <c r="H1090" t="n">
         <v>1503</v>
@@ -32008,7 +32008,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.990220367908478</v>
+        <v>0.990220308303833</v>
       </c>
       <c r="H1091" t="n">
         <v>4143</v>
@@ -32037,7 +32037,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.975938379764557</v>
+        <v>0.975938320159912</v>
       </c>
       <c r="H1092" t="n">
         <v>4779</v>
@@ -32095,7 +32095,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.980699002742767</v>
+        <v>0.980698943138123</v>
       </c>
       <c r="H1094" t="n">
         <v>8025</v>
@@ -32182,7 +32182,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.940709352493286</v>
+        <v>0.940709292888641</v>
       </c>
       <c r="H1097" t="n">
         <v>7780</v>
@@ -32327,7 +32327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.09495520591736</v>
+        <v>1.09495508670807</v>
       </c>
       <c r="H1102" t="n">
         <v>114066</v>
@@ -32356,7 +32356,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1103" t="n">
         <v>155001</v>
@@ -32414,7 +32414,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1105" t="n">
         <v>9642</v>
@@ -32443,7 +32443,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14732265472412</v>
+        <v>1.14732277393341</v>
       </c>
       <c r="H1106" t="n">
         <v>29380</v>
@@ -32501,7 +32501,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1108" t="n">
         <v>51439</v>
@@ -32559,7 +32559,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1110" t="n">
         <v>7650</v>
@@ -32588,7 +32588,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1111" t="n">
         <v>5770</v>
@@ -32646,7 +32646,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1113" t="n">
         <v>10113</v>
@@ -32704,7 +32704,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1115" t="n">
         <v>12644</v>
@@ -32733,7 +32733,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1116" t="n">
         <v>8938</v>
@@ -32849,7 +32849,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.16636538505554</v>
+        <v>1.16636526584625</v>
       </c>
       <c r="H1120" t="n">
         <v>9373</v>
@@ -32878,7 +32878,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.17588675022125</v>
+        <v>1.17588663101196</v>
       </c>
       <c r="H1121" t="n">
         <v>12172</v>
@@ -33023,7 +33023,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.20445072650909</v>
+        <v>1.2044506072998</v>
       </c>
       <c r="H1126" t="n">
         <v>6943</v>
@@ -33052,7 +33052,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.20921146869659</v>
+        <v>1.2092113494873</v>
       </c>
       <c r="H1127" t="n">
         <v>7459</v>
@@ -33139,7 +33139,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.20445072650909</v>
+        <v>1.2044506072998</v>
       </c>
       <c r="H1130" t="n">
         <v>7350</v>
@@ -33197,7 +33197,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.15208339691162</v>
+        <v>1.15208327770233</v>
       </c>
       <c r="H1132" t="n">
         <v>14474</v>
@@ -42889,6 +42889,35 @@
         <v>6330</v>
       </c>
       <c r="I1466" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1467" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1467" t="n">
+        <v>0.670000016689301</v>
+      </c>
+      <c r="D1467" t="n">
+        <v>0.694999992847443</v>
+      </c>
+      <c r="E1467" t="n">
+        <v>0.629999995231628</v>
+      </c>
+      <c r="F1467" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="G1467" t="n">
+        <v>0.649999976158142</v>
+      </c>
+      <c r="H1467" t="n">
+        <v>6452</v>
+      </c>
+      <c r="I1467" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/VNT.MI.xlsx
+++ b/data/VNT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.00049996376038</v>
       </c>
       <c r="G3" t="n">
-        <v>2.74249887466431</v>
+        <v>2.74249839782715</v>
       </c>
       <c r="H3" t="n">
         <v>611000</v>
@@ -485,7 +485,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6414999961853</v>
+        <v>2.64150023460388</v>
       </c>
       <c r="H4" t="n">
         <v>186000</v>
@@ -688,7 +688,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G11" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H11" t="n">
         <v>296000</v>
@@ -746,7 +746,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G13" t="n">
-        <v>3.57379412651062</v>
+        <v>3.5737943649292</v>
       </c>
       <c r="H13" t="n">
         <v>75000</v>
@@ -775,7 +775,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G14" t="n">
-        <v>3.45497250556946</v>
+        <v>3.45497226715088</v>
       </c>
       <c r="H14" t="n">
         <v>116000</v>
@@ -804,7 +804,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G15" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H15" t="n">
         <v>85000</v>
@@ -833,7 +833,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G16" t="n">
-        <v>3.44583201408386</v>
+        <v>3.44583249092102</v>
       </c>
       <c r="H16" t="n">
         <v>29000</v>
@@ -1036,7 +1036,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G23" t="n">
-        <v>3.40927171707153</v>
+        <v>3.40927195549011</v>
       </c>
       <c r="H23" t="n">
         <v>15000</v>
@@ -1094,7 +1094,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G25" t="n">
-        <v>3.3727114200592</v>
+        <v>3.37271118164062</v>
       </c>
       <c r="H25" t="n">
         <v>11000</v>
@@ -1123,7 +1123,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G26" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H26" t="n">
         <v>34000</v>
@@ -1152,7 +1152,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G27" t="n">
-        <v>3.16248798370361</v>
+        <v>3.16248822212219</v>
       </c>
       <c r="H27" t="n">
         <v>62000</v>
@@ -1181,7 +1181,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G28" t="n">
-        <v>3.10764741897583</v>
+        <v>3.10764718055725</v>
       </c>
       <c r="H28" t="n">
         <v>52000</v>
@@ -1297,7 +1297,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.18076825141907</v>
+        <v>3.18076801300049</v>
       </c>
       <c r="H32" t="n">
         <v>40000</v>
@@ -1326,7 +1326,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G33" t="n">
-        <v>3.14420771598816</v>
+        <v>3.14420795440674</v>
       </c>
       <c r="H33" t="n">
         <v>53000</v>
@@ -1384,7 +1384,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G35" t="n">
-        <v>3.0893669128418</v>
+        <v>3.08936715126038</v>
       </c>
       <c r="H35" t="n">
         <v>9000</v>
@@ -1413,7 +1413,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G36" t="n">
-        <v>3.20818877220154</v>
+        <v>3.20818853378296</v>
       </c>
       <c r="H36" t="n">
         <v>50000</v>
@@ -1442,7 +1442,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G37" t="n">
-        <v>3.35443067550659</v>
+        <v>3.35443091392517</v>
       </c>
       <c r="H37" t="n">
         <v>264000</v>
@@ -1529,7 +1529,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G40" t="n">
-        <v>3.31787037849426</v>
+        <v>3.31787061691284</v>
       </c>
       <c r="H40" t="n">
         <v>48000</v>
@@ -1558,7 +1558,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H41" t="n">
         <v>172000</v>
@@ -1587,7 +1587,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G42" t="n">
-        <v>3.82057809829712</v>
+        <v>3.82057762145996</v>
       </c>
       <c r="H42" t="n">
         <v>202000</v>
@@ -1616,7 +1616,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G43" t="n">
-        <v>3.71089601516724</v>
+        <v>3.71089625358582</v>
       </c>
       <c r="H43" t="n">
         <v>172000</v>
@@ -1645,7 +1645,7 @@
         <v>4</v>
       </c>
       <c r="G44" t="n">
-        <v>3.65605568885803</v>
+        <v>3.65605545043945</v>
       </c>
       <c r="H44" t="n">
         <v>80000</v>
@@ -1674,7 +1674,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G45" t="n">
-        <v>3.67433571815491</v>
+        <v>3.67433547973633</v>
       </c>
       <c r="H45" t="n">
         <v>29000</v>
@@ -1761,7 +1761,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G48" t="n">
-        <v>3.67433571815491</v>
+        <v>3.67433547973633</v>
       </c>
       <c r="H48" t="n">
         <v>13000</v>
@@ -1790,7 +1790,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G49" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H49" t="n">
         <v>51000</v>
@@ -1819,7 +1819,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G50" t="n">
-        <v>3.66519570350647</v>
+        <v>3.66519594192505</v>
       </c>
       <c r="H50" t="n">
         <v>11000</v>
@@ -1848,7 +1848,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G51" t="n">
-        <v>3.68347597122192</v>
+        <v>3.6834762096405</v>
       </c>
       <c r="H51" t="n">
         <v>21000</v>
@@ -1906,7 +1906,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G53" t="n">
-        <v>3.56465435028076</v>
+        <v>3.56465411186218</v>
       </c>
       <c r="H53" t="n">
         <v>35000</v>
@@ -1964,7 +1964,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G55" t="n">
-        <v>3.49153280258179</v>
+        <v>3.49153304100037</v>
       </c>
       <c r="H55" t="n">
         <v>18000</v>
@@ -2080,7 +2080,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G59" t="n">
-        <v>3.61949467658997</v>
+        <v>3.61949491500854</v>
       </c>
       <c r="H59" t="n">
         <v>20000</v>
@@ -2167,7 +2167,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G62" t="n">
-        <v>3.62863516807556</v>
+        <v>3.62863492965698</v>
       </c>
       <c r="H62" t="n">
         <v>25000</v>
@@ -2196,7 +2196,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G63" t="n">
-        <v>3.59207463264465</v>
+        <v>3.59207439422607</v>
       </c>
       <c r="H63" t="n">
         <v>11000</v>
@@ -2283,7 +2283,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G66" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H66" t="n">
         <v>28000</v>
@@ -2312,7 +2312,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G67" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H67" t="n">
         <v>24000</v>
@@ -2370,7 +2370,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G69" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H69" t="n">
         <v>12000</v>
@@ -2399,7 +2399,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G70" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H70" t="n">
         <v>14000</v>
@@ -2457,7 +2457,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G72" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H72" t="n">
         <v>23000</v>
@@ -2486,7 +2486,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G73" t="n">
-        <v>3.50986099243164</v>
+        <v>3.5098614692688</v>
       </c>
       <c r="H73" t="n">
         <v>17000</v>
@@ -2544,7 +2544,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G75" t="n">
-        <v>3.4179801940918</v>
+        <v>3.41797995567322</v>
       </c>
       <c r="H75" t="n">
         <v>7500</v>
@@ -2602,7 +2602,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G77" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417798042297</v>
       </c>
       <c r="H77" t="n">
         <v>18000</v>
@@ -2660,7 +2660,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G79" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H79" t="n">
         <v>11000</v>
@@ -2718,7 +2718,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G81" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H81" t="n">
         <v>4500</v>
@@ -2776,7 +2776,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G83" t="n">
-        <v>3.50986099243164</v>
+        <v>3.5098614692688</v>
       </c>
       <c r="H83" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G86" t="n">
-        <v>3.52823758125305</v>
+        <v>3.52823734283447</v>
       </c>
       <c r="H86" t="n">
         <v>5000</v>
@@ -2921,7 +2921,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G88" t="n">
-        <v>3.65687131881714</v>
+        <v>3.65687108039856</v>
       </c>
       <c r="H88" t="n">
         <v>31500</v>
@@ -3008,7 +3008,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G91" t="n">
-        <v>3.63849472999573</v>
+        <v>3.63849496841431</v>
       </c>
       <c r="H91" t="n">
         <v>10500</v>
@@ -3095,7 +3095,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G94" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H94" t="n">
         <v>132500</v>
@@ -3124,7 +3124,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G95" t="n">
-        <v>3.8957622051239</v>
+        <v>3.89576196670532</v>
       </c>
       <c r="H95" t="n">
         <v>105500</v>
@@ -3153,7 +3153,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>4.01520824432373</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H96" t="n">
         <v>76500</v>
@@ -3182,7 +3182,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G97" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H97" t="n">
         <v>373000</v>
@@ -3211,7 +3211,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G98" t="n">
-        <v>5.09021759033203</v>
+        <v>5.09021711349487</v>
       </c>
       <c r="H98" t="n">
         <v>576000</v>
@@ -3240,7 +3240,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>5.60475206375122</v>
+        <v>5.60475158691406</v>
       </c>
       <c r="H99" t="n">
         <v>503500</v>
@@ -3327,7 +3327,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>5.14534616470337</v>
+        <v>5.14534664154053</v>
       </c>
       <c r="H102" t="n">
         <v>73000</v>
@@ -3530,7 +3530,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G109" t="n">
-        <v>5.49449491500854</v>
+        <v>5.49449443817139</v>
       </c>
       <c r="H109" t="n">
         <v>40500</v>
@@ -3559,7 +3559,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G110" t="n">
-        <v>5.53124761581421</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H110" t="n">
         <v>38500</v>
@@ -3617,7 +3617,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G112" t="n">
-        <v>7.00134611129761</v>
+        <v>7.00134563446045</v>
       </c>
       <c r="H112" t="n">
         <v>689000</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H114" t="n">
         <v>284500</v>
@@ -3704,7 +3704,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G115" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H115" t="n">
         <v>297500</v>
@@ -3733,7 +3733,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G116" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H116" t="n">
         <v>89000</v>
@@ -3849,7 +3849,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G120" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H120" t="n">
         <v>58500</v>
@@ -3907,7 +3907,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G122" t="n">
-        <v>7.33211851119995</v>
+        <v>7.33211803436279</v>
       </c>
       <c r="H122" t="n">
         <v>28500</v>
@@ -4023,7 +4023,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G126" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H126" t="n">
         <v>17500</v>
@@ -4052,7 +4052,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G127" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H127" t="n">
         <v>23000</v>
@@ -4081,7 +4081,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>6.87271213531494</v>
+        <v>6.8727126121521</v>
       </c>
       <c r="H128" t="n">
         <v>18500</v>
@@ -4110,7 +4110,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G129" t="n">
-        <v>6.85433673858643</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H129" t="n">
         <v>13500</v>
@@ -4226,7 +4226,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G133" t="n">
-        <v>7.27698945999146</v>
+        <v>7.27698993682861</v>
       </c>
       <c r="H133" t="n">
         <v>58000</v>
@@ -4255,7 +4255,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G134" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H134" t="n">
         <v>126500</v>
@@ -4284,7 +4284,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G135" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H135" t="n">
         <v>150000</v>
@@ -4371,7 +4371,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G138" t="n">
-        <v>7.46075201034546</v>
+        <v>7.46075248718262</v>
       </c>
       <c r="H138" t="n">
         <v>29000</v>
@@ -4400,7 +4400,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G139" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H139" t="n">
         <v>19500</v>
@@ -4429,7 +4429,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G140" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H140" t="n">
         <v>13000</v>
@@ -4487,7 +4487,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G142" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H142" t="n">
         <v>20000</v>
@@ -4574,7 +4574,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G145" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366188049316</v>
       </c>
       <c r="H145" t="n">
         <v>48500</v>
@@ -4632,7 +4632,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G147" t="n">
-        <v>7.99366331100464</v>
+        <v>7.99366188049316</v>
       </c>
       <c r="H147" t="n">
         <v>19000</v>
@@ -4690,7 +4690,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G149" t="n">
-        <v>8.14067363739014</v>
+        <v>8.14067268371582</v>
       </c>
       <c r="H149" t="n">
         <v>53500</v>
@@ -4719,7 +4719,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G150" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H150" t="n">
         <v>23500</v>
@@ -4777,7 +4777,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G152" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H152" t="n">
         <v>34000</v>
@@ -4864,7 +4864,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G155" t="n">
-        <v>7.92015838623047</v>
+        <v>7.92015790939331</v>
       </c>
       <c r="H155" t="n">
         <v>18000</v>
@@ -4893,7 +4893,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G156" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314758300781</v>
       </c>
       <c r="H156" t="n">
         <v>12500</v>
@@ -4922,7 +4922,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G157" t="n">
-        <v>7.69964408874512</v>
+        <v>7.69964361190796</v>
       </c>
       <c r="H157" t="n">
         <v>22500</v>
@@ -4951,7 +4951,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G158" t="n">
-        <v>7.7915244102478</v>
+        <v>7.79152393341064</v>
       </c>
       <c r="H158" t="n">
         <v>15500</v>
@@ -4980,7 +4980,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G159" t="n">
-        <v>7.7915244102478</v>
+        <v>7.79152393341064</v>
       </c>
       <c r="H159" t="n">
         <v>5500</v>
@@ -5009,7 +5009,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G160" t="n">
-        <v>7.64451456069946</v>
+        <v>7.64451360702515</v>
       </c>
       <c r="H160" t="n">
         <v>19000</v>
@@ -5125,7 +5125,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G164" t="n">
-        <v>7.44237613677979</v>
+        <v>7.44237565994263</v>
       </c>
       <c r="H164" t="n">
         <v>19000</v>
@@ -5212,7 +5212,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>7.27698945999146</v>
+        <v>7.27698993682861</v>
       </c>
       <c r="H167" t="n">
         <v>11500</v>
@@ -5270,7 +5270,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G169" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H169" t="n">
         <v>22000</v>
@@ -5299,7 +5299,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G170" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H170" t="n">
         <v>34500</v>
@@ -5328,7 +5328,7 @@
         <v>8.65999984741211</v>
       </c>
       <c r="G171" t="n">
-        <v>7.95691013336182</v>
+        <v>7.95691061019897</v>
       </c>
       <c r="H171" t="n">
         <v>59000</v>
@@ -5357,7 +5357,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G172" t="n">
-        <v>8.14067363739014</v>
+        <v>8.14067268371582</v>
       </c>
       <c r="H172" t="n">
         <v>81500</v>
@@ -5386,7 +5386,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G173" t="n">
-        <v>8.36118793487549</v>
+        <v>8.36118698120117</v>
       </c>
       <c r="H173" t="n">
         <v>85500</v>
@@ -5415,7 +5415,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G174" t="n">
-        <v>7.84665393829346</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H174" t="n">
         <v>112500</v>
@@ -5444,7 +5444,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G175" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801900863647</v>
       </c>
       <c r="H175" t="n">
         <v>33500</v>
@@ -5473,7 +5473,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G176" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H176" t="n">
         <v>29500</v>
@@ -5531,7 +5531,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G178" t="n">
-        <v>7.84665393829346</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H178" t="n">
         <v>19500</v>
@@ -5589,7 +5589,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G180" t="n">
-        <v>7.84665393829346</v>
+        <v>7.84665250778198</v>
       </c>
       <c r="H180" t="n">
         <v>56000</v>
@@ -5618,7 +5618,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G181" t="n">
-        <v>7.77314853668213</v>
+        <v>7.77314758300781</v>
       </c>
       <c r="H181" t="n">
         <v>18500</v>
@@ -5647,7 +5647,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G182" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H182" t="n">
         <v>13500</v>
@@ -5676,7 +5676,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G183" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H183" t="n">
         <v>33500</v>
@@ -5705,7 +5705,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G184" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H184" t="n">
         <v>12000</v>
@@ -5734,7 +5734,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G185" t="n">
-        <v>7.51588153839111</v>
+        <v>7.51588106155396</v>
       </c>
       <c r="H185" t="n">
         <v>12500</v>
@@ -5792,7 +5792,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G187" t="n">
-        <v>7.58938646316528</v>
+        <v>7.58938550949097</v>
       </c>
       <c r="H187" t="n">
         <v>23500</v>
@@ -5821,7 +5821,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G188" t="n">
-        <v>7.46075201034546</v>
+        <v>7.46075248718262</v>
       </c>
       <c r="H188" t="n">
         <v>20500</v>
@@ -5850,7 +5850,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G189" t="n">
-        <v>7.46075201034546</v>
+        <v>7.46075248718262</v>
       </c>
       <c r="H189" t="n">
         <v>19000</v>
@@ -5879,7 +5879,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G190" t="n">
-        <v>7.55263376235962</v>
+        <v>7.55263328552246</v>
       </c>
       <c r="H190" t="n">
         <v>36500</v>
@@ -5908,7 +5908,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G191" t="n">
-        <v>7.71801948547363</v>
+        <v>7.71801900863647</v>
       </c>
       <c r="H191" t="n">
         <v>28000</v>
@@ -5966,7 +5966,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G193" t="n">
-        <v>7.66289138793945</v>
+        <v>7.66289091110229</v>
       </c>
       <c r="H193" t="n">
         <v>15500</v>
@@ -6024,7 +6024,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G195" t="n">
-        <v>7.60776233673096</v>
+        <v>7.60776138305664</v>
       </c>
       <c r="H195" t="n">
         <v>15000</v>
@@ -6053,7 +6053,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G196" t="n">
-        <v>7.57100963592529</v>
+        <v>7.57100915908813</v>
       </c>
       <c r="H196" t="n">
         <v>7500</v>
@@ -6082,7 +6082,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G197" t="n">
-        <v>7.47912836074829</v>
+        <v>7.47912883758545</v>
       </c>
       <c r="H197" t="n">
         <v>15000</v>
@@ -6111,7 +6111,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G198" t="n">
-        <v>7.42399930953979</v>
+        <v>7.42399978637695</v>
       </c>
       <c r="H198" t="n">
         <v>22500</v>
@@ -6140,7 +6140,7 @@
         <v>8.07999992370605</v>
       </c>
       <c r="G199" t="n">
-        <v>7.42399930953979</v>
+        <v>7.42399978637695</v>
       </c>
       <c r="H199" t="n">
         <v>6500</v>
@@ -6198,7 +6198,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G201" t="n">
-        <v>7.33211851119995</v>
+        <v>7.33211803436279</v>
       </c>
       <c r="H201" t="n">
         <v>17500</v>
@@ -6285,7 +6285,7 @@
         <v>7.98000001907349</v>
       </c>
       <c r="G204" t="n">
-        <v>7.33211851119995</v>
+        <v>7.33211803436279</v>
       </c>
       <c r="H204" t="n">
         <v>14000</v>
@@ -6314,7 +6314,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G205" t="n">
-        <v>7.31374263763428</v>
+        <v>7.31374216079712</v>
       </c>
       <c r="H205" t="n">
         <v>14500</v>
@@ -6343,7 +6343,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G206" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H206" t="n">
         <v>10000</v>
@@ -6401,7 +6401,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G208" t="n">
-        <v>7.20348501205444</v>
+        <v>7.2034854888916</v>
       </c>
       <c r="H208" t="n">
         <v>15000</v>
@@ -6430,7 +6430,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G209" t="n">
-        <v>7.22186088562012</v>
+        <v>7.22186136245728</v>
       </c>
       <c r="H209" t="n">
         <v>21500</v>
@@ -6517,7 +6517,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G212" t="n">
-        <v>7.0564751625061</v>
+        <v>7.05647468566895</v>
       </c>
       <c r="H212" t="n">
         <v>19500</v>
@@ -6575,7 +6575,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.83596038818359</v>
+        <v>6.83595991134644</v>
       </c>
       <c r="H214" t="n">
         <v>29500</v>
@@ -6633,7 +6633,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>6.8175835609436</v>
+        <v>6.81758403778076</v>
       </c>
       <c r="H216" t="n">
         <v>17500</v>
@@ -6662,7 +6662,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G217" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H217" t="n">
         <v>63000</v>
@@ -6691,7 +6691,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G218" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H218" t="n">
         <v>22500</v>
@@ -6720,7 +6720,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G219" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H219" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G220" t="n">
-        <v>6.57869291305542</v>
+        <v>6.57869243621826</v>
       </c>
       <c r="H220" t="n">
         <v>12000</v>
@@ -6778,7 +6778,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G221" t="n">
-        <v>6.46843528747559</v>
+        <v>6.46843481063843</v>
       </c>
       <c r="H221" t="n">
         <v>18500</v>
@@ -6807,7 +6807,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G222" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H222" t="n">
         <v>18500</v>
@@ -6836,7 +6836,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G223" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H223" t="n">
         <v>9000</v>
@@ -6865,7 +6865,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G224" t="n">
-        <v>6.85433673858643</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H224" t="n">
         <v>31500</v>
@@ -7213,7 +7213,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G236" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H236" t="n">
         <v>4500</v>
@@ -7242,7 +7242,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G237" t="n">
-        <v>6.85433673858643</v>
+        <v>6.85433626174927</v>
       </c>
       <c r="H237" t="n">
         <v>14500</v>
@@ -7300,7 +7300,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G239" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H239" t="n">
         <v>8000</v>
@@ -7329,7 +7329,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G240" t="n">
-        <v>6.91865301132202</v>
+        <v>6.91865348815918</v>
       </c>
       <c r="H240" t="n">
         <v>10000</v>
@@ -7387,7 +7387,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G242" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H242" t="n">
         <v>21500</v>
@@ -7474,7 +7474,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G245" t="n">
-        <v>6.76245498657227</v>
+        <v>6.76245546340942</v>
       </c>
       <c r="H245" t="n">
         <v>4500</v>
@@ -7648,7 +7648,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G251" t="n">
-        <v>6.57869291305542</v>
+        <v>6.57869243621826</v>
       </c>
       <c r="H251" t="n">
         <v>5000</v>
@@ -7735,7 +7735,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G254" t="n">
-        <v>6.35817766189575</v>
+        <v>6.35817813873291</v>
       </c>
       <c r="H254" t="n">
         <v>14500</v>
@@ -7793,7 +7793,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G256" t="n">
-        <v>6.15603876113892</v>
+        <v>6.15603923797607</v>
       </c>
       <c r="H256" t="n">
         <v>28000</v>
@@ -7822,7 +7822,7 @@
         <v>6.78999996185303</v>
       </c>
       <c r="G257" t="n">
-        <v>6.23873233795166</v>
+        <v>6.23873281478882</v>
       </c>
       <c r="H257" t="n">
         <v>3500</v>
@@ -7909,7 +7909,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G260" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H260" t="n">
         <v>5000</v>
@@ -7938,7 +7938,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G261" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H261" t="n">
         <v>25000</v>
@@ -7967,7 +7967,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G262" t="n">
-        <v>6.79001951217651</v>
+        <v>6.79001903533936</v>
       </c>
       <c r="H262" t="n">
         <v>104000</v>
@@ -8083,7 +8083,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G266" t="n">
-        <v>6.65219783782959</v>
+        <v>6.65219736099243</v>
       </c>
       <c r="H266" t="n">
         <v>20500</v>
@@ -8141,7 +8141,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G268" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H268" t="n">
         <v>11000</v>
@@ -8228,7 +8228,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G271" t="n">
-        <v>6.46843528747559</v>
+        <v>6.46843481063843</v>
       </c>
       <c r="H271" t="n">
         <v>20500</v>
@@ -8286,7 +8286,7 @@
         <v>6.96999979019165</v>
       </c>
       <c r="G273" t="n">
-        <v>6.40411853790283</v>
+        <v>6.40411806106567</v>
       </c>
       <c r="H273" t="n">
         <v>10000</v>
@@ -8315,7 +8315,7 @@
         <v>7.01000022888184</v>
       </c>
       <c r="G274" t="n">
-        <v>6.44087171554565</v>
+        <v>6.4408712387085</v>
       </c>
       <c r="H274" t="n">
         <v>6000</v>
@@ -8344,7 +8344,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G275" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H275" t="n">
         <v>3000</v>
@@ -8489,7 +8489,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G280" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H280" t="n">
         <v>26500</v>
@@ -8518,7 +8518,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G281" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H281" t="n">
         <v>27500</v>
@@ -8547,7 +8547,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G282" t="n">
-        <v>5.73338603973389</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H282" t="n">
         <v>18500</v>
@@ -8750,7 +8750,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>5.60475206375122</v>
+        <v>5.60475158691406</v>
       </c>
       <c r="H289" t="n">
         <v>12500</v>
@@ -8779,7 +8779,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G290" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526779174805</v>
       </c>
       <c r="H290" t="n">
         <v>35000</v>
@@ -8866,7 +8866,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G293" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H293" t="n">
         <v>64000</v>
@@ -8895,7 +8895,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G294" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H294" t="n">
         <v>23500</v>
@@ -8924,7 +8924,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G295" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H295" t="n">
         <v>12500</v>
@@ -8982,7 +8982,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G297" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H297" t="n">
         <v>14500</v>
@@ -9011,7 +9011,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G298" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H298" t="n">
         <v>9000</v>
@@ -9040,7 +9040,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G299" t="n">
-        <v>6.56950426101685</v>
+        <v>6.569504737854</v>
       </c>
       <c r="H299" t="n">
         <v>6000</v>
@@ -9069,7 +9069,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>6.52356386184692</v>
+        <v>6.52356433868408</v>
       </c>
       <c r="H300" t="n">
         <v>39500</v>
@@ -9098,7 +9098,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G301" t="n">
-        <v>6.45924711227417</v>
+        <v>6.45924758911133</v>
       </c>
       <c r="H301" t="n">
         <v>43000</v>
@@ -9127,7 +9127,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>6.45005941390991</v>
+        <v>6.45005893707275</v>
       </c>
       <c r="H302" t="n">
         <v>17500</v>
@@ -9156,7 +9156,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G303" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386043548584</v>
       </c>
       <c r="H303" t="n">
         <v>18000</v>
@@ -9214,7 +9214,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>6.293860912323</v>
+        <v>6.29386043548584</v>
       </c>
       <c r="H305" t="n">
         <v>4000</v>
@@ -9243,7 +9243,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G306" t="n">
-        <v>6.35817766189575</v>
+        <v>6.35817813873291</v>
       </c>
       <c r="H306" t="n">
         <v>8000</v>
@@ -9359,7 +9359,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G310" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H310" t="n">
         <v>7500</v>
@@ -9446,7 +9446,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G313" t="n">
-        <v>6.05497026443481</v>
+        <v>6.05496978759766</v>
       </c>
       <c r="H313" t="n">
         <v>1500</v>
@@ -9533,7 +9533,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G316" t="n">
-        <v>6.13766288757324</v>
+        <v>6.13766241073608</v>
       </c>
       <c r="H316" t="n">
         <v>5500</v>
@@ -9562,7 +9562,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G317" t="n">
-        <v>6.09172248840332</v>
+        <v>6.09172201156616</v>
       </c>
       <c r="H317" t="n">
         <v>1500</v>
@@ -9736,7 +9736,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G323" t="n">
-        <v>5.91714859008789</v>
+        <v>5.91714811325073</v>
       </c>
       <c r="H323" t="n">
         <v>7000</v>
@@ -9765,7 +9765,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G324" t="n">
-        <v>5.82526731491089</v>
+        <v>5.82526779174805</v>
       </c>
       <c r="H324" t="n">
         <v>5000</v>
@@ -9794,7 +9794,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G325" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H325" t="n">
         <v>13000</v>
@@ -9852,7 +9852,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G327" t="n">
-        <v>5.81607866287231</v>
+        <v>5.81607913970947</v>
       </c>
       <c r="H327" t="n">
         <v>14080</v>
@@ -9881,7 +9881,7 @@
         <v>6.30999994277954</v>
       </c>
       <c r="G328" t="n">
-        <v>5.79770278930664</v>
+        <v>5.79770231246948</v>
       </c>
       <c r="H328" t="n">
         <v>8871</v>
@@ -9939,7 +9939,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G330" t="n">
-        <v>5.84364318847656</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H330" t="n">
         <v>2311</v>
@@ -9968,7 +9968,7 @@
         <v>6.5</v>
       </c>
       <c r="G331" t="n">
-        <v>5.97227668762207</v>
+        <v>5.97227716445923</v>
       </c>
       <c r="H331" t="n">
         <v>2229</v>
@@ -9997,7 +9997,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G332" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H332" t="n">
         <v>4456</v>
@@ -10026,7 +10026,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G333" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H333" t="n">
         <v>2022</v>
@@ -10084,7 +10084,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G335" t="n">
-        <v>6.33980178833008</v>
+        <v>6.33980226516724</v>
       </c>
       <c r="H335" t="n">
         <v>25940</v>
@@ -10171,7 +10171,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>6.32142543792725</v>
+        <v>6.3214259147644</v>
       </c>
       <c r="H338" t="n">
         <v>7965</v>
@@ -10258,7 +10258,7 @@
         <v>6.98999977111816</v>
       </c>
       <c r="G341" t="n">
-        <v>6.42249441146851</v>
+        <v>6.42249488830566</v>
       </c>
       <c r="H341" t="n">
         <v>12887</v>
@@ -10287,7 +10287,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G342" t="n">
-        <v>6.41330623626709</v>
+        <v>6.41330671310425</v>
       </c>
       <c r="H342" t="n">
         <v>2560</v>
@@ -10345,7 +10345,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G344" t="n">
-        <v>6.32142543792725</v>
+        <v>6.3214259147644</v>
       </c>
       <c r="H344" t="n">
         <v>13218</v>
@@ -10374,7 +10374,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G345" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H345" t="n">
         <v>2764</v>
@@ -10403,7 +10403,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G346" t="n">
-        <v>6.10091066360474</v>
+        <v>6.10091018676758</v>
       </c>
       <c r="H346" t="n">
         <v>5191</v>
@@ -10490,7 +10490,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G349" t="n">
-        <v>6.07334661483765</v>
+        <v>6.07334613800049</v>
       </c>
       <c r="H349" t="n">
         <v>8810</v>
@@ -10577,7 +10577,7 @@
         <v>6.5</v>
       </c>
       <c r="G352" t="n">
-        <v>5.97227668762207</v>
+        <v>5.97227716445923</v>
       </c>
       <c r="H352" t="n">
         <v>13222</v>
@@ -10635,7 +10635,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G354" t="n">
-        <v>5.27398014068604</v>
+        <v>5.27397918701172</v>
       </c>
       <c r="H354" t="n">
         <v>17836</v>
@@ -10664,7 +10664,7 @@
         <v>5.86999988555908</v>
       </c>
       <c r="G355" t="n">
-        <v>5.39342594146729</v>
+        <v>5.39342498779297</v>
       </c>
       <c r="H355" t="n">
         <v>1874</v>
@@ -10722,7 +10722,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G357" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H357" t="n">
         <v>2284</v>
@@ -10809,7 +10809,7 @@
         <v>6</v>
       </c>
       <c r="G360" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H360" t="n">
         <v>2285</v>
@@ -10896,7 +10896,7 @@
         <v>6.07000017166138</v>
       </c>
       <c r="G363" t="n">
-        <v>5.57718801498413</v>
+        <v>5.57718753814697</v>
       </c>
       <c r="H363" t="n">
         <v>1392</v>
@@ -10925,7 +10925,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G364" t="n">
-        <v>5.43936634063721</v>
+        <v>5.43936586380005</v>
       </c>
       <c r="H364" t="n">
         <v>1105</v>
@@ -11041,7 +11041,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G368" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H368" t="n">
         <v>11426</v>
@@ -11099,7 +11099,7 @@
         <v>6.3899998664856</v>
       </c>
       <c r="G370" t="n">
-        <v>5.87120771408081</v>
+        <v>5.87120723724365</v>
       </c>
       <c r="H370" t="n">
         <v>3154</v>
@@ -11157,7 +11157,7 @@
         <v>6.5</v>
       </c>
       <c r="G372" t="n">
-        <v>5.97227668762207</v>
+        <v>5.97227716445923</v>
       </c>
       <c r="H372" t="n">
         <v>1924</v>
@@ -11186,7 +11186,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G373" t="n">
-        <v>5.94471263885498</v>
+        <v>5.94471216201782</v>
       </c>
       <c r="H373" t="n">
         <v>1000</v>
@@ -11215,7 +11215,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G374" t="n">
-        <v>6.07334661483765</v>
+        <v>6.07334613800049</v>
       </c>
       <c r="H374" t="n">
         <v>4630</v>
@@ -11244,7 +11244,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G375" t="n">
-        <v>6.28467321395874</v>
+        <v>6.28467273712158</v>
       </c>
       <c r="H375" t="n">
         <v>9545</v>
@@ -11302,7 +11302,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G377" t="n">
-        <v>5.73338603973389</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H377" t="n">
         <v>6848</v>
@@ -11360,7 +11360,7 @@
         <v>6.19000005722046</v>
       </c>
       <c r="G379" t="n">
-        <v>5.68744564056396</v>
+        <v>5.68744516372681</v>
       </c>
       <c r="H379" t="n">
         <v>2986</v>
@@ -11418,7 +11418,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G381" t="n">
-        <v>5.78851509094238</v>
+        <v>5.78851461410522</v>
       </c>
       <c r="H381" t="n">
         <v>5665</v>
@@ -11476,7 +11476,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G383" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H383" t="n">
         <v>1054</v>
@@ -11505,7 +11505,7 @@
         <v>6.09000015258789</v>
       </c>
       <c r="G384" t="n">
-        <v>5.59556484222412</v>
+        <v>5.5955638885498</v>
       </c>
       <c r="H384" t="n">
         <v>12595</v>
@@ -11534,7 +11534,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G385" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H385" t="n">
         <v>1810</v>
@@ -11563,7 +11563,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G386" t="n">
-        <v>5.58637619018555</v>
+        <v>5.58637571334839</v>
       </c>
       <c r="H386" t="n">
         <v>2950</v>
@@ -11592,7 +11592,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G387" t="n">
-        <v>5.70582103729248</v>
+        <v>5.70582151412964</v>
       </c>
       <c r="H387" t="n">
         <v>2675</v>
@@ -11650,7 +11650,7 @@
         <v>6.28999996185303</v>
       </c>
       <c r="G389" t="n">
-        <v>5.77932691574097</v>
+        <v>5.77932643890381</v>
       </c>
       <c r="H389" t="n">
         <v>6221</v>
@@ -11679,7 +11679,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G390" t="n">
-        <v>5.78851509094238</v>
+        <v>5.78851461410522</v>
       </c>
       <c r="H390" t="n">
         <v>5008</v>
@@ -11708,7 +11708,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G391" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H391" t="n">
         <v>4247</v>
@@ -11853,7 +11853,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G396" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H396" t="n">
         <v>2491</v>
@@ -11882,7 +11882,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G397" t="n">
-        <v>6.17441558837891</v>
+        <v>6.17441511154175</v>
       </c>
       <c r="H397" t="n">
         <v>1264</v>
@@ -11998,7 +11998,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G401" t="n">
-        <v>5.99065351486206</v>
+        <v>5.9906530380249</v>
       </c>
       <c r="H401" t="n">
         <v>4770</v>
@@ -12056,7 +12056,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G403" t="n">
-        <v>5.84364318847656</v>
+        <v>5.84364366531372</v>
       </c>
       <c r="H403" t="n">
         <v>2709</v>
@@ -12172,7 +12172,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G407" t="n">
-        <v>5.86201953887939</v>
+        <v>5.86202001571655</v>
       </c>
       <c r="H407" t="n">
         <v>1611</v>
@@ -12201,7 +12201,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G408" t="n">
-        <v>5.73338603973389</v>
+        <v>5.73338556289673</v>
       </c>
       <c r="H408" t="n">
         <v>4978</v>
@@ -12259,7 +12259,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G410" t="n">
-        <v>5.89877223968506</v>
+        <v>5.8987717628479</v>
       </c>
       <c r="H410" t="n">
         <v>1853</v>
@@ -12288,7 +12288,7 @@
         <v>6.5</v>
       </c>
       <c r="G411" t="n">
-        <v>5.97227668762207</v>
+        <v>5.97227716445923</v>
       </c>
       <c r="H411" t="n">
         <v>1407</v>
@@ -12317,7 +12317,7 @@
         <v>6.32999992370605</v>
       </c>
       <c r="G412" t="n">
-        <v>5.81607866287231</v>
+        <v>5.81607913970947</v>
       </c>
       <c r="H412" t="n">
         <v>2753</v>
@@ -12375,7 +12375,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G414" t="n">
-        <v>5.78851509094238</v>
+        <v>5.78851461410522</v>
       </c>
       <c r="H414" t="n">
         <v>7162</v>
@@ -12404,7 +12404,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G415" t="n">
-        <v>5.63231658935547</v>
+        <v>5.63231706619263</v>
       </c>
       <c r="H415" t="n">
         <v>4705</v>
@@ -12462,7 +12462,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G417" t="n">
-        <v>5.53124761581421</v>
+        <v>5.53124713897705</v>
       </c>
       <c r="H417" t="n">
         <v>1848</v>
@@ -12491,7 +12491,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G418" t="n">
-        <v>5.60475206375122</v>
+        <v>5.60475158691406</v>
       </c>
       <c r="H418" t="n">
         <v>1001</v>
@@ -12549,7 +12549,7 @@
         <v>6</v>
       </c>
       <c r="G420" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H420" t="n">
         <v>2335</v>
@@ -12578,7 +12578,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G421" t="n">
-        <v>5.69663333892822</v>
+        <v>5.69663286209106</v>
       </c>
       <c r="H421" t="n">
         <v>4496</v>
@@ -12636,7 +12636,7 @@
         <v>6</v>
       </c>
       <c r="G423" t="n">
-        <v>5.51287078857422</v>
+        <v>5.51287126541138</v>
       </c>
       <c r="H423" t="n">
         <v>3401</v>
@@ -12694,7 +12694,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G425" t="n">
-        <v>5.41180181503296</v>
+        <v>5.4118013381958</v>
       </c>
       <c r="H425" t="n">
         <v>3167</v>
@@ -12781,7 +12781,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G428" t="n">
-        <v>5.27398014068604</v>
+        <v>5.27397918701172</v>
       </c>
       <c r="H428" t="n">
         <v>3146</v>
@@ -12839,7 +12839,7 @@
         <v>5.78999996185303</v>
       </c>
       <c r="G430" t="n">
-        <v>5.31992101669312</v>
+        <v>5.31992053985596</v>
       </c>
       <c r="H430" t="n">
         <v>4924</v>
@@ -12897,7 +12897,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G432" t="n">
-        <v>5.38423776626587</v>
+        <v>5.38423728942871</v>
       </c>
       <c r="H432" t="n">
         <v>3519</v>
@@ -12984,7 +12984,7 @@
         <v>5.5</v>
       </c>
       <c r="G435" t="n">
-        <v>5.05346536636353</v>
+        <v>5.05346488952637</v>
       </c>
       <c r="H435" t="n">
         <v>15369</v>
@@ -13013,7 +13013,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G436" t="n">
-        <v>4.86970329284668</v>
+        <v>4.86970281600952</v>
       </c>
       <c r="H436" t="n">
         <v>13180</v>
@@ -13042,7 +13042,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G437" t="n">
-        <v>4.73188161849976</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H437" t="n">
         <v>15638</v>
@@ -13071,7 +13071,7 @@
         <v>5.09000015258789</v>
       </c>
       <c r="G438" t="n">
-        <v>4.67675256729126</v>
+        <v>4.6767520904541</v>
       </c>
       <c r="H438" t="n">
         <v>13127</v>
@@ -13100,7 +13100,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G439" t="n">
-        <v>4.58487033843994</v>
+        <v>4.58487129211426</v>
       </c>
       <c r="H439" t="n">
         <v>4452</v>
@@ -13129,7 +13129,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G440" t="n">
-        <v>4.57568311691284</v>
+        <v>4.57568264007568</v>
       </c>
       <c r="H440" t="n">
         <v>3846</v>
@@ -13187,7 +13187,7 @@
         <v>5</v>
       </c>
       <c r="G442" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H442" t="n">
         <v>3292</v>
@@ -13245,7 +13245,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G444" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029644012451</v>
       </c>
       <c r="H444" t="n">
         <v>14966</v>
@@ -13361,7 +13361,7 @@
         <v>5</v>
       </c>
       <c r="G448" t="n">
-        <v>4.59405946731567</v>
+        <v>4.59405899047852</v>
       </c>
       <c r="H448" t="n">
         <v>24980</v>
@@ -13419,7 +13419,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G450" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H450" t="n">
         <v>8026</v>
@@ -13477,7 +13477,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G452" t="n">
-        <v>4.41948509216309</v>
+        <v>4.41948461532593</v>
       </c>
       <c r="H452" t="n">
         <v>45286</v>
@@ -13593,7 +13593,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G456" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H456" t="n">
         <v>10262</v>
@@ -13622,7 +13622,7 @@
         <v>4.88500022888184</v>
       </c>
       <c r="G457" t="n">
-        <v>4.48839569091797</v>
+        <v>4.48839616775513</v>
       </c>
       <c r="H457" t="n">
         <v>11036</v>
@@ -13651,7 +13651,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G458" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H458" t="n">
         <v>3652</v>
@@ -13680,7 +13680,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G459" t="n">
-        <v>4.47461414337158</v>
+        <v>4.47461366653442</v>
       </c>
       <c r="H459" t="n">
         <v>11746</v>
@@ -13796,7 +13796,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G463" t="n">
-        <v>4.52974271774292</v>
+        <v>4.52974224090576</v>
       </c>
       <c r="H463" t="n">
         <v>15140</v>
@@ -13854,7 +13854,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G465" t="n">
-        <v>4.49758434295654</v>
+        <v>4.49758386611938</v>
       </c>
       <c r="H465" t="n">
         <v>9324</v>
@@ -13883,7 +13883,7 @@
         <v>4.94500017166138</v>
       </c>
       <c r="G466" t="n">
-        <v>4.54352474212646</v>
+        <v>4.54352426528931</v>
       </c>
       <c r="H466" t="n">
         <v>8377</v>
@@ -13912,7 +13912,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G467" t="n">
-        <v>4.43786096572876</v>
+        <v>4.43786144256592</v>
       </c>
       <c r="H467" t="n">
         <v>6325</v>
@@ -13970,7 +13970,7 @@
         <v>4.875</v>
       </c>
       <c r="G469" t="n">
-        <v>4.47920751571655</v>
+        <v>4.47920799255371</v>
       </c>
       <c r="H469" t="n">
         <v>1653</v>
@@ -13999,7 +13999,7 @@
         <v>4.89499998092651</v>
       </c>
       <c r="G470" t="n">
-        <v>4.49758434295654</v>
+        <v>4.49758386611938</v>
       </c>
       <c r="H470" t="n">
         <v>305</v>
@@ -14086,7 +14086,7 @@
         <v>4.77500009536743</v>
       </c>
       <c r="G473" t="n">
-        <v>4.38732671737671</v>
+        <v>4.38732624053955</v>
       </c>
       <c r="H473" t="n">
         <v>3916</v>
@@ -14173,7 +14173,7 @@
         <v>4.86499977111816</v>
       </c>
       <c r="G476" t="n">
-        <v>4.47001886367798</v>
+        <v>4.47001934051514</v>
       </c>
       <c r="H476" t="n">
         <v>6268</v>
@@ -14231,7 +14231,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H478" t="n">
         <v>4551</v>
@@ -14289,7 +14289,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G480" t="n">
-        <v>4.2724757194519</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H480" t="n">
         <v>8400</v>
@@ -14376,7 +14376,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G483" t="n">
-        <v>3.92332696914673</v>
+        <v>3.92332625389099</v>
       </c>
       <c r="H483" t="n">
         <v>27347</v>
@@ -14405,7 +14405,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G484" t="n">
-        <v>3.91413903236389</v>
+        <v>3.91413879394531</v>
       </c>
       <c r="H484" t="n">
         <v>16325</v>
@@ -14434,7 +14434,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G485" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H485" t="n">
         <v>4207</v>
@@ -14463,7 +14463,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G486" t="n">
-        <v>3.97845506668091</v>
+        <v>3.97845530509949</v>
       </c>
       <c r="H486" t="n">
         <v>10566</v>
@@ -14579,7 +14579,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G490" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469275474548</v>
       </c>
       <c r="H490" t="n">
         <v>12595</v>
@@ -14608,7 +14608,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G491" t="n">
-        <v>3.82225728034973</v>
+        <v>3.82225680351257</v>
       </c>
       <c r="H491" t="n">
         <v>2924</v>
@@ -14695,7 +14695,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G494" t="n">
-        <v>3.83144569396973</v>
+        <v>3.83144545555115</v>
       </c>
       <c r="H494" t="n">
         <v>10321</v>
@@ -14724,7 +14724,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G495" t="n">
-        <v>3.85900974273682</v>
+        <v>3.85900950431824</v>
       </c>
       <c r="H495" t="n">
         <v>5373</v>
@@ -14753,7 +14753,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G496" t="n">
-        <v>3.79469323158264</v>
+        <v>3.79469275474548</v>
       </c>
       <c r="H496" t="n">
         <v>3796</v>
@@ -14782,7 +14782,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G497" t="n">
-        <v>3.93251490592957</v>
+        <v>3.93251514434814</v>
       </c>
       <c r="H497" t="n">
         <v>8274</v>
@@ -14927,7 +14927,7 @@
         <v>4.36999988555908</v>
       </c>
       <c r="G502" t="n">
-        <v>4.01520824432373</v>
+        <v>4.01520729064941</v>
       </c>
       <c r="H502" t="n">
         <v>8779</v>
@@ -14985,7 +14985,7 @@
         <v>4.7350001335144</v>
       </c>
       <c r="G504" t="n">
-        <v>4.35057401657104</v>
+        <v>4.35057353973389</v>
       </c>
       <c r="H504" t="n">
         <v>35126</v>
@@ -15014,7 +15014,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G505" t="n">
-        <v>4.2724757194519</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H505" t="n">
         <v>17677</v>
@@ -15072,7 +15072,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G507" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H507" t="n">
         <v>9121</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029644012451</v>
       </c>
       <c r="H508" t="n">
         <v>3615</v>
@@ -15130,7 +15130,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G509" t="n">
-        <v>4.43786096572876</v>
+        <v>4.43786144256592</v>
       </c>
       <c r="H509" t="n">
         <v>7266</v>
@@ -15159,7 +15159,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G510" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029644012451</v>
       </c>
       <c r="H510" t="n">
         <v>6857</v>
@@ -15217,7 +15217,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G512" t="n">
-        <v>4.30003929138184</v>
+        <v>4.30003881454468</v>
       </c>
       <c r="H512" t="n">
         <v>5794</v>
@@ -15275,7 +15275,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G514" t="n">
-        <v>4.40570306777954</v>
+        <v>4.40570259094238</v>
       </c>
       <c r="H514" t="n">
         <v>4889</v>
@@ -15362,7 +15362,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G517" t="n">
-        <v>4.391921043396</v>
+        <v>4.39192056655884</v>
       </c>
       <c r="H517" t="n">
         <v>7436</v>
@@ -15391,7 +15391,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G518" t="n">
-        <v>4.31841564178467</v>
+        <v>4.31841516494751</v>
       </c>
       <c r="H518" t="n">
         <v>5744</v>
@@ -15420,7 +15420,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G519" t="n">
-        <v>4.37354469299316</v>
+        <v>4.37354421615601</v>
       </c>
       <c r="H519" t="n">
         <v>11351</v>
@@ -15449,7 +15449,7 @@
         <v>5.15000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>4.73188161849976</v>
+        <v>4.7318811416626</v>
       </c>
       <c r="H520" t="n">
         <v>62686</v>
@@ -15536,7 +15536,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G523" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H523" t="n">
         <v>16347</v>
@@ -15565,7 +15565,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G524" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H524" t="n">
         <v>11142</v>
@@ -15594,7 +15594,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H525" t="n">
         <v>6708</v>
@@ -15623,7 +15623,7 @@
         <v>5.17000007629395</v>
       </c>
       <c r="G526" t="n">
-        <v>4.75025749206543</v>
+        <v>4.75025701522827</v>
       </c>
       <c r="H526" t="n">
         <v>7054</v>
@@ -15681,7 +15681,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G528" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H528" t="n">
         <v>7274</v>
@@ -15710,7 +15710,7 @@
         <v>5.32999992370605</v>
       </c>
       <c r="G529" t="n">
-        <v>4.89726686477661</v>
+        <v>4.89726638793945</v>
       </c>
       <c r="H529" t="n">
         <v>14250</v>
@@ -15739,7 +15739,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G530" t="n">
-        <v>4.85132646560669</v>
+        <v>4.85132694244385</v>
       </c>
       <c r="H530" t="n">
         <v>3028</v>
@@ -15768,7 +15768,7 @@
         <v>5.21000003814697</v>
       </c>
       <c r="G531" t="n">
-        <v>4.78700923919678</v>
+        <v>4.78700971603394</v>
       </c>
       <c r="H531" t="n">
         <v>4381</v>
@@ -15826,7 +15826,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G533" t="n">
-        <v>4.90645551681519</v>
+        <v>4.90645503997803</v>
       </c>
       <c r="H533" t="n">
         <v>5784</v>
@@ -15855,7 +15855,7 @@
         <v>5.26999998092651</v>
       </c>
       <c r="G534" t="n">
-        <v>4.84213829040527</v>
+        <v>4.84213876724243</v>
       </c>
       <c r="H534" t="n">
         <v>5758</v>
@@ -15884,7 +15884,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G535" t="n">
-        <v>5.09021759033203</v>
+        <v>5.09021711349487</v>
       </c>
       <c r="H535" t="n">
         <v>24385</v>
@@ -16000,7 +16000,7 @@
         <v>5.30999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>4.87889099121094</v>
+        <v>4.87889051437378</v>
       </c>
       <c r="H539" t="n">
         <v>6892</v>
@@ -16029,7 +16029,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G540" t="n">
-        <v>4.85132646560669</v>
+        <v>4.85132694244385</v>
       </c>
       <c r="H540" t="n">
         <v>5649</v>
@@ -16087,7 +16087,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G542" t="n">
-        <v>4.86970329284668</v>
+        <v>4.86970281600952</v>
       </c>
       <c r="H542" t="n">
         <v>3105</v>
@@ -16116,7 +16116,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G543" t="n">
-        <v>4.79619789123535</v>
+        <v>4.79619741439819</v>
       </c>
       <c r="H543" t="n">
         <v>1688</v>
@@ -16261,7 +16261,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G548" t="n">
-        <v>4.41029739379883</v>
+        <v>4.41029644012451</v>
       </c>
       <c r="H548" t="n">
         <v>5791</v>
@@ -16319,7 +16319,7 @@
         <v>4.79500007629395</v>
       </c>
       <c r="G550" t="n">
-        <v>4.40570306777954</v>
+        <v>4.40570259094238</v>
       </c>
       <c r="H550" t="n">
         <v>4930</v>
@@ -16348,7 +16348,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G551" t="n">
-        <v>4.20815849304199</v>
+        <v>4.20815801620483</v>
       </c>
       <c r="H551" t="n">
         <v>18005</v>
@@ -16406,7 +16406,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G553" t="n">
-        <v>4.2724757194519</v>
+        <v>4.27247524261475</v>
       </c>
       <c r="H553" t="n">
         <v>1650</v>
@@ -16435,7 +16435,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G554" t="n">
-        <v>4.22653484344482</v>
+        <v>4.22653436660767</v>
       </c>
       <c r="H554" t="n">
         <v>2710</v>
@@ -16493,7 +16493,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G556" t="n">
-        <v>4.15302991867065</v>
+        <v>4.1530294418335</v>
       </c>
       <c r="H556" t="n">
         <v>3648</v>
@@ -16522,7 +16522,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G557" t="n">
-        <v>4.12546491622925</v>
+        <v>4.12546539306641</v>
       </c>
       <c r="H557" t="n">
         <v>7122</v>
@@ -16551,7 +16551,7 @@
         <v>4.24499988555908</v>
       </c>
       <c r="G558" t="n">
-        <v>3.90035581588745</v>
+        <v>3.90035629272461</v>
       </c>
       <c r="H558" t="n">
         <v>78936</v>
@@ -16609,7 +16609,7 @@
         <v>4.06500005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>3.73497033119202</v>
+        <v>3.73497009277344</v>
       </c>
       <c r="H560" t="n">
         <v>18999</v>
@@ -16638,7 +16638,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G561" t="n">
-        <v>3.77631688117981</v>
+        <v>3.77631664276123</v>
       </c>
       <c r="H561" t="n">
         <v>14097</v>
@@ -16754,7 +16754,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G565" t="n">
-        <v>3.65687131881714</v>
+        <v>3.65687108039856</v>
       </c>
       <c r="H565" t="n">
         <v>350</v>
@@ -16783,7 +16783,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G566" t="n">
-        <v>3.57417821884155</v>
+        <v>3.57417798042297</v>
       </c>
       <c r="H566" t="n">
         <v>6203</v>
@@ -16812,7 +16812,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G567" t="n">
-        <v>3.66605925559998</v>
+        <v>3.6660590171814</v>
       </c>
       <c r="H567" t="n">
         <v>5620</v>
@@ -16899,7 +16899,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G570" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H570" t="n">
         <v>38613</v>
@@ -16928,7 +16928,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G571" t="n">
-        <v>3.38122749328613</v>
+        <v>3.38122773170471</v>
       </c>
       <c r="H571" t="n">
         <v>7214</v>
@@ -16957,7 +16957,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G572" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H572" t="n">
         <v>40710</v>
@@ -16986,7 +16986,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G573" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H573" t="n">
         <v>28469</v>
@@ -17015,7 +17015,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G574" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H574" t="n">
         <v>22621</v>
@@ -17044,7 +17044,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G575" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H575" t="n">
         <v>2675</v>
@@ -17073,7 +17073,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G576" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H576" t="n">
         <v>1539</v>
@@ -17131,7 +17131,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G578" t="n">
-        <v>3.06883144378662</v>
+        <v>3.06883120536804</v>
       </c>
       <c r="H578" t="n">
         <v>17701</v>
@@ -17160,7 +17160,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G579" t="n">
-        <v>3.09639596939087</v>
+        <v>3.09639573097229</v>
       </c>
       <c r="H579" t="n">
         <v>10888</v>
@@ -17247,7 +17247,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G582" t="n">
-        <v>3.07801938056946</v>
+        <v>3.07801961898804</v>
       </c>
       <c r="H582" t="n">
         <v>2310</v>
@@ -17276,7 +17276,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G583" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H583" t="n">
         <v>18949</v>
@@ -17305,7 +17305,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G584" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H584" t="n">
         <v>25151</v>
@@ -17392,7 +17392,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G587" t="n">
-        <v>3.5006730556488</v>
+        <v>3.50067281723022</v>
       </c>
       <c r="H587" t="n">
         <v>4318</v>
@@ -17450,7 +17450,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G589" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H589" t="n">
         <v>11400</v>
@@ -17479,7 +17479,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G590" t="n">
-        <v>3.9417028427124</v>
+        <v>3.94170308113098</v>
       </c>
       <c r="H590" t="n">
         <v>70490</v>
@@ -17624,7 +17624,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G595" t="n">
-        <v>3.55580186843872</v>
+        <v>3.55580163002014</v>
       </c>
       <c r="H595" t="n">
         <v>9575</v>
@@ -17711,7 +17711,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G598" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H598" t="n">
         <v>3630</v>
@@ -17740,7 +17740,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G599" t="n">
-        <v>3.61093044281006</v>
+        <v>3.61093068122864</v>
       </c>
       <c r="H599" t="n">
         <v>8376</v>
@@ -17798,7 +17798,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G601" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H601" t="n">
         <v>18937</v>
@@ -17827,7 +17827,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G602" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H602" t="n">
         <v>23557</v>
@@ -17856,7 +17856,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G603" t="n">
-        <v>3.23421764373779</v>
+        <v>3.23421740531921</v>
       </c>
       <c r="H603" t="n">
         <v>2415</v>
@@ -17885,7 +17885,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G604" t="n">
-        <v>3.24340581893921</v>
+        <v>3.24340558052063</v>
       </c>
       <c r="H604" t="n">
         <v>8247</v>
@@ -17943,7 +17943,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G606" t="n">
-        <v>3.28015804290771</v>
+        <v>3.28015828132629</v>
       </c>
       <c r="H606" t="n">
         <v>4093</v>
@@ -17972,7 +17972,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>3.32609891891479</v>
+        <v>3.32609868049622</v>
       </c>
       <c r="H607" t="n">
         <v>1705</v>
@@ -18001,7 +18001,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G608" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H608" t="n">
         <v>18506</v>
@@ -18030,7 +18030,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G609" t="n">
-        <v>3.26178193092346</v>
+        <v>3.26178216934204</v>
       </c>
       <c r="H609" t="n">
         <v>2325</v>
@@ -18059,7 +18059,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G610" t="n">
-        <v>3.18827724456787</v>
+        <v>3.18827700614929</v>
       </c>
       <c r="H610" t="n">
         <v>6723</v>
@@ -18088,7 +18088,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G611" t="n">
-        <v>3.16990089416504</v>
+        <v>3.16990113258362</v>
       </c>
       <c r="H611" t="n">
         <v>4629</v>
@@ -18146,7 +18146,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G613" t="n">
-        <v>3.14233660697937</v>
+        <v>3.14233636856079</v>
       </c>
       <c r="H613" t="n">
         <v>1790</v>
@@ -18175,7 +18175,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G614" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H614" t="n">
         <v>18656</v>
@@ -18204,7 +18204,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G615" t="n">
-        <v>3.12396049499512</v>
+        <v>3.12396025657654</v>
       </c>
       <c r="H615" t="n">
         <v>1399</v>
@@ -18233,7 +18233,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G616" t="n">
-        <v>3.15152478218079</v>
+        <v>3.15152454376221</v>
       </c>
       <c r="H616" t="n">
         <v>4300</v>
@@ -18262,7 +18262,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G617" t="n">
-        <v>3.07801938056946</v>
+        <v>3.07801961898804</v>
       </c>
       <c r="H617" t="n">
         <v>10279</v>
@@ -18291,7 +18291,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G618" t="n">
-        <v>3.11477208137512</v>
+        <v>3.1147723197937</v>
       </c>
       <c r="H618" t="n">
         <v>1345</v>
@@ -18349,7 +18349,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G620" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H620" t="n">
         <v>26152</v>
@@ -18407,7 +18407,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G622" t="n">
-        <v>2.84831666946411</v>
+        <v>2.84831643104553</v>
       </c>
       <c r="H622" t="n">
         <v>13986</v>
@@ -18436,7 +18436,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G623" t="n">
-        <v>2.89425754547119</v>
+        <v>2.89425730705261</v>
       </c>
       <c r="H623" t="n">
         <v>25740</v>
@@ -18523,7 +18523,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G626" t="n">
-        <v>2.95857429504395</v>
+        <v>2.95857405662537</v>
       </c>
       <c r="H626" t="n">
         <v>14381</v>
@@ -18552,7 +18552,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G627" t="n">
-        <v>2.9310097694397</v>
+        <v>2.93101000785828</v>
       </c>
       <c r="H627" t="n">
         <v>10185</v>
@@ -18639,7 +18639,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G630" t="n">
-        <v>3.03276824951172</v>
+        <v>3.03276801109314</v>
       </c>
       <c r="H630" t="n">
         <v>1951</v>
@@ -18697,7 +18697,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G632" t="n">
-        <v>2.90252661705017</v>
+        <v>2.90252637863159</v>
       </c>
       <c r="H632" t="n">
         <v>10235</v>
@@ -18929,7 +18929,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G640" t="n">
-        <v>2.85601186752319</v>
+        <v>2.85601162910461</v>
       </c>
       <c r="H640" t="n">
         <v>11783</v>
@@ -18987,7 +18987,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G642" t="n">
-        <v>2.52110505104065</v>
+        <v>2.52110481262207</v>
       </c>
       <c r="H642" t="n">
         <v>95598</v>
@@ -19103,7 +19103,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G646" t="n">
-        <v>2.56761980056763</v>
+        <v>2.56761932373047</v>
       </c>
       <c r="H646" t="n">
         <v>8131</v>
@@ -19161,7 +19161,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G648" t="n">
-        <v>2.42807507514954</v>
+        <v>2.42807483673096</v>
       </c>
       <c r="H648" t="n">
         <v>23503</v>
@@ -19248,7 +19248,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G651" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H651" t="n">
         <v>18483</v>
@@ -19335,7 +19335,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G654" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H654" t="n">
         <v>19145</v>
@@ -19364,7 +19364,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G655" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H655" t="n">
         <v>11634</v>
@@ -19393,7 +19393,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G656" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H656" t="n">
         <v>10081</v>
@@ -19509,7 +19509,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G660" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H660" t="n">
         <v>4896</v>
@@ -19770,7 +19770,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.51180195808411</v>
+        <v>2.51180171966553</v>
       </c>
       <c r="H669" t="n">
         <v>22344</v>
@@ -19886,7 +19886,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H673" t="n">
         <v>536</v>
@@ -19915,7 +19915,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G674" t="n">
-        <v>2.40946912765503</v>
+        <v>2.40946936607361</v>
       </c>
       <c r="H674" t="n">
         <v>1569</v>
@@ -20089,7 +20089,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G680" t="n">
-        <v>2.40016603469849</v>
+        <v>2.40016627311707</v>
       </c>
       <c r="H680" t="n">
         <v>1700</v>
@@ -20118,7 +20118,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>2.41877222061157</v>
+        <v>2.41877198219299</v>
       </c>
       <c r="H681" t="n">
         <v>3858</v>
@@ -20176,7 +20176,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G683" t="n">
-        <v>2.29783344268799</v>
+        <v>2.29783368110657</v>
       </c>
       <c r="H683" t="n">
         <v>7367</v>
@@ -20205,7 +20205,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G684" t="n">
-        <v>2.4931960105896</v>
+        <v>2.49319577217102</v>
       </c>
       <c r="H684" t="n">
         <v>12276</v>
@@ -20350,7 +20350,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G689" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H689" t="n">
         <v>73294</v>
@@ -20379,7 +20379,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G690" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H690" t="n">
         <v>18911</v>
@@ -20437,7 +20437,7 @@
         <v>1.25499999523163</v>
       </c>
       <c r="G692" t="n">
-        <v>1.16752278804779</v>
+        <v>1.1675226688385</v>
       </c>
       <c r="H692" t="n">
         <v>88258</v>
@@ -20495,7 +20495,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G694" t="n">
-        <v>1.74895834922791</v>
+        <v>1.74895823001862</v>
       </c>
       <c r="H694" t="n">
         <v>231606</v>
@@ -20524,7 +20524,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.95362365245819</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H695" t="n">
         <v>235716</v>
@@ -20640,7 +20640,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G699" t="n">
-        <v>1.54429304599762</v>
+        <v>1.54429292678833</v>
       </c>
       <c r="H699" t="n">
         <v>36020</v>
@@ -20669,7 +20669,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G700" t="n">
-        <v>1.51638412475586</v>
+        <v>1.51638400554657</v>
       </c>
       <c r="H700" t="n">
         <v>7380</v>
@@ -20698,7 +20698,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G701" t="n">
-        <v>1.4884752035141</v>
+        <v>1.48847508430481</v>
       </c>
       <c r="H701" t="n">
         <v>13536</v>
@@ -20727,7 +20727,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G702" t="n">
-        <v>1.45126330852509</v>
+        <v>1.4512631893158</v>
       </c>
       <c r="H702" t="n">
         <v>19933</v>
@@ -20814,7 +20814,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G705" t="n">
-        <v>1.44196033477783</v>
+        <v>1.44196021556854</v>
       </c>
       <c r="H705" t="n">
         <v>12919</v>
@@ -21046,7 +21046,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G713" t="n">
-        <v>1.51638412475586</v>
+        <v>1.51638400554657</v>
       </c>
       <c r="H713" t="n">
         <v>7640</v>
@@ -21104,7 +21104,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G715" t="n">
-        <v>1.58615636825562</v>
+        <v>1.5861564874649</v>
       </c>
       <c r="H715" t="n">
         <v>9473</v>
@@ -21133,7 +21133,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G716" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H716" t="n">
         <v>14629</v>
@@ -21191,7 +21191,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G718" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H718" t="n">
         <v>5148</v>
@@ -21220,7 +21220,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G719" t="n">
-        <v>1.59545946121216</v>
+        <v>1.59545934200287</v>
       </c>
       <c r="H719" t="n">
         <v>9455</v>
@@ -21249,7 +21249,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G720" t="n">
-        <v>1.63267123699188</v>
+        <v>1.63267111778259</v>
       </c>
       <c r="H720" t="n">
         <v>7920</v>
@@ -21307,7 +21307,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G722" t="n">
-        <v>1.55359590053558</v>
+        <v>1.55359578132629</v>
       </c>
       <c r="H722" t="n">
         <v>2574</v>
@@ -21336,7 +21336,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G723" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H723" t="n">
         <v>5633</v>
@@ -21423,7 +21423,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G726" t="n">
-        <v>1.92571485042572</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H726" t="n">
         <v>75327</v>
@@ -21510,7 +21510,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G729" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H729" t="n">
         <v>21650</v>
@@ -21568,7 +21568,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G731" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H731" t="n">
         <v>2155</v>
@@ -21597,7 +21597,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G732" t="n">
-        <v>2.14898610115051</v>
+        <v>2.14898586273193</v>
       </c>
       <c r="H732" t="n">
         <v>89764</v>
@@ -21626,7 +21626,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G733" t="n">
-        <v>2.42807507514954</v>
+        <v>2.42807483673096</v>
       </c>
       <c r="H733" t="n">
         <v>201386</v>
@@ -21742,7 +21742,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G737" t="n">
-        <v>2.18619799613953</v>
+        <v>2.18619775772095</v>
       </c>
       <c r="H737" t="n">
         <v>12209</v>
@@ -21771,7 +21771,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G738" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H738" t="n">
         <v>41345</v>
@@ -21800,7 +21800,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G739" t="n">
-        <v>2.19550085067749</v>
+        <v>2.19550061225891</v>
       </c>
       <c r="H739" t="n">
         <v>13585</v>
@@ -21887,7 +21887,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G742" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H742" t="n">
         <v>4041</v>
@@ -21916,7 +21916,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G743" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H743" t="n">
         <v>27715</v>
@@ -21974,7 +21974,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G745" t="n">
-        <v>2.00944185256958</v>
+        <v>2.009441614151</v>
       </c>
       <c r="H745" t="n">
         <v>22944</v>
@@ -22090,7 +22090,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G749" t="n">
-        <v>2.33504557609558</v>
+        <v>2.335045337677</v>
       </c>
       <c r="H749" t="n">
         <v>46515</v>
@@ -22148,7 +22148,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H751" t="n">
         <v>7609</v>
@@ -22177,7 +22177,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G752" t="n">
-        <v>2.21410703659058</v>
+        <v>2.214106798172</v>
       </c>
       <c r="H752" t="n">
         <v>18450</v>
@@ -22206,7 +22206,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G753" t="n">
-        <v>2.24201607704163</v>
+        <v>2.24201583862305</v>
       </c>
       <c r="H753" t="n">
         <v>7610</v>
@@ -22235,7 +22235,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G754" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H754" t="n">
         <v>54449</v>
@@ -22264,7 +22264,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G755" t="n">
-        <v>2.2885308265686</v>
+        <v>2.28853058815002</v>
       </c>
       <c r="H755" t="n">
         <v>13384</v>
@@ -22293,7 +22293,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G756" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H756" t="n">
         <v>6173</v>
@@ -22322,7 +22322,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G757" t="n">
-        <v>2.26062178611755</v>
+        <v>2.26062154769897</v>
       </c>
       <c r="H757" t="n">
         <v>9025</v>
@@ -22467,7 +22467,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G762" t="n">
-        <v>2.16759181022644</v>
+        <v>2.16759204864502</v>
       </c>
       <c r="H762" t="n">
         <v>4601</v>
@@ -22583,7 +22583,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G766" t="n">
-        <v>2.26992464065552</v>
+        <v>2.26992440223694</v>
       </c>
       <c r="H766" t="n">
         <v>6724</v>
@@ -22757,7 +22757,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G772" t="n">
-        <v>2.13038015365601</v>
+        <v>2.13037991523743</v>
       </c>
       <c r="H772" t="n">
         <v>12685</v>
@@ -22873,7 +22873,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G776" t="n">
-        <v>2.13968324661255</v>
+        <v>2.13968300819397</v>
       </c>
       <c r="H776" t="n">
         <v>3302</v>
@@ -22931,7 +22931,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G778" t="n">
-        <v>1.98153281211853</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H778" t="n">
         <v>10623</v>
@@ -22960,7 +22960,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G779" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H779" t="n">
         <v>6646</v>
@@ -23018,7 +23018,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G781" t="n">
-        <v>2.08386540412903</v>
+        <v>2.08386516571045</v>
       </c>
       <c r="H781" t="n">
         <v>400</v>
@@ -23047,7 +23047,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G782" t="n">
-        <v>1.98153281211853</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H782" t="n">
         <v>7820</v>
@@ -23076,7 +23076,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G783" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292638778687</v>
       </c>
       <c r="H783" t="n">
         <v>12163</v>
@@ -23105,7 +23105,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G784" t="n">
-        <v>1.99083566665649</v>
+        <v>1.9908355474472</v>
       </c>
       <c r="H784" t="n">
         <v>1181</v>
@@ -23134,7 +23134,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G785" t="n">
-        <v>1.89780580997467</v>
+        <v>1.89780569076538</v>
       </c>
       <c r="H785" t="n">
         <v>4151</v>
@@ -23163,7 +23163,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G786" t="n">
-        <v>1.92571485042572</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H786" t="n">
         <v>22188</v>
@@ -23221,7 +23221,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>2.05595660209656</v>
+        <v>2.05595636367798</v>
       </c>
       <c r="H788" t="n">
         <v>13900</v>
@@ -23279,7 +23279,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>2.03735065460205</v>
+        <v>2.03735017776489</v>
       </c>
       <c r="H790" t="n">
         <v>6918</v>
@@ -23308,7 +23308,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G791" t="n">
-        <v>2.00944185256958</v>
+        <v>2.009441614151</v>
       </c>
       <c r="H791" t="n">
         <v>2800</v>
@@ -23366,7 +23366,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G793" t="n">
-        <v>1.98153281211853</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H793" t="n">
         <v>8905</v>
@@ -23395,7 +23395,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G794" t="n">
-        <v>1.98153281211853</v>
+        <v>1.98153269290924</v>
       </c>
       <c r="H794" t="n">
         <v>13577</v>
@@ -23424,7 +23424,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G795" t="n">
-        <v>1.95362365245819</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H795" t="n">
         <v>8911</v>
@@ -23453,7 +23453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G796" t="n">
-        <v>1.95362365245819</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H796" t="n">
         <v>3170</v>
@@ -23482,7 +23482,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G797" t="n">
-        <v>1.95362365245819</v>
+        <v>1.9536235332489</v>
       </c>
       <c r="H797" t="n">
         <v>15172</v>
@@ -23511,7 +23511,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G798" t="n">
-        <v>1.92571485042572</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H798" t="n">
         <v>16878</v>
@@ -23598,7 +23598,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G801" t="n">
-        <v>1.92571485042572</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H801" t="n">
         <v>1502</v>
@@ -23656,7 +23656,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G803" t="n">
-        <v>1.78617024421692</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H803" t="n">
         <v>3999</v>
@@ -23714,7 +23714,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G805" t="n">
-        <v>1.77686715126038</v>
+        <v>1.77686727046967</v>
       </c>
       <c r="H805" t="n">
         <v>1</v>
@@ -23801,7 +23801,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G808" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H808" t="n">
         <v>8701</v>
@@ -23946,7 +23946,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G813" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H813" t="n">
         <v>3750</v>
@@ -24062,7 +24062,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G817" t="n">
-        <v>1.4884752035141</v>
+        <v>1.48847508430481</v>
       </c>
       <c r="H817" t="n">
         <v>14735</v>
@@ -24178,7 +24178,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G821" t="n">
-        <v>1.63267123699188</v>
+        <v>1.63267111778259</v>
       </c>
       <c r="H821" t="n">
         <v>16193</v>
@@ -24265,7 +24265,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G824" t="n">
-        <v>1.64197421073914</v>
+        <v>1.64197409152985</v>
       </c>
       <c r="H824" t="n">
         <v>17867</v>
@@ -24294,7 +24294,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.63732266426086</v>
+        <v>1.63732254505157</v>
       </c>
       <c r="H825" t="n">
         <v>2580</v>
@@ -24410,7 +24410,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G829" t="n">
-        <v>1.67453444004059</v>
+        <v>1.67453455924988</v>
       </c>
       <c r="H829" t="n">
         <v>19930</v>
@@ -24468,7 +24468,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G831" t="n">
-        <v>1.81873059272766</v>
+        <v>1.81873047351837</v>
       </c>
       <c r="H831" t="n">
         <v>14506</v>
@@ -24584,7 +24584,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G835" t="n">
-        <v>1.9722295999527</v>
+        <v>1.97222936153412</v>
       </c>
       <c r="H835" t="n">
         <v>50956</v>
@@ -24613,7 +24613,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G836" t="n">
-        <v>1.92571485042572</v>
+        <v>1.92571461200714</v>
       </c>
       <c r="H836" t="n">
         <v>55529</v>
@@ -24961,7 +24961,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G848" t="n">
-        <v>1.81873059272766</v>
+        <v>1.81873047351837</v>
       </c>
       <c r="H848" t="n">
         <v>1500</v>
@@ -25019,7 +25019,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G850" t="n">
-        <v>1.78617024421692</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H850" t="n">
         <v>10425</v>
@@ -25048,7 +25048,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G851" t="n">
-        <v>1.78617024421692</v>
+        <v>1.78617000579834</v>
       </c>
       <c r="H851" t="n">
         <v>616</v>
@@ -25135,7 +25135,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G854" t="n">
-        <v>1.93501770496368</v>
+        <v>1.93501758575439</v>
       </c>
       <c r="H854" t="n">
         <v>16193</v>
@@ -25280,7 +25280,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G859" t="n">
-        <v>1.94432067871094</v>
+        <v>1.94432055950165</v>
       </c>
       <c r="H859" t="n">
         <v>23244</v>
@@ -25309,7 +25309,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G860" t="n">
-        <v>1.96292650699615</v>
+        <v>1.96292638778687</v>
       </c>
       <c r="H860" t="n">
         <v>19342</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>2.18991017341614</v>
+        <v>2.18991041183472</v>
       </c>
       <c r="H864" t="n">
         <v>29824</v>
@@ -25454,7 +25454,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G865" t="n">
-        <v>2.1803891658783</v>
+        <v>2.18038892745972</v>
       </c>
       <c r="H865" t="n">
         <v>18169</v>
@@ -25541,7 +25541,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G868" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H868" t="n">
         <v>12463</v>
@@ -25599,7 +25599,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G870" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H870" t="n">
         <v>14204</v>
@@ -25628,7 +25628,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G871" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H871" t="n">
         <v>10741</v>
@@ -25686,7 +25686,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G873" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H873" t="n">
         <v>1780</v>
@@ -25715,7 +25715,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H874" t="n">
         <v>11963</v>
@@ -25860,7 +25860,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G879" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H879" t="n">
         <v>9646</v>
@@ -25918,7 +25918,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G881" t="n">
-        <v>2.05661177635193</v>
+        <v>2.05661153793335</v>
       </c>
       <c r="H881" t="n">
         <v>4363</v>
@@ -25947,7 +25947,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G882" t="n">
-        <v>1.98044061660767</v>
+        <v>1.98044073581696</v>
       </c>
       <c r="H882" t="n">
         <v>3757</v>
@@ -26005,7 +26005,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G884" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H884" t="n">
         <v>3933</v>
@@ -26092,7 +26092,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G887" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H887" t="n">
         <v>1502</v>
@@ -26121,7 +26121,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H888" t="n">
         <v>2991</v>
@@ -26150,7 +26150,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G889" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H889" t="n">
         <v>500</v>
@@ -26179,7 +26179,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G890" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H890" t="n">
         <v>500</v>
@@ -26208,7 +26208,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G891" t="n">
-        <v>1.95187664031982</v>
+        <v>1.95187675952911</v>
       </c>
       <c r="H891" t="n">
         <v>1750</v>
@@ -26237,7 +26237,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G892" t="n">
-        <v>1.9994832277298</v>
+        <v>1.99948346614838</v>
       </c>
       <c r="H892" t="n">
         <v>3562</v>
@@ -26295,7 +26295,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G894" t="n">
-        <v>1.98996186256409</v>
+        <v>1.98996198177338</v>
       </c>
       <c r="H894" t="n">
         <v>2771</v>
@@ -27542,7 +27542,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G937" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H937" t="n">
         <v>12954</v>
@@ -27716,7 +27716,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G943" t="n">
-        <v>1.6948002576828</v>
+        <v>1.69480013847351</v>
       </c>
       <c r="H943" t="n">
         <v>13769</v>
@@ -27745,7 +27745,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G944" t="n">
-        <v>1.61862945556641</v>
+        <v>1.6186295747757</v>
       </c>
       <c r="H944" t="n">
         <v>22282</v>
@@ -27774,7 +27774,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G945" t="n">
-        <v>1.54245853424072</v>
+        <v>1.54245865345001</v>
       </c>
       <c r="H945" t="n">
         <v>13946</v>
@@ -27890,7 +27890,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G949" t="n">
-        <v>1.35679233074188</v>
+        <v>1.35679221153259</v>
       </c>
       <c r="H949" t="n">
         <v>12733</v>
@@ -27948,7 +27948,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G951" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H951" t="n">
         <v>18171</v>
@@ -28006,7 +28006,7 @@
         <v>1.37999999523163</v>
       </c>
       <c r="G953" t="n">
-        <v>1.31394624710083</v>
+        <v>1.31394612789154</v>
       </c>
       <c r="H953" t="n">
         <v>17476</v>
@@ -28122,7 +28122,7 @@
         <v>1.41499996185303</v>
       </c>
       <c r="G957" t="n">
-        <v>1.34727096557617</v>
+        <v>1.34727084636688</v>
       </c>
       <c r="H957" t="n">
         <v>10390</v>
@@ -28151,7 +28151,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G958" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H958" t="n">
         <v>120160</v>
@@ -28296,7 +28296,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G963" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H963" t="n">
         <v>70383</v>
@@ -28354,7 +28354,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G965" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H965" t="n">
         <v>11079</v>
@@ -28470,7 +28470,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G969" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H969" t="n">
         <v>5589</v>
@@ -28644,7 +28644,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G975" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H975" t="n">
         <v>16278</v>
@@ -28876,7 +28876,7 @@
         <v>0.889999985694885</v>
       </c>
       <c r="G983" t="n">
-        <v>0.8474001288414</v>
+        <v>0.847400069236755</v>
       </c>
       <c r="H983" t="n">
         <v>11888</v>
@@ -28934,7 +28934,7 @@
         <v>0.98199999332428</v>
       </c>
       <c r="G985" t="n">
-        <v>0.934996545314789</v>
+        <v>0.934996485710144</v>
       </c>
       <c r="H985" t="n">
         <v>22093</v>
@@ -28963,7 +28963,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G986" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H986" t="n">
         <v>24435</v>
@@ -29108,7 +29108,7 @@
         <v>1.19500005245209</v>
       </c>
       <c r="G991" t="n">
-        <v>1.1378014087677</v>
+        <v>1.13780128955841</v>
       </c>
       <c r="H991" t="n">
         <v>4904</v>
@@ -29137,7 +29137,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G992" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H992" t="n">
         <v>18073</v>
@@ -29253,7 +29253,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G996" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H996" t="n">
         <v>11904</v>
@@ -29282,7 +29282,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G997" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H997" t="n">
         <v>4540</v>
@@ -29427,7 +29427,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1002" t="n">
         <v>2974</v>
@@ -29485,7 +29485,7 @@
         <v>1.08000004291534</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.02830588817596</v>
+        <v>1.02830576896667</v>
       </c>
       <c r="H1004" t="n">
         <v>11264</v>
@@ -29630,7 +29630,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1009" t="n">
         <v>18426</v>
@@ -29659,7 +29659,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1010" t="n">
         <v>2505</v>
@@ -29978,7 +29978,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1021" t="n">
         <v>5361</v>
@@ -30036,7 +30036,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1023" t="n">
         <v>1000</v>
@@ -30123,7 +30123,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1026" t="n">
         <v>3669</v>
@@ -30152,7 +30152,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1027" t="n">
         <v>8946</v>
@@ -30268,7 +30268,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1031" t="n">
         <v>6700</v>
@@ -30326,7 +30326,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1033" t="n">
         <v>2860</v>
@@ -30384,7 +30384,7 @@
         <v>1.1599999666214</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.10447645187378</v>
+        <v>1.10447657108307</v>
       </c>
       <c r="H1035" t="n">
         <v>7202</v>
@@ -30413,7 +30413,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1036" t="n">
         <v>3000</v>
@@ -30442,7 +30442,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1037" t="n">
         <v>3042</v>
@@ -30558,7 +30558,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1041" t="n">
         <v>702</v>
@@ -30616,7 +30616,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1043" t="n">
         <v>5703</v>
@@ -30674,7 +30674,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1045" t="n">
         <v>3810</v>
@@ -30703,7 +30703,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1046" t="n">
         <v>3045</v>
@@ -30732,7 +30732,7 @@
         <v>1.14499998092651</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.09019458293915</v>
+        <v>1.09019446372986</v>
       </c>
       <c r="H1047" t="n">
         <v>4337</v>
@@ -30993,7 +30993,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1056" t="n">
         <v>15939</v>
@@ -31138,7 +31138,7 @@
         <v>1.10000002384186</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.04734838008881</v>
+        <v>1.0473484992981</v>
       </c>
       <c r="H1061" t="n">
         <v>5653</v>
@@ -31225,7 +31225,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1064" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1064" t="n">
         <v>7815</v>
@@ -31254,7 +31254,7 @@
         <v>1.07000005245209</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.01878452301025</v>
+        <v>1.01878440380096</v>
       </c>
       <c r="H1065" t="n">
         <v>2000</v>
@@ -31312,7 +31312,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1067" t="n">
         <v>2310</v>
@@ -31341,7 +31341,7 @@
         <v>1.05999994277954</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.00926303863525</v>
+        <v>1.00926291942596</v>
       </c>
       <c r="H1068" t="n">
         <v>8960</v>
@@ -31370,7 +31370,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1069" t="n">
         <v>9201</v>
@@ -31428,7 +31428,7 @@
         <v>0.930000007152557</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.885485470294952</v>
+        <v>0.885485529899597</v>
       </c>
       <c r="H1071" t="n">
         <v>7123</v>
@@ -31834,7 +31834,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1085" t="n">
         <v>14616</v>
@@ -31863,7 +31863,7 @@
         <v>1.04999995231628</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.999741613864899</v>
+        <v>0.999741733074188</v>
       </c>
       <c r="H1086" t="n">
         <v>7925</v>
@@ -31979,7 +31979,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1090" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1090" t="n">
         <v>1503</v>
@@ -32008,7 +32008,7 @@
         <v>1.03999996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.990220308303833</v>
+        <v>0.990220367908478</v>
       </c>
       <c r="H1091" t="n">
         <v>4143</v>
@@ -32037,7 +32037,7 @@
         <v>1.02499997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>0.975938320159912</v>
+        <v>0.975938379764557</v>
       </c>
       <c r="H1092" t="n">
         <v>4779</v>
@@ -32095,7 +32095,7 @@
         <v>1.02999997138977</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.980698943138123</v>
+        <v>0.980699002742767</v>
       </c>
       <c r="H1094" t="n">
         <v>8025</v>
@@ -32182,7 +32182,7 @@
         <v>0.987999975681305</v>
       </c>
       <c r="G1097" t="n">
-        <v>0.940709292888641</v>
+        <v>0.940709352493286</v>
       </c>
       <c r="H1097" t="n">
         <v>7780</v>
@@ -32327,7 +32327,7 @@
         <v>1.14999997615814</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.09495508670807</v>
+        <v>1.09495520591736</v>
       </c>
       <c r="H1102" t="n">
         <v>114066</v>
@@ -32356,7 +32356,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1103" t="n">
         <v>155001</v>
@@ -32414,7 +32414,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1105" t="n">
         <v>9642</v>
@@ -32443,7 +32443,7 @@
         <v>1.20500004291534</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.14732277393341</v>
+        <v>1.14732265472412</v>
       </c>
       <c r="H1106" t="n">
         <v>29380</v>
@@ -32501,7 +32501,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1108" t="n">
         <v>51439</v>
@@ -32559,7 +32559,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1110" t="n">
         <v>7650</v>
@@ -32588,7 +32588,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1111" t="n">
         <v>5770</v>
@@ -32646,7 +32646,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1113" t="n">
         <v>10113</v>
@@ -32704,7 +32704,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1115" t="n">
         <v>12644</v>
@@ -32733,7 +32733,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1116" t="n">
         <v>8938</v>
@@ -32849,7 +32849,7 @@
         <v>1.22500002384186</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.16636526584625</v>
+        <v>1.16636538505554</v>
       </c>
       <c r="H1120" t="n">
         <v>9373</v>
@@ -32878,7 +32878,7 @@
         <v>1.23500001430511</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.17588663101196</v>
+        <v>1.17588675022125</v>
       </c>
       <c r="H1121" t="n">
         <v>12172</v>
@@ -33023,7 +33023,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1126" t="n">
         <v>6943</v>
@@ -33052,7 +33052,7 @@
         <v>1.26999998092651</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.2092113494873</v>
+        <v>1.20921146869659</v>
       </c>
       <c r="H1127" t="n">
         <v>7459</v>
@@ -33139,7 +33139,7 @@
         <v>1.26499998569489</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.2044506072998</v>
+        <v>1.20445072650909</v>
       </c>
       <c r="H1130" t="n">
         <v>7350</v>
@@ -33197,7 +33197,7 @@
         <v>1.21000003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.15208327770233</v>
+        <v>1.15208339691162</v>
       </c>
       <c r="H1132" t="n">
         <v>14474</v>
@@ -42918,6 +42918,35 @@
         <v>6452</v>
       </c>
       <c r="I1467" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1468" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1468" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="D1468" t="n">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="E1468" t="n">
+        <v>0.605000019073486</v>
+      </c>
+      <c r="F1468" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="G1468" t="n">
+        <v>0.634999990463257</v>
+      </c>
+      <c r="H1468" t="n">
+        <v>9210</v>
+      </c>
+      <c r="I1468" t="s">
         <v>9</v>
       </c>
     </row>
